--- a/Versão5/FABR/Ontologia_FABRI.xlsx
+++ b/Versão5/FABR/Ontologia_FABRI.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\FABR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{870F7124-C8E2-41A3-A07D-A6CD52506B45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53BE15F3-FBB4-4D09-A5CE-965D5DCD2AF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="527" activeTab="1" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="527" activeTab="4" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="31" r:id="rId1"/>
@@ -1042,9 +1042,6 @@
     <t>Mec.Fabricante</t>
   </si>
   <si>
-    <t>Mec.Fornecimento</t>
-  </si>
-  <si>
     <t>Mec.Projetista</t>
   </si>
   <si>
@@ -1060,9 +1057,6 @@
     <t>Mob.Fabricante</t>
   </si>
   <si>
-    <t>Mob.Fornecimento</t>
-  </si>
-  <si>
     <t>Mob.Projetista</t>
   </si>
   <si>
@@ -1093,9 +1087,6 @@
     <t>Lab.Fabricante</t>
   </si>
   <si>
-    <t>Lab.Fornecimento</t>
-  </si>
-  <si>
     <t>Lab.Projetista</t>
   </si>
   <si>
@@ -1111,9 +1102,6 @@
     <t>Ins.Fabricante</t>
   </si>
   <si>
-    <t>Ins.Fornecimento</t>
-  </si>
-  <si>
     <t>Ins.Projetista</t>
   </si>
   <si>
@@ -1123,15 +1111,9 @@
     <t>Arq.Consultor</t>
   </si>
   <si>
-    <t>Arq.EmpresArq.Consultora</t>
-  </si>
-  <si>
     <t>Arq.Fabricante</t>
   </si>
   <si>
-    <t>Arq.Fornecimento</t>
-  </si>
-  <si>
     <t>Arq.Projetista</t>
   </si>
   <si>
@@ -1147,9 +1129,6 @@
     <t>Est.Fabricante</t>
   </si>
   <si>
-    <t>Est.Fornecimento</t>
-  </si>
-  <si>
     <t>Est.Projetista</t>
   </si>
   <si>
@@ -1165,9 +1144,6 @@
     <t>Geo.Fabricante</t>
   </si>
   <si>
-    <t>Geo.Fornecimento</t>
-  </si>
-  <si>
     <t>Geo.Projetista</t>
   </si>
   <si>
@@ -1183,9 +1159,6 @@
     <t>Hos.Fabricante</t>
   </si>
   <si>
-    <t>Hos.Fornecimento</t>
-  </si>
-  <si>
     <t>Hos.Projetista</t>
   </si>
   <si>
@@ -1201,9 +1174,6 @@
     <t>Ino.Fabricante</t>
   </si>
   <si>
-    <t>Ino.Fornecimento</t>
-  </si>
-  <si>
     <t>Ino.Projetista</t>
   </si>
   <si>
@@ -1213,15 +1183,9 @@
     <t>Acu.Consultor</t>
   </si>
   <si>
-    <t>Acu.EmpresAcu.Consultora</t>
-  </si>
-  <si>
     <t>Acu.Fabricante</t>
   </si>
   <si>
-    <t>Acu.Fornecimento</t>
-  </si>
-  <si>
     <t>Acu.Projetista</t>
   </si>
   <si>
@@ -1237,9 +1201,6 @@
     <t>Ger.Fabricante</t>
   </si>
   <si>
-    <t>Ger.Fornecimento</t>
-  </si>
-  <si>
     <t>Ger.Projetista</t>
   </si>
   <si>
@@ -1255,9 +1216,6 @@
     <t>Ilu.Fabricante</t>
   </si>
   <si>
-    <t>Ilu.Fornecimento</t>
-  </si>
-  <si>
     <t>Ilu.Projetista</t>
   </si>
   <si>
@@ -1303,9 +1261,6 @@
     <t>Tel.Fabricante</t>
   </si>
   <si>
-    <t>Tel.Fornecimento</t>
-  </si>
-  <si>
     <t>Tel.Projetista</t>
   </si>
   <si>
@@ -1456,48 +1411,9 @@
     <t>[ 3E.64 ]</t>
   </si>
   <si>
-    <t>Arq.Venda</t>
-  </si>
-  <si>
     <t>Arq.Compra</t>
   </si>
   <si>
-    <t>Est.Venda</t>
-  </si>
-  <si>
-    <t>Geo.Venda</t>
-  </si>
-  <si>
-    <t>Hos.Venda</t>
-  </si>
-  <si>
-    <t>Ins.Venda</t>
-  </si>
-  <si>
-    <t>Lab.Venda</t>
-  </si>
-  <si>
-    <t>Mob.Venda</t>
-  </si>
-  <si>
-    <t>Mec.Venda</t>
-  </si>
-  <si>
-    <t>Ino.Venda</t>
-  </si>
-  <si>
-    <t>Acu.Venda</t>
-  </si>
-  <si>
-    <t>Ger.Venda</t>
-  </si>
-  <si>
-    <t>Ilu.Venda</t>
-  </si>
-  <si>
-    <t>Tel.Venda</t>
-  </si>
-  <si>
     <t>Tel.Compra</t>
   </si>
   <si>
@@ -1940,6 +1856,90 @@
   </si>
   <si>
     <t>"Fabricante de sistemas de iluminação convencional, industrial e varejo."</t>
+  </si>
+  <si>
+    <t>Acu.Fornecedor</t>
+  </si>
+  <si>
+    <t>Arq.Fornecedor</t>
+  </si>
+  <si>
+    <t>Est.Fornecedor</t>
+  </si>
+  <si>
+    <t>Geo.Fornecedor</t>
+  </si>
+  <si>
+    <t>Ger.Fornecedor</t>
+  </si>
+  <si>
+    <t>Hos.Fornecedor</t>
+  </si>
+  <si>
+    <t>Ilu.Fornecedor</t>
+  </si>
+  <si>
+    <t>Ino.Fornecedor</t>
+  </si>
+  <si>
+    <t>Ins.Fornecedor</t>
+  </si>
+  <si>
+    <t>Lab.Fornecedor</t>
+  </si>
+  <si>
+    <t>Mec.Fornecedor</t>
+  </si>
+  <si>
+    <t>Mob.Fornecedor</t>
+  </si>
+  <si>
+    <t>Tel.Fornecedor</t>
+  </si>
+  <si>
+    <t>Acu.Vendedor</t>
+  </si>
+  <si>
+    <t>Arq.Vendedor</t>
+  </si>
+  <si>
+    <t>Est.Vendedor</t>
+  </si>
+  <si>
+    <t>Geo.Vendedor</t>
+  </si>
+  <si>
+    <t>Ger.Vendedor</t>
+  </si>
+  <si>
+    <t>Hos.Vendedor</t>
+  </si>
+  <si>
+    <t>Ilu.Vendedor</t>
+  </si>
+  <si>
+    <t>Ino.Vendedor</t>
+  </si>
+  <si>
+    <t>Ins.Vendedor</t>
+  </si>
+  <si>
+    <t>Lab.Vendedor</t>
+  </si>
+  <si>
+    <t>Mec.Vendedor</t>
+  </si>
+  <si>
+    <t>Mob.Vendedor</t>
+  </si>
+  <si>
+    <t>Tel.Vendedor</t>
+  </si>
+  <si>
+    <t>Acu.Empresa.Consultora</t>
+  </si>
+  <si>
+    <t>Arq.Empresa.Consultora</t>
   </si>
 </sst>
 </file>
@@ -2915,15 +2915,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1124724F-B8C4-4B86-9028-743FC73CDDB0}">
   <dimension ref="A1:C24"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="10.5" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="10.5" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.28515625" style="13" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="53.7109375" style="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="3.42578125" style="49" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="9.140625" style="13"/>
+    <col min="1" max="1" width="10.3046875" style="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="53.69140625" style="13" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="3.3828125" style="49" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.15234375" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="10" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" s="10" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
@@ -2934,7 +2934,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>17</v>
       </c>
@@ -2945,7 +2945,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>18</v>
       </c>
@@ -2956,7 +2956,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>7</v>
       </c>
@@ -2967,7 +2967,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>6</v>
       </c>
@@ -2979,7 +2979,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>8</v>
       </c>
@@ -2991,7 +2991,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>4</v>
       </c>
@@ -3002,7 +3002,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="8" spans="1:3" s="46" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" s="46" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="2" t="s">
         <v>5</v>
       </c>
@@ -3013,7 +3013,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>20</v>
       </c>
@@ -3024,7 +3024,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>22</v>
       </c>
@@ -3035,7 +3035,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>0</v>
       </c>
@@ -3046,7 +3046,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>1</v>
       </c>
@@ -3057,7 +3057,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>23</v>
       </c>
@@ -3068,7 +3068,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>24</v>
       </c>
@@ -3079,7 +3079,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>25</v>
       </c>
@@ -3090,7 +3090,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>26</v>
       </c>
@@ -3101,7 +3101,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>10</v>
       </c>
@@ -3112,19 +3112,19 @@
         <v>88</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>27</v>
       </c>
       <c r="B18" s="5">
         <f ca="1">NOW()</f>
-        <v>46063.648207986109</v>
+        <v>46136.469790740739</v>
       </c>
       <c r="C18" s="48" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>28</v>
       </c>
@@ -3135,7 +3135,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>29</v>
       </c>
@@ -3146,7 +3146,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>11</v>
       </c>
@@ -3157,7 +3157,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:3" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
         <v>32</v>
       </c>
@@ -3168,7 +3168,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:3" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="4" t="s">
         <v>33</v>
       </c>
@@ -3180,7 +3180,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="24" spans="1:3" s="46" customFormat="1" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" s="46" customFormat="1" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="4" t="s">
         <v>86</v>
       </c>
@@ -3200,34 +3200,34 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{348BB721-29D9-4DD8-81B8-03CCB3CE3CCF}">
   <dimension ref="A1:AA148"/>
-  <sheetFormatPr defaultColWidth="2.7109375" defaultRowHeight="6.6" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="2.69140625" defaultRowHeight="6.65" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.28515625" customWidth="1"/>
-    <col min="2" max="2" width="4.5703125" customWidth="1"/>
-    <col min="3" max="3" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.28515625" customWidth="1"/>
-    <col min="5" max="5" width="11.5703125" customWidth="1"/>
-    <col min="6" max="6" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="6.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="6.5703125" customWidth="1"/>
+    <col min="1" max="1" width="2.3046875" customWidth="1"/>
+    <col min="2" max="2" width="4.53515625" customWidth="1"/>
+    <col min="3" max="3" width="8.15234375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.3046875" customWidth="1"/>
+    <col min="5" max="5" width="11.53515625" customWidth="1"/>
+    <col min="6" max="6" width="15.15234375" customWidth="1"/>
+    <col min="7" max="11" width="6.3828125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.53515625" customWidth="1"/>
     <col min="13" max="13" width="5" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.85546875" customWidth="1"/>
-    <col min="15" max="15" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="36.42578125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="32.5703125" customWidth="1"/>
-    <col min="18" max="18" width="4.42578125" style="34" customWidth="1"/>
-    <col min="19" max="19" width="6.85546875" style="34" customWidth="1"/>
-    <col min="20" max="20" width="12.7109375" style="34" customWidth="1"/>
-    <col min="21" max="21" width="11.5703125" style="34" customWidth="1"/>
-    <col min="22" max="22" width="6.28515625" style="38" customWidth="1"/>
+    <col min="14" max="14" width="10.84375" customWidth="1"/>
+    <col min="15" max="15" width="13.53515625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="36.3828125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="32.53515625" customWidth="1"/>
+    <col min="18" max="18" width="4.3828125" style="34" customWidth="1"/>
+    <col min="19" max="19" width="6.84375" style="34" customWidth="1"/>
+    <col min="20" max="20" width="12.69140625" style="34" customWidth="1"/>
+    <col min="21" max="21" width="11.53515625" style="34" customWidth="1"/>
+    <col min="22" max="22" width="6.3046875" style="38" customWidth="1"/>
     <col min="23" max="23" width="7" style="38" customWidth="1"/>
-    <col min="24" max="24" width="6.140625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="10.28515625" customWidth="1"/>
-    <col min="26" max="26" width="16.42578125" customWidth="1"/>
-    <col min="27" max="27" width="31.140625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="6.15234375" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="10.3046875" customWidth="1"/>
+    <col min="26" max="26" width="16.3828125" customWidth="1"/>
+    <col min="27" max="27" width="31.15234375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:27" ht="34" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="24">
         <v>0</v>
       </c>
@@ -3310,7 +3310,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="2" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="51">
         <v>2</v>
       </c>
@@ -3404,7 +3404,7 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard.</v>
       </c>
     </row>
-    <row r="3" spans="1:27" s="55" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:27" s="55" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="51">
         <v>3</v>
       </c>
@@ -3421,7 +3421,7 @@
         <v>165</v>
       </c>
       <c r="F3" s="57" t="s">
-        <v>477</v>
+        <v>449</v>
       </c>
       <c r="G3" s="28" t="s">
         <v>9</v>
@@ -3455,7 +3455,7 @@
         <v>Acu Compra</v>
       </c>
       <c r="P3" s="23" t="s">
-        <v>497</v>
+        <v>469</v>
       </c>
       <c r="Q3" s="26" t="str">
         <f>_xlfn.TRANSLATE(P3,"pt","es")</f>
@@ -3490,14 +3490,14 @@
         <v>9</v>
       </c>
       <c r="Z3" s="41" t="s">
-        <v>499</v>
+        <v>471</v>
       </c>
       <c r="AA3" s="45" t="str">
         <f>_xlfn.TRANSLATE(P3,"pt","en")</f>
         <v>Acoustics Supplier: It is a purchase of products</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="51">
         <v>4</v>
       </c>
@@ -3514,7 +3514,7 @@
         <v>165</v>
       </c>
       <c r="F4" s="57" t="s">
-        <v>378</v>
+        <v>368</v>
       </c>
       <c r="G4" s="28" t="s">
         <v>9</v>
@@ -3583,14 +3583,14 @@
         <v>9</v>
       </c>
       <c r="Z4" s="41" t="s">
-        <v>428</v>
+        <v>413</v>
       </c>
       <c r="AA4" s="45" t="str">
         <f>_xlfn.TRANSLATE(P4,"pt","en")</f>
         <v>Acoustics Supplier: is a self-employed consultant</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="51">
         <v>5</v>
       </c>
@@ -3607,7 +3607,7 @@
         <v>165</v>
       </c>
       <c r="F5" s="57" t="s">
-        <v>561</v>
+        <v>533</v>
       </c>
       <c r="G5" s="28" t="s">
         <v>9</v>
@@ -3628,19 +3628,19 @@
         <v>95</v>
       </c>
       <c r="M5" s="23" t="s">
-        <v>512</v>
+        <v>484</v>
       </c>
       <c r="N5" s="23" t="s">
-        <v>537</v>
+        <v>509</v>
       </c>
       <c r="O5" s="23" t="s">
-        <v>538</v>
+        <v>510</v>
       </c>
       <c r="P5" s="23" t="s">
-        <v>574</v>
+        <v>546</v>
       </c>
       <c r="Q5" s="26" t="s">
-        <v>596</v>
+        <v>568</v>
       </c>
       <c r="R5" s="42" t="s">
         <v>9</v>
@@ -3649,16 +3649,16 @@
         <v>95</v>
       </c>
       <c r="T5" s="43" t="s">
-        <v>512</v>
+        <v>484</v>
       </c>
       <c r="U5" s="43" t="s">
-        <v>537</v>
+        <v>509</v>
       </c>
       <c r="V5" s="41" t="s">
         <v>184</v>
       </c>
       <c r="W5" s="60" t="s">
-        <v>539</v>
+        <v>511</v>
       </c>
       <c r="X5" s="41" t="s">
         <v>9</v>
@@ -3667,13 +3667,13 @@
         <v>9</v>
       </c>
       <c r="Z5" s="41" t="s">
-        <v>565</v>
+        <v>537</v>
       </c>
       <c r="AA5" s="45" t="s">
-        <v>586</v>
-      </c>
-    </row>
-    <row r="6" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="51">
         <v>6</v>
       </c>
@@ -3690,7 +3690,7 @@
         <v>165</v>
       </c>
       <c r="F6" s="57" t="s">
-        <v>379</v>
+        <v>620</v>
       </c>
       <c r="G6" s="28" t="s">
         <v>9</v>
@@ -3721,7 +3721,7 @@
       </c>
       <c r="O6" s="23" t="str">
         <f t="shared" si="3"/>
-        <v>Acu EmpresAcu Consultora</v>
+        <v>Acu Empresa Consultora</v>
       </c>
       <c r="P6" s="23" t="s">
         <v>172</v>
@@ -3759,14 +3759,14 @@
         <v>9</v>
       </c>
       <c r="Z6" s="41" t="s">
-        <v>428</v>
+        <v>413</v>
       </c>
       <c r="AA6" s="45" t="str">
         <f t="shared" ref="AA6:AA13" si="7">_xlfn.TRANSLATE(P6,"pt","en")</f>
         <v>Supplier in the acoustics segment: it is a consulting company</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="51">
         <v>7</v>
       </c>
@@ -3783,7 +3783,7 @@
         <v>165</v>
       </c>
       <c r="F7" s="57" t="s">
-        <v>380</v>
+        <v>369</v>
       </c>
       <c r="G7" s="28" t="s">
         <v>9</v>
@@ -3852,14 +3852,14 @@
         <v>9</v>
       </c>
       <c r="Z7" s="41" t="s">
-        <v>419</v>
+        <v>404</v>
       </c>
       <c r="AA7" s="45" t="str">
         <f t="shared" si="7"/>
         <v>Acoustics Segment Supplier: is a manufacturer of products</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="51">
         <v>8</v>
       </c>
@@ -3876,7 +3876,7 @@
         <v>165</v>
       </c>
       <c r="F8" s="57" t="s">
-        <v>381</v>
+        <v>594</v>
       </c>
       <c r="G8" s="28" t="s">
         <v>9</v>
@@ -3907,7 +3907,7 @@
       </c>
       <c r="O8" s="23" t="str">
         <f t="shared" si="3"/>
-        <v>Acu Fornecimento</v>
+        <v>Acu Fornecedor</v>
       </c>
       <c r="P8" s="23" t="s">
         <v>175</v>
@@ -3945,14 +3945,14 @@
         <v>9</v>
       </c>
       <c r="Z8" s="41" t="s">
-        <v>426</v>
+        <v>411</v>
       </c>
       <c r="AA8" s="45" t="str">
         <f t="shared" si="7"/>
         <v>Acoustics segment supplier: is a supplier</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="51">
         <v>9</v>
       </c>
@@ -3969,7 +3969,7 @@
         <v>165</v>
       </c>
       <c r="F9" s="57" t="s">
-        <v>382</v>
+        <v>370</v>
       </c>
       <c r="G9" s="28" t="s">
         <v>9</v>
@@ -4038,14 +4038,14 @@
         <v>9</v>
       </c>
       <c r="Z9" s="41" t="s">
-        <v>430</v>
+        <v>415</v>
       </c>
       <c r="AA9" s="45" t="str">
         <f t="shared" si="7"/>
         <v>Acoustics Supplier: is a Designer or Design Company</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="51">
         <v>10</v>
       </c>
@@ -4062,7 +4062,7 @@
         <v>165</v>
       </c>
       <c r="F10" s="57" t="s">
-        <v>383</v>
+        <v>371</v>
       </c>
       <c r="G10" s="28" t="s">
         <v>9</v>
@@ -4131,14 +4131,14 @@
         <v>9</v>
       </c>
       <c r="Z10" s="41" t="s">
-        <v>429</v>
+        <v>414</v>
       </c>
       <c r="AA10" s="45" t="str">
         <f t="shared" si="7"/>
         <v>Acoustics Supplier: It's a Service</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="51">
         <v>11</v>
       </c>
@@ -4155,7 +4155,7 @@
         <v>165</v>
       </c>
       <c r="F11" s="57" t="s">
-        <v>470</v>
+        <v>607</v>
       </c>
       <c r="G11" s="28" t="s">
         <v>9</v>
@@ -4186,10 +4186,10 @@
       </c>
       <c r="O11" s="23" t="str">
         <f t="shared" si="3"/>
-        <v>Acu Venda</v>
+        <v>Acu Vendedor</v>
       </c>
       <c r="P11" s="23" t="s">
-        <v>508</v>
+        <v>480</v>
       </c>
       <c r="Q11" s="26" t="str">
         <f t="shared" si="4"/>
@@ -4224,14 +4224,14 @@
         <v>9</v>
       </c>
       <c r="Z11" s="41" t="s">
-        <v>427</v>
+        <v>412</v>
       </c>
       <c r="AA11" s="45" t="str">
         <f t="shared" si="7"/>
         <v>Supplier in the acoustics segment: it is a sale of products</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="51">
         <v>12</v>
       </c>
@@ -4248,7 +4248,7 @@
         <v>96</v>
       </c>
       <c r="F12" s="57" t="s">
-        <v>461</v>
+        <v>445</v>
       </c>
       <c r="G12" s="28" t="s">
         <v>9</v>
@@ -4282,7 +4282,7 @@
         <v>Arq Compra</v>
       </c>
       <c r="P12" s="23" t="s">
-        <v>488</v>
+        <v>460</v>
       </c>
       <c r="Q12" s="26" t="str">
         <f t="shared" si="4"/>
@@ -4317,14 +4317,14 @@
         <v>9</v>
       </c>
       <c r="Z12" s="41" t="s">
-        <v>499</v>
+        <v>471</v>
       </c>
       <c r="AA12" s="45" t="str">
         <f t="shared" si="7"/>
         <v>Architecture Vendor: It's a purchase of products</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="51">
         <v>13</v>
       </c>
@@ -4341,7 +4341,7 @@
         <v>96</v>
       </c>
       <c r="F13" s="57" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="G13" s="28" t="s">
         <v>9</v>
@@ -4410,14 +4410,14 @@
         <v>9</v>
       </c>
       <c r="Z13" s="41" t="s">
-        <v>428</v>
+        <v>413</v>
       </c>
       <c r="AA13" s="45" t="str">
         <f t="shared" si="7"/>
         <v>Architecture Vendor: is a self-employed consultant</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="51">
         <v>14</v>
       </c>
@@ -4434,7 +4434,7 @@
         <v>96</v>
       </c>
       <c r="F14" s="57" t="s">
-        <v>552</v>
+        <v>524</v>
       </c>
       <c r="G14" s="28" t="s">
         <v>9</v>
@@ -4455,19 +4455,19 @@
         <v>95</v>
       </c>
       <c r="M14" s="23" t="s">
-        <v>512</v>
+        <v>484</v>
       </c>
       <c r="N14" s="23" t="s">
-        <v>549</v>
+        <v>521</v>
       </c>
       <c r="O14" s="23" t="s">
-        <v>550</v>
+        <v>522</v>
       </c>
       <c r="P14" s="23" t="s">
-        <v>604</v>
+        <v>576</v>
       </c>
       <c r="Q14" s="26" t="s">
-        <v>603</v>
+        <v>575</v>
       </c>
       <c r="R14" s="42" t="s">
         <v>9</v>
@@ -4476,16 +4476,16 @@
         <v>95</v>
       </c>
       <c r="T14" s="43" t="s">
-        <v>512</v>
+        <v>484</v>
       </c>
       <c r="U14" s="43" t="s">
-        <v>549</v>
+        <v>521</v>
       </c>
       <c r="V14" s="41" t="s">
         <v>184</v>
       </c>
       <c r="W14" s="60" t="s">
-        <v>551</v>
+        <v>523</v>
       </c>
       <c r="X14" s="41" t="s">
         <v>9</v>
@@ -4494,13 +4494,13 @@
         <v>9</v>
       </c>
       <c r="Z14" s="41" t="s">
-        <v>565</v>
+        <v>537</v>
       </c>
       <c r="AA14" s="45" t="s">
-        <v>590</v>
-      </c>
-    </row>
-    <row r="15" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="51">
         <v>15</v>
       </c>
@@ -4517,7 +4517,7 @@
         <v>96</v>
       </c>
       <c r="F15" s="57" t="s">
-        <v>349</v>
+        <v>621</v>
       </c>
       <c r="G15" s="28" t="s">
         <v>9</v>
@@ -4548,7 +4548,7 @@
       </c>
       <c r="O15" s="23" t="str">
         <f t="shared" si="9"/>
-        <v>Arq EmpresArq Consultora</v>
+        <v>Arq Empresa Consultora</v>
       </c>
       <c r="P15" s="23" t="s">
         <v>168</v>
@@ -4586,14 +4586,14 @@
         <v>9</v>
       </c>
       <c r="Z15" s="41" t="s">
-        <v>428</v>
+        <v>413</v>
       </c>
       <c r="AA15" s="45" t="str">
         <f t="shared" ref="AA15:AA22" si="13">_xlfn.TRANSLATE(P15,"pt","en")</f>
         <v>Supplier in the architecture segment: it is a consulting company</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="51">
         <v>16</v>
       </c>
@@ -4610,7 +4610,7 @@
         <v>96</v>
       </c>
       <c r="F16" s="57" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="G16" s="28" t="s">
         <v>9</v>
@@ -4679,14 +4679,14 @@
         <v>9</v>
       </c>
       <c r="Z16" s="41" t="s">
-        <v>419</v>
+        <v>404</v>
       </c>
       <c r="AA16" s="45" t="str">
         <f t="shared" si="13"/>
         <v>Architecture Vendor: is a manufacturer of products</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="51">
         <v>17</v>
       </c>
@@ -4703,7 +4703,7 @@
         <v>96</v>
       </c>
       <c r="F17" s="57" t="s">
-        <v>351</v>
+        <v>595</v>
       </c>
       <c r="G17" s="28" t="s">
         <v>9</v>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="O17" s="23" t="str">
         <f t="shared" si="9"/>
-        <v>Arq Fornecimento</v>
+        <v>Arq Fornecedor</v>
       </c>
       <c r="P17" s="23" t="s">
         <v>174</v>
@@ -4772,14 +4772,14 @@
         <v>9</v>
       </c>
       <c r="Z17" s="41" t="s">
-        <v>426</v>
+        <v>411</v>
       </c>
       <c r="AA17" s="45" t="str">
         <f t="shared" si="13"/>
         <v>Architecture Vendor: is a vendor</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="51">
         <v>18</v>
       </c>
@@ -4796,7 +4796,7 @@
         <v>96</v>
       </c>
       <c r="F18" s="57" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="G18" s="28" t="s">
         <v>9</v>
@@ -4865,14 +4865,14 @@
         <v>9</v>
       </c>
       <c r="Z18" s="41" t="s">
-        <v>420</v>
+        <v>405</v>
       </c>
       <c r="AA18" s="45" t="str">
         <f t="shared" si="13"/>
         <v>Architecture Vendor: is a Designer or Design Company</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="51">
         <v>19</v>
       </c>
@@ -4889,7 +4889,7 @@
         <v>96</v>
       </c>
       <c r="F19" s="57" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="G19" s="28" t="s">
         <v>9</v>
@@ -4958,14 +4958,14 @@
         <v>9</v>
       </c>
       <c r="Z19" s="41" t="s">
-        <v>429</v>
+        <v>414</v>
       </c>
       <c r="AA19" s="45" t="str">
         <f t="shared" si="13"/>
         <v>Architecture Vendor: It's a service</v>
       </c>
     </row>
-    <row r="20" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="51">
         <v>20</v>
       </c>
@@ -4982,7 +4982,7 @@
         <v>96</v>
       </c>
       <c r="F20" s="57" t="s">
-        <v>460</v>
+        <v>608</v>
       </c>
       <c r="G20" s="28" t="s">
         <v>9</v>
@@ -5013,10 +5013,10 @@
       </c>
       <c r="O20" s="23" t="str">
         <f t="shared" si="9"/>
-        <v>Arq Venda</v>
+        <v>Arq Vendedor</v>
       </c>
       <c r="P20" s="23" t="s">
-        <v>604</v>
+        <v>576</v>
       </c>
       <c r="Q20" s="26" t="str">
         <f t="shared" si="10"/>
@@ -5051,14 +5051,14 @@
         <v>9</v>
       </c>
       <c r="Z20" s="41" t="s">
-        <v>427</v>
+        <v>412</v>
       </c>
       <c r="AA20" s="45" t="str">
         <f t="shared" si="13"/>
         <v>Architecture Vendor: It's a product sale</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="51">
         <v>21</v>
       </c>
@@ -5075,7 +5075,7 @@
         <v>97</v>
       </c>
       <c r="F21" s="57" t="s">
-        <v>485</v>
+        <v>457</v>
       </c>
       <c r="G21" s="28" t="s">
         <v>9</v>
@@ -5109,7 +5109,7 @@
         <v>Est Compra</v>
       </c>
       <c r="P21" s="23" t="s">
-        <v>489</v>
+        <v>461</v>
       </c>
       <c r="Q21" s="26" t="str">
         <f t="shared" si="10"/>
@@ -5144,14 +5144,14 @@
         <v>9</v>
       </c>
       <c r="Z21" s="41" t="s">
-        <v>499</v>
+        <v>471</v>
       </c>
       <c r="AA21" s="45" t="str">
         <f t="shared" si="13"/>
         <v>Supplier in the structure segment: it is a purchase of products</v>
       </c>
     </row>
-    <row r="22" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="51">
         <v>22</v>
       </c>
@@ -5168,7 +5168,7 @@
         <v>97</v>
       </c>
       <c r="F22" s="57" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="G22" s="28" t="s">
         <v>9</v>
@@ -5237,14 +5237,14 @@
         <v>9</v>
       </c>
       <c r="Z22" s="41" t="s">
-        <v>428</v>
+        <v>413</v>
       </c>
       <c r="AA22" s="45" t="str">
         <f t="shared" si="13"/>
         <v>Structure segment supplier: is a self-employed consultant</v>
       </c>
     </row>
-    <row r="23" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="51">
         <v>23</v>
       </c>
@@ -5261,7 +5261,7 @@
         <v>97</v>
       </c>
       <c r="F23" s="57" t="s">
-        <v>553</v>
+        <v>525</v>
       </c>
       <c r="G23" s="28" t="s">
         <v>9</v>
@@ -5282,19 +5282,19 @@
         <v>95</v>
       </c>
       <c r="M23" s="23" t="s">
-        <v>512</v>
+        <v>484</v>
       </c>
       <c r="N23" s="23" t="s">
-        <v>513</v>
+        <v>485</v>
       </c>
       <c r="O23" s="23" t="s">
-        <v>514</v>
+        <v>486</v>
       </c>
       <c r="P23" s="23" t="s">
-        <v>566</v>
+        <v>538</v>
       </c>
       <c r="Q23" s="26" t="s">
-        <v>591</v>
+        <v>563</v>
       </c>
       <c r="R23" s="42" t="s">
         <v>9</v>
@@ -5303,16 +5303,16 @@
         <v>95</v>
       </c>
       <c r="T23" s="43" t="s">
-        <v>512</v>
+        <v>484</v>
       </c>
       <c r="U23" s="43" t="s">
-        <v>513</v>
+        <v>485</v>
       </c>
       <c r="V23" s="41" t="s">
         <v>184</v>
       </c>
       <c r="W23" s="60" t="s">
-        <v>515</v>
+        <v>487</v>
       </c>
       <c r="X23" s="41" t="s">
         <v>9</v>
@@ -5321,13 +5321,13 @@
         <v>9</v>
       </c>
       <c r="Z23" s="41" t="s">
-        <v>565</v>
+        <v>537</v>
       </c>
       <c r="AA23" s="45" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="24" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="24" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="51">
         <v>24</v>
       </c>
@@ -5344,7 +5344,7 @@
         <v>97</v>
       </c>
       <c r="F24" s="57" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="G24" s="28" t="s">
         <v>9</v>
@@ -5413,14 +5413,14 @@
         <v>9</v>
       </c>
       <c r="Z24" s="41" t="s">
-        <v>428</v>
+        <v>413</v>
       </c>
       <c r="AA24" s="45" t="str">
         <f t="shared" ref="AA24:AA31" si="19">_xlfn.TRANSLATE(P24,"pt","en")</f>
         <v>Supplier of the structure segment: it is a consulting company</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="51">
         <v>25</v>
       </c>
@@ -5437,7 +5437,7 @@
         <v>97</v>
       </c>
       <c r="F25" s="57" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="G25" s="28" t="s">
         <v>9</v>
@@ -5506,14 +5506,14 @@
         <v>9</v>
       </c>
       <c r="Z25" s="41" t="s">
-        <v>419</v>
+        <v>404</v>
       </c>
       <c r="AA25" s="45" t="str">
         <f t="shared" si="19"/>
         <v>Supplier of the structure segment: it is a manufacturer of products</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="51">
         <v>26</v>
       </c>
@@ -5530,7 +5530,7 @@
         <v>97</v>
       </c>
       <c r="F26" s="57" t="s">
-        <v>357</v>
+        <v>596</v>
       </c>
       <c r="G26" s="28" t="s">
         <v>9</v>
@@ -5561,7 +5561,7 @@
       </c>
       <c r="O26" s="23" t="str">
         <f t="shared" si="15"/>
-        <v>Est Fornecimento</v>
+        <v>Est Fornecedor</v>
       </c>
       <c r="P26" s="23" t="s">
         <v>176</v>
@@ -5599,14 +5599,14 @@
         <v>9</v>
       </c>
       <c r="Z26" s="41" t="s">
-        <v>426</v>
+        <v>411</v>
       </c>
       <c r="AA26" s="45" t="str">
         <f t="shared" si="19"/>
         <v>Structure segment supplier: is a supplier</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="51">
         <v>27</v>
       </c>
@@ -5623,7 +5623,7 @@
         <v>97</v>
       </c>
       <c r="F27" s="57" t="s">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="G27" s="28" t="s">
         <v>9</v>
@@ -5692,14 +5692,14 @@
         <v>9</v>
       </c>
       <c r="Z27" s="41" t="s">
-        <v>421</v>
+        <v>406</v>
       </c>
       <c r="AA27" s="45" t="str">
         <f t="shared" si="19"/>
         <v>Supplier in the structure segment: is a Designer or Design Company</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="51">
         <v>28</v>
       </c>
@@ -5716,7 +5716,7 @@
         <v>97</v>
       </c>
       <c r="F28" s="57" t="s">
-        <v>359</v>
+        <v>352</v>
       </c>
       <c r="G28" s="28" t="s">
         <v>9</v>
@@ -5785,14 +5785,14 @@
         <v>9</v>
       </c>
       <c r="Z28" s="41" t="s">
-        <v>429</v>
+        <v>414</v>
       </c>
       <c r="AA28" s="45" t="str">
         <f t="shared" si="19"/>
         <v>Structure segment supplier: it is a service</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="51">
         <v>29</v>
       </c>
@@ -5809,7 +5809,7 @@
         <v>97</v>
       </c>
       <c r="F29" s="57" t="s">
-        <v>462</v>
+        <v>609</v>
       </c>
       <c r="G29" s="28" t="s">
         <v>9</v>
@@ -5840,10 +5840,10 @@
       </c>
       <c r="O29" s="23" t="str">
         <f t="shared" si="15"/>
-        <v>Est Venda</v>
+        <v>Est Vendedor</v>
       </c>
       <c r="P29" s="23" t="s">
-        <v>500</v>
+        <v>472</v>
       </c>
       <c r="Q29" s="26" t="str">
         <f t="shared" si="16"/>
@@ -5878,14 +5878,14 @@
         <v>9</v>
       </c>
       <c r="Z29" s="41" t="s">
-        <v>427</v>
+        <v>412</v>
       </c>
       <c r="AA29" s="45" t="str">
         <f t="shared" si="19"/>
         <v>Structure segment supplier: it is a sale of products</v>
       </c>
     </row>
-    <row r="30" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="51">
         <v>30</v>
       </c>
@@ -5902,7 +5902,7 @@
         <v>185</v>
       </c>
       <c r="F30" s="57" t="s">
-        <v>484</v>
+        <v>456</v>
       </c>
       <c r="G30" s="28" t="s">
         <v>9</v>
@@ -5936,7 +5936,7 @@
         <v>Geo Compra</v>
       </c>
       <c r="P30" s="23" t="s">
-        <v>490</v>
+        <v>462</v>
       </c>
       <c r="Q30" s="26" t="str">
         <f t="shared" si="16"/>
@@ -5971,14 +5971,14 @@
         <v>9</v>
       </c>
       <c r="Z30" s="41" t="s">
-        <v>499</v>
+        <v>471</v>
       </c>
       <c r="AA30" s="45" t="str">
         <f t="shared" si="19"/>
         <v>Geotechnical segment supplier: it is a purchase of products</v>
       </c>
     </row>
-    <row r="31" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="51">
         <v>31</v>
       </c>
@@ -5995,7 +5995,7 @@
         <v>185</v>
       </c>
       <c r="F31" s="57" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="G31" s="28" t="s">
         <v>9</v>
@@ -6064,14 +6064,14 @@
         <v>9</v>
       </c>
       <c r="Z31" s="41" t="s">
-        <v>428</v>
+        <v>413</v>
       </c>
       <c r="AA31" s="45" t="str">
         <f t="shared" si="19"/>
         <v>Geotechnical Supplier: is a self-employed consultant</v>
       </c>
     </row>
-    <row r="32" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="51">
         <v>32</v>
       </c>
@@ -6088,7 +6088,7 @@
         <v>185</v>
       </c>
       <c r="F32" s="57" t="s">
-        <v>554</v>
+        <v>526</v>
       </c>
       <c r="G32" s="28" t="s">
         <v>9</v>
@@ -6109,19 +6109,19 @@
         <v>95</v>
       </c>
       <c r="M32" s="23" t="s">
-        <v>512</v>
+        <v>484</v>
       </c>
       <c r="N32" s="23" t="s">
-        <v>516</v>
+        <v>488</v>
       </c>
       <c r="O32" s="23" t="s">
-        <v>517</v>
+        <v>489</v>
       </c>
       <c r="P32" s="23" t="s">
-        <v>567</v>
+        <v>539</v>
       </c>
       <c r="Q32" s="26" t="s">
-        <v>592</v>
+        <v>564</v>
       </c>
       <c r="R32" s="42" t="s">
         <v>9</v>
@@ -6130,16 +6130,16 @@
         <v>95</v>
       </c>
       <c r="T32" s="43" t="s">
-        <v>512</v>
+        <v>484</v>
       </c>
       <c r="U32" s="43" t="s">
-        <v>516</v>
+        <v>488</v>
       </c>
       <c r="V32" s="41" t="s">
         <v>184</v>
       </c>
       <c r="W32" s="60" t="s">
-        <v>518</v>
+        <v>490</v>
       </c>
       <c r="X32" s="41" t="s">
         <v>9</v>
@@ -6148,13 +6148,13 @@
         <v>9</v>
       </c>
       <c r="Z32" s="41" t="s">
-        <v>565</v>
+        <v>537</v>
       </c>
       <c r="AA32" s="45" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="33" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="33" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="51">
         <v>33</v>
       </c>
@@ -6171,7 +6171,7 @@
         <v>185</v>
       </c>
       <c r="F33" s="57" t="s">
-        <v>361</v>
+        <v>354</v>
       </c>
       <c r="G33" s="28" t="s">
         <v>9</v>
@@ -6240,14 +6240,14 @@
         <v>9</v>
       </c>
       <c r="Z33" s="41" t="s">
-        <v>428</v>
+        <v>413</v>
       </c>
       <c r="AA33" s="45" t="str">
         <f t="shared" ref="AA33:AA40" si="25">_xlfn.TRANSLATE(P33,"pt","en")</f>
         <v>Supplier in the geotechnical segment: it is a consulting company</v>
       </c>
     </row>
-    <row r="34" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="51">
         <v>34</v>
       </c>
@@ -6264,7 +6264,7 @@
         <v>185</v>
       </c>
       <c r="F34" s="57" t="s">
-        <v>362</v>
+        <v>355</v>
       </c>
       <c r="G34" s="28" t="s">
         <v>9</v>
@@ -6333,14 +6333,14 @@
         <v>9</v>
       </c>
       <c r="Z34" s="41" t="s">
-        <v>419</v>
+        <v>404</v>
       </c>
       <c r="AA34" s="45" t="str">
         <f t="shared" si="25"/>
         <v>Geotechnical Segment Supplier: is a manufacturer of</v>
       </c>
     </row>
-    <row r="35" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="51">
         <v>35</v>
       </c>
@@ -6357,7 +6357,7 @@
         <v>185</v>
       </c>
       <c r="F35" s="57" t="s">
-        <v>363</v>
+        <v>597</v>
       </c>
       <c r="G35" s="28" t="s">
         <v>9</v>
@@ -6388,7 +6388,7 @@
       </c>
       <c r="O35" s="23" t="str">
         <f t="shared" si="21"/>
-        <v>Geo Fornecimento</v>
+        <v>Geo Fornecedor</v>
       </c>
       <c r="P35" s="23" t="s">
         <v>177</v>
@@ -6426,14 +6426,14 @@
         <v>9</v>
       </c>
       <c r="Z35" s="41" t="s">
-        <v>426</v>
+        <v>411</v>
       </c>
       <c r="AA35" s="45" t="str">
         <f t="shared" si="25"/>
         <v>Geotechnical Segment Supplier: is a supplier</v>
       </c>
     </row>
-    <row r="36" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="51">
         <v>36</v>
       </c>
@@ -6450,7 +6450,7 @@
         <v>185</v>
       </c>
       <c r="F36" s="57" t="s">
-        <v>364</v>
+        <v>356</v>
       </c>
       <c r="G36" s="28" t="s">
         <v>9</v>
@@ -6519,14 +6519,14 @@
         <v>9</v>
       </c>
       <c r="Z36" s="41" t="s">
-        <v>421</v>
+        <v>406</v>
       </c>
       <c r="AA36" s="45" t="str">
         <f t="shared" si="25"/>
         <v>Geotechnical Segment Supplier: is a Designer or Design Company</v>
       </c>
     </row>
-    <row r="37" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="51">
         <v>37</v>
       </c>
@@ -6543,7 +6543,7 @@
         <v>185</v>
       </c>
       <c r="F37" s="57" t="s">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="G37" s="28" t="s">
         <v>9</v>
@@ -6612,14 +6612,14 @@
         <v>9</v>
       </c>
       <c r="Z37" s="41" t="s">
-        <v>429</v>
+        <v>414</v>
       </c>
       <c r="AA37" s="45" t="str">
         <f t="shared" si="25"/>
         <v>Geotechnical Supplier: It's a Service</v>
       </c>
     </row>
-    <row r="38" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" s="51">
         <v>38</v>
       </c>
@@ -6636,7 +6636,7 @@
         <v>185</v>
       </c>
       <c r="F38" s="57" t="s">
-        <v>463</v>
+        <v>610</v>
       </c>
       <c r="G38" s="28" t="s">
         <v>9</v>
@@ -6667,10 +6667,10 @@
       </c>
       <c r="O38" s="23" t="str">
         <f t="shared" si="21"/>
-        <v>Geo Venda</v>
+        <v>Geo Vendedor</v>
       </c>
       <c r="P38" s="23" t="s">
-        <v>501</v>
+        <v>473</v>
       </c>
       <c r="Q38" s="26" t="str">
         <f t="shared" si="22"/>
@@ -6705,14 +6705,14 @@
         <v>9</v>
       </c>
       <c r="Z38" s="41" t="s">
-        <v>427</v>
+        <v>412</v>
       </c>
       <c r="AA38" s="45" t="str">
         <f t="shared" si="25"/>
         <v>Geotechnical Segment Supplier: It is a sale of products</v>
       </c>
     </row>
-    <row r="39" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A39" s="51">
         <v>39</v>
       </c>
@@ -6729,7 +6729,7 @@
         <v>221</v>
       </c>
       <c r="F39" s="57" t="s">
-        <v>476</v>
+        <v>448</v>
       </c>
       <c r="G39" s="28" t="s">
         <v>9</v>
@@ -6763,7 +6763,7 @@
         <v>Ger Compra</v>
       </c>
       <c r="P39" s="23" t="s">
-        <v>498</v>
+        <v>470</v>
       </c>
       <c r="Q39" s="26" t="str">
         <f t="shared" si="22"/>
@@ -6798,14 +6798,14 @@
         <v>9</v>
       </c>
       <c r="Z39" s="41" t="s">
-        <v>499</v>
+        <v>471</v>
       </c>
       <c r="AA39" s="45" t="str">
         <f t="shared" si="25"/>
         <v>General segment supplier: it is a purchase of products</v>
       </c>
     </row>
-    <row r="40" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A40" s="51">
         <v>40</v>
       </c>
@@ -6822,7 +6822,7 @@
         <v>221</v>
       </c>
       <c r="F40" s="57" t="s">
-        <v>384</v>
+        <v>372</v>
       </c>
       <c r="G40" s="28" t="s">
         <v>9</v>
@@ -6891,14 +6891,14 @@
         <v>9</v>
       </c>
       <c r="Z40" s="41" t="s">
-        <v>428</v>
+        <v>413</v>
       </c>
       <c r="AA40" s="45" t="str">
         <f t="shared" si="25"/>
         <v>General segment supplier: is a self-employed consultant</v>
       </c>
     </row>
-    <row r="41" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A41" s="51">
         <v>41</v>
       </c>
@@ -6915,7 +6915,7 @@
         <v>221</v>
       </c>
       <c r="F41" s="57" t="s">
-        <v>562</v>
+        <v>534</v>
       </c>
       <c r="G41" s="28" t="s">
         <v>9</v>
@@ -6936,19 +6936,19 @@
         <v>95</v>
       </c>
       <c r="M41" s="23" t="s">
+        <v>484</v>
+      </c>
+      <c r="N41" s="23" t="s">
         <v>512</v>
       </c>
-      <c r="N41" s="23" t="s">
-        <v>540</v>
-      </c>
       <c r="O41" s="23" t="s">
-        <v>541</v>
+        <v>513</v>
       </c>
       <c r="P41" s="23" t="s">
-        <v>575</v>
+        <v>547</v>
       </c>
       <c r="Q41" s="26" t="s">
-        <v>597</v>
+        <v>569</v>
       </c>
       <c r="R41" s="42" t="s">
         <v>9</v>
@@ -6957,16 +6957,16 @@
         <v>95</v>
       </c>
       <c r="T41" s="43" t="s">
+        <v>484</v>
+      </c>
+      <c r="U41" s="43" t="s">
         <v>512</v>
-      </c>
-      <c r="U41" s="43" t="s">
-        <v>540</v>
       </c>
       <c r="V41" s="41" t="s">
         <v>184</v>
       </c>
       <c r="W41" s="60" t="s">
-        <v>542</v>
+        <v>514</v>
       </c>
       <c r="X41" s="41" t="s">
         <v>9</v>
@@ -6975,13 +6975,13 @@
         <v>9</v>
       </c>
       <c r="Z41" s="41" t="s">
-        <v>565</v>
+        <v>537</v>
       </c>
       <c r="AA41" s="45" t="s">
-        <v>587</v>
-      </c>
-    </row>
-    <row r="42" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="42" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A42" s="51">
         <v>42</v>
       </c>
@@ -6998,7 +6998,7 @@
         <v>221</v>
       </c>
       <c r="F42" s="57" t="s">
-        <v>385</v>
+        <v>373</v>
       </c>
       <c r="G42" s="28" t="s">
         <v>9</v>
@@ -7067,14 +7067,14 @@
         <v>9</v>
       </c>
       <c r="Z42" s="41" t="s">
-        <v>428</v>
+        <v>413</v>
       </c>
       <c r="AA42" s="45" t="str">
         <f t="shared" ref="AA42:AA49" si="31">_xlfn.TRANSLATE(P42,"pt","en")</f>
         <v>General segment supplier: it is a consulting company</v>
       </c>
     </row>
-    <row r="43" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A43" s="51">
         <v>43</v>
       </c>
@@ -7091,7 +7091,7 @@
         <v>221</v>
       </c>
       <c r="F43" s="57" t="s">
-        <v>386</v>
+        <v>374</v>
       </c>
       <c r="G43" s="28" t="s">
         <v>9</v>
@@ -7160,14 +7160,14 @@
         <v>9</v>
       </c>
       <c r="Z43" s="41" t="s">
-        <v>419</v>
+        <v>404</v>
       </c>
       <c r="AA43" s="45" t="str">
         <f t="shared" si="31"/>
         <v>General segment supplier: is a manufacturer of products</v>
       </c>
     </row>
-    <row r="44" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A44" s="51">
         <v>44</v>
       </c>
@@ -7184,7 +7184,7 @@
         <v>221</v>
       </c>
       <c r="F44" s="57" t="s">
-        <v>387</v>
+        <v>598</v>
       </c>
       <c r="G44" s="28" t="s">
         <v>9</v>
@@ -7215,7 +7215,7 @@
       </c>
       <c r="O44" s="23" t="str">
         <f t="shared" si="27"/>
-        <v>Ger Fornecimento</v>
+        <v>Ger Fornecedor</v>
       </c>
       <c r="P44" s="23" t="s">
         <v>189</v>
@@ -7253,14 +7253,14 @@
         <v>9</v>
       </c>
       <c r="Z44" s="41" t="s">
-        <v>426</v>
+        <v>411</v>
       </c>
       <c r="AA44" s="45" t="str">
         <f t="shared" si="31"/>
         <v>General segment supplier: is a supplier</v>
       </c>
     </row>
-    <row r="45" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A45" s="51">
         <v>45</v>
       </c>
@@ -7277,7 +7277,7 @@
         <v>221</v>
       </c>
       <c r="F45" s="57" t="s">
-        <v>388</v>
+        <v>375</v>
       </c>
       <c r="G45" s="28" t="s">
         <v>9</v>
@@ -7346,14 +7346,14 @@
         <v>9</v>
       </c>
       <c r="Z45" s="41" t="s">
-        <v>430</v>
+        <v>415</v>
       </c>
       <c r="AA45" s="45" t="str">
         <f t="shared" si="31"/>
         <v>General Segment Supplier: is a Designer or Design Company</v>
       </c>
     </row>
-    <row r="46" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A46" s="51">
         <v>46</v>
       </c>
@@ -7370,7 +7370,7 @@
         <v>221</v>
       </c>
       <c r="F46" s="57" t="s">
-        <v>389</v>
+        <v>376</v>
       </c>
       <c r="G46" s="28" t="s">
         <v>9</v>
@@ -7439,14 +7439,14 @@
         <v>9</v>
       </c>
       <c r="Z46" s="41" t="s">
-        <v>429</v>
+        <v>414</v>
       </c>
       <c r="AA46" s="45" t="str">
         <f t="shared" si="31"/>
         <v>General Segment Supplier: It is a service</v>
       </c>
     </row>
-    <row r="47" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A47" s="51">
         <v>47</v>
       </c>
@@ -7463,7 +7463,7 @@
         <v>221</v>
       </c>
       <c r="F47" s="57" t="s">
-        <v>471</v>
+        <v>611</v>
       </c>
       <c r="G47" s="28" t="s">
         <v>9</v>
@@ -7494,10 +7494,10 @@
       </c>
       <c r="O47" s="23" t="str">
         <f t="shared" si="27"/>
-        <v>Ger Venda</v>
+        <v>Ger Vendedor</v>
       </c>
       <c r="P47" s="23" t="s">
-        <v>509</v>
+        <v>481</v>
       </c>
       <c r="Q47" s="26" t="str">
         <f t="shared" si="28"/>
@@ -7532,14 +7532,14 @@
         <v>9</v>
       </c>
       <c r="Z47" s="41" t="s">
-        <v>427</v>
+        <v>412</v>
       </c>
       <c r="AA47" s="45" t="str">
         <f t="shared" si="31"/>
         <v>General segment supplier: it is a sale of products</v>
       </c>
     </row>
-    <row r="48" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A48" s="51">
         <v>48</v>
       </c>
@@ -7556,7 +7556,7 @@
         <v>101</v>
       </c>
       <c r="F48" s="57" t="s">
-        <v>483</v>
+        <v>455</v>
       </c>
       <c r="G48" s="28" t="s">
         <v>9</v>
@@ -7590,7 +7590,7 @@
         <v>Hos Compra</v>
       </c>
       <c r="P48" s="23" t="s">
-        <v>491</v>
+        <v>463</v>
       </c>
       <c r="Q48" s="26" t="str">
         <f t="shared" si="28"/>
@@ -7625,14 +7625,14 @@
         <v>9</v>
       </c>
       <c r="Z48" s="41" t="s">
-        <v>499</v>
+        <v>471</v>
       </c>
       <c r="AA48" s="45" t="str">
         <f t="shared" si="31"/>
         <v>Hospital segment supplier: it is a purchase of products</v>
       </c>
     </row>
-    <row r="49" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="51">
         <v>49</v>
       </c>
@@ -7649,7 +7649,7 @@
         <v>101</v>
       </c>
       <c r="F49" s="57" t="s">
-        <v>366</v>
+        <v>358</v>
       </c>
       <c r="G49" s="28" t="s">
         <v>9</v>
@@ -7718,14 +7718,14 @@
         <v>9</v>
       </c>
       <c r="Z49" s="41" t="s">
-        <v>423</v>
+        <v>408</v>
       </c>
       <c r="AA49" s="45" t="str">
         <f t="shared" si="31"/>
         <v>Hospital Segment Supplier: is a self-employed consultant</v>
       </c>
     </row>
-    <row r="50" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A50" s="51">
         <v>50</v>
       </c>
@@ -7742,7 +7742,7 @@
         <v>101</v>
       </c>
       <c r="F50" s="57" t="s">
-        <v>555</v>
+        <v>527</v>
       </c>
       <c r="G50" s="28" t="s">
         <v>9</v>
@@ -7763,19 +7763,19 @@
         <v>95</v>
       </c>
       <c r="M50" s="23" t="s">
-        <v>512</v>
+        <v>484</v>
       </c>
       <c r="N50" s="23" t="s">
-        <v>519</v>
+        <v>491</v>
       </c>
       <c r="O50" s="23" t="s">
-        <v>520</v>
+        <v>492</v>
       </c>
       <c r="P50" s="23" t="s">
-        <v>568</v>
+        <v>540</v>
       </c>
       <c r="Q50" s="26" t="s">
-        <v>593</v>
+        <v>565</v>
       </c>
       <c r="R50" s="42" t="s">
         <v>9</v>
@@ -7784,16 +7784,16 @@
         <v>95</v>
       </c>
       <c r="T50" s="43" t="s">
-        <v>512</v>
+        <v>484</v>
       </c>
       <c r="U50" s="43" t="s">
-        <v>519</v>
+        <v>491</v>
       </c>
       <c r="V50" s="41" t="s">
         <v>184</v>
       </c>
       <c r="W50" s="60" t="s">
-        <v>521</v>
+        <v>493</v>
       </c>
       <c r="X50" s="41" t="s">
         <v>9</v>
@@ -7802,13 +7802,13 @@
         <v>9</v>
       </c>
       <c r="Z50" s="41" t="s">
-        <v>565</v>
+        <v>537</v>
       </c>
       <c r="AA50" s="45" t="s">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="51" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="51" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A51" s="51">
         <v>51</v>
       </c>
@@ -7825,7 +7825,7 @@
         <v>101</v>
       </c>
       <c r="F51" s="57" t="s">
-        <v>367</v>
+        <v>359</v>
       </c>
       <c r="G51" s="28" t="s">
         <v>9</v>
@@ -7894,14 +7894,14 @@
         <v>9</v>
       </c>
       <c r="Z51" s="41" t="s">
-        <v>423</v>
+        <v>408</v>
       </c>
       <c r="AA51" s="45" t="str">
         <f t="shared" ref="AA51:AA58" si="37">_xlfn.TRANSLATE(P51,"pt","en")</f>
         <v>Supplier in the hospital segment: it is a consulting company</v>
       </c>
     </row>
-    <row r="52" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A52" s="51">
         <v>52</v>
       </c>
@@ -7918,7 +7918,7 @@
         <v>101</v>
       </c>
       <c r="F52" s="57" t="s">
-        <v>368</v>
+        <v>360</v>
       </c>
       <c r="G52" s="28" t="s">
         <v>9</v>
@@ -7987,14 +7987,14 @@
         <v>9</v>
       </c>
       <c r="Z52" s="41" t="s">
-        <v>419</v>
+        <v>404</v>
       </c>
       <c r="AA52" s="45" t="str">
         <f t="shared" si="37"/>
         <v>Supplier in the hospital segment: it is a manufacturer of products</v>
       </c>
     </row>
-    <row r="53" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A53" s="51">
         <v>53</v>
       </c>
@@ -8011,7 +8011,7 @@
         <v>101</v>
       </c>
       <c r="F53" s="57" t="s">
-        <v>369</v>
+        <v>599</v>
       </c>
       <c r="G53" s="28" t="s">
         <v>9</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="O53" s="23" t="str">
         <f t="shared" si="33"/>
-        <v>Hos Fornecimento</v>
+        <v>Hos Fornecedor</v>
       </c>
       <c r="P53" s="23" t="s">
         <v>180</v>
@@ -8080,14 +8080,14 @@
         <v>9</v>
       </c>
       <c r="Z53" s="41" t="s">
-        <v>426</v>
+        <v>411</v>
       </c>
       <c r="AA53" s="45" t="str">
         <f t="shared" si="37"/>
         <v>Hospital Segment Supplier: is a supplier</v>
       </c>
     </row>
-    <row r="54" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A54" s="51">
         <v>54</v>
       </c>
@@ -8104,7 +8104,7 @@
         <v>101</v>
       </c>
       <c r="F54" s="57" t="s">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="G54" s="28" t="s">
         <v>9</v>
@@ -8173,14 +8173,14 @@
         <v>9</v>
       </c>
       <c r="Z54" s="41" t="s">
-        <v>424</v>
+        <v>409</v>
       </c>
       <c r="AA54" s="45" t="str">
         <f t="shared" si="37"/>
         <v>Supplier in the hospital segment: is a Designer or Design Company</v>
       </c>
     </row>
-    <row r="55" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A55" s="51">
         <v>55</v>
       </c>
@@ -8197,7 +8197,7 @@
         <v>101</v>
       </c>
       <c r="F55" s="57" t="s">
-        <v>371</v>
+        <v>362</v>
       </c>
       <c r="G55" s="28" t="s">
         <v>9</v>
@@ -8266,14 +8266,14 @@
         <v>9</v>
       </c>
       <c r="Z55" s="41" t="s">
-        <v>425</v>
+        <v>410</v>
       </c>
       <c r="AA55" s="45" t="str">
         <f t="shared" si="37"/>
         <v>Supplier in the hospital segment: it is a service</v>
       </c>
     </row>
-    <row r="56" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A56" s="51">
         <v>56</v>
       </c>
@@ -8290,7 +8290,7 @@
         <v>101</v>
       </c>
       <c r="F56" s="57" t="s">
-        <v>464</v>
+        <v>612</v>
       </c>
       <c r="G56" s="28" t="s">
         <v>9</v>
@@ -8321,10 +8321,10 @@
       </c>
       <c r="O56" s="23" t="str">
         <f t="shared" si="33"/>
-        <v>Hos Venda</v>
+        <v>Hos Vendedor</v>
       </c>
       <c r="P56" s="23" t="s">
-        <v>502</v>
+        <v>474</v>
       </c>
       <c r="Q56" s="26" t="str">
         <f t="shared" si="34"/>
@@ -8359,14 +8359,14 @@
         <v>9</v>
       </c>
       <c r="Z56" s="41" t="s">
-        <v>427</v>
+        <v>412</v>
       </c>
       <c r="AA56" s="45" t="str">
         <f t="shared" si="37"/>
         <v>Supplier in the hospital segment: it is a sale of products</v>
       </c>
     </row>
-    <row r="57" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A57" s="51">
         <v>57</v>
       </c>
@@ -8383,7 +8383,7 @@
         <v>318</v>
       </c>
       <c r="F57" s="57" t="s">
-        <v>475</v>
+        <v>447</v>
       </c>
       <c r="G57" s="28" t="s">
         <v>9</v>
@@ -8417,7 +8417,7 @@
         <v>Ilu Compra</v>
       </c>
       <c r="P57" s="23" t="s">
-        <v>486</v>
+        <v>458</v>
       </c>
       <c r="Q57" s="26" t="str">
         <f t="shared" si="34"/>
@@ -8452,14 +8452,14 @@
         <v>9</v>
       </c>
       <c r="Z57" s="41" t="s">
-        <v>499</v>
+        <v>471</v>
       </c>
       <c r="AA57" s="45" t="str">
         <f t="shared" si="37"/>
         <v>Lighting segment supplier: it is a purchase of products</v>
       </c>
     </row>
-    <row r="58" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A58" s="51">
         <v>58</v>
       </c>
@@ -8476,7 +8476,7 @@
         <v>318</v>
       </c>
       <c r="F58" s="57" t="s">
-        <v>390</v>
+        <v>377</v>
       </c>
       <c r="G58" s="28" t="s">
         <v>9</v>
@@ -8545,14 +8545,14 @@
         <v>9</v>
       </c>
       <c r="Z58" s="41" t="s">
-        <v>428</v>
+        <v>413</v>
       </c>
       <c r="AA58" s="45" t="str">
         <f t="shared" si="37"/>
         <v>Lighting Segment Supplier: is a self-employed consultant</v>
       </c>
     </row>
-    <row r="59" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A59" s="51">
         <v>59</v>
       </c>
@@ -8569,7 +8569,7 @@
         <v>318</v>
       </c>
       <c r="F59" s="57" t="s">
-        <v>563</v>
+        <v>535</v>
       </c>
       <c r="G59" s="28" t="s">
         <v>9</v>
@@ -8590,19 +8590,19 @@
         <v>95</v>
       </c>
       <c r="M59" s="23" t="s">
-        <v>512</v>
+        <v>484</v>
       </c>
       <c r="N59" s="23" t="s">
-        <v>543</v>
+        <v>515</v>
       </c>
       <c r="O59" s="23" t="s">
-        <v>544</v>
+        <v>516</v>
       </c>
       <c r="P59" s="23" t="s">
-        <v>576</v>
+        <v>548</v>
       </c>
       <c r="Q59" s="26" t="s">
-        <v>598</v>
+        <v>570</v>
       </c>
       <c r="R59" s="42" t="s">
         <v>9</v>
@@ -8611,16 +8611,16 @@
         <v>95</v>
       </c>
       <c r="T59" s="43" t="s">
-        <v>512</v>
+        <v>484</v>
       </c>
       <c r="U59" s="43" t="s">
-        <v>543</v>
+        <v>515</v>
       </c>
       <c r="V59" s="41" t="s">
         <v>184</v>
       </c>
       <c r="W59" s="60" t="s">
-        <v>545</v>
+        <v>517</v>
       </c>
       <c r="X59" s="41" t="s">
         <v>9</v>
@@ -8629,13 +8629,13 @@
         <v>9</v>
       </c>
       <c r="Z59" s="41" t="s">
-        <v>565</v>
+        <v>537</v>
       </c>
       <c r="AA59" s="45" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="60" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="60" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A60" s="51">
         <v>60</v>
       </c>
@@ -8652,7 +8652,7 @@
         <v>318</v>
       </c>
       <c r="F60" s="57" t="s">
-        <v>391</v>
+        <v>378</v>
       </c>
       <c r="G60" s="28" t="s">
         <v>9</v>
@@ -8721,14 +8721,14 @@
         <v>9</v>
       </c>
       <c r="Z60" s="41" t="s">
-        <v>428</v>
+        <v>413</v>
       </c>
       <c r="AA60" s="45" t="str">
         <f t="shared" ref="AA60:AA67" si="43">_xlfn.TRANSLATE(P60,"pt","en")</f>
         <v>Supplier in the lighting segment: it is a consulting company</v>
       </c>
     </row>
-    <row r="61" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A61" s="51">
         <v>61</v>
       </c>
@@ -8745,7 +8745,7 @@
         <v>318</v>
       </c>
       <c r="F61" s="57" t="s">
-        <v>392</v>
+        <v>379</v>
       </c>
       <c r="G61" s="28" t="s">
         <v>9</v>
@@ -8814,14 +8814,14 @@
         <v>9</v>
       </c>
       <c r="Z61" s="41" t="s">
-        <v>419</v>
+        <v>404</v>
       </c>
       <c r="AA61" s="45" t="str">
         <f t="shared" si="43"/>
         <v>Lighting Segment Supplier: is a manufacturer of products</v>
       </c>
     </row>
-    <row r="62" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A62" s="51">
         <v>62</v>
       </c>
@@ -8838,7 +8838,7 @@
         <v>318</v>
       </c>
       <c r="F62" s="57" t="s">
-        <v>393</v>
+        <v>600</v>
       </c>
       <c r="G62" s="28" t="s">
         <v>9</v>
@@ -8869,7 +8869,7 @@
       </c>
       <c r="O62" s="23" t="str">
         <f t="shared" si="39"/>
-        <v>Ilu Fornecimento</v>
+        <v>Ilu Fornecedor</v>
       </c>
       <c r="P62" s="23" t="s">
         <v>315</v>
@@ -8907,14 +8907,14 @@
         <v>9</v>
       </c>
       <c r="Z62" s="41" t="s">
-        <v>426</v>
+        <v>411</v>
       </c>
       <c r="AA62" s="45" t="str">
         <f t="shared" si="43"/>
         <v>Lighting segment supplier: is a supplier</v>
       </c>
     </row>
-    <row r="63" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A63" s="51">
         <v>63</v>
       </c>
@@ -8931,7 +8931,7 @@
         <v>318</v>
       </c>
       <c r="F63" s="57" t="s">
-        <v>394</v>
+        <v>380</v>
       </c>
       <c r="G63" s="28" t="s">
         <v>9</v>
@@ -9000,14 +9000,14 @@
         <v>9</v>
       </c>
       <c r="Z63" s="41" t="s">
-        <v>430</v>
+        <v>415</v>
       </c>
       <c r="AA63" s="45" t="str">
         <f t="shared" si="43"/>
         <v>Lighting Segment Supplier: is a Designer or Design Company</v>
       </c>
     </row>
-    <row r="64" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A64" s="51">
         <v>64</v>
       </c>
@@ -9024,7 +9024,7 @@
         <v>318</v>
       </c>
       <c r="F64" s="57" t="s">
-        <v>395</v>
+        <v>381</v>
       </c>
       <c r="G64" s="28" t="s">
         <v>9</v>
@@ -9093,14 +9093,14 @@
         <v>9</v>
       </c>
       <c r="Z64" s="41" t="s">
-        <v>429</v>
+        <v>414</v>
       </c>
       <c r="AA64" s="45" t="str">
         <f t="shared" si="43"/>
         <v>Lighting Segment Supplier: It's a Service</v>
       </c>
     </row>
-    <row r="65" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A65" s="51">
         <v>65</v>
       </c>
@@ -9117,7 +9117,7 @@
         <v>318</v>
       </c>
       <c r="F65" s="57" t="s">
-        <v>472</v>
+        <v>613</v>
       </c>
       <c r="G65" s="28" t="s">
         <v>9</v>
@@ -9148,10 +9148,10 @@
       </c>
       <c r="O65" s="23" t="str">
         <f t="shared" si="39"/>
-        <v>Ilu Venda</v>
+        <v>Ilu Vendedor</v>
       </c>
       <c r="P65" s="23" t="s">
-        <v>510</v>
+        <v>482</v>
       </c>
       <c r="Q65" s="26" t="str">
         <f t="shared" si="40"/>
@@ -9186,14 +9186,14 @@
         <v>9</v>
       </c>
       <c r="Z65" s="41" t="s">
-        <v>427</v>
+        <v>412</v>
       </c>
       <c r="AA65" s="45" t="str">
         <f t="shared" si="43"/>
         <v>Lighting Segment Supplier: It is a sale of products</v>
       </c>
     </row>
-    <row r="66" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A66" s="51">
         <v>66</v>
       </c>
@@ -9210,7 +9210,7 @@
         <v>99</v>
       </c>
       <c r="F66" s="57" t="s">
-        <v>478</v>
+        <v>450</v>
       </c>
       <c r="G66" s="28" t="s">
         <v>9</v>
@@ -9244,7 +9244,7 @@
         <v>Ino Compra</v>
       </c>
       <c r="P66" s="23" t="s">
-        <v>496</v>
+        <v>468</v>
       </c>
       <c r="Q66" s="26" t="str">
         <f t="shared" si="40"/>
@@ -9279,14 +9279,14 @@
         <v>9</v>
       </c>
       <c r="Z66" s="41" t="s">
-        <v>499</v>
+        <v>471</v>
       </c>
       <c r="AA66" s="45" t="str">
         <f t="shared" si="43"/>
         <v>Innovation Segment Supplier: It is a purchase of products</v>
       </c>
     </row>
-    <row r="67" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A67" s="51">
         <v>67</v>
       </c>
@@ -9303,7 +9303,7 @@
         <v>99</v>
       </c>
       <c r="F67" s="57" t="s">
-        <v>372</v>
+        <v>363</v>
       </c>
       <c r="G67" s="28" t="s">
         <v>9</v>
@@ -9372,14 +9372,14 @@
         <v>9</v>
       </c>
       <c r="Z67" s="41" t="s">
-        <v>428</v>
+        <v>413</v>
       </c>
       <c r="AA67" s="45" t="str">
         <f t="shared" si="43"/>
         <v>Innovation Segment Provider: is a self-employed consultant</v>
       </c>
     </row>
-    <row r="68" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A68" s="51">
         <v>68</v>
       </c>
@@ -9396,7 +9396,7 @@
         <v>99</v>
       </c>
       <c r="F68" s="57" t="s">
-        <v>560</v>
+        <v>532</v>
       </c>
       <c r="G68" s="28" t="s">
         <v>9</v>
@@ -9417,19 +9417,19 @@
         <v>95</v>
       </c>
       <c r="M68" s="23" t="s">
-        <v>512</v>
+        <v>484</v>
       </c>
       <c r="N68" s="23" t="s">
-        <v>534</v>
+        <v>506</v>
       </c>
       <c r="O68" s="23" t="s">
-        <v>535</v>
+        <v>507</v>
       </c>
       <c r="P68" s="23" t="s">
+        <v>545</v>
+      </c>
+      <c r="Q68" s="26" t="s">
         <v>573</v>
-      </c>
-      <c r="Q68" s="26" t="s">
-        <v>601</v>
       </c>
       <c r="R68" s="42" t="s">
         <v>9</v>
@@ -9438,16 +9438,16 @@
         <v>95</v>
       </c>
       <c r="T68" s="43" t="s">
-        <v>512</v>
+        <v>484</v>
       </c>
       <c r="U68" s="43" t="s">
-        <v>534</v>
+        <v>506</v>
       </c>
       <c r="V68" s="41" t="s">
         <v>184</v>
       </c>
       <c r="W68" s="60" t="s">
-        <v>536</v>
+        <v>508</v>
       </c>
       <c r="X68" s="41" t="s">
         <v>9</v>
@@ -9456,13 +9456,13 @@
         <v>9</v>
       </c>
       <c r="Z68" s="41" t="s">
-        <v>565</v>
+        <v>537</v>
       </c>
       <c r="AA68" s="45" t="s">
-        <v>585</v>
-      </c>
-    </row>
-    <row r="69" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="69" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A69" s="51">
         <v>69</v>
       </c>
@@ -9479,7 +9479,7 @@
         <v>99</v>
       </c>
       <c r="F69" s="57" t="s">
-        <v>373</v>
+        <v>364</v>
       </c>
       <c r="G69" s="28" t="s">
         <v>9</v>
@@ -9548,14 +9548,14 @@
         <v>9</v>
       </c>
       <c r="Z69" s="41" t="s">
-        <v>428</v>
+        <v>413</v>
       </c>
       <c r="AA69" s="45" t="str">
         <f t="shared" ref="AA69:AA76" si="49">_xlfn.TRANSLATE(P69,"pt","en")</f>
         <v>Supplier of the innovation segment: it is a consulting company</v>
       </c>
     </row>
-    <row r="70" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A70" s="51">
         <v>70</v>
       </c>
@@ -9572,7 +9572,7 @@
         <v>99</v>
       </c>
       <c r="F70" s="57" t="s">
-        <v>374</v>
+        <v>365</v>
       </c>
       <c r="G70" s="28" t="s">
         <v>9</v>
@@ -9641,14 +9641,14 @@
         <v>9</v>
       </c>
       <c r="Z70" s="41" t="s">
-        <v>419</v>
+        <v>404</v>
       </c>
       <c r="AA70" s="45" t="str">
         <f t="shared" si="49"/>
         <v>Innovation Segment Supplier: is a manufacturer of products</v>
       </c>
     </row>
-    <row r="71" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A71" s="51">
         <v>71</v>
       </c>
@@ -9665,7 +9665,7 @@
         <v>99</v>
       </c>
       <c r="F71" s="57" t="s">
-        <v>375</v>
+        <v>601</v>
       </c>
       <c r="G71" s="28" t="s">
         <v>9</v>
@@ -9696,7 +9696,7 @@
       </c>
       <c r="O71" s="23" t="str">
         <f t="shared" si="45"/>
-        <v>Ino Fornecimento</v>
+        <v>Ino Fornecedor</v>
       </c>
       <c r="P71" s="23" t="s">
         <v>182</v>
@@ -9734,14 +9734,14 @@
         <v>9</v>
       </c>
       <c r="Z71" s="41" t="s">
-        <v>426</v>
+        <v>411</v>
       </c>
       <c r="AA71" s="45" t="str">
         <f t="shared" si="49"/>
         <v>Innovation Segment Supplier: is a supplier</v>
       </c>
     </row>
-    <row r="72" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A72" s="51">
         <v>72</v>
       </c>
@@ -9758,7 +9758,7 @@
         <v>99</v>
       </c>
       <c r="F72" s="57" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="G72" s="28" t="s">
         <v>9</v>
@@ -9827,14 +9827,14 @@
         <v>9</v>
       </c>
       <c r="Z72" s="41" t="s">
-        <v>430</v>
+        <v>415</v>
       </c>
       <c r="AA72" s="45" t="str">
         <f t="shared" si="49"/>
         <v>Innovation Segment Supplier: is a Designer or Design Company</v>
       </c>
     </row>
-    <row r="73" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A73" s="51">
         <v>73</v>
       </c>
@@ -9851,7 +9851,7 @@
         <v>99</v>
       </c>
       <c r="F73" s="57" t="s">
-        <v>377</v>
+        <v>367</v>
       </c>
       <c r="G73" s="28" t="s">
         <v>9</v>
@@ -9920,14 +9920,14 @@
         <v>9</v>
       </c>
       <c r="Z73" s="41" t="s">
-        <v>429</v>
+        <v>414</v>
       </c>
       <c r="AA73" s="45" t="str">
         <f t="shared" si="49"/>
         <v>Innovation Supplier: It's a Service</v>
       </c>
     </row>
-    <row r="74" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A74" s="51">
         <v>74</v>
       </c>
@@ -9944,7 +9944,7 @@
         <v>99</v>
       </c>
       <c r="F74" s="57" t="s">
-        <v>469</v>
+        <v>614</v>
       </c>
       <c r="G74" s="28" t="s">
         <v>9</v>
@@ -9975,10 +9975,10 @@
       </c>
       <c r="O74" s="23" t="str">
         <f t="shared" si="45"/>
-        <v>Ino Venda</v>
+        <v>Ino Vendedor</v>
       </c>
       <c r="P74" s="23" t="s">
-        <v>507</v>
+        <v>479</v>
       </c>
       <c r="Q74" s="26" t="str">
         <f t="shared" si="46"/>
@@ -10013,14 +10013,14 @@
         <v>9</v>
       </c>
       <c r="Z74" s="41" t="s">
-        <v>427</v>
+        <v>412</v>
       </c>
       <c r="AA74" s="45" t="str">
         <f t="shared" si="49"/>
         <v>Supplier of the innovation segment: it is a sale of products</v>
       </c>
     </row>
-    <row r="75" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A75" s="51">
         <v>75</v>
       </c>
@@ -10037,7 +10037,7 @@
         <v>98</v>
       </c>
       <c r="F75" s="57" t="s">
-        <v>482</v>
+        <v>454</v>
       </c>
       <c r="G75" s="28" t="s">
         <v>9</v>
@@ -10071,7 +10071,7 @@
         <v>Ins Compra</v>
       </c>
       <c r="P75" s="23" t="s">
-        <v>492</v>
+        <v>464</v>
       </c>
       <c r="Q75" s="26" t="str">
         <f t="shared" si="46"/>
@@ -10106,14 +10106,14 @@
         <v>9</v>
       </c>
       <c r="Z75" s="41" t="s">
-        <v>499</v>
+        <v>471</v>
       </c>
       <c r="AA75" s="45" t="str">
         <f t="shared" si="49"/>
         <v>Facilities segment supplier: it is a purchase of products</v>
       </c>
     </row>
-    <row r="76" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A76" s="51">
         <v>76</v>
       </c>
@@ -10130,7 +10130,7 @@
         <v>98</v>
       </c>
       <c r="F76" s="57" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="G76" s="28" t="s">
         <v>9</v>
@@ -10199,14 +10199,14 @@
         <v>9</v>
       </c>
       <c r="Z76" s="41" t="s">
-        <v>428</v>
+        <v>413</v>
       </c>
       <c r="AA76" s="45" t="str">
         <f t="shared" si="49"/>
         <v>Facilities Segment Provider: is a self-employed consultant</v>
       </c>
     </row>
-    <row r="77" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A77" s="51">
         <v>77</v>
       </c>
@@ -10223,7 +10223,7 @@
         <v>98</v>
       </c>
       <c r="F77" s="57" t="s">
-        <v>556</v>
+        <v>528</v>
       </c>
       <c r="G77" s="28" t="s">
         <v>9</v>
@@ -10244,19 +10244,19 @@
         <v>95</v>
       </c>
       <c r="M77" s="23" t="s">
-        <v>512</v>
+        <v>484</v>
       </c>
       <c r="N77" s="23" t="s">
-        <v>522</v>
+        <v>494</v>
       </c>
       <c r="O77" s="23" t="s">
-        <v>523</v>
+        <v>495</v>
       </c>
       <c r="P77" s="23" t="s">
-        <v>569</v>
+        <v>541</v>
       </c>
       <c r="Q77" s="26" t="s">
-        <v>602</v>
+        <v>574</v>
       </c>
       <c r="R77" s="42" t="s">
         <v>9</v>
@@ -10265,16 +10265,16 @@
         <v>95</v>
       </c>
       <c r="T77" s="43" t="s">
-        <v>512</v>
+        <v>484</v>
       </c>
       <c r="U77" s="43" t="s">
-        <v>522</v>
+        <v>494</v>
       </c>
       <c r="V77" s="41" t="s">
         <v>184</v>
       </c>
       <c r="W77" s="60" t="s">
-        <v>524</v>
+        <v>496</v>
       </c>
       <c r="X77" s="41" t="s">
         <v>9</v>
@@ -10283,13 +10283,13 @@
         <v>9</v>
       </c>
       <c r="Z77" s="41" t="s">
-        <v>565</v>
+        <v>537</v>
       </c>
       <c r="AA77" s="45" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="78" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="78" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A78" s="51">
         <v>78</v>
       </c>
@@ -10306,7 +10306,7 @@
         <v>98</v>
       </c>
       <c r="F78" s="57" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="G78" s="28" t="s">
         <v>9</v>
@@ -10375,14 +10375,14 @@
         <v>9</v>
       </c>
       <c r="Z78" s="41" t="s">
-        <v>428</v>
+        <v>413</v>
       </c>
       <c r="AA78" s="45" t="str">
         <f t="shared" ref="AA78:AA85" si="55">_xlfn.TRANSLATE(P78,"pt","en")</f>
         <v>Supplier in the facilities segment: it is a consulting company</v>
       </c>
     </row>
-    <row r="79" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A79" s="51">
         <v>79</v>
       </c>
@@ -10399,7 +10399,7 @@
         <v>98</v>
       </c>
       <c r="F79" s="57" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="G79" s="28" t="s">
         <v>9</v>
@@ -10468,14 +10468,14 @@
         <v>9</v>
       </c>
       <c r="Z79" s="41" t="s">
-        <v>419</v>
+        <v>404</v>
       </c>
       <c r="AA79" s="45" t="str">
         <f t="shared" si="55"/>
         <v>Supplier in the installation segment: is a manufacturer of products</v>
       </c>
     </row>
-    <row r="80" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A80" s="51">
         <v>80</v>
       </c>
@@ -10492,7 +10492,7 @@
         <v>98</v>
       </c>
       <c r="F80" s="57" t="s">
-        <v>345</v>
+        <v>602</v>
       </c>
       <c r="G80" s="28" t="s">
         <v>9</v>
@@ -10523,7 +10523,7 @@
       </c>
       <c r="O80" s="23" t="str">
         <f t="shared" si="51"/>
-        <v>Ins Fornecimento</v>
+        <v>Ins Fornecedor</v>
       </c>
       <c r="P80" s="23" t="s">
         <v>178</v>
@@ -10561,14 +10561,14 @@
         <v>9</v>
       </c>
       <c r="Z80" s="41" t="s">
-        <v>426</v>
+        <v>411</v>
       </c>
       <c r="AA80" s="45" t="str">
         <f t="shared" si="55"/>
         <v>Facilities Segment Supplier: is a supplier</v>
       </c>
     </row>
-    <row r="81" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A81" s="51">
         <v>81</v>
       </c>
@@ -10585,7 +10585,7 @@
         <v>98</v>
       </c>
       <c r="F81" s="57" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="G81" s="28" t="s">
         <v>9</v>
@@ -10654,14 +10654,14 @@
         <v>9</v>
       </c>
       <c r="Z81" s="41" t="s">
-        <v>421</v>
+        <v>406</v>
       </c>
       <c r="AA81" s="45" t="str">
         <f t="shared" si="55"/>
         <v>Installation Segment Supplier: is a Designer or Design Company</v>
       </c>
     </row>
-    <row r="82" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A82" s="51">
         <v>82</v>
       </c>
@@ -10678,7 +10678,7 @@
         <v>98</v>
       </c>
       <c r="F82" s="57" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="G82" s="28" t="s">
         <v>9</v>
@@ -10747,14 +10747,14 @@
         <v>9</v>
       </c>
       <c r="Z82" s="41" t="s">
-        <v>429</v>
+        <v>414</v>
       </c>
       <c r="AA82" s="45" t="str">
         <f t="shared" si="55"/>
         <v>Facilities Segment Provider: It's a Service</v>
       </c>
     </row>
-    <row r="83" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A83" s="51">
         <v>83</v>
       </c>
@@ -10771,7 +10771,7 @@
         <v>98</v>
       </c>
       <c r="F83" s="57" t="s">
-        <v>465</v>
+        <v>615</v>
       </c>
       <c r="G83" s="28" t="s">
         <v>9</v>
@@ -10802,10 +10802,10 @@
       </c>
       <c r="O83" s="23" t="str">
         <f t="shared" si="51"/>
-        <v>Ins Venda</v>
+        <v>Ins Vendedor</v>
       </c>
       <c r="P83" s="23" t="s">
-        <v>503</v>
+        <v>475</v>
       </c>
       <c r="Q83" s="26" t="str">
         <f t="shared" si="52"/>
@@ -10840,14 +10840,14 @@
         <v>9</v>
       </c>
       <c r="Z83" s="41" t="s">
-        <v>427</v>
+        <v>412</v>
       </c>
       <c r="AA83" s="45" t="str">
         <f t="shared" si="55"/>
         <v>Supplier in the facilities segment: it is a sale of products</v>
       </c>
     </row>
-    <row r="84" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A84" s="51">
         <v>84</v>
       </c>
@@ -10864,7 +10864,7 @@
         <v>102</v>
       </c>
       <c r="F84" s="57" t="s">
-        <v>481</v>
+        <v>453</v>
       </c>
       <c r="G84" s="28" t="s">
         <v>9</v>
@@ -10898,7 +10898,7 @@
         <v>Lab Compra</v>
       </c>
       <c r="P84" s="23" t="s">
-        <v>493</v>
+        <v>465</v>
       </c>
       <c r="Q84" s="26" t="str">
         <f t="shared" si="52"/>
@@ -10933,14 +10933,14 @@
         <v>9</v>
       </c>
       <c r="Z84" s="41" t="s">
-        <v>499</v>
+        <v>471</v>
       </c>
       <c r="AA84" s="45" t="str">
         <f t="shared" si="55"/>
         <v>Supplier in the laboratory segment: it is a purchase of products</v>
       </c>
     </row>
-    <row r="85" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A85" s="51">
         <v>85</v>
       </c>
@@ -10957,7 +10957,7 @@
         <v>102</v>
       </c>
       <c r="F85" s="57" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="G85" s="28" t="s">
         <v>9</v>
@@ -11026,14 +11026,14 @@
         <v>9</v>
       </c>
       <c r="Z85" s="41" t="s">
-        <v>428</v>
+        <v>413</v>
       </c>
       <c r="AA85" s="45" t="str">
         <f t="shared" si="55"/>
         <v>Laboratory Segment Supplier: is a self-employed consultant</v>
       </c>
     </row>
-    <row r="86" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A86" s="51">
         <v>86</v>
       </c>
@@ -11050,7 +11050,7 @@
         <v>102</v>
       </c>
       <c r="F86" s="57" t="s">
-        <v>557</v>
+        <v>529</v>
       </c>
       <c r="G86" s="28" t="s">
         <v>9</v>
@@ -11071,19 +11071,19 @@
         <v>95</v>
       </c>
       <c r="M86" s="23" t="s">
-        <v>512</v>
+        <v>484</v>
       </c>
       <c r="N86" s="23" t="s">
-        <v>525</v>
+        <v>497</v>
       </c>
       <c r="O86" s="23" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="P86" s="23" t="s">
-        <v>570</v>
+        <v>542</v>
       </c>
       <c r="Q86" s="26" t="s">
-        <v>594</v>
+        <v>566</v>
       </c>
       <c r="R86" s="42" t="s">
         <v>9</v>
@@ -11092,16 +11092,16 @@
         <v>95</v>
       </c>
       <c r="T86" s="43" t="s">
-        <v>512</v>
+        <v>484</v>
       </c>
       <c r="U86" s="43" t="s">
-        <v>525</v>
+        <v>497</v>
       </c>
       <c r="V86" s="41" t="s">
         <v>184</v>
       </c>
       <c r="W86" s="60" t="s">
-        <v>527</v>
+        <v>499</v>
       </c>
       <c r="X86" s="41" t="s">
         <v>9</v>
@@ -11110,13 +11110,13 @@
         <v>9</v>
       </c>
       <c r="Z86" s="41" t="s">
-        <v>565</v>
+        <v>537</v>
       </c>
       <c r="AA86" s="45" t="s">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="87" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="87" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A87" s="51">
         <v>87</v>
       </c>
@@ -11133,7 +11133,7 @@
         <v>102</v>
       </c>
       <c r="F87" s="57" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="G87" s="28" t="s">
         <v>9</v>
@@ -11202,14 +11202,14 @@
         <v>9</v>
       </c>
       <c r="Z87" s="41" t="s">
-        <v>428</v>
+        <v>413</v>
       </c>
       <c r="AA87" s="45" t="str">
         <f t="shared" ref="AA87:AA94" si="61">_xlfn.TRANSLATE(P87,"pt","en")</f>
         <v>Supplier in the laboratory segment: it is a consulting company</v>
       </c>
     </row>
-    <row r="88" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A88" s="51">
         <v>88</v>
       </c>
@@ -11226,7 +11226,7 @@
         <v>102</v>
       </c>
       <c r="F88" s="57" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="G88" s="28" t="s">
         <v>9</v>
@@ -11295,14 +11295,14 @@
         <v>9</v>
       </c>
       <c r="Z88" s="41" t="s">
-        <v>419</v>
+        <v>404</v>
       </c>
       <c r="AA88" s="45" t="str">
         <f t="shared" si="61"/>
         <v>Supplier of the laboratory segment: it is a manufacturer of products</v>
       </c>
     </row>
-    <row r="89" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A89" s="51">
         <v>89</v>
       </c>
@@ -11319,7 +11319,7 @@
         <v>102</v>
       </c>
       <c r="F89" s="57" t="s">
-        <v>339</v>
+        <v>603</v>
       </c>
       <c r="G89" s="28" t="s">
         <v>9</v>
@@ -11350,7 +11350,7 @@
       </c>
       <c r="O89" s="23" t="str">
         <f t="shared" si="57"/>
-        <v>Lab Fornecimento</v>
+        <v>Lab Fornecedor</v>
       </c>
       <c r="P89" s="23" t="s">
         <v>181</v>
@@ -11388,14 +11388,14 @@
         <v>9</v>
       </c>
       <c r="Z89" s="41" t="s">
-        <v>426</v>
+        <v>411</v>
       </c>
       <c r="AA89" s="45" t="str">
         <f t="shared" si="61"/>
         <v>Supplier in the laboratory segment: is a supplier</v>
       </c>
     </row>
-    <row r="90" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A90" s="51">
         <v>90</v>
       </c>
@@ -11412,7 +11412,7 @@
         <v>102</v>
       </c>
       <c r="F90" s="57" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="G90" s="28" t="s">
         <v>9</v>
@@ -11481,14 +11481,14 @@
         <v>9</v>
       </c>
       <c r="Z90" s="41" t="s">
-        <v>430</v>
+        <v>415</v>
       </c>
       <c r="AA90" s="45" t="str">
         <f t="shared" si="61"/>
         <v>Laboratory Segment Supplier: is a Designer or Design Company</v>
       </c>
     </row>
-    <row r="91" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A91" s="51">
         <v>91</v>
       </c>
@@ -11505,7 +11505,7 @@
         <v>102</v>
       </c>
       <c r="F91" s="57" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="G91" s="28" t="s">
         <v>9</v>
@@ -11574,14 +11574,14 @@
         <v>9</v>
       </c>
       <c r="Z91" s="41" t="s">
-        <v>429</v>
+        <v>414</v>
       </c>
       <c r="AA91" s="45" t="str">
         <f t="shared" si="61"/>
         <v>Supplier in the laboratory segment: it is a service</v>
       </c>
     </row>
-    <row r="92" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A92" s="51">
         <v>92</v>
       </c>
@@ -11598,7 +11598,7 @@
         <v>102</v>
       </c>
       <c r="F92" s="57" t="s">
-        <v>466</v>
+        <v>616</v>
       </c>
       <c r="G92" s="28" t="s">
         <v>9</v>
@@ -11629,10 +11629,10 @@
       </c>
       <c r="O92" s="23" t="str">
         <f t="shared" si="57"/>
-        <v>Lab Venda</v>
+        <v>Lab Vendedor</v>
       </c>
       <c r="P92" s="23" t="s">
-        <v>504</v>
+        <v>476</v>
       </c>
       <c r="Q92" s="26" t="str">
         <f t="shared" si="58"/>
@@ -11667,14 +11667,14 @@
         <v>9</v>
       </c>
       <c r="Z92" s="41" t="s">
-        <v>427</v>
+        <v>412</v>
       </c>
       <c r="AA92" s="45" t="str">
         <f t="shared" si="61"/>
         <v>Supplier of the laboratory segment: it is a sale of products</v>
       </c>
     </row>
-    <row r="93" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A93" s="51">
         <v>93</v>
       </c>
@@ -11688,10 +11688,10 @@
         <v>311</v>
       </c>
       <c r="E93" s="52" t="s">
-        <v>404</v>
+        <v>390</v>
       </c>
       <c r="F93" s="57" t="s">
-        <v>479</v>
+        <v>451</v>
       </c>
       <c r="G93" s="28" t="s">
         <v>9</v>
@@ -11725,7 +11725,7 @@
         <v>Mec Compra</v>
       </c>
       <c r="P93" s="23" t="s">
-        <v>495</v>
+        <v>467</v>
       </c>
       <c r="Q93" s="26" t="str">
         <f t="shared" si="58"/>
@@ -11760,14 +11760,14 @@
         <v>9</v>
       </c>
       <c r="Z93" s="41" t="s">
-        <v>499</v>
+        <v>471</v>
       </c>
       <c r="AA93" s="45" t="str">
         <f t="shared" si="61"/>
         <v>Supplier in the mechanical equipment segment: it is a purchase of products</v>
       </c>
     </row>
-    <row r="94" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A94" s="51">
         <v>94</v>
       </c>
@@ -11781,7 +11781,7 @@
         <v>311</v>
       </c>
       <c r="E94" s="52" t="s">
-        <v>404</v>
+        <v>390</v>
       </c>
       <c r="F94" s="57" t="s">
         <v>319</v>
@@ -11818,7 +11818,7 @@
         <v>Mec Consultor</v>
       </c>
       <c r="P94" s="23" t="s">
-        <v>418</v>
+        <v>403</v>
       </c>
       <c r="Q94" s="26" t="str">
         <f t="shared" si="58"/>
@@ -11853,14 +11853,14 @@
         <v>9</v>
       </c>
       <c r="Z94" s="41" t="s">
-        <v>428</v>
+        <v>413</v>
       </c>
       <c r="AA94" s="45" t="str">
         <f t="shared" si="61"/>
         <v>Supplier in the mechanical equipment segment: is a self-employed consultant</v>
       </c>
     </row>
-    <row r="95" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A95" s="51">
         <v>95</v>
       </c>
@@ -11874,10 +11874,10 @@
         <v>311</v>
       </c>
       <c r="E95" s="52" t="s">
-        <v>404</v>
+        <v>390</v>
       </c>
       <c r="F95" s="57" t="s">
-        <v>559</v>
+        <v>531</v>
       </c>
       <c r="G95" s="28" t="s">
         <v>9</v>
@@ -11898,19 +11898,19 @@
         <v>95</v>
       </c>
       <c r="M95" s="23" t="s">
-        <v>512</v>
+        <v>484</v>
       </c>
       <c r="N95" s="23" t="s">
-        <v>531</v>
+        <v>503</v>
       </c>
       <c r="O95" s="23" t="s">
-        <v>532</v>
+        <v>504</v>
       </c>
       <c r="P95" s="23" t="s">
+        <v>544</v>
+      </c>
+      <c r="Q95" s="26" t="s">
         <v>572</v>
-      </c>
-      <c r="Q95" s="26" t="s">
-        <v>600</v>
       </c>
       <c r="R95" s="42" t="s">
         <v>9</v>
@@ -11919,16 +11919,16 @@
         <v>95</v>
       </c>
       <c r="T95" s="43" t="s">
-        <v>512</v>
+        <v>484</v>
       </c>
       <c r="U95" s="43" t="s">
-        <v>531</v>
+        <v>503</v>
       </c>
       <c r="V95" s="41" t="s">
         <v>184</v>
       </c>
       <c r="W95" s="60" t="s">
-        <v>533</v>
+        <v>505</v>
       </c>
       <c r="X95" s="41" t="s">
         <v>9</v>
@@ -11937,13 +11937,13 @@
         <v>9</v>
       </c>
       <c r="Z95" s="41" t="s">
-        <v>565</v>
+        <v>537</v>
       </c>
       <c r="AA95" s="45" t="s">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="96" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="96" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A96" s="51">
         <v>96</v>
       </c>
@@ -11957,7 +11957,7 @@
         <v>311</v>
       </c>
       <c r="E96" s="52" t="s">
-        <v>404</v>
+        <v>390</v>
       </c>
       <c r="F96" s="57" t="s">
         <v>320</v>
@@ -11994,7 +11994,7 @@
         <v>Mec Empresa Consultora</v>
       </c>
       <c r="P96" s="23" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="Q96" s="26" t="str">
         <f t="shared" ref="Q96:Q103" si="64">_xlfn.TRANSLATE(P96,"pt","es")</f>
@@ -12029,14 +12029,14 @@
         <v>9</v>
       </c>
       <c r="Z96" s="41" t="s">
-        <v>428</v>
+        <v>413</v>
       </c>
       <c r="AA96" s="45" t="str">
         <f t="shared" ref="AA96:AA103" si="67">_xlfn.TRANSLATE(P96,"pt","en")</f>
         <v>Supplier in the mechanical equipment segment: it is a consulting company</v>
       </c>
     </row>
-    <row r="97" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A97" s="51">
         <v>97</v>
       </c>
@@ -12050,7 +12050,7 @@
         <v>311</v>
       </c>
       <c r="E97" s="52" t="s">
-        <v>404</v>
+        <v>390</v>
       </c>
       <c r="F97" s="57" t="s">
         <v>321</v>
@@ -12087,7 +12087,7 @@
         <v>Mec Fabricante</v>
       </c>
       <c r="P97" s="23" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="Q97" s="26" t="str">
         <f t="shared" si="64"/>
@@ -12122,14 +12122,14 @@
         <v>9</v>
       </c>
       <c r="Z97" s="41" t="s">
-        <v>419</v>
+        <v>404</v>
       </c>
       <c r="AA97" s="45" t="str">
         <f t="shared" si="67"/>
         <v>Supplier in the mechanical equipment segment: it is a manufacturer of products</v>
       </c>
     </row>
-    <row r="98" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A98" s="51">
         <v>98</v>
       </c>
@@ -12143,10 +12143,10 @@
         <v>311</v>
       </c>
       <c r="E98" s="52" t="s">
-        <v>404</v>
+        <v>390</v>
       </c>
       <c r="F98" s="57" t="s">
-        <v>322</v>
+        <v>604</v>
       </c>
       <c r="G98" s="28" t="s">
         <v>9</v>
@@ -12177,10 +12177,10 @@
       </c>
       <c r="O98" s="23" t="str">
         <f t="shared" si="63"/>
-        <v>Mec Fornecimento</v>
+        <v>Mec Fornecedor</v>
       </c>
       <c r="P98" s="23" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="Q98" s="26" t="str">
         <f t="shared" si="64"/>
@@ -12215,14 +12215,14 @@
         <v>9</v>
       </c>
       <c r="Z98" s="41" t="s">
-        <v>426</v>
+        <v>411</v>
       </c>
       <c r="AA98" s="45" t="str">
         <f t="shared" si="67"/>
         <v>Supplier in the mechanical equipment segment: it is a supplier</v>
       </c>
     </row>
-    <row r="99" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A99" s="51">
         <v>99</v>
       </c>
@@ -12236,10 +12236,10 @@
         <v>311</v>
       </c>
       <c r="E99" s="52" t="s">
-        <v>404</v>
+        <v>390</v>
       </c>
       <c r="F99" s="57" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G99" s="28" t="s">
         <v>9</v>
@@ -12273,7 +12273,7 @@
         <v>Mec Projetista</v>
       </c>
       <c r="P99" s="23" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="Q99" s="26" t="str">
         <f t="shared" si="64"/>
@@ -12308,14 +12308,14 @@
         <v>9</v>
       </c>
       <c r="Z99" s="41" t="s">
-        <v>422</v>
+        <v>407</v>
       </c>
       <c r="AA99" s="45" t="str">
         <f t="shared" si="67"/>
         <v>Supplier in the mechanical equipment segment: is a Designer or Design Company</v>
       </c>
     </row>
-    <row r="100" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A100" s="51">
         <v>100</v>
       </c>
@@ -12329,10 +12329,10 @@
         <v>311</v>
       </c>
       <c r="E100" s="52" t="s">
-        <v>404</v>
+        <v>390</v>
       </c>
       <c r="F100" s="57" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="G100" s="28" t="s">
         <v>9</v>
@@ -12366,7 +12366,7 @@
         <v>Mec Serviço</v>
       </c>
       <c r="P100" s="23" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="Q100" s="26" t="str">
         <f t="shared" si="64"/>
@@ -12401,14 +12401,14 @@
         <v>9</v>
       </c>
       <c r="Z100" s="41" t="s">
-        <v>429</v>
+        <v>414</v>
       </c>
       <c r="AA100" s="45" t="str">
         <f t="shared" si="67"/>
         <v>Supplier in the mechanical equipment segment: it is a service</v>
       </c>
     </row>
-    <row r="101" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A101" s="51">
         <v>101</v>
       </c>
@@ -12422,10 +12422,10 @@
         <v>311</v>
       </c>
       <c r="E101" s="52" t="s">
-        <v>404</v>
+        <v>390</v>
       </c>
       <c r="F101" s="57" t="s">
-        <v>468</v>
+        <v>617</v>
       </c>
       <c r="G101" s="28" t="s">
         <v>9</v>
@@ -12456,10 +12456,10 @@
       </c>
       <c r="O101" s="23" t="str">
         <f t="shared" si="63"/>
-        <v>Mec Venda</v>
+        <v>Mec Vendedor</v>
       </c>
       <c r="P101" s="23" t="s">
-        <v>506</v>
+        <v>478</v>
       </c>
       <c r="Q101" s="26" t="str">
         <f t="shared" si="64"/>
@@ -12494,14 +12494,14 @@
         <v>9</v>
       </c>
       <c r="Z101" s="41" t="s">
-        <v>427</v>
+        <v>412</v>
       </c>
       <c r="AA101" s="45" t="str">
         <f t="shared" si="67"/>
         <v>Supplier in the mechanical equipment segment: it is a sale of products</v>
       </c>
     </row>
-    <row r="102" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A102" s="51">
         <v>102</v>
       </c>
@@ -12518,7 +12518,7 @@
         <v>100</v>
       </c>
       <c r="F102" s="57" t="s">
-        <v>480</v>
+        <v>452</v>
       </c>
       <c r="G102" s="28" t="s">
         <v>9</v>
@@ -12552,7 +12552,7 @@
         <v>Mob Compra</v>
       </c>
       <c r="P102" s="23" t="s">
-        <v>494</v>
+        <v>466</v>
       </c>
       <c r="Q102" s="26" t="str">
         <f t="shared" si="64"/>
@@ -12587,14 +12587,14 @@
         <v>9</v>
       </c>
       <c r="Z102" s="41" t="s">
-        <v>499</v>
+        <v>471</v>
       </c>
       <c r="AA102" s="45" t="str">
         <f t="shared" si="67"/>
         <v>Furniture supplier: it is a purchase of products</v>
       </c>
     </row>
-    <row r="103" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A103" s="51">
         <v>103</v>
       </c>
@@ -12611,7 +12611,7 @@
         <v>100</v>
       </c>
       <c r="F103" s="57" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="G103" s="28" t="s">
         <v>9</v>
@@ -12680,14 +12680,14 @@
         <v>9</v>
       </c>
       <c r="Z103" s="41" t="s">
-        <v>428</v>
+        <v>413</v>
       </c>
       <c r="AA103" s="45" t="str">
         <f t="shared" si="67"/>
         <v>Furniture supplier: is a self-employed consultant</v>
       </c>
     </row>
-    <row r="104" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A104" s="51">
         <v>104</v>
       </c>
@@ -12704,7 +12704,7 @@
         <v>100</v>
       </c>
       <c r="F104" s="57" t="s">
-        <v>558</v>
+        <v>530</v>
       </c>
       <c r="G104" s="28" t="s">
         <v>9</v>
@@ -12725,19 +12725,19 @@
         <v>95</v>
       </c>
       <c r="M104" s="23" t="s">
-        <v>512</v>
+        <v>484</v>
       </c>
       <c r="N104" s="23" t="s">
-        <v>528</v>
+        <v>500</v>
       </c>
       <c r="O104" s="23" t="s">
-        <v>529</v>
+        <v>501</v>
       </c>
       <c r="P104" s="23" t="s">
-        <v>571</v>
+        <v>543</v>
       </c>
       <c r="Q104" s="26" t="s">
-        <v>595</v>
+        <v>567</v>
       </c>
       <c r="R104" s="42" t="s">
         <v>9</v>
@@ -12746,16 +12746,16 @@
         <v>95</v>
       </c>
       <c r="T104" s="43" t="s">
-        <v>512</v>
+        <v>484</v>
       </c>
       <c r="U104" s="43" t="s">
-        <v>528</v>
+        <v>500</v>
       </c>
       <c r="V104" s="41" t="s">
         <v>184</v>
       </c>
       <c r="W104" s="60" t="s">
-        <v>530</v>
+        <v>502</v>
       </c>
       <c r="X104" s="41" t="s">
         <v>9</v>
@@ -12764,13 +12764,13 @@
         <v>9</v>
       </c>
       <c r="Z104" s="41" t="s">
-        <v>565</v>
+        <v>537</v>
       </c>
       <c r="AA104" s="45" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="105" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="105" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A105" s="51">
         <v>105</v>
       </c>
@@ -12787,7 +12787,7 @@
         <v>100</v>
       </c>
       <c r="F105" s="57" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="G105" s="28" t="s">
         <v>9</v>
@@ -12856,14 +12856,14 @@
         <v>9</v>
       </c>
       <c r="Z105" s="41" t="s">
-        <v>428</v>
+        <v>413</v>
       </c>
       <c r="AA105" s="45" t="str">
         <f t="shared" ref="AA105:AA112" si="73">_xlfn.TRANSLATE(P105,"pt","en")</f>
         <v>Supplier of the furniture segment: it is a consulting company</v>
       </c>
     </row>
-    <row r="106" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A106" s="51">
         <v>106</v>
       </c>
@@ -12880,7 +12880,7 @@
         <v>100</v>
       </c>
       <c r="F106" s="57" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="G106" s="28" t="s">
         <v>9</v>
@@ -12949,14 +12949,14 @@
         <v>9</v>
       </c>
       <c r="Z106" s="41" t="s">
-        <v>419</v>
+        <v>404</v>
       </c>
       <c r="AA106" s="45" t="str">
         <f t="shared" si="73"/>
         <v>Furniture segment supplier: is a manufacturer of products</v>
       </c>
     </row>
-    <row r="107" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A107" s="51">
         <v>107</v>
       </c>
@@ -12973,7 +12973,7 @@
         <v>100</v>
       </c>
       <c r="F107" s="57" t="s">
-        <v>328</v>
+        <v>605</v>
       </c>
       <c r="G107" s="28" t="s">
         <v>9</v>
@@ -13004,7 +13004,7 @@
       </c>
       <c r="O107" s="23" t="str">
         <f t="shared" si="69"/>
-        <v>Mob Fornecimento</v>
+        <v>Mob Fornecedor</v>
       </c>
       <c r="P107" s="23" t="s">
         <v>179</v>
@@ -13042,14 +13042,14 @@
         <v>9</v>
       </c>
       <c r="Z107" s="41" t="s">
-        <v>426</v>
+        <v>411</v>
       </c>
       <c r="AA107" s="45" t="str">
         <f t="shared" si="73"/>
         <v>Furniture Supplier: is a supplier</v>
       </c>
     </row>
-    <row r="108" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A108" s="51">
         <v>108</v>
       </c>
@@ -13066,7 +13066,7 @@
         <v>100</v>
       </c>
       <c r="F108" s="57" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="G108" s="28" t="s">
         <v>9</v>
@@ -13135,14 +13135,14 @@
         <v>9</v>
       </c>
       <c r="Z108" s="41" t="s">
-        <v>430</v>
+        <v>415</v>
       </c>
       <c r="AA108" s="45" t="str">
         <f t="shared" si="73"/>
         <v>Furniture Supplier: is a Designer or Design Company</v>
       </c>
     </row>
-    <row r="109" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A109" s="51">
         <v>109</v>
       </c>
@@ -13159,7 +13159,7 @@
         <v>100</v>
       </c>
       <c r="F109" s="57" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="G109" s="28" t="s">
         <v>9</v>
@@ -13228,14 +13228,14 @@
         <v>9</v>
       </c>
       <c r="Z109" s="41" t="s">
-        <v>429</v>
+        <v>414</v>
       </c>
       <c r="AA109" s="45" t="str">
         <f t="shared" si="73"/>
         <v>Furniture supplier: it is a service</v>
       </c>
     </row>
-    <row r="110" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A110" s="51">
         <v>110</v>
       </c>
@@ -13252,7 +13252,7 @@
         <v>100</v>
       </c>
       <c r="F110" s="57" t="s">
-        <v>467</v>
+        <v>618</v>
       </c>
       <c r="G110" s="28" t="s">
         <v>9</v>
@@ -13283,10 +13283,10 @@
       </c>
       <c r="O110" s="23" t="str">
         <f t="shared" si="69"/>
-        <v>Mob Venda</v>
+        <v>Mob Vendedor</v>
       </c>
       <c r="P110" s="23" t="s">
-        <v>505</v>
+        <v>477</v>
       </c>
       <c r="Q110" s="26" t="str">
         <f t="shared" si="70"/>
@@ -13321,14 +13321,14 @@
         <v>9</v>
       </c>
       <c r="Z110" s="41" t="s">
-        <v>427</v>
+        <v>412</v>
       </c>
       <c r="AA110" s="45" t="str">
         <f t="shared" si="73"/>
         <v>Furniture Supplier: It is a sale of products</v>
       </c>
     </row>
-    <row r="111" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A111" s="51">
         <v>111</v>
       </c>
@@ -13342,10 +13342,10 @@
         <v>311</v>
       </c>
       <c r="E111" s="52" t="s">
-        <v>405</v>
+        <v>391</v>
       </c>
       <c r="F111" s="57" t="s">
-        <v>474</v>
+        <v>446</v>
       </c>
       <c r="G111" s="28" t="s">
         <v>9</v>
@@ -13379,7 +13379,7 @@
         <v>Tel Compra</v>
       </c>
       <c r="P111" s="23" t="s">
-        <v>487</v>
+        <v>459</v>
       </c>
       <c r="Q111" s="26" t="str">
         <f t="shared" si="70"/>
@@ -13414,14 +13414,14 @@
         <v>9</v>
       </c>
       <c r="Z111" s="41" t="s">
-        <v>499</v>
+        <v>471</v>
       </c>
       <c r="AA111" s="45" t="str">
         <f t="shared" si="73"/>
         <v>Telecom supplier: it is a purchase of products</v>
       </c>
     </row>
-    <row r="112" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A112" s="51">
         <v>112</v>
       </c>
@@ -13435,10 +13435,10 @@
         <v>311</v>
       </c>
       <c r="E112" s="52" t="s">
-        <v>405</v>
+        <v>391</v>
       </c>
       <c r="F112" s="57" t="s">
-        <v>406</v>
+        <v>392</v>
       </c>
       <c r="G112" s="28" t="s">
         <v>9</v>
@@ -13472,7 +13472,7 @@
         <v>Tel Consultor</v>
       </c>
       <c r="P112" s="23" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
       <c r="Q112" s="26" t="str">
         <f t="shared" si="70"/>
@@ -13507,14 +13507,14 @@
         <v>9</v>
       </c>
       <c r="Z112" s="41" t="s">
-        <v>428</v>
+        <v>413</v>
       </c>
       <c r="AA112" s="45" t="str">
         <f t="shared" si="73"/>
         <v>Telecom supplier: is a self-employed consultant</v>
       </c>
     </row>
-    <row r="113" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A113" s="51">
         <v>113</v>
       </c>
@@ -13528,10 +13528,10 @@
         <v>311</v>
       </c>
       <c r="E113" s="52" t="s">
-        <v>405</v>
+        <v>391</v>
       </c>
       <c r="F113" s="57" t="s">
-        <v>564</v>
+        <v>536</v>
       </c>
       <c r="G113" s="28" t="s">
         <v>9</v>
@@ -13552,19 +13552,19 @@
         <v>95</v>
       </c>
       <c r="M113" s="23" t="s">
-        <v>512</v>
+        <v>484</v>
       </c>
       <c r="N113" s="23" t="s">
-        <v>546</v>
+        <v>518</v>
       </c>
       <c r="O113" s="23" t="s">
-        <v>547</v>
+        <v>519</v>
       </c>
       <c r="P113" s="23" t="s">
-        <v>577</v>
+        <v>549</v>
       </c>
       <c r="Q113" s="26" t="s">
-        <v>599</v>
+        <v>571</v>
       </c>
       <c r="R113" s="42" t="s">
         <v>9</v>
@@ -13573,16 +13573,16 @@
         <v>95</v>
       </c>
       <c r="T113" s="43" t="s">
-        <v>512</v>
+        <v>484</v>
       </c>
       <c r="U113" s="43" t="s">
-        <v>546</v>
+        <v>518</v>
       </c>
       <c r="V113" s="41" t="s">
         <v>184</v>
       </c>
       <c r="W113" s="60" t="s">
-        <v>548</v>
+        <v>520</v>
       </c>
       <c r="X113" s="41" t="s">
         <v>9</v>
@@ -13591,13 +13591,13 @@
         <v>9</v>
       </c>
       <c r="Z113" s="41" t="s">
-        <v>565</v>
+        <v>537</v>
       </c>
       <c r="AA113" s="45" t="s">
-        <v>589</v>
-      </c>
-    </row>
-    <row r="114" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="114" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A114" s="51">
         <v>114</v>
       </c>
@@ -13611,10 +13611,10 @@
         <v>311</v>
       </c>
       <c r="E114" s="52" t="s">
-        <v>405</v>
+        <v>391</v>
       </c>
       <c r="F114" s="57" t="s">
-        <v>407</v>
+        <v>393</v>
       </c>
       <c r="G114" s="28" t="s">
         <v>9</v>
@@ -13648,7 +13648,7 @@
         <v>Tel Empresa Consultora</v>
       </c>
       <c r="P114" s="23" t="s">
-        <v>412</v>
+        <v>397</v>
       </c>
       <c r="Q114" s="26" t="str">
         <f t="shared" ref="Q114:Q148" si="78">_xlfn.TRANSLATE(P114,"pt","es")</f>
@@ -13683,14 +13683,14 @@
         <v>9</v>
       </c>
       <c r="Z114" s="41" t="s">
-        <v>428</v>
+        <v>413</v>
       </c>
       <c r="AA114" s="45" t="str">
         <f t="shared" ref="AA114:AA148" si="83">_xlfn.TRANSLATE(P114,"pt","en")</f>
         <v>Telecom supplier: it is a consulting company</v>
       </c>
     </row>
-    <row r="115" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A115" s="51">
         <v>115</v>
       </c>
@@ -13704,10 +13704,10 @@
         <v>311</v>
       </c>
       <c r="E115" s="52" t="s">
-        <v>405</v>
+        <v>391</v>
       </c>
       <c r="F115" s="57" t="s">
-        <v>408</v>
+        <v>394</v>
       </c>
       <c r="G115" s="28" t="s">
         <v>9</v>
@@ -13741,7 +13741,7 @@
         <v>Tel Fabricante</v>
       </c>
       <c r="P115" s="23" t="s">
-        <v>413</v>
+        <v>398</v>
       </c>
       <c r="Q115" s="26" t="str">
         <f t="shared" si="78"/>
@@ -13776,14 +13776,14 @@
         <v>9</v>
       </c>
       <c r="Z115" s="41" t="s">
-        <v>419</v>
+        <v>404</v>
       </c>
       <c r="AA115" s="45" t="str">
         <f t="shared" si="83"/>
         <v>Telecom Segment Supplier: is a manufacturer of telecom products</v>
       </c>
     </row>
-    <row r="116" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A116" s="51">
         <v>116</v>
       </c>
@@ -13797,10 +13797,10 @@
         <v>311</v>
       </c>
       <c r="E116" s="52" t="s">
-        <v>405</v>
+        <v>391</v>
       </c>
       <c r="F116" s="57" t="s">
-        <v>409</v>
+        <v>606</v>
       </c>
       <c r="G116" s="28" t="s">
         <v>9</v>
@@ -13831,10 +13831,10 @@
       </c>
       <c r="O116" s="23" t="str">
         <f t="shared" si="77"/>
-        <v>Tel Fornecimento</v>
+        <v>Tel Fornecedor</v>
       </c>
       <c r="P116" s="23" t="s">
-        <v>414</v>
+        <v>399</v>
       </c>
       <c r="Q116" s="26" t="str">
         <f t="shared" si="78"/>
@@ -13869,14 +13869,14 @@
         <v>9</v>
       </c>
       <c r="Z116" s="41" t="s">
-        <v>426</v>
+        <v>411</v>
       </c>
       <c r="AA116" s="45" t="str">
         <f t="shared" si="83"/>
         <v>Telecom Segment Supplier: is a supplier</v>
       </c>
     </row>
-    <row r="117" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A117" s="51">
         <v>117</v>
       </c>
@@ -13890,10 +13890,10 @@
         <v>311</v>
       </c>
       <c r="E117" s="52" t="s">
-        <v>405</v>
+        <v>391</v>
       </c>
       <c r="F117" s="57" t="s">
-        <v>410</v>
+        <v>395</v>
       </c>
       <c r="G117" s="28" t="s">
         <v>9</v>
@@ -13927,7 +13927,7 @@
         <v>Tel Projetista</v>
       </c>
       <c r="P117" s="23" t="s">
-        <v>415</v>
+        <v>400</v>
       </c>
       <c r="Q117" s="26" t="str">
         <f t="shared" si="78"/>
@@ -13962,14 +13962,14 @@
         <v>9</v>
       </c>
       <c r="Z117" s="41" t="s">
-        <v>430</v>
+        <v>415</v>
       </c>
       <c r="AA117" s="45" t="str">
         <f t="shared" si="83"/>
         <v>Telecom Segment Supplier: is a Designer or Design Company</v>
       </c>
     </row>
-    <row r="118" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A118" s="51">
         <v>118</v>
       </c>
@@ -13983,10 +13983,10 @@
         <v>311</v>
       </c>
       <c r="E118" s="52" t="s">
-        <v>405</v>
+        <v>391</v>
       </c>
       <c r="F118" s="57" t="s">
-        <v>411</v>
+        <v>396</v>
       </c>
       <c r="G118" s="28" t="s">
         <v>9</v>
@@ -14020,7 +14020,7 @@
         <v>Tel Serviço</v>
       </c>
       <c r="P118" s="23" t="s">
-        <v>416</v>
+        <v>401</v>
       </c>
       <c r="Q118" s="26" t="str">
         <f t="shared" si="78"/>
@@ -14055,14 +14055,14 @@
         <v>9</v>
       </c>
       <c r="Z118" s="41" t="s">
-        <v>429</v>
+        <v>414</v>
       </c>
       <c r="AA118" s="45" t="str">
         <f t="shared" si="83"/>
         <v>Telecom Segment Supplier: It's a Service</v>
       </c>
     </row>
-    <row r="119" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A119" s="51">
         <v>119</v>
       </c>
@@ -14076,10 +14076,10 @@
         <v>311</v>
       </c>
       <c r="E119" s="52" t="s">
-        <v>405</v>
+        <v>391</v>
       </c>
       <c r="F119" s="57" t="s">
-        <v>473</v>
+        <v>619</v>
       </c>
       <c r="G119" s="28" t="s">
         <v>9</v>
@@ -14110,10 +14110,10 @@
       </c>
       <c r="O119" s="23" t="str">
         <f t="shared" si="77"/>
-        <v>Tel Venda</v>
+        <v>Tel Vendedor</v>
       </c>
       <c r="P119" s="23" t="s">
-        <v>511</v>
+        <v>483</v>
       </c>
       <c r="Q119" s="26" t="str">
         <f t="shared" si="78"/>
@@ -14148,14 +14148,14 @@
         <v>9</v>
       </c>
       <c r="Z119" s="41" t="s">
-        <v>427</v>
+        <v>412</v>
       </c>
       <c r="AA119" s="45" t="str">
         <f t="shared" si="83"/>
         <v>Telecom segment supplier: it is a sale of products</v>
       </c>
     </row>
-    <row r="120" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A120" s="51">
         <v>120</v>
       </c>
@@ -14241,14 +14241,14 @@
         <v>9</v>
       </c>
       <c r="Z120" s="50" t="s">
-        <v>431</v>
+        <v>416</v>
       </c>
       <c r="AA120" s="45" t="str">
         <f t="shared" si="83"/>
         <v>It is a product or element of the geotechnical segment</v>
       </c>
     </row>
-    <row r="121" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A121" s="51">
         <v>121</v>
       </c>
@@ -14334,14 +14334,14 @@
         <v>9</v>
       </c>
       <c r="Z121" s="50" t="s">
-        <v>432</v>
+        <v>417</v>
       </c>
       <c r="AA121" s="45" t="str">
         <f t="shared" si="83"/>
         <v>It is a product or element of the construction site segment</v>
       </c>
     </row>
-    <row r="122" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A122" s="51">
         <v>122</v>
       </c>
@@ -14427,14 +14427,14 @@
         <v>9</v>
       </c>
       <c r="Z122" s="50" t="s">
-        <v>433</v>
+        <v>418</v>
       </c>
       <c r="AA122" s="45" t="str">
         <f t="shared" si="83"/>
         <v>It is a product or element of the drainage segment</v>
       </c>
     </row>
-    <row r="123" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A123" s="51">
         <v>123</v>
       </c>
@@ -14520,14 +14520,14 @@
         <v>9</v>
       </c>
       <c r="Z123" s="50" t="s">
-        <v>434</v>
+        <v>419</v>
       </c>
       <c r="AA123" s="45" t="str">
         <f t="shared" si="83"/>
         <v>It is a product or element of the traffic and paving segment</v>
       </c>
     </row>
-    <row r="124" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A124" s="51">
         <v>124</v>
       </c>
@@ -14613,14 +14613,14 @@
         <v>9</v>
       </c>
       <c r="Z124" s="50" t="s">
-        <v>435</v>
+        <v>420</v>
       </c>
       <c r="AA124" s="45" t="str">
         <f t="shared" si="83"/>
         <v>It is a product or element of the foundation structure segment</v>
       </c>
     </row>
-    <row r="125" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A125" s="51">
         <v>125</v>
       </c>
@@ -14706,14 +14706,14 @@
         <v>9</v>
       </c>
       <c r="Z125" s="50" t="s">
-        <v>436</v>
+        <v>421</v>
       </c>
       <c r="AA125" s="45" t="str">
         <f t="shared" si="83"/>
         <v>It is a product or element of the structure segment</v>
       </c>
     </row>
-    <row r="126" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A126" s="51">
         <v>126</v>
       </c>
@@ -14799,14 +14799,14 @@
         <v>9</v>
       </c>
       <c r="Z126" s="50" t="s">
-        <v>437</v>
+        <v>422</v>
       </c>
       <c r="AA126" s="45" t="str">
         <f t="shared" si="83"/>
         <v>It is a product or element of the sealing, walls and roofs segment</v>
       </c>
     </row>
-    <row r="127" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A127" s="51">
         <v>127</v>
       </c>
@@ -14892,14 +14892,14 @@
         <v>9</v>
       </c>
       <c r="Z127" s="50" t="s">
-        <v>438</v>
+        <v>423</v>
       </c>
       <c r="AA127" s="45" t="str">
         <f t="shared" si="83"/>
         <v>It is a product or element of the finished segment</v>
       </c>
     </row>
-    <row r="128" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A128" s="51">
         <v>128</v>
       </c>
@@ -14985,14 +14985,14 @@
         <v>9</v>
       </c>
       <c r="Z128" s="50" t="s">
-        <v>439</v>
+        <v>424</v>
       </c>
       <c r="AA128" s="45" t="str">
         <f t="shared" si="83"/>
         <v>It is a product or element of the openings and frames segment</v>
       </c>
     </row>
-    <row r="129" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A129" s="51">
         <v>129</v>
       </c>
@@ -15078,14 +15078,14 @@
         <v>9</v>
       </c>
       <c r="Z129" s="50" t="s">
-        <v>440</v>
+        <v>425</v>
       </c>
       <c r="AA129" s="45" t="str">
         <f t="shared" si="83"/>
         <v>It is a product or element of the acoustics segment</v>
       </c>
     </row>
-    <row r="130" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A130" s="51">
         <v>130</v>
       </c>
@@ -15171,14 +15171,14 @@
         <v>9</v>
       </c>
       <c r="Z130" s="50" t="s">
-        <v>441</v>
+        <v>426</v>
       </c>
       <c r="AA130" s="45" t="str">
         <f t="shared" si="83"/>
         <v>It is a product or element of the electrical segment</v>
       </c>
     </row>
-    <row r="131" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A131" s="51">
         <v>131</v>
       </c>
@@ -15264,14 +15264,14 @@
         <v>9</v>
       </c>
       <c r="Z131" s="50" t="s">
-        <v>442</v>
+        <v>427</v>
       </c>
       <c r="AA131" s="45" t="str">
         <f t="shared" si="83"/>
         <v>It is a product or element of the Lighting segment</v>
       </c>
     </row>
-    <row r="132" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A132" s="51">
         <v>132</v>
       </c>
@@ -15357,14 +15357,14 @@
         <v>9</v>
       </c>
       <c r="Z132" s="50" t="s">
-        <v>443</v>
+        <v>428</v>
       </c>
       <c r="AA132" s="45" t="str">
         <f t="shared" si="83"/>
         <v>It is a product or element of the exhaust and ventilation segment</v>
       </c>
     </row>
-    <row r="133" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A133" s="51">
         <v>133</v>
       </c>
@@ -15450,14 +15450,14 @@
         <v>9</v>
       </c>
       <c r="Z133" s="50" t="s">
-        <v>444</v>
+        <v>429</v>
       </c>
       <c r="AA133" s="45" t="str">
         <f t="shared" si="83"/>
         <v>It is a product or element of the urban telecom network segment</v>
       </c>
     </row>
-    <row r="134" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A134" s="51">
         <v>134</v>
       </c>
@@ -15543,14 +15543,14 @@
         <v>9</v>
       </c>
       <c r="Z134" s="50" t="s">
-        <v>445</v>
+        <v>430</v>
       </c>
       <c r="AA134" s="45" t="str">
         <f t="shared" si="83"/>
         <v>It is a product or element of the building telecom network segment</v>
       </c>
     </row>
-    <row r="135" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A135" s="51">
         <v>135</v>
       </c>
@@ -15636,14 +15636,14 @@
         <v>9</v>
       </c>
       <c r="Z135" s="50" t="s">
-        <v>446</v>
+        <v>431</v>
       </c>
       <c r="AA135" s="45" t="str">
         <f t="shared" si="83"/>
         <v>It is a product or element of the urban hydraulics network segment</v>
       </c>
     </row>
-    <row r="136" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A136" s="51">
         <v>136</v>
       </c>
@@ -15729,14 +15729,14 @@
         <v>9</v>
       </c>
       <c r="Z136" s="50" t="s">
-        <v>447</v>
+        <v>432</v>
       </c>
       <c r="AA136" s="45" t="str">
         <f t="shared" si="83"/>
         <v>It is a product or element of the building hydraulic network segment</v>
       </c>
     </row>
-    <row r="137" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A137" s="51">
         <v>137</v>
       </c>
@@ -15822,14 +15822,14 @@
         <v>9</v>
       </c>
       <c r="Z137" s="50" t="s">
-        <v>448</v>
+        <v>433</v>
       </c>
       <c r="AA137" s="45" t="str">
         <f t="shared" si="83"/>
         <v>It is a product or element of the rainwater network segment</v>
       </c>
     </row>
-    <row r="138" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A138" s="51">
         <v>138</v>
       </c>
@@ -15915,14 +15915,14 @@
         <v>9</v>
       </c>
       <c r="Z138" s="50" t="s">
-        <v>449</v>
+        <v>434</v>
       </c>
       <c r="AA138" s="45" t="str">
         <f t="shared" si="83"/>
         <v>It is a product or element of the building sewer network segment</v>
       </c>
     </row>
-    <row r="139" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A139" s="51">
         <v>139</v>
       </c>
@@ -16008,14 +16008,14 @@
         <v>9</v>
       </c>
       <c r="Z139" s="50" t="s">
-        <v>450</v>
+        <v>435</v>
       </c>
       <c r="AA139" s="45" t="str">
         <f t="shared" si="83"/>
         <v>It is a product or element of the urban sewer network segment</v>
       </c>
     </row>
-    <row r="140" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A140" s="51">
         <v>140</v>
       </c>
@@ -16101,14 +16101,14 @@
         <v>9</v>
       </c>
       <c r="Z140" s="50" t="s">
-        <v>451</v>
+        <v>436</v>
       </c>
       <c r="AA140" s="45" t="str">
         <f t="shared" si="83"/>
         <v>It is a product or element of the waste treatment segment</v>
       </c>
     </row>
-    <row r="141" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A141" s="51">
         <v>141</v>
       </c>
@@ -16194,14 +16194,14 @@
         <v>9</v>
       </c>
       <c r="Z141" s="50" t="s">
-        <v>452</v>
+        <v>437</v>
       </c>
       <c r="AA141" s="45" t="str">
         <f t="shared" si="83"/>
         <v>It is a product or element of the refrigeration segment</v>
       </c>
     </row>
-    <row r="142" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A142" s="51">
         <v>142</v>
       </c>
@@ -16287,14 +16287,14 @@
         <v>9</v>
       </c>
       <c r="Z142" s="50" t="s">
-        <v>453</v>
+        <v>438</v>
       </c>
       <c r="AA142" s="45" t="str">
         <f t="shared" si="83"/>
         <v>It is a product or element of the heating segment</v>
       </c>
     </row>
-    <row r="143" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A143" s="51">
         <v>143</v>
       </c>
@@ -16380,14 +16380,14 @@
         <v>9</v>
       </c>
       <c r="Z143" s="50" t="s">
-        <v>454</v>
+        <v>439</v>
       </c>
       <c r="AA143" s="45" t="str">
         <f t="shared" si="83"/>
         <v>It is a product or element of the gas segment</v>
       </c>
     </row>
-    <row r="144" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A144" s="51">
         <v>144</v>
       </c>
@@ -16473,14 +16473,14 @@
         <v>9</v>
       </c>
       <c r="Z144" s="50" t="s">
-        <v>455</v>
+        <v>440</v>
       </c>
       <c r="AA144" s="45" t="str">
         <f t="shared" si="83"/>
         <v>It is a product or element of the furniture segment</v>
       </c>
     </row>
-    <row r="145" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A145" s="51">
         <v>145</v>
       </c>
@@ -16566,14 +16566,14 @@
         <v>9</v>
       </c>
       <c r="Z145" s="50" t="s">
-        <v>456</v>
+        <v>441</v>
       </c>
       <c r="AA145" s="45" t="str">
         <f t="shared" si="83"/>
         <v>It is a product or element of the automation segment</v>
       </c>
     </row>
-    <row r="146" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A146" s="51">
         <v>146</v>
       </c>
@@ -16659,14 +16659,14 @@
         <v>9</v>
       </c>
       <c r="Z146" s="50" t="s">
-        <v>457</v>
+        <v>442</v>
       </c>
       <c r="AA146" s="45" t="str">
         <f t="shared" si="83"/>
         <v>It is a product or element of the lightning protection segment</v>
       </c>
     </row>
-    <row r="147" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A147" s="51">
         <v>147</v>
       </c>
@@ -16752,14 +16752,14 @@
         <v>9</v>
       </c>
       <c r="Z147" s="50" t="s">
-        <v>458</v>
+        <v>443</v>
       </c>
       <c r="AA147" s="45" t="str">
         <f t="shared" si="83"/>
         <v>It is a product or element of the fire protection segment</v>
       </c>
     </row>
-    <row r="148" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A148" s="51">
         <v>148</v>
       </c>
@@ -16845,7 +16845,7 @@
         <v>9</v>
       </c>
       <c r="Z148" s="50" t="s">
-        <v>459</v>
+        <v>444</v>
       </c>
       <c r="AA148" s="45" t="str">
         <f t="shared" si="83"/>
@@ -16907,17 +16907,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{779E4F22-2568-4D5A-A538-DD63A5C43724}">
   <dimension ref="A1:U2"/>
-  <sheetFormatPr defaultColWidth="5.7109375" defaultRowHeight="7.9" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="5.69140625" defaultRowHeight="7.95" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="1.28515625" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.140625" style="12" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="1.3046875" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.15234375" style="12" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="7" style="12" customWidth="1"/>
-    <col min="4" max="10" width="5.140625" style="12" bestFit="1" customWidth="1"/>
-    <col min="11" max="21" width="5.5703125" style="21" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="5.7109375" style="21"/>
+    <col min="4" max="10" width="5.15234375" style="12" bestFit="1" customWidth="1"/>
+    <col min="11" max="21" width="5.53515625" style="21" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="5.69140625" style="21"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="16.5" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:21" ht="15.45" x14ac:dyDescent="0.2">
       <c r="A1" s="19">
         <v>1</v>
       </c>
@@ -16982,7 +16982,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="8.25" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:21" ht="7.75" x14ac:dyDescent="0.2">
       <c r="A2" s="19">
         <v>2</v>
       </c>
@@ -17055,16 +17055,16 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4328B84A-AA24-421E-9F4E-92D6A71CA3BE}">
   <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="1.42578125" style="13" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4.140625" style="13" customWidth="1"/>
-    <col min="3" max="3" width="7.42578125" style="13" customWidth="1"/>
-    <col min="4" max="4" width="7.7109375" style="13" customWidth="1"/>
-    <col min="5" max="16384" width="9.140625" style="13"/>
+    <col min="1" max="1" width="1.3828125" style="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.15234375" style="13" customWidth="1"/>
+    <col min="3" max="3" width="7.3828125" style="13" customWidth="1"/>
+    <col min="4" max="4" width="7.69140625" style="13" customWidth="1"/>
+    <col min="5" max="16384" width="9.15234375" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="6.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:4" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="8">
         <v>1</v>
       </c>
@@ -17078,7 +17078,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="6.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:4" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="7">
         <v>2</v>
       </c>
@@ -17092,7 +17092,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="6.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:4" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="7">
         <v>3</v>
       </c>
@@ -17114,42 +17114,42 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3D50BAA-DAEA-47D5-8FAA-A68A87918655}">
   <dimension ref="A1:AE32"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="6" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="6" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.5703125" style="55" customWidth="1"/>
-    <col min="2" max="2" width="10.5703125" style="55" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="7.140625" style="55" customWidth="1"/>
-    <col min="5" max="5" width="9.7109375" style="55" customWidth="1"/>
-    <col min="6" max="6" width="2.42578125" style="65" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="2.85546875" style="65" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="3.140625" style="65" customWidth="1"/>
-    <col min="9" max="9" width="2.85546875" style="65" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="4.5703125" style="63" customWidth="1"/>
-    <col min="11" max="11" width="29.85546875" style="63" customWidth="1"/>
-    <col min="12" max="12" width="3.7109375" style="63" customWidth="1"/>
-    <col min="13" max="13" width="21.28515625" style="64" customWidth="1"/>
-    <col min="14" max="14" width="6.140625" style="63" customWidth="1"/>
-    <col min="15" max="15" width="60.5703125" style="63" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="2.42578125" style="63" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="2.85546875" style="65" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="2.42578125" style="63" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="2.85546875" style="65" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="2.140625" style="63" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="2.85546875" style="65" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="2.42578125" style="63" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="2.85546875" style="65" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="2.42578125" style="55" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="2.85546875" style="55" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="2.42578125" style="63" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="2.85546875" style="63" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="2.42578125" style="63" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="2.85546875" style="63" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="2.42578125" style="63" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="2.85546875" style="63" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="55"/>
+    <col min="1" max="1" width="2.53515625" style="55" customWidth="1"/>
+    <col min="2" max="2" width="10.53515625" style="55" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="7.15234375" style="55" customWidth="1"/>
+    <col min="5" max="5" width="9.69140625" style="55" customWidth="1"/>
+    <col min="6" max="6" width="2.3828125" style="65" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="2.84375" style="65" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="3.15234375" style="65" customWidth="1"/>
+    <col min="9" max="9" width="2.84375" style="65" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="4.53515625" style="63" customWidth="1"/>
+    <col min="11" max="11" width="29.84375" style="63" customWidth="1"/>
+    <col min="12" max="12" width="3.69140625" style="63" customWidth="1"/>
+    <col min="13" max="13" width="21.3046875" style="64" customWidth="1"/>
+    <col min="14" max="14" width="6.15234375" style="63" customWidth="1"/>
+    <col min="15" max="15" width="60.53515625" style="63" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="2.3828125" style="63" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="2.84375" style="65" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="2.3828125" style="63" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="2.84375" style="65" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="2.15234375" style="63" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="2.84375" style="65" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="2.3828125" style="63" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="2.84375" style="65" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="2.3828125" style="55" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="2.84375" style="55" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="2.3828125" style="63" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="2.84375" style="63" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="2.3828125" style="63" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="2.84375" style="63" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="2.3828125" style="63" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="2.84375" style="63" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.15234375" style="55"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" ht="14.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="14" t="s">
         <v>30</v>
       </c>
@@ -17244,12 +17244,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:31" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="16">
         <v>2</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>613</v>
+        <v>585</v>
       </c>
       <c r="C2" s="57" t="s">
         <v>94</v>
@@ -17276,7 +17276,7 @@
         <v>16</v>
       </c>
       <c r="K2" s="18" t="s">
-        <v>615</v>
+        <v>587</v>
       </c>
       <c r="L2" s="33" t="s">
         <v>9</v>
@@ -17339,12 +17339,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:31" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:31" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="16">
         <v>3</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>614</v>
+        <v>586</v>
       </c>
       <c r="C3" s="57" t="s">
         <v>94</v>
@@ -17353,7 +17353,7 @@
         <v>79</v>
       </c>
       <c r="E3" s="37" t="s">
-        <v>613</v>
+        <v>585</v>
       </c>
       <c r="F3" s="67" t="s">
         <v>9</v>
@@ -17371,7 +17371,7 @@
         <v>16</v>
       </c>
       <c r="K3" s="18" t="s">
-        <v>616</v>
+        <v>588</v>
       </c>
       <c r="L3" s="33" t="s">
         <v>9</v>
@@ -17434,7 +17434,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:31" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:31" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="16">
         <v>4</v>
       </c>
@@ -17442,13 +17442,13 @@
         <v>254</v>
       </c>
       <c r="C4" s="57" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="D4" s="36" t="s">
         <v>79</v>
       </c>
       <c r="E4" s="37" t="s">
-        <v>614</v>
+        <v>586</v>
       </c>
       <c r="F4" s="67" t="s">
         <v>9</v>
@@ -17478,7 +17478,7 @@
         <v>234</v>
       </c>
       <c r="O4" s="18" t="s">
-        <v>620</v>
+        <v>592</v>
       </c>
       <c r="P4" s="33" t="s">
         <v>9</v>
@@ -17529,7 +17529,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:31" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:31" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="16">
         <v>5</v>
       </c>
@@ -17537,13 +17537,13 @@
         <v>256</v>
       </c>
       <c r="C5" s="57" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="D5" s="36" t="s">
         <v>79</v>
       </c>
       <c r="E5" s="37" t="s">
-        <v>614</v>
+        <v>586</v>
       </c>
       <c r="F5" s="67" t="s">
         <v>9</v>
@@ -17624,7 +17624,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:31" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:31" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="16">
         <v>6</v>
       </c>
@@ -17632,13 +17632,13 @@
         <v>259</v>
       </c>
       <c r="C6" s="57" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="D6" s="36" t="s">
         <v>79</v>
       </c>
       <c r="E6" s="37" t="s">
-        <v>614</v>
+        <v>586</v>
       </c>
       <c r="F6" s="67" t="s">
         <v>9</v>
@@ -17719,7 +17719,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:31" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:31" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="16">
         <v>7</v>
       </c>
@@ -17727,13 +17727,13 @@
         <v>302</v>
       </c>
       <c r="C7" s="57" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="D7" s="36" t="s">
         <v>79</v>
       </c>
       <c r="E7" s="37" t="s">
-        <v>614</v>
+        <v>586</v>
       </c>
       <c r="F7" s="67" t="s">
         <v>9</v>
@@ -17814,7 +17814,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:31" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:31" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="16">
         <v>8</v>
       </c>
@@ -17822,13 +17822,13 @@
         <v>260</v>
       </c>
       <c r="C8" s="57" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="D8" s="36" t="s">
         <v>79</v>
       </c>
       <c r="E8" s="37" t="s">
-        <v>614</v>
+        <v>586</v>
       </c>
       <c r="F8" s="67" t="s">
         <v>9</v>
@@ -17909,12 +17909,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:31" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:31" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="16">
         <v>9</v>
       </c>
       <c r="B9" s="66" t="s">
-        <v>396</v>
+        <v>382</v>
       </c>
       <c r="C9" s="57" t="s">
         <v>321</v>
@@ -17923,7 +17923,7 @@
         <v>79</v>
       </c>
       <c r="E9" s="37" t="s">
-        <v>614</v>
+        <v>586</v>
       </c>
       <c r="F9" s="67" t="s">
         <v>9</v>
@@ -17941,19 +17941,19 @@
         <v>16</v>
       </c>
       <c r="K9" s="18" t="s">
-        <v>398</v>
+        <v>384</v>
       </c>
       <c r="L9" s="33" t="s">
         <v>222</v>
       </c>
       <c r="M9" s="62" t="s">
-        <v>399</v>
+        <v>385</v>
       </c>
       <c r="N9" s="33" t="s">
         <v>251</v>
       </c>
       <c r="O9" s="18" t="s">
-        <v>401</v>
+        <v>387</v>
       </c>
       <c r="P9" s="33" t="s">
         <v>9</v>
@@ -18004,12 +18004,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:31" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:31" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="16">
         <v>10</v>
       </c>
       <c r="B10" s="66" t="s">
-        <v>403</v>
+        <v>389</v>
       </c>
       <c r="C10" s="57" t="s">
         <v>321</v>
@@ -18018,7 +18018,7 @@
         <v>79</v>
       </c>
       <c r="E10" s="37" t="s">
-        <v>614</v>
+        <v>586</v>
       </c>
       <c r="F10" s="67" t="s">
         <v>9</v>
@@ -18036,19 +18036,19 @@
         <v>16</v>
       </c>
       <c r="K10" s="18" t="s">
-        <v>398</v>
+        <v>384</v>
       </c>
       <c r="L10" s="33" t="s">
         <v>222</v>
       </c>
       <c r="M10" s="62" t="s">
-        <v>402</v>
+        <v>388</v>
       </c>
       <c r="N10" s="33" t="s">
         <v>251</v>
       </c>
       <c r="O10" s="18" t="s">
-        <v>401</v>
+        <v>387</v>
       </c>
       <c r="P10" s="33" t="s">
         <v>9</v>
@@ -18099,12 +18099,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:31" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:31" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="16">
         <v>11</v>
       </c>
       <c r="B11" s="66" t="s">
-        <v>397</v>
+        <v>383</v>
       </c>
       <c r="C11" s="57" t="s">
         <v>321</v>
@@ -18113,7 +18113,7 @@
         <v>79</v>
       </c>
       <c r="E11" s="37" t="s">
-        <v>614</v>
+        <v>586</v>
       </c>
       <c r="F11" s="67" t="s">
         <v>9</v>
@@ -18131,19 +18131,19 @@
         <v>16</v>
       </c>
       <c r="K11" s="18" t="s">
-        <v>398</v>
+        <v>384</v>
       </c>
       <c r="L11" s="33" t="s">
         <v>222</v>
       </c>
       <c r="M11" s="62" t="s">
-        <v>400</v>
+        <v>386</v>
       </c>
       <c r="N11" s="33" t="s">
         <v>251</v>
       </c>
       <c r="O11" s="18" t="s">
-        <v>401</v>
+        <v>387</v>
       </c>
       <c r="P11" s="33" t="s">
         <v>9</v>
@@ -18194,7 +18194,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:31" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:31" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="16">
         <v>12</v>
       </c>
@@ -18202,13 +18202,13 @@
         <v>275</v>
       </c>
       <c r="C12" s="57" t="s">
-        <v>368</v>
+        <v>360</v>
       </c>
       <c r="D12" s="36" t="s">
         <v>79</v>
       </c>
       <c r="E12" s="37" t="s">
-        <v>614</v>
+        <v>586</v>
       </c>
       <c r="F12" s="67" t="s">
         <v>9</v>
@@ -18289,7 +18289,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:31" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:31" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="16">
         <v>13</v>
       </c>
@@ -18297,13 +18297,13 @@
         <v>272</v>
       </c>
       <c r="C13" s="57" t="s">
-        <v>380</v>
+        <v>369</v>
       </c>
       <c r="D13" s="36" t="s">
         <v>79</v>
       </c>
       <c r="E13" s="37" t="s">
-        <v>614</v>
+        <v>586</v>
       </c>
       <c r="F13" s="67" t="s">
         <v>9</v>
@@ -18384,21 +18384,21 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:31" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:31" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="16">
         <v>14</v>
       </c>
       <c r="B14" s="66" t="s">
-        <v>605</v>
+        <v>577</v>
       </c>
       <c r="C14" s="57" t="s">
-        <v>392</v>
+        <v>379</v>
       </c>
       <c r="D14" s="36" t="s">
         <v>79</v>
       </c>
       <c r="E14" s="37" t="s">
-        <v>614</v>
+        <v>586</v>
       </c>
       <c r="F14" s="67" t="s">
         <v>9</v>
@@ -18416,19 +18416,19 @@
         <v>16</v>
       </c>
       <c r="K14" s="18" t="s">
-        <v>609</v>
+        <v>581</v>
       </c>
       <c r="L14" s="33" t="s">
         <v>222</v>
       </c>
       <c r="M14" s="62" t="s">
-        <v>607</v>
+        <v>579</v>
       </c>
       <c r="N14" s="33" t="s">
         <v>251</v>
       </c>
       <c r="O14" s="18" t="s">
-        <v>618</v>
+        <v>590</v>
       </c>
       <c r="P14" s="33" t="s">
         <v>9</v>
@@ -18479,21 +18479,21 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:31" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:31" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="16">
         <v>15</v>
       </c>
       <c r="B15" s="66" t="s">
-        <v>606</v>
+        <v>578</v>
       </c>
       <c r="C15" s="57" t="s">
-        <v>392</v>
+        <v>379</v>
       </c>
       <c r="D15" s="36" t="s">
         <v>79</v>
       </c>
       <c r="E15" s="37" t="s">
-        <v>614</v>
+        <v>586</v>
       </c>
       <c r="F15" s="67" t="s">
         <v>9</v>
@@ -18511,19 +18511,19 @@
         <v>16</v>
       </c>
       <c r="K15" s="18" t="s">
-        <v>621</v>
+        <v>593</v>
       </c>
       <c r="L15" s="33" t="s">
         <v>222</v>
       </c>
       <c r="M15" s="62" t="s">
-        <v>612</v>
+        <v>584</v>
       </c>
       <c r="N15" s="33" t="s">
         <v>251</v>
       </c>
       <c r="O15" s="18" t="s">
-        <v>617</v>
+        <v>589</v>
       </c>
       <c r="P15" s="33" t="s">
         <v>9</v>
@@ -18574,21 +18574,21 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:31" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:31" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="16">
         <v>16</v>
       </c>
       <c r="B16" s="66" t="s">
-        <v>610</v>
+        <v>582</v>
       </c>
       <c r="C16" s="57" t="s">
-        <v>392</v>
+        <v>379</v>
       </c>
       <c r="D16" s="36" t="s">
         <v>79</v>
       </c>
       <c r="E16" s="37" t="s">
-        <v>614</v>
+        <v>586</v>
       </c>
       <c r="F16" s="67" t="s">
         <v>9</v>
@@ -18606,19 +18606,19 @@
         <v>16</v>
       </c>
       <c r="K16" s="18" t="s">
-        <v>608</v>
+        <v>580</v>
       </c>
       <c r="L16" s="33" t="s">
         <v>222</v>
       </c>
       <c r="M16" s="62" t="s">
-        <v>611</v>
+        <v>583</v>
       </c>
       <c r="N16" s="33" t="s">
         <v>251</v>
       </c>
       <c r="O16" s="18" t="s">
-        <v>618</v>
+        <v>590</v>
       </c>
       <c r="P16" s="33" t="s">
         <v>9</v>
@@ -18669,7 +18669,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:31" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:31" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="16">
         <v>17</v>
       </c>
@@ -18677,13 +18677,13 @@
         <v>223</v>
       </c>
       <c r="C17" s="57" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="D17" s="36" t="s">
         <v>79</v>
       </c>
       <c r="E17" s="37" t="s">
-        <v>614</v>
+        <v>586</v>
       </c>
       <c r="F17" s="67" t="s">
         <v>9</v>
@@ -18713,7 +18713,7 @@
         <v>234</v>
       </c>
       <c r="O17" s="18" t="s">
-        <v>619</v>
+        <v>591</v>
       </c>
       <c r="P17" s="33" t="s">
         <v>9</v>
@@ -18764,7 +18764,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:31" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:31" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="16">
         <v>18</v>
       </c>
@@ -18772,13 +18772,13 @@
         <v>285</v>
       </c>
       <c r="C18" s="57" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="D18" s="36" t="s">
         <v>79</v>
       </c>
       <c r="E18" s="37" t="s">
-        <v>614</v>
+        <v>586</v>
       </c>
       <c r="F18" s="67" t="s">
         <v>9</v>
@@ -18859,7 +18859,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:31" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:31" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="16">
         <v>19</v>
       </c>
@@ -18867,13 +18867,13 @@
         <v>280</v>
       </c>
       <c r="C19" s="57" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="D19" s="36" t="s">
         <v>79</v>
       </c>
       <c r="E19" s="37" t="s">
-        <v>614</v>
+        <v>586</v>
       </c>
       <c r="F19" s="67" t="s">
         <v>9</v>
@@ -18954,7 +18954,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:31" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:31" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="16">
         <v>20</v>
       </c>
@@ -18962,13 +18962,13 @@
         <v>282</v>
       </c>
       <c r="C20" s="57" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="D20" s="36" t="s">
         <v>79</v>
       </c>
       <c r="E20" s="37" t="s">
-        <v>614</v>
+        <v>586</v>
       </c>
       <c r="F20" s="67" t="s">
         <v>9</v>
@@ -19049,7 +19049,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:31" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:31" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="16">
         <v>21</v>
       </c>
@@ -19057,13 +19057,13 @@
         <v>245</v>
       </c>
       <c r="C21" s="57" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="D21" s="36" t="s">
         <v>79</v>
       </c>
       <c r="E21" s="37" t="s">
-        <v>614</v>
+        <v>586</v>
       </c>
       <c r="F21" s="67" t="s">
         <v>9</v>
@@ -19144,7 +19144,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:31" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:31" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="16">
         <v>22</v>
       </c>
@@ -19152,13 +19152,13 @@
         <v>253</v>
       </c>
       <c r="C22" s="57" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="D22" s="36" t="s">
         <v>79</v>
       </c>
       <c r="E22" s="37" t="s">
-        <v>614</v>
+        <v>586</v>
       </c>
       <c r="F22" s="67" t="s">
         <v>9</v>
@@ -19239,7 +19239,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:31" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:31" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="16">
         <v>23</v>
       </c>
@@ -19247,13 +19247,13 @@
         <v>219</v>
       </c>
       <c r="C23" s="57" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="D23" s="36" t="s">
         <v>79</v>
       </c>
       <c r="E23" s="37" t="s">
-        <v>614</v>
+        <v>586</v>
       </c>
       <c r="F23" s="67" t="s">
         <v>9</v>
@@ -19334,7 +19334,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:31" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:31" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="16">
         <v>24</v>
       </c>
@@ -19342,13 +19342,13 @@
         <v>220</v>
       </c>
       <c r="C24" s="57" t="s">
-        <v>386</v>
+        <v>374</v>
       </c>
       <c r="D24" s="36" t="s">
         <v>79</v>
       </c>
       <c r="E24" s="37" t="s">
-        <v>614</v>
+        <v>586</v>
       </c>
       <c r="F24" s="67" t="s">
         <v>9</v>
@@ -19429,7 +19429,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:31" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:31" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="16">
         <v>25</v>
       </c>
@@ -19437,13 +19437,13 @@
         <v>235</v>
       </c>
       <c r="C25" s="57" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="D25" s="36" t="s">
         <v>79</v>
       </c>
       <c r="E25" s="37" t="s">
-        <v>614</v>
+        <v>586</v>
       </c>
       <c r="F25" s="67" t="s">
         <v>9</v>
@@ -19524,7 +19524,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:31" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:31" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="16">
         <v>26</v>
       </c>
@@ -19532,13 +19532,13 @@
         <v>236</v>
       </c>
       <c r="C26" s="57" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="D26" s="36" t="s">
         <v>79</v>
       </c>
       <c r="E26" s="37" t="s">
-        <v>614</v>
+        <v>586</v>
       </c>
       <c r="F26" s="67" t="s">
         <v>9</v>
@@ -19619,7 +19619,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:31" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:31" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="16">
         <v>27</v>
       </c>
@@ -19627,13 +19627,13 @@
         <v>246</v>
       </c>
       <c r="C27" s="57" t="s">
-        <v>471</v>
+        <v>611</v>
       </c>
       <c r="D27" s="36" t="s">
         <v>79</v>
       </c>
       <c r="E27" s="37" t="s">
-        <v>614</v>
+        <v>586</v>
       </c>
       <c r="F27" s="67" t="s">
         <v>9</v>
@@ -19714,7 +19714,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="1:31" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:31" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="16">
         <v>28</v>
       </c>
@@ -19728,7 +19728,7 @@
         <v>79</v>
       </c>
       <c r="E28" s="37" t="s">
-        <v>614</v>
+        <v>586</v>
       </c>
       <c r="F28" s="67" t="s">
         <v>9</v>
@@ -19809,7 +19809,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="29" spans="1:31" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:31" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="16">
         <v>29</v>
       </c>
@@ -19823,7 +19823,7 @@
         <v>79</v>
       </c>
       <c r="E29" s="37" t="s">
-        <v>614</v>
+        <v>586</v>
       </c>
       <c r="F29" s="67" t="s">
         <v>9</v>
@@ -19904,7 +19904,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="30" spans="1:31" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:31" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="16">
         <v>30</v>
       </c>
@@ -19918,7 +19918,7 @@
         <v>79</v>
       </c>
       <c r="E30" s="37" t="s">
-        <v>614</v>
+        <v>586</v>
       </c>
       <c r="F30" s="67" t="s">
         <v>9</v>
@@ -19999,7 +19999,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="31" spans="1:31" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:31" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="16">
         <v>31</v>
       </c>
@@ -20013,7 +20013,7 @@
         <v>79</v>
       </c>
       <c r="E31" s="37" t="s">
-        <v>614</v>
+        <v>586</v>
       </c>
       <c r="F31" s="67" t="s">
         <v>9</v>
@@ -20094,7 +20094,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:31" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:31" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="16">
         <v>32</v>
       </c>
@@ -20108,7 +20108,7 @@
         <v>79</v>
       </c>
       <c r="E32" s="37" t="s">
-        <v>614</v>
+        <v>586</v>
       </c>
       <c r="F32" s="67" t="s">
         <v>9</v>

--- a/Versão5/FABR/Ontologia_FABRI.xlsx
+++ b/Versão5/FABR/Ontologia_FABRI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\FABR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62327FFC-C723-49A4-8CE9-9A9C79EE8049}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71E7BD9B-3EA3-444B-A840-E66D1B2A6063}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="527" activeTab="4" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3912" uniqueCount="895">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3912" uniqueCount="899">
   <si>
     <t>Edição</t>
   </si>
@@ -820,9 +820,6 @@
     <t>Alberflex</t>
   </si>
   <si>
-    <t>"Sistemas de mobiliário corporativo: mesas, mesas elevatórias, cadeiras, sofás modulares, paineis privativos, cabines acústicas, divisórias, nichos, sistemas de arquivos, armários, divisores."</t>
-  </si>
-  <si>
     <t>"Tubulações predias em PVC: tubos de alimentação e esgoto, conexões, ralos e acessórios para hidráulica predial."</t>
   </si>
   <si>
@@ -835,15 +832,6 @@
     <t>"Elementos de concreto pre-fabricado: colunas, vigas, lajes alveolares."</t>
   </si>
   <si>
-    <t>"Fornecedor de produtos: Amanco, Quartzolit, Lorenzetti, Deca, Portobello, Ceusa, Incepa, Eucatex, Eliane, Suvinil, Coral, Vedacit e Viapol."</t>
-  </si>
-  <si>
-    <t>"Especializada em moveis de aço para a indústria: prateleiras, bancadas, mesas de separação, armários para ferramentas, arquivos e ficharios de aço, balções, roupeiros, carrinhos de transporte."</t>
-  </si>
-  <si>
-    <t>"Sistemas de mobiliário corporativo: mesas, estações plataforma, cadeiras, suportes, paineis, divisórias, nichos, sistemas de arquivos, armários, divisores."</t>
-  </si>
-  <si>
     <t>AtenuaSom</t>
   </si>
   <si>
@@ -1168,9 +1156,6 @@
     <t>"Fabricante de equipamento de transporte vertical."</t>
   </si>
   <si>
-    <t>"Sistemas de transporte vertical: elevadores de passageiros e de cargas, escadas rolantes e esteiras rolantes."</t>
-  </si>
-  <si>
     <t>Tke</t>
   </si>
   <si>
@@ -1717,12 +1702,6 @@
     <t>"Contêiner do catálogo de Fabricante de usados no projeto Prj.Nome.01."</t>
   </si>
   <si>
-    <t>"Sistemas de iluminação: lâmpadas e fitas de leds, luminárias exteriores e interiores, luminárias pendentes e embutidas, arandelas, balizadores, postes, projetores, drivers."</t>
-  </si>
-  <si>
-    <t>"Sistemas de iluminação: lâmpadas de leds, luminárias exteriores e interiores, luminárias pendentes e embutidas, arandelas, balizadores, postes, projetores."</t>
-  </si>
-  <si>
     <t>"Peças para saneamento básico em ferro fundido dúctil: tubos, conexões, válvulas e acessórios."</t>
   </si>
   <si>
@@ -2759,6 +2738,39 @@
   </si>
   <si>
     <t>Prj.Projeto.01</t>
+  </si>
+  <si>
+    <t>"Lâmpadas de leds, luminárias exteriores e interiores, luminárias pendentes e embutidas, arandelas, balizadores, postes, projetores."</t>
+  </si>
+  <si>
+    <t>"Lâmpadas e fitas de leds, luminárias exteriores e interiores, luminárias pendentes e embutidas, arandelas, balizadores, postes, projetores, drivers."</t>
+  </si>
+  <si>
+    <t>"Elevadores de passageiros e de cargas, escadas rolantes e esteiras rolantes."</t>
+  </si>
+  <si>
+    <t>"Mesas, mesas elevatórias, cadeiras, sofás modulares, paineis privativos, cabines acústicas, divisórias, nichos, sistemas de arquivos, armários, divisores."</t>
+  </si>
+  <si>
+    <t>"Prateleiras, bancadas, mesas de separação, armários para ferramentas, arquivos e ficharios de aço, balções, roupeiros, carrinhos de transporte."</t>
+  </si>
+  <si>
+    <t>"Mesas, estações plataforma, cadeiras, suportes, paineis, divisórias, nichos, sistemas de arquivos, armários, divisores."</t>
+  </si>
+  <si>
+    <t>"Sistemas de iluminação."</t>
+  </si>
+  <si>
+    <t>"Sistemas de transporte vertical."</t>
+  </si>
+  <si>
+    <t>"Sistemas de mobiliário corporativo."</t>
+  </si>
+  <si>
+    <t>"Moveis de aço para a indústria."</t>
+  </si>
+  <si>
+    <t>"Tubos de alimentação e esgoto em PVC, conexões, ralos e acessórios para hidráulica predial."</t>
   </si>
 </sst>
 </file>
@@ -3824,7 +3836,7 @@
       </c>
       <c r="B18" s="5">
         <f ca="1">NOW()</f>
-        <v>46213.777307175929</v>
+        <v>46214.376212037037</v>
       </c>
       <c r="C18" s="40" t="s">
         <v>88</v>
@@ -4021,7 +4033,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="56" t="s">
-        <v>583</v>
+        <v>576</v>
       </c>
       <c r="C2" s="57" t="s">
         <v>94</v>
@@ -4030,10 +4042,10 @@
         <v>160</v>
       </c>
       <c r="E2" s="56" t="s">
-        <v>580</v>
+        <v>573</v>
       </c>
       <c r="F2" s="57" t="s">
-        <v>584</v>
+        <v>577</v>
       </c>
       <c r="G2" s="50" t="s">
         <v>9</v>
@@ -4067,10 +4079,10 @@
         <v>No Projeto</v>
       </c>
       <c r="P2" s="37" t="s">
-        <v>581</v>
+        <v>574</v>
       </c>
       <c r="Q2" s="37" t="s">
-        <v>593</v>
+        <v>586</v>
       </c>
       <c r="R2" s="52" t="s">
         <v>9</v>
@@ -4104,7 +4116,7 @@
         <v>9</v>
       </c>
       <c r="AA2" s="37" t="s">
-        <v>731</v>
+        <v>724</v>
       </c>
     </row>
     <row r="3" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -4112,7 +4124,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="56" t="s">
-        <v>583</v>
+        <v>576</v>
       </c>
       <c r="C3" s="57" t="s">
         <v>94</v>
@@ -4121,10 +4133,10 @@
         <v>160</v>
       </c>
       <c r="E3" s="56" t="s">
-        <v>582</v>
+        <v>575</v>
       </c>
       <c r="F3" s="57" t="s">
-        <v>585</v>
+        <v>578</v>
       </c>
       <c r="G3" s="50" t="s">
         <v>9</v>
@@ -4158,10 +4170,10 @@
         <v>Requisito Espacial</v>
       </c>
       <c r="P3" s="37" t="s">
-        <v>586</v>
+        <v>579</v>
       </c>
       <c r="Q3" s="37" t="s">
-        <v>594</v>
+        <v>587</v>
       </c>
       <c r="R3" s="52" t="s">
         <v>9</v>
@@ -4195,7 +4207,7 @@
         <v>9</v>
       </c>
       <c r="AA3" s="37" t="s">
-        <v>732</v>
+        <v>725</v>
       </c>
     </row>
     <row r="4" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -4203,7 +4215,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="56" t="s">
-        <v>583</v>
+        <v>576</v>
       </c>
       <c r="C4" s="57" t="s">
         <v>94</v>
@@ -4212,10 +4224,10 @@
         <v>160</v>
       </c>
       <c r="E4" s="56" t="s">
-        <v>582</v>
+        <v>575</v>
       </c>
       <c r="F4" s="57" t="s">
-        <v>587</v>
+        <v>580</v>
       </c>
       <c r="G4" s="50" t="s">
         <v>9</v>
@@ -4249,10 +4261,10 @@
         <v>Requisito Mobiliário</v>
       </c>
       <c r="P4" s="37" t="s">
+        <v>581</v>
+      </c>
+      <c r="Q4" s="37" t="s">
         <v>588</v>
-      </c>
-      <c r="Q4" s="37" t="s">
-        <v>595</v>
       </c>
       <c r="R4" s="52" t="s">
         <v>9</v>
@@ -4286,7 +4298,7 @@
         <v>9</v>
       </c>
       <c r="AA4" s="37" t="s">
-        <v>733</v>
+        <v>726</v>
       </c>
     </row>
     <row r="5" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -4294,7 +4306,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="56" t="s">
-        <v>583</v>
+        <v>576</v>
       </c>
       <c r="C5" s="57" t="s">
         <v>94</v>
@@ -4303,10 +4315,10 @@
         <v>160</v>
       </c>
       <c r="E5" s="56" t="s">
+        <v>575</v>
+      </c>
+      <c r="F5" s="57" t="s">
         <v>582</v>
-      </c>
-      <c r="F5" s="57" t="s">
-        <v>589</v>
       </c>
       <c r="G5" s="50" t="s">
         <v>9</v>
@@ -4340,10 +4352,10 @@
         <v>Requisito Equipamento</v>
       </c>
       <c r="P5" s="37" t="s">
-        <v>590</v>
+        <v>583</v>
       </c>
       <c r="Q5" s="37" t="s">
-        <v>596</v>
+        <v>589</v>
       </c>
       <c r="R5" s="52" t="s">
         <v>9</v>
@@ -4377,7 +4389,7 @@
         <v>9</v>
       </c>
       <c r="AA5" s="37" t="s">
-        <v>734</v>
+        <v>727</v>
       </c>
     </row>
     <row r="6" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -4385,7 +4397,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="56" t="s">
-        <v>583</v>
+        <v>576</v>
       </c>
       <c r="C6" s="57" t="s">
         <v>94</v>
@@ -4394,10 +4406,10 @@
         <v>160</v>
       </c>
       <c r="E6" s="56" t="s">
-        <v>582</v>
+        <v>575</v>
       </c>
       <c r="F6" s="57" t="s">
-        <v>591</v>
+        <v>584</v>
       </c>
       <c r="G6" s="50" t="s">
         <v>9</v>
@@ -4431,10 +4443,10 @@
         <v>Requisito Sistemas</v>
       </c>
       <c r="P6" s="37" t="s">
-        <v>592</v>
+        <v>585</v>
       </c>
       <c r="Q6" s="37" t="s">
-        <v>597</v>
+        <v>590</v>
       </c>
       <c r="R6" s="52" t="s">
         <v>9</v>
@@ -4468,7 +4480,7 @@
         <v>9</v>
       </c>
       <c r="AA6" s="37" t="s">
-        <v>735</v>
+        <v>728</v>
       </c>
     </row>
     <row r="7" spans="1:27" s="43" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.4">
@@ -4482,13 +4494,13 @@
         <v>95</v>
       </c>
       <c r="D7" s="56" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E7" s="56" t="s">
         <v>162</v>
       </c>
       <c r="F7" s="58" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="G7" s="50" t="s">
         <v>9</v>
@@ -4522,10 +4534,10 @@
         <v>Acu Compra</v>
       </c>
       <c r="P7" s="54" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="Q7" s="55" t="s">
-        <v>598</v>
+        <v>591</v>
       </c>
       <c r="R7" s="52" t="s">
         <v>9</v>
@@ -4556,10 +4568,10 @@
         <v>9</v>
       </c>
       <c r="Z7" s="53" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="AA7" s="37" t="s">
-        <v>736</v>
+        <v>729</v>
       </c>
     </row>
     <row r="8" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -4573,13 +4585,13 @@
         <v>95</v>
       </c>
       <c r="D8" s="56" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E8" s="56" t="s">
         <v>162</v>
       </c>
       <c r="F8" s="58" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="G8" s="50" t="s">
         <v>9</v>
@@ -4616,7 +4628,7 @@
         <v>168</v>
       </c>
       <c r="Q8" s="55" t="s">
-        <v>599</v>
+        <v>592</v>
       </c>
       <c r="R8" s="52" t="s">
         <v>9</v>
@@ -4647,10 +4659,10 @@
         <v>9</v>
       </c>
       <c r="Z8" s="53" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="AA8" s="37" t="s">
-        <v>737</v>
+        <v>730</v>
       </c>
     </row>
     <row r="9" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -4664,13 +4676,13 @@
         <v>95</v>
       </c>
       <c r="D9" s="56" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E9" s="56" t="s">
         <v>162</v>
       </c>
       <c r="F9" s="58" t="s">
-        <v>496</v>
+        <v>491</v>
       </c>
       <c r="G9" s="50" t="s">
         <v>9</v>
@@ -4691,19 +4703,19 @@
         <v>95</v>
       </c>
       <c r="M9" s="54" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="N9" s="54" t="s">
-        <v>477</v>
+        <v>472</v>
       </c>
       <c r="O9" s="54" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="P9" s="54" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="Q9" s="55" t="s">
-        <v>531</v>
+        <v>526</v>
       </c>
       <c r="R9" s="52" t="s">
         <v>9</v>
@@ -4712,10 +4724,10 @@
         <v>95</v>
       </c>
       <c r="T9" s="53" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="U9" s="53" t="s">
-        <v>477</v>
+        <v>472</v>
       </c>
       <c r="V9" s="37" t="s">
         <v>181</v>
@@ -4731,10 +4743,10 @@
         <v>9</v>
       </c>
       <c r="Z9" s="53" t="s">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="AA9" s="37" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
     </row>
     <row r="10" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -4748,13 +4760,13 @@
         <v>95</v>
       </c>
       <c r="D10" s="56" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E10" s="56" t="s">
         <v>162</v>
       </c>
       <c r="F10" s="58" t="s">
-        <v>578</v>
+        <v>571</v>
       </c>
       <c r="G10" s="50" t="s">
         <v>9</v>
@@ -4791,7 +4803,7 @@
         <v>169</v>
       </c>
       <c r="Q10" s="55" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="R10" s="52" t="s">
         <v>9</v>
@@ -4822,10 +4834,10 @@
         <v>9</v>
       </c>
       <c r="Z10" s="53" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="AA10" s="37" t="s">
-        <v>738</v>
+        <v>731</v>
       </c>
     </row>
     <row r="11" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -4839,13 +4851,13 @@
         <v>95</v>
       </c>
       <c r="D11" s="56" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E11" s="56" t="s">
         <v>162</v>
       </c>
       <c r="F11" s="58" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="G11" s="50" t="s">
         <v>9</v>
@@ -4882,7 +4894,7 @@
         <v>170</v>
       </c>
       <c r="Q11" s="55" t="s">
-        <v>601</v>
+        <v>594</v>
       </c>
       <c r="R11" s="52" t="s">
         <v>9</v>
@@ -4913,10 +4925,10 @@
         <v>9</v>
       </c>
       <c r="Z11" s="53" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="AA11" s="37" t="s">
-        <v>739</v>
+        <v>732</v>
       </c>
     </row>
     <row r="12" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -4930,13 +4942,13 @@
         <v>95</v>
       </c>
       <c r="D12" s="56" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E12" s="56" t="s">
         <v>162</v>
       </c>
       <c r="F12" s="58" t="s">
-        <v>552</v>
+        <v>545</v>
       </c>
       <c r="G12" s="50" t="s">
         <v>9</v>
@@ -4973,7 +4985,7 @@
         <v>172</v>
       </c>
       <c r="Q12" s="55" t="s">
-        <v>602</v>
+        <v>595</v>
       </c>
       <c r="R12" s="52" t="s">
         <v>9</v>
@@ -5004,10 +5016,10 @@
         <v>9</v>
       </c>
       <c r="Z12" s="53" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="AA12" s="37" t="s">
-        <v>740</v>
+        <v>733</v>
       </c>
     </row>
     <row r="13" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -5021,13 +5033,13 @@
         <v>95</v>
       </c>
       <c r="D13" s="56" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E13" s="56" t="s">
         <v>162</v>
       </c>
       <c r="F13" s="58" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="G13" s="50" t="s">
         <v>9</v>
@@ -5064,7 +5076,7 @@
         <v>229</v>
       </c>
       <c r="Q13" s="55" t="s">
-        <v>603</v>
+        <v>596</v>
       </c>
       <c r="R13" s="52" t="s">
         <v>9</v>
@@ -5095,10 +5107,10 @@
         <v>9</v>
       </c>
       <c r="Z13" s="53" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="AA13" s="37" t="s">
-        <v>741</v>
+        <v>734</v>
       </c>
     </row>
     <row r="14" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -5112,13 +5124,13 @@
         <v>95</v>
       </c>
       <c r="D14" s="56" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E14" s="56" t="s">
         <v>162</v>
       </c>
       <c r="F14" s="58" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="G14" s="50" t="s">
         <v>9</v>
@@ -5155,7 +5167,7 @@
         <v>167</v>
       </c>
       <c r="Q14" s="55" t="s">
-        <v>604</v>
+        <v>597</v>
       </c>
       <c r="R14" s="52" t="s">
         <v>9</v>
@@ -5186,10 +5198,10 @@
         <v>9</v>
       </c>
       <c r="Z14" s="53" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="AA14" s="37" t="s">
-        <v>742</v>
+        <v>735</v>
       </c>
     </row>
     <row r="15" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -5203,13 +5215,13 @@
         <v>95</v>
       </c>
       <c r="D15" s="56" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E15" s="56" t="s">
         <v>162</v>
       </c>
       <c r="F15" s="58" t="s">
-        <v>565</v>
+        <v>558</v>
       </c>
       <c r="G15" s="50" t="s">
         <v>9</v>
@@ -5243,10 +5255,10 @@
         <v>Acu Vendedor</v>
       </c>
       <c r="P15" s="54" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="Q15" s="55" t="s">
-        <v>605</v>
+        <v>598</v>
       </c>
       <c r="R15" s="52" t="s">
         <v>9</v>
@@ -5277,10 +5289,10 @@
         <v>9</v>
       </c>
       <c r="Z15" s="53" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="AA15" s="37" t="s">
-        <v>743</v>
+        <v>736</v>
       </c>
     </row>
     <row r="16" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -5294,13 +5306,13 @@
         <v>95</v>
       </c>
       <c r="D16" s="56" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E16" s="56" t="s">
         <v>96</v>
       </c>
       <c r="F16" s="58" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="G16" s="50" t="s">
         <v>9</v>
@@ -5334,10 +5346,10 @@
         <v>Arq Compra</v>
       </c>
       <c r="P16" s="54" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="Q16" s="55" t="s">
-        <v>606</v>
+        <v>599</v>
       </c>
       <c r="R16" s="52" t="s">
         <v>9</v>
@@ -5368,10 +5380,10 @@
         <v>9</v>
       </c>
       <c r="Z16" s="53" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="AA16" s="37" t="s">
-        <v>744</v>
+        <v>737</v>
       </c>
     </row>
     <row r="17" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -5385,13 +5397,13 @@
         <v>95</v>
       </c>
       <c r="D17" s="56" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E17" s="56" t="s">
         <v>96</v>
       </c>
       <c r="F17" s="58" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="G17" s="50" t="s">
         <v>9</v>
@@ -5428,7 +5440,7 @@
         <v>164</v>
       </c>
       <c r="Q17" s="55" t="s">
-        <v>607</v>
+        <v>600</v>
       </c>
       <c r="R17" s="52" t="s">
         <v>9</v>
@@ -5459,10 +5471,10 @@
         <v>9</v>
       </c>
       <c r="Z17" s="53" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="AA17" s="37" t="s">
-        <v>745</v>
+        <v>738</v>
       </c>
     </row>
     <row r="18" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -5476,13 +5488,13 @@
         <v>95</v>
       </c>
       <c r="D18" s="56" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E18" s="56" t="s">
         <v>96</v>
       </c>
       <c r="F18" s="58" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="G18" s="50" t="s">
         <v>9</v>
@@ -5503,19 +5515,19 @@
         <v>95</v>
       </c>
       <c r="M18" s="54" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="N18" s="54" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="O18" s="54" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="P18" s="54" t="s">
-        <v>539</v>
+        <v>534</v>
       </c>
       <c r="Q18" s="55" t="s">
-        <v>538</v>
+        <v>533</v>
       </c>
       <c r="R18" s="52" t="s">
         <v>9</v>
@@ -5524,10 +5536,10 @@
         <v>95</v>
       </c>
       <c r="T18" s="53" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="U18" s="53" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="V18" s="37" t="s">
         <v>181</v>
@@ -5543,10 +5555,10 @@
         <v>9</v>
       </c>
       <c r="Z18" s="53" t="s">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="AA18" s="37" t="s">
-        <v>525</v>
+        <v>520</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -5560,13 +5572,13 @@
         <v>95</v>
       </c>
       <c r="D19" s="56" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E19" s="56" t="s">
         <v>96</v>
       </c>
       <c r="F19" s="58" t="s">
-        <v>579</v>
+        <v>572</v>
       </c>
       <c r="G19" s="50" t="s">
         <v>9</v>
@@ -5603,7 +5615,7 @@
         <v>165</v>
       </c>
       <c r="Q19" s="55" t="s">
-        <v>608</v>
+        <v>601</v>
       </c>
       <c r="R19" s="52" t="s">
         <v>9</v>
@@ -5634,10 +5646,10 @@
         <v>9</v>
       </c>
       <c r="Z19" s="53" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="AA19" s="37" t="s">
-        <v>746</v>
+        <v>739</v>
       </c>
     </row>
     <row r="20" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -5651,13 +5663,13 @@
         <v>95</v>
       </c>
       <c r="D20" s="56" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E20" s="56" t="s">
         <v>96</v>
       </c>
       <c r="F20" s="58" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="G20" s="50" t="s">
         <v>9</v>
@@ -5694,7 +5706,7 @@
         <v>166</v>
       </c>
       <c r="Q20" s="55" t="s">
-        <v>609</v>
+        <v>602</v>
       </c>
       <c r="R20" s="52" t="s">
         <v>9</v>
@@ -5725,10 +5737,10 @@
         <v>9</v>
       </c>
       <c r="Z20" s="53" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="AA20" s="37" t="s">
-        <v>747</v>
+        <v>740</v>
       </c>
     </row>
     <row r="21" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -5742,13 +5754,13 @@
         <v>95</v>
       </c>
       <c r="D21" s="56" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E21" s="56" t="s">
         <v>96</v>
       </c>
       <c r="F21" s="58" t="s">
-        <v>553</v>
+        <v>546</v>
       </c>
       <c r="G21" s="50" t="s">
         <v>9</v>
@@ -5785,7 +5797,7 @@
         <v>171</v>
       </c>
       <c r="Q21" s="55" t="s">
-        <v>610</v>
+        <v>603</v>
       </c>
       <c r="R21" s="52" t="s">
         <v>9</v>
@@ -5816,10 +5828,10 @@
         <v>9</v>
       </c>
       <c r="Z21" s="53" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="AA21" s="37" t="s">
-        <v>748</v>
+        <v>741</v>
       </c>
     </row>
     <row r="22" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -5833,13 +5845,13 @@
         <v>95</v>
       </c>
       <c r="D22" s="56" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E22" s="56" t="s">
         <v>96</v>
       </c>
       <c r="F22" s="58" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="G22" s="50" t="s">
         <v>9</v>
@@ -5876,7 +5888,7 @@
         <v>221</v>
       </c>
       <c r="Q22" s="55" t="s">
-        <v>611</v>
+        <v>604</v>
       </c>
       <c r="R22" s="52" t="s">
         <v>9</v>
@@ -5907,10 +5919,10 @@
         <v>9</v>
       </c>
       <c r="Z22" s="53" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="AA22" s="37" t="s">
-        <v>749</v>
+        <v>742</v>
       </c>
     </row>
     <row r="23" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -5924,13 +5936,13 @@
         <v>95</v>
       </c>
       <c r="D23" s="56" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E23" s="56" t="s">
         <v>96</v>
       </c>
       <c r="F23" s="58" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="G23" s="50" t="s">
         <v>9</v>
@@ -5967,7 +5979,7 @@
         <v>163</v>
       </c>
       <c r="Q23" s="55" t="s">
-        <v>612</v>
+        <v>605</v>
       </c>
       <c r="R23" s="52" t="s">
         <v>9</v>
@@ -5998,10 +6010,10 @@
         <v>9</v>
       </c>
       <c r="Z23" s="53" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="AA23" s="37" t="s">
-        <v>750</v>
+        <v>743</v>
       </c>
     </row>
     <row r="24" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -6015,13 +6027,13 @@
         <v>95</v>
       </c>
       <c r="D24" s="56" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E24" s="56" t="s">
         <v>96</v>
       </c>
       <c r="F24" s="58" t="s">
-        <v>566</v>
+        <v>559</v>
       </c>
       <c r="G24" s="50" t="s">
         <v>9</v>
@@ -6055,10 +6067,10 @@
         <v>Arq Vendedor</v>
       </c>
       <c r="P24" s="54" t="s">
-        <v>539</v>
+        <v>534</v>
       </c>
       <c r="Q24" s="55" t="s">
-        <v>613</v>
+        <v>606</v>
       </c>
       <c r="R24" s="52" t="s">
         <v>9</v>
@@ -6089,10 +6101,10 @@
         <v>9</v>
       </c>
       <c r="Z24" s="53" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="AA24" s="37" t="s">
-        <v>751</v>
+        <v>744</v>
       </c>
     </row>
     <row r="25" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -6106,13 +6118,13 @@
         <v>95</v>
       </c>
       <c r="D25" s="56" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E25" s="56" t="s">
         <v>97</v>
       </c>
       <c r="F25" s="58" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="G25" s="50" t="s">
         <v>9</v>
@@ -6146,10 +6158,10 @@
         <v>Est Compra</v>
       </c>
       <c r="P25" s="54" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="Q25" s="55" t="s">
-        <v>614</v>
+        <v>607</v>
       </c>
       <c r="R25" s="52" t="s">
         <v>9</v>
@@ -6180,10 +6192,10 @@
         <v>9</v>
       </c>
       <c r="Z25" s="53" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="AA25" s="37" t="s">
-        <v>752</v>
+        <v>745</v>
       </c>
     </row>
     <row r="26" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -6197,13 +6209,13 @@
         <v>95</v>
       </c>
       <c r="D26" s="56" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E26" s="56" t="s">
         <v>97</v>
       </c>
       <c r="F26" s="58" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="G26" s="50" t="s">
         <v>9</v>
@@ -6240,7 +6252,7 @@
         <v>104</v>
       </c>
       <c r="Q26" s="55" t="s">
-        <v>615</v>
+        <v>608</v>
       </c>
       <c r="R26" s="52" t="s">
         <v>9</v>
@@ -6271,10 +6283,10 @@
         <v>9</v>
       </c>
       <c r="Z26" s="53" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="AA26" s="37" t="s">
-        <v>753</v>
+        <v>746</v>
       </c>
     </row>
     <row r="27" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -6288,13 +6300,13 @@
         <v>95</v>
       </c>
       <c r="D27" s="56" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E27" s="56" t="s">
         <v>97</v>
       </c>
       <c r="F27" s="58" t="s">
-        <v>488</v>
+        <v>483</v>
       </c>
       <c r="G27" s="50" t="s">
         <v>9</v>
@@ -6315,19 +6327,19 @@
         <v>95</v>
       </c>
       <c r="M27" s="54" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="N27" s="54" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="O27" s="54" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="P27" s="54" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="Q27" s="55" t="s">
-        <v>526</v>
+        <v>521</v>
       </c>
       <c r="R27" s="52" t="s">
         <v>9</v>
@@ -6336,10 +6348,10 @@
         <v>95</v>
       </c>
       <c r="T27" s="53" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="U27" s="53" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="V27" s="37" t="s">
         <v>181</v>
@@ -6355,10 +6367,10 @@
         <v>9</v>
       </c>
       <c r="Z27" s="53" t="s">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="AA27" s="37" t="s">
-        <v>513</v>
+        <v>508</v>
       </c>
     </row>
     <row r="28" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -6372,13 +6384,13 @@
         <v>95</v>
       </c>
       <c r="D28" s="56" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E28" s="56" t="s">
         <v>97</v>
       </c>
       <c r="F28" s="58" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="G28" s="50" t="s">
         <v>9</v>
@@ -6415,7 +6427,7 @@
         <v>105</v>
       </c>
       <c r="Q28" s="55" t="s">
-        <v>616</v>
+        <v>609</v>
       </c>
       <c r="R28" s="52" t="s">
         <v>9</v>
@@ -6446,10 +6458,10 @@
         <v>9</v>
       </c>
       <c r="Z28" s="53" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="AA28" s="37" t="s">
-        <v>754</v>
+        <v>747</v>
       </c>
     </row>
     <row r="29" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -6463,13 +6475,13 @@
         <v>95</v>
       </c>
       <c r="D29" s="56" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E29" s="56" t="s">
         <v>97</v>
       </c>
       <c r="F29" s="58" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="G29" s="50" t="s">
         <v>9</v>
@@ -6506,7 +6518,7 @@
         <v>106</v>
       </c>
       <c r="Q29" s="55" t="s">
-        <v>617</v>
+        <v>610</v>
       </c>
       <c r="R29" s="52" t="s">
         <v>9</v>
@@ -6537,10 +6549,10 @@
         <v>9</v>
       </c>
       <c r="Z29" s="53" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="AA29" s="37" t="s">
-        <v>755</v>
+        <v>748</v>
       </c>
     </row>
     <row r="30" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -6554,13 +6566,13 @@
         <v>95</v>
       </c>
       <c r="D30" s="56" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E30" s="56" t="s">
         <v>97</v>
       </c>
       <c r="F30" s="58" t="s">
-        <v>554</v>
+        <v>547</v>
       </c>
       <c r="G30" s="50" t="s">
         <v>9</v>
@@ -6597,7 +6609,7 @@
         <v>173</v>
       </c>
       <c r="Q30" s="55" t="s">
-        <v>618</v>
+        <v>611</v>
       </c>
       <c r="R30" s="52" t="s">
         <v>9</v>
@@ -6628,10 +6640,10 @@
         <v>9</v>
       </c>
       <c r="Z30" s="53" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="AA30" s="37" t="s">
-        <v>756</v>
+        <v>749</v>
       </c>
     </row>
     <row r="31" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -6645,13 +6657,13 @@
         <v>95</v>
       </c>
       <c r="D31" s="56" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E31" s="56" t="s">
         <v>97</v>
       </c>
       <c r="F31" s="58" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="G31" s="50" t="s">
         <v>9</v>
@@ -6688,7 +6700,7 @@
         <v>222</v>
       </c>
       <c r="Q31" s="55" t="s">
-        <v>619</v>
+        <v>612</v>
       </c>
       <c r="R31" s="52" t="s">
         <v>9</v>
@@ -6719,10 +6731,10 @@
         <v>9</v>
       </c>
       <c r="Z31" s="53" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="AA31" s="37" t="s">
-        <v>757</v>
+        <v>750</v>
       </c>
     </row>
     <row r="32" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -6736,13 +6748,13 @@
         <v>95</v>
       </c>
       <c r="D32" s="56" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E32" s="56" t="s">
         <v>97</v>
       </c>
       <c r="F32" s="58" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="G32" s="50" t="s">
         <v>9</v>
@@ -6779,7 +6791,7 @@
         <v>103</v>
       </c>
       <c r="Q32" s="55" t="s">
-        <v>620</v>
+        <v>613</v>
       </c>
       <c r="R32" s="52" t="s">
         <v>9</v>
@@ -6810,10 +6822,10 @@
         <v>9</v>
       </c>
       <c r="Z32" s="53" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="AA32" s="37" t="s">
-        <v>758</v>
+        <v>751</v>
       </c>
     </row>
     <row r="33" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -6827,13 +6839,13 @@
         <v>95</v>
       </c>
       <c r="D33" s="56" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E33" s="56" t="s">
         <v>97</v>
       </c>
       <c r="F33" s="58" t="s">
-        <v>567</v>
+        <v>560</v>
       </c>
       <c r="G33" s="50" t="s">
         <v>9</v>
@@ -6867,10 +6879,10 @@
         <v>Est Vendedor</v>
       </c>
       <c r="P33" s="54" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="Q33" s="55" t="s">
-        <v>621</v>
+        <v>614</v>
       </c>
       <c r="R33" s="52" t="s">
         <v>9</v>
@@ -6901,10 +6913,10 @@
         <v>9</v>
       </c>
       <c r="Z33" s="53" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="AA33" s="37" t="s">
-        <v>759</v>
+        <v>752</v>
       </c>
     </row>
     <row r="34" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -6918,13 +6930,13 @@
         <v>95</v>
       </c>
       <c r="D34" s="56" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E34" s="56" t="s">
         <v>182</v>
       </c>
       <c r="F34" s="58" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="G34" s="50" t="s">
         <v>9</v>
@@ -6958,10 +6970,10 @@
         <v>Geo Compra</v>
       </c>
       <c r="P34" s="54" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="Q34" s="55" t="s">
-        <v>622</v>
+        <v>615</v>
       </c>
       <c r="R34" s="52" t="s">
         <v>9</v>
@@ -6992,10 +7004,10 @@
         <v>9</v>
       </c>
       <c r="Z34" s="53" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="AA34" s="37" t="s">
-        <v>760</v>
+        <v>753</v>
       </c>
     </row>
     <row r="35" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -7009,13 +7021,13 @@
         <v>95</v>
       </c>
       <c r="D35" s="56" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E35" s="56" t="s">
         <v>182</v>
       </c>
       <c r="F35" s="58" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="G35" s="50" t="s">
         <v>9</v>
@@ -7052,7 +7064,7 @@
         <v>124</v>
       </c>
       <c r="Q35" s="55" t="s">
-        <v>623</v>
+        <v>616</v>
       </c>
       <c r="R35" s="52" t="s">
         <v>9</v>
@@ -7083,10 +7095,10 @@
         <v>9</v>
       </c>
       <c r="Z35" s="53" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="AA35" s="37" t="s">
-        <v>761</v>
+        <v>754</v>
       </c>
     </row>
     <row r="36" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -7100,13 +7112,13 @@
         <v>95</v>
       </c>
       <c r="D36" s="56" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E36" s="56" t="s">
         <v>182</v>
       </c>
       <c r="F36" s="58" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="G36" s="50" t="s">
         <v>9</v>
@@ -7127,19 +7139,19 @@
         <v>95</v>
       </c>
       <c r="M36" s="54" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="N36" s="54" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="O36" s="54" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="P36" s="54" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
       <c r="Q36" s="55" t="s">
-        <v>527</v>
+        <v>522</v>
       </c>
       <c r="R36" s="52" t="s">
         <v>9</v>
@@ -7148,10 +7160,10 @@
         <v>95</v>
       </c>
       <c r="T36" s="53" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="U36" s="53" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="V36" s="37" t="s">
         <v>181</v>
@@ -7167,10 +7179,10 @@
         <v>9</v>
       </c>
       <c r="Z36" s="53" t="s">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="AA36" s="37" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
     </row>
     <row r="37" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -7184,13 +7196,13 @@
         <v>95</v>
       </c>
       <c r="D37" s="56" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E37" s="56" t="s">
         <v>182</v>
       </c>
       <c r="F37" s="58" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="G37" s="50" t="s">
         <v>9</v>
@@ -7227,7 +7239,7 @@
         <v>125</v>
       </c>
       <c r="Q37" s="55" t="s">
-        <v>624</v>
+        <v>617</v>
       </c>
       <c r="R37" s="52" t="s">
         <v>9</v>
@@ -7258,10 +7270,10 @@
         <v>9</v>
       </c>
       <c r="Z37" s="53" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="AA37" s="37" t="s">
-        <v>762</v>
+        <v>755</v>
       </c>
     </row>
     <row r="38" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -7275,13 +7287,13 @@
         <v>95</v>
       </c>
       <c r="D38" s="56" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E38" s="56" t="s">
         <v>182</v>
       </c>
       <c r="F38" s="58" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="G38" s="50" t="s">
         <v>9</v>
@@ -7318,7 +7330,7 @@
         <v>126</v>
       </c>
       <c r="Q38" s="55" t="s">
-        <v>625</v>
+        <v>618</v>
       </c>
       <c r="R38" s="52" t="s">
         <v>9</v>
@@ -7349,10 +7361,10 @@
         <v>9</v>
       </c>
       <c r="Z38" s="53" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="AA38" s="37" t="s">
-        <v>763</v>
+        <v>756</v>
       </c>
     </row>
     <row r="39" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -7366,13 +7378,13 @@
         <v>95</v>
       </c>
       <c r="D39" s="56" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E39" s="56" t="s">
         <v>182</v>
       </c>
       <c r="F39" s="58" t="s">
-        <v>555</v>
+        <v>548</v>
       </c>
       <c r="G39" s="50" t="s">
         <v>9</v>
@@ -7409,7 +7421,7 @@
         <v>174</v>
       </c>
       <c r="Q39" s="55" t="s">
-        <v>626</v>
+        <v>619</v>
       </c>
       <c r="R39" s="52" t="s">
         <v>9</v>
@@ -7440,10 +7452,10 @@
         <v>9</v>
       </c>
       <c r="Z39" s="53" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="AA39" s="37" t="s">
-        <v>764</v>
+        <v>757</v>
       </c>
     </row>
     <row r="40" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -7457,13 +7469,13 @@
         <v>95</v>
       </c>
       <c r="D40" s="56" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E40" s="56" t="s">
         <v>182</v>
       </c>
       <c r="F40" s="58" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="G40" s="50" t="s">
         <v>9</v>
@@ -7500,7 +7512,7 @@
         <v>223</v>
       </c>
       <c r="Q40" s="55" t="s">
-        <v>627</v>
+        <v>620</v>
       </c>
       <c r="R40" s="52" t="s">
         <v>9</v>
@@ -7531,10 +7543,10 @@
         <v>9</v>
       </c>
       <c r="Z40" s="53" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="AA40" s="37" t="s">
-        <v>765</v>
+        <v>758</v>
       </c>
     </row>
     <row r="41" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -7548,13 +7560,13 @@
         <v>95</v>
       </c>
       <c r="D41" s="56" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E41" s="56" t="s">
         <v>182</v>
       </c>
       <c r="F41" s="58" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="G41" s="50" t="s">
         <v>9</v>
@@ -7591,7 +7603,7 @@
         <v>123</v>
       </c>
       <c r="Q41" s="55" t="s">
-        <v>628</v>
+        <v>621</v>
       </c>
       <c r="R41" s="52" t="s">
         <v>9</v>
@@ -7622,10 +7634,10 @@
         <v>9</v>
       </c>
       <c r="Z41" s="53" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="AA41" s="37" t="s">
-        <v>766</v>
+        <v>759</v>
       </c>
     </row>
     <row r="42" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -7639,13 +7651,13 @@
         <v>95</v>
       </c>
       <c r="D42" s="56" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E42" s="56" t="s">
         <v>182</v>
       </c>
       <c r="F42" s="58" t="s">
-        <v>568</v>
+        <v>561</v>
       </c>
       <c r="G42" s="50" t="s">
         <v>9</v>
@@ -7679,10 +7691,10 @@
         <v>Geo Vendedor</v>
       </c>
       <c r="P42" s="54" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="Q42" s="55" t="s">
-        <v>629</v>
+        <v>622</v>
       </c>
       <c r="R42" s="52" t="s">
         <v>9</v>
@@ -7713,10 +7725,10 @@
         <v>9</v>
       </c>
       <c r="Z42" s="53" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="AA42" s="37" t="s">
-        <v>767</v>
+        <v>760</v>
       </c>
     </row>
     <row r="43" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -7730,13 +7742,13 @@
         <v>95</v>
       </c>
       <c r="D43" s="56" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E43" s="56" t="s">
         <v>218</v>
       </c>
       <c r="F43" s="58" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="G43" s="50" t="s">
         <v>9</v>
@@ -7770,10 +7782,10 @@
         <v>Ger Compra</v>
       </c>
       <c r="P43" s="54" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="Q43" s="55" t="s">
-        <v>630</v>
+        <v>623</v>
       </c>
       <c r="R43" s="52" t="s">
         <v>9</v>
@@ -7804,10 +7816,10 @@
         <v>9</v>
       </c>
       <c r="Z43" s="53" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="AA43" s="37" t="s">
-        <v>768</v>
+        <v>761</v>
       </c>
     </row>
     <row r="44" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -7821,13 +7833,13 @@
         <v>95</v>
       </c>
       <c r="D44" s="56" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E44" s="56" t="s">
         <v>218</v>
       </c>
       <c r="F44" s="58" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="G44" s="50" t="s">
         <v>9</v>
@@ -7864,7 +7876,7 @@
         <v>183</v>
       </c>
       <c r="Q44" s="55" t="s">
-        <v>631</v>
+        <v>624</v>
       </c>
       <c r="R44" s="52" t="s">
         <v>9</v>
@@ -7895,10 +7907,10 @@
         <v>9</v>
       </c>
       <c r="Z44" s="53" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="AA44" s="37" t="s">
-        <v>769</v>
+        <v>762</v>
       </c>
     </row>
     <row r="45" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -7912,13 +7924,13 @@
         <v>95</v>
       </c>
       <c r="D45" s="56" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E45" s="56" t="s">
         <v>218</v>
       </c>
       <c r="F45" s="58" t="s">
-        <v>497</v>
+        <v>492</v>
       </c>
       <c r="G45" s="50" t="s">
         <v>9</v>
@@ -7939,19 +7951,19 @@
         <v>95</v>
       </c>
       <c r="M45" s="54" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="N45" s="54" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
       <c r="O45" s="54" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="P45" s="54" t="s">
-        <v>510</v>
+        <v>505</v>
       </c>
       <c r="Q45" s="55" t="s">
-        <v>532</v>
+        <v>527</v>
       </c>
       <c r="R45" s="52" t="s">
         <v>9</v>
@@ -7960,10 +7972,10 @@
         <v>95</v>
       </c>
       <c r="T45" s="53" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="U45" s="53" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
       <c r="V45" s="37" t="s">
         <v>181</v>
@@ -7979,10 +7991,10 @@
         <v>9</v>
       </c>
       <c r="Z45" s="53" t="s">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="AA45" s="37" t="s">
-        <v>522</v>
+        <v>517</v>
       </c>
     </row>
     <row r="46" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -7996,13 +8008,13 @@
         <v>95</v>
       </c>
       <c r="D46" s="56" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E46" s="56" t="s">
         <v>218</v>
       </c>
       <c r="F46" s="58" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="G46" s="50" t="s">
         <v>9</v>
@@ -8039,7 +8051,7 @@
         <v>184</v>
       </c>
       <c r="Q46" s="55" t="s">
-        <v>632</v>
+        <v>625</v>
       </c>
       <c r="R46" s="52" t="s">
         <v>9</v>
@@ -8070,10 +8082,10 @@
         <v>9</v>
       </c>
       <c r="Z46" s="53" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="AA46" s="37" t="s">
-        <v>770</v>
+        <v>763</v>
       </c>
     </row>
     <row r="47" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -8087,13 +8099,13 @@
         <v>95</v>
       </c>
       <c r="D47" s="56" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E47" s="56" t="s">
         <v>218</v>
       </c>
       <c r="F47" s="58" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="G47" s="50" t="s">
         <v>9</v>
@@ -8130,7 +8142,7 @@
         <v>185</v>
       </c>
       <c r="Q47" s="55" t="s">
-        <v>633</v>
+        <v>626</v>
       </c>
       <c r="R47" s="52" t="s">
         <v>9</v>
@@ -8161,10 +8173,10 @@
         <v>9</v>
       </c>
       <c r="Z47" s="53" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="AA47" s="37" t="s">
-        <v>771</v>
+        <v>764</v>
       </c>
     </row>
     <row r="48" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -8178,13 +8190,13 @@
         <v>95</v>
       </c>
       <c r="D48" s="56" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E48" s="56" t="s">
         <v>218</v>
       </c>
       <c r="F48" s="58" t="s">
-        <v>556</v>
+        <v>549</v>
       </c>
       <c r="G48" s="50" t="s">
         <v>9</v>
@@ -8221,7 +8233,7 @@
         <v>186</v>
       </c>
       <c r="Q48" s="55" t="s">
-        <v>634</v>
+        <v>627</v>
       </c>
       <c r="R48" s="52" t="s">
         <v>9</v>
@@ -8252,10 +8264,10 @@
         <v>9</v>
       </c>
       <c r="Z48" s="53" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="AA48" s="37" t="s">
-        <v>772</v>
+        <v>765</v>
       </c>
     </row>
     <row r="49" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -8269,13 +8281,13 @@
         <v>95</v>
       </c>
       <c r="D49" s="56" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E49" s="56" t="s">
         <v>218</v>
       </c>
       <c r="F49" s="58" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="G49" s="50" t="s">
         <v>9</v>
@@ -8312,7 +8324,7 @@
         <v>230</v>
       </c>
       <c r="Q49" s="55" t="s">
-        <v>635</v>
+        <v>628</v>
       </c>
       <c r="R49" s="52" t="s">
         <v>9</v>
@@ -8343,10 +8355,10 @@
         <v>9</v>
       </c>
       <c r="Z49" s="53" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="AA49" s="37" t="s">
-        <v>773</v>
+        <v>766</v>
       </c>
     </row>
     <row r="50" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -8360,13 +8372,13 @@
         <v>95</v>
       </c>
       <c r="D50" s="56" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E50" s="56" t="s">
         <v>218</v>
       </c>
       <c r="F50" s="58" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="G50" s="50" t="s">
         <v>9</v>
@@ -8403,7 +8415,7 @@
         <v>187</v>
       </c>
       <c r="Q50" s="55" t="s">
-        <v>636</v>
+        <v>629</v>
       </c>
       <c r="R50" s="52" t="s">
         <v>9</v>
@@ -8434,10 +8446,10 @@
         <v>9</v>
       </c>
       <c r="Z50" s="53" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="AA50" s="37" t="s">
-        <v>774</v>
+        <v>767</v>
       </c>
     </row>
     <row r="51" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -8451,13 +8463,13 @@
         <v>95</v>
       </c>
       <c r="D51" s="56" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E51" s="56" t="s">
         <v>218</v>
       </c>
       <c r="F51" s="58" t="s">
-        <v>569</v>
+        <v>562</v>
       </c>
       <c r="G51" s="50" t="s">
         <v>9</v>
@@ -8491,10 +8503,10 @@
         <v>Ger Vendedor</v>
       </c>
       <c r="P51" s="54" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="Q51" s="55" t="s">
-        <v>637</v>
+        <v>630</v>
       </c>
       <c r="R51" s="52" t="s">
         <v>9</v>
@@ -8525,10 +8537,10 @@
         <v>9</v>
       </c>
       <c r="Z51" s="53" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="AA51" s="37" t="s">
-        <v>775</v>
+        <v>768</v>
       </c>
     </row>
     <row r="52" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -8542,13 +8554,13 @@
         <v>95</v>
       </c>
       <c r="D52" s="56" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E52" s="56" t="s">
         <v>101</v>
       </c>
       <c r="F52" s="58" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="G52" s="50" t="s">
         <v>9</v>
@@ -8582,10 +8594,10 @@
         <v>Hos Compra</v>
       </c>
       <c r="P52" s="54" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="Q52" s="55" t="s">
-        <v>638</v>
+        <v>631</v>
       </c>
       <c r="R52" s="52" t="s">
         <v>9</v>
@@ -8616,10 +8628,10 @@
         <v>9</v>
       </c>
       <c r="Z52" s="53" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="AA52" s="37" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
     </row>
     <row r="53" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -8633,13 +8645,13 @@
         <v>95</v>
       </c>
       <c r="D53" s="56" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E53" s="56" t="s">
         <v>101</v>
       </c>
       <c r="F53" s="58" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="G53" s="50" t="s">
         <v>9</v>
@@ -8676,7 +8688,7 @@
         <v>128</v>
       </c>
       <c r="Q53" s="55" t="s">
-        <v>639</v>
+        <v>632</v>
       </c>
       <c r="R53" s="52" t="s">
         <v>9</v>
@@ -8707,10 +8719,10 @@
         <v>9</v>
       </c>
       <c r="Z53" s="53" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="AA53" s="37" t="s">
-        <v>777</v>
+        <v>770</v>
       </c>
     </row>
     <row r="54" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -8724,13 +8736,13 @@
         <v>95</v>
       </c>
       <c r="D54" s="56" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E54" s="56" t="s">
         <v>101</v>
       </c>
       <c r="F54" s="58" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="G54" s="50" t="s">
         <v>9</v>
@@ -8751,19 +8763,19 @@
         <v>95</v>
       </c>
       <c r="M54" s="54" t="s">
+        <v>455</v>
+      </c>
+      <c r="N54" s="54" t="s">
         <v>460</v>
       </c>
-      <c r="N54" s="54" t="s">
-        <v>465</v>
-      </c>
       <c r="O54" s="54" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="P54" s="54" t="s">
-        <v>503</v>
+        <v>498</v>
       </c>
       <c r="Q54" s="55" t="s">
-        <v>528</v>
+        <v>523</v>
       </c>
       <c r="R54" s="52" t="s">
         <v>9</v>
@@ -8772,10 +8784,10 @@
         <v>95</v>
       </c>
       <c r="T54" s="53" t="s">
+        <v>455</v>
+      </c>
+      <c r="U54" s="53" t="s">
         <v>460</v>
-      </c>
-      <c r="U54" s="53" t="s">
-        <v>465</v>
       </c>
       <c r="V54" s="37" t="s">
         <v>181</v>
@@ -8791,10 +8803,10 @@
         <v>9</v>
       </c>
       <c r="Z54" s="53" t="s">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="AA54" s="37" t="s">
-        <v>515</v>
+        <v>510</v>
       </c>
     </row>
     <row r="55" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -8808,13 +8820,13 @@
         <v>95</v>
       </c>
       <c r="D55" s="56" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E55" s="56" t="s">
         <v>101</v>
       </c>
       <c r="F55" s="58" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="G55" s="50" t="s">
         <v>9</v>
@@ -8851,7 +8863,7 @@
         <v>129</v>
       </c>
       <c r="Q55" s="55" t="s">
-        <v>640</v>
+        <v>633</v>
       </c>
       <c r="R55" s="52" t="s">
         <v>9</v>
@@ -8882,10 +8894,10 @@
         <v>9</v>
       </c>
       <c r="Z55" s="53" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="AA55" s="37" t="s">
-        <v>778</v>
+        <v>771</v>
       </c>
     </row>
     <row r="56" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -8899,13 +8911,13 @@
         <v>95</v>
       </c>
       <c r="D56" s="56" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E56" s="56" t="s">
         <v>101</v>
       </c>
       <c r="F56" s="58" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="G56" s="50" t="s">
         <v>9</v>
@@ -8942,7 +8954,7 @@
         <v>130</v>
       </c>
       <c r="Q56" s="55" t="s">
-        <v>641</v>
+        <v>634</v>
       </c>
       <c r="R56" s="52" t="s">
         <v>9</v>
@@ -8973,10 +8985,10 @@
         <v>9</v>
       </c>
       <c r="Z56" s="53" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="AA56" s="37" t="s">
-        <v>779</v>
+        <v>772</v>
       </c>
     </row>
     <row r="57" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -8990,13 +9002,13 @@
         <v>95</v>
       </c>
       <c r="D57" s="56" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E57" s="56" t="s">
         <v>101</v>
       </c>
       <c r="F57" s="58" t="s">
-        <v>557</v>
+        <v>550</v>
       </c>
       <c r="G57" s="50" t="s">
         <v>9</v>
@@ -9033,7 +9045,7 @@
         <v>177</v>
       </c>
       <c r="Q57" s="55" t="s">
-        <v>642</v>
+        <v>635</v>
       </c>
       <c r="R57" s="52" t="s">
         <v>9</v>
@@ -9064,10 +9076,10 @@
         <v>9</v>
       </c>
       <c r="Z57" s="53" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="AA57" s="37" t="s">
-        <v>780</v>
+        <v>773</v>
       </c>
     </row>
     <row r="58" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -9081,13 +9093,13 @@
         <v>95</v>
       </c>
       <c r="D58" s="56" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E58" s="56" t="s">
         <v>101</v>
       </c>
       <c r="F58" s="58" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="G58" s="50" t="s">
         <v>9</v>
@@ -9124,7 +9136,7 @@
         <v>224</v>
       </c>
       <c r="Q58" s="55" t="s">
-        <v>643</v>
+        <v>636</v>
       </c>
       <c r="R58" s="52" t="s">
         <v>9</v>
@@ -9155,10 +9167,10 @@
         <v>9</v>
       </c>
       <c r="Z58" s="53" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="AA58" s="37" t="s">
-        <v>781</v>
+        <v>774</v>
       </c>
     </row>
     <row r="59" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -9172,13 +9184,13 @@
         <v>95</v>
       </c>
       <c r="D59" s="56" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E59" s="56" t="s">
         <v>101</v>
       </c>
       <c r="F59" s="58" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="G59" s="50" t="s">
         <v>9</v>
@@ -9215,7 +9227,7 @@
         <v>127</v>
       </c>
       <c r="Q59" s="55" t="s">
-        <v>644</v>
+        <v>637</v>
       </c>
       <c r="R59" s="52" t="s">
         <v>9</v>
@@ -9246,10 +9258,10 @@
         <v>9</v>
       </c>
       <c r="Z59" s="53" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="AA59" s="37" t="s">
-        <v>782</v>
+        <v>775</v>
       </c>
     </row>
     <row r="60" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -9263,13 +9275,13 @@
         <v>95</v>
       </c>
       <c r="D60" s="56" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E60" s="56" t="s">
         <v>101</v>
       </c>
       <c r="F60" s="58" t="s">
-        <v>570</v>
+        <v>563</v>
       </c>
       <c r="G60" s="50" t="s">
         <v>9</v>
@@ -9303,10 +9315,10 @@
         <v>Hos Vendedor</v>
       </c>
       <c r="P60" s="54" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="Q60" s="55" t="s">
-        <v>645</v>
+        <v>638</v>
       </c>
       <c r="R60" s="52" t="s">
         <v>9</v>
@@ -9337,10 +9349,10 @@
         <v>9</v>
       </c>
       <c r="Z60" s="53" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="AA60" s="37" t="s">
-        <v>783</v>
+        <v>776</v>
       </c>
     </row>
     <row r="61" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -9354,13 +9366,13 @@
         <v>95</v>
       </c>
       <c r="D61" s="56" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E61" s="56" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="F61" s="58" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="G61" s="50" t="s">
         <v>9</v>
@@ -9394,10 +9406,10 @@
         <v>Ilu Compra</v>
       </c>
       <c r="P61" s="54" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="Q61" s="55" t="s">
-        <v>646</v>
+        <v>639</v>
       </c>
       <c r="R61" s="52" t="s">
         <v>9</v>
@@ -9428,10 +9440,10 @@
         <v>9</v>
       </c>
       <c r="Z61" s="53" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="AA61" s="37" t="s">
-        <v>784</v>
+        <v>777</v>
       </c>
     </row>
     <row r="62" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -9445,13 +9457,13 @@
         <v>95</v>
       </c>
       <c r="D62" s="56" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E62" s="56" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="F62" s="58" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="G62" s="50" t="s">
         <v>9</v>
@@ -9485,10 +9497,10 @@
         <v>Ilu Consultor</v>
       </c>
       <c r="P62" s="54" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="Q62" s="55" t="s">
-        <v>647</v>
+        <v>640</v>
       </c>
       <c r="R62" s="52" t="s">
         <v>9</v>
@@ -9519,10 +9531,10 @@
         <v>9</v>
       </c>
       <c r="Z62" s="53" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="AA62" s="37" t="s">
-        <v>785</v>
+        <v>778</v>
       </c>
     </row>
     <row r="63" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -9536,13 +9548,13 @@
         <v>95</v>
       </c>
       <c r="D63" s="56" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E63" s="56" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="F63" s="58" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="G63" s="50" t="s">
         <v>9</v>
@@ -9563,19 +9575,19 @@
         <v>95</v>
       </c>
       <c r="M63" s="54" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="N63" s="54" t="s">
-        <v>481</v>
+        <v>476</v>
       </c>
       <c r="O63" s="54" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="P63" s="54" t="s">
-        <v>511</v>
+        <v>506</v>
       </c>
       <c r="Q63" s="55" t="s">
-        <v>533</v>
+        <v>528</v>
       </c>
       <c r="R63" s="52" t="s">
         <v>9</v>
@@ -9584,10 +9596,10 @@
         <v>95</v>
       </c>
       <c r="T63" s="53" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="U63" s="53" t="s">
-        <v>481</v>
+        <v>476</v>
       </c>
       <c r="V63" s="37" t="s">
         <v>181</v>
@@ -9603,10 +9615,10 @@
         <v>9</v>
       </c>
       <c r="Z63" s="53" t="s">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="AA63" s="37" t="s">
-        <v>523</v>
+        <v>518</v>
       </c>
     </row>
     <row r="64" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -9620,13 +9632,13 @@
         <v>95</v>
       </c>
       <c r="D64" s="56" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E64" s="56" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="F64" s="58" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="G64" s="50" t="s">
         <v>9</v>
@@ -9660,10 +9672,10 @@
         <v>Ilu Empresa Consultora</v>
       </c>
       <c r="P64" s="54" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="Q64" s="55" t="s">
-        <v>648</v>
+        <v>641</v>
       </c>
       <c r="R64" s="52" t="s">
         <v>9</v>
@@ -9694,10 +9706,10 @@
         <v>9</v>
       </c>
       <c r="Z64" s="53" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="AA64" s="37" t="s">
-        <v>786</v>
+        <v>779</v>
       </c>
     </row>
     <row r="65" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -9711,13 +9723,13 @@
         <v>95</v>
       </c>
       <c r="D65" s="56" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E65" s="56" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="F65" s="58" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="G65" s="50" t="s">
         <v>9</v>
@@ -9751,10 +9763,10 @@
         <v>Ilu Fabricante</v>
       </c>
       <c r="P65" s="54" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="Q65" s="55" t="s">
-        <v>649</v>
+        <v>642</v>
       </c>
       <c r="R65" s="52" t="s">
         <v>9</v>
@@ -9785,10 +9797,10 @@
         <v>9</v>
       </c>
       <c r="Z65" s="53" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="AA65" s="37" t="s">
-        <v>787</v>
+        <v>780</v>
       </c>
     </row>
     <row r="66" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -9802,13 +9814,13 @@
         <v>95</v>
       </c>
       <c r="D66" s="56" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E66" s="56" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="F66" s="58" t="s">
-        <v>558</v>
+        <v>551</v>
       </c>
       <c r="G66" s="50" t="s">
         <v>9</v>
@@ -9842,10 +9854,10 @@
         <v>Ilu Fornecedor</v>
       </c>
       <c r="P66" s="54" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="Q66" s="55" t="s">
-        <v>650</v>
+        <v>643</v>
       </c>
       <c r="R66" s="52" t="s">
         <v>9</v>
@@ -9876,10 +9888,10 @@
         <v>9</v>
       </c>
       <c r="Z66" s="53" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="AA66" s="37" t="s">
-        <v>788</v>
+        <v>781</v>
       </c>
     </row>
     <row r="67" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -9893,13 +9905,13 @@
         <v>95</v>
       </c>
       <c r="D67" s="56" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E67" s="56" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="F67" s="58" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="G67" s="50" t="s">
         <v>9</v>
@@ -9933,10 +9945,10 @@
         <v>Ilu Projetista</v>
       </c>
       <c r="P67" s="54" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="Q67" s="55" t="s">
-        <v>651</v>
+        <v>644</v>
       </c>
       <c r="R67" s="52" t="s">
         <v>9</v>
@@ -9967,10 +9979,10 @@
         <v>9</v>
       </c>
       <c r="Z67" s="53" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="AA67" s="37" t="s">
-        <v>789</v>
+        <v>782</v>
       </c>
     </row>
     <row r="68" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -9984,13 +9996,13 @@
         <v>95</v>
       </c>
       <c r="D68" s="56" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E68" s="56" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="F68" s="58" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="G68" s="50" t="s">
         <v>9</v>
@@ -10024,10 +10036,10 @@
         <v>Ilu Serviço</v>
       </c>
       <c r="P68" s="54" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="Q68" s="55" t="s">
-        <v>652</v>
+        <v>645</v>
       </c>
       <c r="R68" s="52" t="s">
         <v>9</v>
@@ -10058,10 +10070,10 @@
         <v>9</v>
       </c>
       <c r="Z68" s="53" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="AA68" s="37" t="s">
-        <v>790</v>
+        <v>783</v>
       </c>
     </row>
     <row r="69" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -10075,13 +10087,13 @@
         <v>95</v>
       </c>
       <c r="D69" s="56" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E69" s="56" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="F69" s="58" t="s">
-        <v>571</v>
+        <v>564</v>
       </c>
       <c r="G69" s="50" t="s">
         <v>9</v>
@@ -10115,10 +10127,10 @@
         <v>Ilu Vendedor</v>
       </c>
       <c r="P69" s="54" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="Q69" s="55" t="s">
-        <v>653</v>
+        <v>646</v>
       </c>
       <c r="R69" s="52" t="s">
         <v>9</v>
@@ -10149,10 +10161,10 @@
         <v>9</v>
       </c>
       <c r="Z69" s="53" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="AA69" s="37" t="s">
-        <v>791</v>
+        <v>784</v>
       </c>
     </row>
     <row r="70" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -10166,13 +10178,13 @@
         <v>95</v>
       </c>
       <c r="D70" s="56" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E70" s="56" t="s">
         <v>99</v>
       </c>
       <c r="F70" s="58" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="G70" s="50" t="s">
         <v>9</v>
@@ -10206,10 +10218,10 @@
         <v>Ino Compra</v>
       </c>
       <c r="P70" s="54" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="Q70" s="55" t="s">
-        <v>654</v>
+        <v>647</v>
       </c>
       <c r="R70" s="52" t="s">
         <v>9</v>
@@ -10240,10 +10252,10 @@
         <v>9</v>
       </c>
       <c r="Z70" s="53" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="AA70" s="37" t="s">
-        <v>792</v>
+        <v>785</v>
       </c>
     </row>
     <row r="71" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -10257,13 +10269,13 @@
         <v>95</v>
       </c>
       <c r="D71" s="56" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E71" s="56" t="s">
         <v>99</v>
       </c>
       <c r="F71" s="58" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="G71" s="50" t="s">
         <v>9</v>
@@ -10300,7 +10312,7 @@
         <v>120</v>
       </c>
       <c r="Q71" s="55" t="s">
-        <v>655</v>
+        <v>648</v>
       </c>
       <c r="R71" s="52" t="s">
         <v>9</v>
@@ -10331,10 +10343,10 @@
         <v>9</v>
       </c>
       <c r="Z71" s="53" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="AA71" s="37" t="s">
-        <v>793</v>
+        <v>786</v>
       </c>
     </row>
     <row r="72" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -10348,13 +10360,13 @@
         <v>95</v>
       </c>
       <c r="D72" s="56" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E72" s="56" t="s">
         <v>99</v>
       </c>
       <c r="F72" s="58" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="G72" s="50" t="s">
         <v>9</v>
@@ -10375,19 +10387,19 @@
         <v>95</v>
       </c>
       <c r="M72" s="54" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="N72" s="54" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="O72" s="54" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="P72" s="54" t="s">
-        <v>508</v>
+        <v>503</v>
       </c>
       <c r="Q72" s="55" t="s">
-        <v>536</v>
+        <v>531</v>
       </c>
       <c r="R72" s="52" t="s">
         <v>9</v>
@@ -10396,10 +10408,10 @@
         <v>95</v>
       </c>
       <c r="T72" s="53" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="U72" s="53" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="V72" s="37" t="s">
         <v>181</v>
@@ -10415,10 +10427,10 @@
         <v>9</v>
       </c>
       <c r="Z72" s="53" t="s">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="AA72" s="37" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
     </row>
     <row r="73" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -10432,13 +10444,13 @@
         <v>95</v>
       </c>
       <c r="D73" s="56" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E73" s="56" t="s">
         <v>99</v>
       </c>
       <c r="F73" s="58" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="G73" s="50" t="s">
         <v>9</v>
@@ -10475,7 +10487,7 @@
         <v>121</v>
       </c>
       <c r="Q73" s="55" t="s">
-        <v>656</v>
+        <v>649</v>
       </c>
       <c r="R73" s="52" t="s">
         <v>9</v>
@@ -10506,10 +10518,10 @@
         <v>9</v>
       </c>
       <c r="Z73" s="53" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="AA73" s="37" t="s">
-        <v>794</v>
+        <v>787</v>
       </c>
     </row>
     <row r="74" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -10523,13 +10535,13 @@
         <v>95</v>
       </c>
       <c r="D74" s="56" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E74" s="56" t="s">
         <v>99</v>
       </c>
       <c r="F74" s="58" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="G74" s="50" t="s">
         <v>9</v>
@@ -10566,7 +10578,7 @@
         <v>122</v>
       </c>
       <c r="Q74" s="55" t="s">
-        <v>657</v>
+        <v>650</v>
       </c>
       <c r="R74" s="52" t="s">
         <v>9</v>
@@ -10597,10 +10609,10 @@
         <v>9</v>
       </c>
       <c r="Z74" s="53" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="AA74" s="37" t="s">
-        <v>795</v>
+        <v>788</v>
       </c>
     </row>
     <row r="75" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -10614,13 +10626,13 @@
         <v>95</v>
       </c>
       <c r="D75" s="56" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E75" s="56" t="s">
         <v>99</v>
       </c>
       <c r="F75" s="58" t="s">
-        <v>559</v>
+        <v>552</v>
       </c>
       <c r="G75" s="50" t="s">
         <v>9</v>
@@ -10657,7 +10669,7 @@
         <v>179</v>
       </c>
       <c r="Q75" s="55" t="s">
-        <v>658</v>
+        <v>651</v>
       </c>
       <c r="R75" s="52" t="s">
         <v>9</v>
@@ -10688,10 +10700,10 @@
         <v>9</v>
       </c>
       <c r="Z75" s="53" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="AA75" s="37" t="s">
-        <v>796</v>
+        <v>789</v>
       </c>
     </row>
     <row r="76" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -10705,13 +10717,13 @@
         <v>95</v>
       </c>
       <c r="D76" s="56" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E76" s="56" t="s">
         <v>99</v>
       </c>
       <c r="F76" s="58" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="G76" s="50" t="s">
         <v>9</v>
@@ -10748,7 +10760,7 @@
         <v>228</v>
       </c>
       <c r="Q76" s="55" t="s">
-        <v>659</v>
+        <v>652</v>
       </c>
       <c r="R76" s="52" t="s">
         <v>9</v>
@@ -10779,10 +10791,10 @@
         <v>9</v>
       </c>
       <c r="Z76" s="53" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="AA76" s="37" t="s">
-        <v>797</v>
+        <v>790</v>
       </c>
     </row>
     <row r="77" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -10796,13 +10808,13 @@
         <v>95</v>
       </c>
       <c r="D77" s="56" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E77" s="56" t="s">
         <v>99</v>
       </c>
       <c r="F77" s="58" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="G77" s="50" t="s">
         <v>9</v>
@@ -10839,7 +10851,7 @@
         <v>119</v>
       </c>
       <c r="Q77" s="55" t="s">
-        <v>660</v>
+        <v>653</v>
       </c>
       <c r="R77" s="52" t="s">
         <v>9</v>
@@ -10870,10 +10882,10 @@
         <v>9</v>
       </c>
       <c r="Z77" s="53" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="AA77" s="37" t="s">
-        <v>798</v>
+        <v>791</v>
       </c>
     </row>
     <row r="78" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -10887,13 +10899,13 @@
         <v>95</v>
       </c>
       <c r="D78" s="56" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E78" s="56" t="s">
         <v>99</v>
       </c>
       <c r="F78" s="58" t="s">
-        <v>572</v>
+        <v>565</v>
       </c>
       <c r="G78" s="50" t="s">
         <v>9</v>
@@ -10927,10 +10939,10 @@
         <v>Ino Vendedor</v>
       </c>
       <c r="P78" s="54" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="Q78" s="55" t="s">
-        <v>661</v>
+        <v>654</v>
       </c>
       <c r="R78" s="52" t="s">
         <v>9</v>
@@ -10961,10 +10973,10 @@
         <v>9</v>
       </c>
       <c r="Z78" s="53" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="AA78" s="37" t="s">
-        <v>799</v>
+        <v>792</v>
       </c>
     </row>
     <row r="79" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -10978,13 +10990,13 @@
         <v>95</v>
       </c>
       <c r="D79" s="56" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E79" s="56" t="s">
         <v>98</v>
       </c>
       <c r="F79" s="58" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="G79" s="50" t="s">
         <v>9</v>
@@ -11018,10 +11030,10 @@
         <v>Ins Compra</v>
       </c>
       <c r="P79" s="54" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="Q79" s="55" t="s">
-        <v>662</v>
+        <v>655</v>
       </c>
       <c r="R79" s="52" t="s">
         <v>9</v>
@@ -11052,10 +11064,10 @@
         <v>9</v>
       </c>
       <c r="Z79" s="53" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="AA79" s="37" t="s">
-        <v>800</v>
+        <v>793</v>
       </c>
     </row>
     <row r="80" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -11069,13 +11081,13 @@
         <v>95</v>
       </c>
       <c r="D80" s="56" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E80" s="56" t="s">
         <v>98</v>
       </c>
       <c r="F80" s="58" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="G80" s="50" t="s">
         <v>9</v>
@@ -11112,7 +11124,7 @@
         <v>108</v>
       </c>
       <c r="Q80" s="55" t="s">
-        <v>663</v>
+        <v>656</v>
       </c>
       <c r="R80" s="52" t="s">
         <v>9</v>
@@ -11143,10 +11155,10 @@
         <v>9</v>
       </c>
       <c r="Z80" s="53" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="AA80" s="37" t="s">
-        <v>801</v>
+        <v>794</v>
       </c>
     </row>
     <row r="81" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -11160,13 +11172,13 @@
         <v>95</v>
       </c>
       <c r="D81" s="56" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E81" s="56" t="s">
         <v>98</v>
       </c>
       <c r="F81" s="58" t="s">
-        <v>491</v>
+        <v>486</v>
       </c>
       <c r="G81" s="50" t="s">
         <v>9</v>
@@ -11187,19 +11199,19 @@
         <v>95</v>
       </c>
       <c r="M81" s="54" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="N81" s="54" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="O81" s="54" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="P81" s="54" t="s">
-        <v>504</v>
+        <v>499</v>
       </c>
       <c r="Q81" s="55" t="s">
-        <v>537</v>
+        <v>532</v>
       </c>
       <c r="R81" s="52" t="s">
         <v>9</v>
@@ -11208,10 +11220,10 @@
         <v>95</v>
       </c>
       <c r="T81" s="53" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="U81" s="53" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="V81" s="37" t="s">
         <v>181</v>
@@ -11227,10 +11239,10 @@
         <v>9</v>
       </c>
       <c r="Z81" s="53" t="s">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="AA81" s="37" t="s">
-        <v>516</v>
+        <v>511</v>
       </c>
     </row>
     <row r="82" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -11244,13 +11256,13 @@
         <v>95</v>
       </c>
       <c r="D82" s="56" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E82" s="56" t="s">
         <v>98</v>
       </c>
       <c r="F82" s="58" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="G82" s="50" t="s">
         <v>9</v>
@@ -11287,7 +11299,7 @@
         <v>109</v>
       </c>
       <c r="Q82" s="55" t="s">
-        <v>664</v>
+        <v>657</v>
       </c>
       <c r="R82" s="52" t="s">
         <v>9</v>
@@ -11318,10 +11330,10 @@
         <v>9</v>
       </c>
       <c r="Z82" s="53" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="AA82" s="37" t="s">
-        <v>802</v>
+        <v>795</v>
       </c>
     </row>
     <row r="83" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -11335,13 +11347,13 @@
         <v>95</v>
       </c>
       <c r="D83" s="56" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E83" s="56" t="s">
         <v>98</v>
       </c>
       <c r="F83" s="58" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="G83" s="50" t="s">
         <v>9</v>
@@ -11378,7 +11390,7 @@
         <v>110</v>
       </c>
       <c r="Q83" s="55" t="s">
-        <v>665</v>
+        <v>658</v>
       </c>
       <c r="R83" s="52" t="s">
         <v>9</v>
@@ -11409,10 +11421,10 @@
         <v>9</v>
       </c>
       <c r="Z83" s="53" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="AA83" s="37" t="s">
-        <v>803</v>
+        <v>796</v>
       </c>
     </row>
     <row r="84" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -11426,13 +11438,13 @@
         <v>95</v>
       </c>
       <c r="D84" s="56" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E84" s="56" t="s">
         <v>98</v>
       </c>
       <c r="F84" s="58" t="s">
-        <v>560</v>
+        <v>553</v>
       </c>
       <c r="G84" s="50" t="s">
         <v>9</v>
@@ -11469,7 +11481,7 @@
         <v>175</v>
       </c>
       <c r="Q84" s="55" t="s">
-        <v>666</v>
+        <v>659</v>
       </c>
       <c r="R84" s="52" t="s">
         <v>9</v>
@@ -11500,10 +11512,10 @@
         <v>9</v>
       </c>
       <c r="Z84" s="53" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="AA84" s="37" t="s">
-        <v>804</v>
+        <v>797</v>
       </c>
     </row>
     <row r="85" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -11517,13 +11529,13 @@
         <v>95</v>
       </c>
       <c r="D85" s="56" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E85" s="56" t="s">
         <v>98</v>
       </c>
       <c r="F85" s="58" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="G85" s="50" t="s">
         <v>9</v>
@@ -11560,7 +11572,7 @@
         <v>225</v>
       </c>
       <c r="Q85" s="55" t="s">
-        <v>667</v>
+        <v>660</v>
       </c>
       <c r="R85" s="52" t="s">
         <v>9</v>
@@ -11591,10 +11603,10 @@
         <v>9</v>
       </c>
       <c r="Z85" s="53" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="AA85" s="37" t="s">
-        <v>805</v>
+        <v>798</v>
       </c>
     </row>
     <row r="86" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -11608,13 +11620,13 @@
         <v>95</v>
       </c>
       <c r="D86" s="56" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E86" s="56" t="s">
         <v>98</v>
       </c>
       <c r="F86" s="58" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="G86" s="50" t="s">
         <v>9</v>
@@ -11651,7 +11663,7 @@
         <v>107</v>
       </c>
       <c r="Q86" s="55" t="s">
-        <v>668</v>
+        <v>661</v>
       </c>
       <c r="R86" s="52" t="s">
         <v>9</v>
@@ -11682,10 +11694,10 @@
         <v>9</v>
       </c>
       <c r="Z86" s="53" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="AA86" s="37" t="s">
-        <v>806</v>
+        <v>799</v>
       </c>
     </row>
     <row r="87" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -11699,13 +11711,13 @@
         <v>95</v>
       </c>
       <c r="D87" s="56" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E87" s="56" t="s">
         <v>98</v>
       </c>
       <c r="F87" s="58" t="s">
-        <v>573</v>
+        <v>566</v>
       </c>
       <c r="G87" s="50" t="s">
         <v>9</v>
@@ -11739,10 +11751,10 @@
         <v>Ins Vendedor</v>
       </c>
       <c r="P87" s="54" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="Q87" s="55" t="s">
-        <v>669</v>
+        <v>662</v>
       </c>
       <c r="R87" s="52" t="s">
         <v>9</v>
@@ -11773,10 +11785,10 @@
         <v>9</v>
       </c>
       <c r="Z87" s="53" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="AA87" s="37" t="s">
-        <v>807</v>
+        <v>800</v>
       </c>
     </row>
     <row r="88" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -11790,13 +11802,13 @@
         <v>95</v>
       </c>
       <c r="D88" s="56" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E88" s="56" t="s">
         <v>102</v>
       </c>
       <c r="F88" s="58" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="G88" s="50" t="s">
         <v>9</v>
@@ -11830,10 +11842,10 @@
         <v>Lab Compra</v>
       </c>
       <c r="P88" s="54" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="Q88" s="55" t="s">
-        <v>670</v>
+        <v>663</v>
       </c>
       <c r="R88" s="52" t="s">
         <v>9</v>
@@ -11864,10 +11876,10 @@
         <v>9</v>
       </c>
       <c r="Z88" s="53" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="AA88" s="37" t="s">
-        <v>808</v>
+        <v>801</v>
       </c>
     </row>
     <row r="89" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -11881,13 +11893,13 @@
         <v>95</v>
       </c>
       <c r="D89" s="56" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E89" s="56" t="s">
         <v>102</v>
       </c>
       <c r="F89" s="58" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="G89" s="50" t="s">
         <v>9</v>
@@ -11924,7 +11936,7 @@
         <v>116</v>
       </c>
       <c r="Q89" s="55" t="s">
-        <v>671</v>
+        <v>664</v>
       </c>
       <c r="R89" s="52" t="s">
         <v>9</v>
@@ -11955,10 +11967,10 @@
         <v>9</v>
       </c>
       <c r="Z89" s="53" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="AA89" s="37" t="s">
-        <v>809</v>
+        <v>802</v>
       </c>
     </row>
     <row r="90" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -11972,13 +11984,13 @@
         <v>95</v>
       </c>
       <c r="D90" s="56" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E90" s="56" t="s">
         <v>102</v>
       </c>
       <c r="F90" s="58" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="G90" s="50" t="s">
         <v>9</v>
@@ -11999,19 +12011,19 @@
         <v>95</v>
       </c>
       <c r="M90" s="54" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="N90" s="54" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="O90" s="54" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="P90" s="54" t="s">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="Q90" s="55" t="s">
-        <v>529</v>
+        <v>524</v>
       </c>
       <c r="R90" s="52" t="s">
         <v>9</v>
@@ -12020,10 +12032,10 @@
         <v>95</v>
       </c>
       <c r="T90" s="53" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="U90" s="53" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="V90" s="37" t="s">
         <v>181</v>
@@ -12039,10 +12051,10 @@
         <v>9</v>
       </c>
       <c r="Z90" s="53" t="s">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="AA90" s="37" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
     </row>
     <row r="91" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -12056,13 +12068,13 @@
         <v>95</v>
       </c>
       <c r="D91" s="56" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E91" s="56" t="s">
         <v>102</v>
       </c>
       <c r="F91" s="58" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="G91" s="50" t="s">
         <v>9</v>
@@ -12099,7 +12111,7 @@
         <v>117</v>
       </c>
       <c r="Q91" s="55" t="s">
-        <v>672</v>
+        <v>665</v>
       </c>
       <c r="R91" s="52" t="s">
         <v>9</v>
@@ -12130,10 +12142,10 @@
         <v>9</v>
       </c>
       <c r="Z91" s="53" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="AA91" s="37" t="s">
-        <v>810</v>
+        <v>803</v>
       </c>
     </row>
     <row r="92" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -12147,13 +12159,13 @@
         <v>95</v>
       </c>
       <c r="D92" s="56" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E92" s="56" t="s">
         <v>102</v>
       </c>
       <c r="F92" s="58" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="G92" s="50" t="s">
         <v>9</v>
@@ -12190,7 +12202,7 @@
         <v>118</v>
       </c>
       <c r="Q92" s="55" t="s">
-        <v>673</v>
+        <v>666</v>
       </c>
       <c r="R92" s="52" t="s">
         <v>9</v>
@@ -12221,10 +12233,10 @@
         <v>9</v>
       </c>
       <c r="Z92" s="53" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="AA92" s="37" t="s">
-        <v>811</v>
+        <v>804</v>
       </c>
     </row>
     <row r="93" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -12238,13 +12250,13 @@
         <v>95</v>
       </c>
       <c r="D93" s="56" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E93" s="56" t="s">
         <v>102</v>
       </c>
       <c r="F93" s="58" t="s">
-        <v>561</v>
+        <v>554</v>
       </c>
       <c r="G93" s="50" t="s">
         <v>9</v>
@@ -12281,7 +12293,7 @@
         <v>178</v>
       </c>
       <c r="Q93" s="55" t="s">
-        <v>674</v>
+        <v>667</v>
       </c>
       <c r="R93" s="52" t="s">
         <v>9</v>
@@ -12312,10 +12324,10 @@
         <v>9</v>
       </c>
       <c r="Z93" s="53" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="AA93" s="37" t="s">
-        <v>812</v>
+        <v>805</v>
       </c>
     </row>
     <row r="94" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -12329,13 +12341,13 @@
         <v>95</v>
       </c>
       <c r="D94" s="56" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E94" s="56" t="s">
         <v>102</v>
       </c>
       <c r="F94" s="58" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G94" s="50" t="s">
         <v>9</v>
@@ -12372,7 +12384,7 @@
         <v>226</v>
       </c>
       <c r="Q94" s="55" t="s">
-        <v>675</v>
+        <v>668</v>
       </c>
       <c r="R94" s="52" t="s">
         <v>9</v>
@@ -12403,10 +12415,10 @@
         <v>9</v>
       </c>
       <c r="Z94" s="53" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="AA94" s="37" t="s">
-        <v>813</v>
+        <v>806</v>
       </c>
     </row>
     <row r="95" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -12420,13 +12432,13 @@
         <v>95</v>
       </c>
       <c r="D95" s="56" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E95" s="56" t="s">
         <v>102</v>
       </c>
       <c r="F95" s="58" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="G95" s="50" t="s">
         <v>9</v>
@@ -12463,7 +12475,7 @@
         <v>115</v>
       </c>
       <c r="Q95" s="55" t="s">
-        <v>676</v>
+        <v>669</v>
       </c>
       <c r="R95" s="52" t="s">
         <v>9</v>
@@ -12494,10 +12506,10 @@
         <v>9</v>
       </c>
       <c r="Z95" s="53" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="AA95" s="37" t="s">
-        <v>814</v>
+        <v>807</v>
       </c>
     </row>
     <row r="96" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -12511,13 +12523,13 @@
         <v>95</v>
       </c>
       <c r="D96" s="56" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E96" s="56" t="s">
         <v>102</v>
       </c>
       <c r="F96" s="58" t="s">
-        <v>574</v>
+        <v>567</v>
       </c>
       <c r="G96" s="50" t="s">
         <v>9</v>
@@ -12551,10 +12563,10 @@
         <v>Lab Vendedor</v>
       </c>
       <c r="P96" s="54" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="Q96" s="55" t="s">
-        <v>677</v>
+        <v>670</v>
       </c>
       <c r="R96" s="52" t="s">
         <v>9</v>
@@ -12585,10 +12597,10 @@
         <v>9</v>
       </c>
       <c r="Z96" s="53" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="AA96" s="37" t="s">
-        <v>815</v>
+        <v>808</v>
       </c>
     </row>
     <row r="97" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -12602,13 +12614,13 @@
         <v>95</v>
       </c>
       <c r="D97" s="56" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E97" s="56" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="F97" s="58" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="G97" s="50" t="s">
         <v>9</v>
@@ -12642,10 +12654,10 @@
         <v>Mec Compra</v>
       </c>
       <c r="P97" s="54" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="Q97" s="55" t="s">
-        <v>678</v>
+        <v>671</v>
       </c>
       <c r="R97" s="52" t="s">
         <v>9</v>
@@ -12676,10 +12688,10 @@
         <v>9</v>
       </c>
       <c r="Z97" s="53" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="AA97" s="37" t="s">
-        <v>816</v>
+        <v>809</v>
       </c>
     </row>
     <row r="98" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -12693,13 +12705,13 @@
         <v>95</v>
       </c>
       <c r="D98" s="56" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E98" s="56" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="F98" s="58" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="G98" s="50" t="s">
         <v>9</v>
@@ -12733,10 +12745,10 @@
         <v>Mec Consultor</v>
       </c>
       <c r="P98" s="54" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="Q98" s="55" t="s">
-        <v>679</v>
+        <v>672</v>
       </c>
       <c r="R98" s="52" t="s">
         <v>9</v>
@@ -12767,10 +12779,10 @@
         <v>9</v>
       </c>
       <c r="Z98" s="53" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="AA98" s="37" t="s">
-        <v>817</v>
+        <v>810</v>
       </c>
     </row>
     <row r="99" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -12784,13 +12796,13 @@
         <v>95</v>
       </c>
       <c r="D99" s="56" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E99" s="56" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="F99" s="58" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="G99" s="50" t="s">
         <v>9</v>
@@ -12811,19 +12823,19 @@
         <v>95</v>
       </c>
       <c r="M99" s="54" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="N99" s="54" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="O99" s="54" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="P99" s="54" t="s">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="Q99" s="55" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="R99" s="52" t="s">
         <v>9</v>
@@ -12832,10 +12844,10 @@
         <v>95</v>
       </c>
       <c r="T99" s="53" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="U99" s="53" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="V99" s="37" t="s">
         <v>181</v>
@@ -12851,10 +12863,10 @@
         <v>9</v>
       </c>
       <c r="Z99" s="53" t="s">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="AA99" s="37" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
     </row>
     <row r="100" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -12868,13 +12880,13 @@
         <v>95</v>
       </c>
       <c r="D100" s="56" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E100" s="56" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="F100" s="58" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="G100" s="50" t="s">
         <v>9</v>
@@ -12908,10 +12920,10 @@
         <v>Mec Empresa Consultora</v>
       </c>
       <c r="P100" s="54" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="Q100" s="55" t="s">
-        <v>680</v>
+        <v>673</v>
       </c>
       <c r="R100" s="52" t="s">
         <v>9</v>
@@ -12942,10 +12954,10 @@
         <v>9</v>
       </c>
       <c r="Z100" s="53" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="AA100" s="37" t="s">
-        <v>818</v>
+        <v>811</v>
       </c>
     </row>
     <row r="101" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -12959,13 +12971,13 @@
         <v>95</v>
       </c>
       <c r="D101" s="56" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E101" s="56" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="F101" s="58" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="G101" s="50" t="s">
         <v>9</v>
@@ -12999,10 +13011,10 @@
         <v>Mec Fabricante</v>
       </c>
       <c r="P101" s="54" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="Q101" s="55" t="s">
-        <v>681</v>
+        <v>674</v>
       </c>
       <c r="R101" s="52" t="s">
         <v>9</v>
@@ -13033,10 +13045,10 @@
         <v>9</v>
       </c>
       <c r="Z101" s="53" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="AA101" s="37" t="s">
-        <v>819</v>
+        <v>812</v>
       </c>
     </row>
     <row r="102" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -13050,13 +13062,13 @@
         <v>95</v>
       </c>
       <c r="D102" s="56" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E102" s="56" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="F102" s="58" t="s">
-        <v>562</v>
+        <v>555</v>
       </c>
       <c r="G102" s="50" t="s">
         <v>9</v>
@@ -13090,10 +13102,10 @@
         <v>Mec Fornecedor</v>
       </c>
       <c r="P102" s="54" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="Q102" s="55" t="s">
-        <v>682</v>
+        <v>675</v>
       </c>
       <c r="R102" s="52" t="s">
         <v>9</v>
@@ -13124,10 +13136,10 @@
         <v>9</v>
       </c>
       <c r="Z102" s="53" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="AA102" s="37" t="s">
-        <v>820</v>
+        <v>813</v>
       </c>
     </row>
     <row r="103" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -13141,13 +13153,13 @@
         <v>95</v>
       </c>
       <c r="D103" s="56" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E103" s="56" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="F103" s="58" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="G103" s="50" t="s">
         <v>9</v>
@@ -13181,10 +13193,10 @@
         <v>Mec Projetista</v>
       </c>
       <c r="P103" s="54" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="Q103" s="55" t="s">
-        <v>683</v>
+        <v>676</v>
       </c>
       <c r="R103" s="52" t="s">
         <v>9</v>
@@ -13215,10 +13227,10 @@
         <v>9</v>
       </c>
       <c r="Z103" s="53" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="AA103" s="37" t="s">
-        <v>821</v>
+        <v>814</v>
       </c>
     </row>
     <row r="104" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -13232,13 +13244,13 @@
         <v>95</v>
       </c>
       <c r="D104" s="56" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E104" s="56" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="F104" s="58" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="G104" s="50" t="s">
         <v>9</v>
@@ -13272,10 +13284,10 @@
         <v>Mec Serviço</v>
       </c>
       <c r="P104" s="54" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="Q104" s="55" t="s">
-        <v>684</v>
+        <v>677</v>
       </c>
       <c r="R104" s="52" t="s">
         <v>9</v>
@@ -13306,10 +13318,10 @@
         <v>9</v>
       </c>
       <c r="Z104" s="53" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="AA104" s="37" t="s">
-        <v>822</v>
+        <v>815</v>
       </c>
     </row>
     <row r="105" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -13323,13 +13335,13 @@
         <v>95</v>
       </c>
       <c r="D105" s="56" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E105" s="56" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="F105" s="58" t="s">
-        <v>575</v>
+        <v>568</v>
       </c>
       <c r="G105" s="50" t="s">
         <v>9</v>
@@ -13363,10 +13375,10 @@
         <v>Mec Vendedor</v>
       </c>
       <c r="P105" s="54" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="Q105" s="55" t="s">
-        <v>685</v>
+        <v>678</v>
       </c>
       <c r="R105" s="52" t="s">
         <v>9</v>
@@ -13397,10 +13409,10 @@
         <v>9</v>
       </c>
       <c r="Z105" s="53" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="AA105" s="37" t="s">
-        <v>823</v>
+        <v>816</v>
       </c>
     </row>
     <row r="106" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -13414,13 +13426,13 @@
         <v>95</v>
       </c>
       <c r="D106" s="56" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E106" s="56" t="s">
         <v>100</v>
       </c>
       <c r="F106" s="58" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="G106" s="50" t="s">
         <v>9</v>
@@ -13454,10 +13466,10 @@
         <v>Mob Compra</v>
       </c>
       <c r="P106" s="54" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="Q106" s="55" t="s">
-        <v>686</v>
+        <v>679</v>
       </c>
       <c r="R106" s="52" t="s">
         <v>9</v>
@@ -13488,10 +13500,10 @@
         <v>9</v>
       </c>
       <c r="Z106" s="53" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="AA106" s="37" t="s">
-        <v>824</v>
+        <v>817</v>
       </c>
     </row>
     <row r="107" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -13505,13 +13517,13 @@
         <v>95</v>
       </c>
       <c r="D107" s="56" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E107" s="56" t="s">
         <v>100</v>
       </c>
       <c r="F107" s="58" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="G107" s="50" t="s">
         <v>9</v>
@@ -13548,7 +13560,7 @@
         <v>112</v>
       </c>
       <c r="Q107" s="55" t="s">
-        <v>687</v>
+        <v>680</v>
       </c>
       <c r="R107" s="52" t="s">
         <v>9</v>
@@ -13579,10 +13591,10 @@
         <v>9</v>
       </c>
       <c r="Z107" s="53" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="AA107" s="37" t="s">
-        <v>825</v>
+        <v>818</v>
       </c>
     </row>
     <row r="108" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -13596,13 +13608,13 @@
         <v>95</v>
       </c>
       <c r="D108" s="56" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E108" s="56" t="s">
         <v>100</v>
       </c>
       <c r="F108" s="58" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="G108" s="50" t="s">
         <v>9</v>
@@ -13623,19 +13635,19 @@
         <v>95</v>
       </c>
       <c r="M108" s="54" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="N108" s="54" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="O108" s="54" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="P108" s="54" t="s">
-        <v>506</v>
+        <v>501</v>
       </c>
       <c r="Q108" s="55" t="s">
-        <v>530</v>
+        <v>525</v>
       </c>
       <c r="R108" s="52" t="s">
         <v>9</v>
@@ -13644,10 +13656,10 @@
         <v>95</v>
       </c>
       <c r="T108" s="53" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="U108" s="53" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="V108" s="37" t="s">
         <v>181</v>
@@ -13663,10 +13675,10 @@
         <v>9</v>
       </c>
       <c r="Z108" s="53" t="s">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="AA108" s="37" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
     </row>
     <row r="109" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -13680,13 +13692,13 @@
         <v>95</v>
       </c>
       <c r="D109" s="56" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E109" s="56" t="s">
         <v>100</v>
       </c>
       <c r="F109" s="58" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="G109" s="50" t="s">
         <v>9</v>
@@ -13723,7 +13735,7 @@
         <v>113</v>
       </c>
       <c r="Q109" s="55" t="s">
-        <v>688</v>
+        <v>681</v>
       </c>
       <c r="R109" s="52" t="s">
         <v>9</v>
@@ -13754,10 +13766,10 @@
         <v>9</v>
       </c>
       <c r="Z109" s="53" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="AA109" s="37" t="s">
-        <v>826</v>
+        <v>819</v>
       </c>
     </row>
     <row r="110" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -13771,13 +13783,13 @@
         <v>95</v>
       </c>
       <c r="D110" s="56" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E110" s="56" t="s">
         <v>100</v>
       </c>
       <c r="F110" s="58" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="G110" s="50" t="s">
         <v>9</v>
@@ -13814,7 +13826,7 @@
         <v>114</v>
       </c>
       <c r="Q110" s="55" t="s">
-        <v>689</v>
+        <v>682</v>
       </c>
       <c r="R110" s="52" t="s">
         <v>9</v>
@@ -13845,10 +13857,10 @@
         <v>9</v>
       </c>
       <c r="Z110" s="53" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="AA110" s="37" t="s">
-        <v>827</v>
+        <v>820</v>
       </c>
     </row>
     <row r="111" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -13862,13 +13874,13 @@
         <v>95</v>
       </c>
       <c r="D111" s="56" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E111" s="56" t="s">
         <v>100</v>
       </c>
       <c r="F111" s="58" t="s">
-        <v>563</v>
+        <v>556</v>
       </c>
       <c r="G111" s="50" t="s">
         <v>9</v>
@@ -13905,7 +13917,7 @@
         <v>176</v>
       </c>
       <c r="Q111" s="55" t="s">
-        <v>690</v>
+        <v>683</v>
       </c>
       <c r="R111" s="52" t="s">
         <v>9</v>
@@ -13936,10 +13948,10 @@
         <v>9</v>
       </c>
       <c r="Z111" s="53" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="AA111" s="37" t="s">
-        <v>828</v>
+        <v>821</v>
       </c>
     </row>
     <row r="112" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -13953,13 +13965,13 @@
         <v>95</v>
       </c>
       <c r="D112" s="56" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E112" s="56" t="s">
         <v>100</v>
       </c>
       <c r="F112" s="58" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="G112" s="50" t="s">
         <v>9</v>
@@ -13996,7 +14008,7 @@
         <v>227</v>
       </c>
       <c r="Q112" s="55" t="s">
-        <v>691</v>
+        <v>684</v>
       </c>
       <c r="R112" s="52" t="s">
         <v>9</v>
@@ -14027,10 +14039,10 @@
         <v>9</v>
       </c>
       <c r="Z112" s="53" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="AA112" s="37" t="s">
-        <v>829</v>
+        <v>822</v>
       </c>
     </row>
     <row r="113" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -14044,13 +14056,13 @@
         <v>95</v>
       </c>
       <c r="D113" s="56" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E113" s="56" t="s">
         <v>100</v>
       </c>
       <c r="F113" s="58" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="G113" s="50" t="s">
         <v>9</v>
@@ -14087,7 +14099,7 @@
         <v>111</v>
       </c>
       <c r="Q113" s="55" t="s">
-        <v>692</v>
+        <v>685</v>
       </c>
       <c r="R113" s="52" t="s">
         <v>9</v>
@@ -14118,10 +14130,10 @@
         <v>9</v>
       </c>
       <c r="Z113" s="53" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="AA113" s="37" t="s">
-        <v>830</v>
+        <v>823</v>
       </c>
     </row>
     <row r="114" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -14135,13 +14147,13 @@
         <v>95</v>
       </c>
       <c r="D114" s="56" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E114" s="56" t="s">
         <v>100</v>
       </c>
       <c r="F114" s="58" t="s">
-        <v>576</v>
+        <v>569</v>
       </c>
       <c r="G114" s="50" t="s">
         <v>9</v>
@@ -14175,10 +14187,10 @@
         <v>Mob Vendedor</v>
       </c>
       <c r="P114" s="54" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="Q114" s="55" t="s">
-        <v>693</v>
+        <v>686</v>
       </c>
       <c r="R114" s="52" t="s">
         <v>9</v>
@@ -14209,10 +14221,10 @@
         <v>9</v>
       </c>
       <c r="Z114" s="53" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="AA114" s="37" t="s">
-        <v>831</v>
+        <v>824</v>
       </c>
     </row>
     <row r="115" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -14226,13 +14238,13 @@
         <v>95</v>
       </c>
       <c r="D115" s="56" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E115" s="56" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="F115" s="58" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="G115" s="50" t="s">
         <v>9</v>
@@ -14266,10 +14278,10 @@
         <v>Tel Compra</v>
       </c>
       <c r="P115" s="54" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="Q115" s="55" t="s">
-        <v>694</v>
+        <v>687</v>
       </c>
       <c r="R115" s="52" t="s">
         <v>9</v>
@@ -14300,10 +14312,10 @@
         <v>9</v>
       </c>
       <c r="Z115" s="53" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="AA115" s="37" t="s">
-        <v>832</v>
+        <v>825</v>
       </c>
     </row>
     <row r="116" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -14317,13 +14329,13 @@
         <v>95</v>
       </c>
       <c r="D116" s="56" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E116" s="56" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="F116" s="58" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="G116" s="50" t="s">
         <v>9</v>
@@ -14357,10 +14369,10 @@
         <v>Tel Consultor</v>
       </c>
       <c r="P116" s="54" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="Q116" s="55" t="s">
-        <v>695</v>
+        <v>688</v>
       </c>
       <c r="R116" s="52" t="s">
         <v>9</v>
@@ -14391,10 +14403,10 @@
         <v>9</v>
       </c>
       <c r="Z116" s="53" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="AA116" s="37" t="s">
-        <v>833</v>
+        <v>826</v>
       </c>
     </row>
     <row r="117" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -14408,13 +14420,13 @@
         <v>95</v>
       </c>
       <c r="D117" s="56" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E117" s="56" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="F117" s="58" t="s">
-        <v>499</v>
+        <v>494</v>
       </c>
       <c r="G117" s="50" t="s">
         <v>9</v>
@@ -14435,19 +14447,19 @@
         <v>95</v>
       </c>
       <c r="M117" s="54" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="N117" s="54" t="s">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="O117" s="54" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="P117" s="54" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="Q117" s="55" t="s">
-        <v>534</v>
+        <v>529</v>
       </c>
       <c r="R117" s="52" t="s">
         <v>9</v>
@@ -14456,10 +14468,10 @@
         <v>95</v>
       </c>
       <c r="T117" s="53" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="U117" s="53" t="s">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="V117" s="37" t="s">
         <v>181</v>
@@ -14475,10 +14487,10 @@
         <v>9</v>
       </c>
       <c r="Z117" s="53" t="s">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="AA117" s="37" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
     </row>
     <row r="118" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -14492,13 +14504,13 @@
         <v>95</v>
       </c>
       <c r="D118" s="56" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E118" s="56" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="F118" s="58" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="G118" s="50" t="s">
         <v>9</v>
@@ -14532,10 +14544,10 @@
         <v>Tel Empresa Consultora</v>
       </c>
       <c r="P118" s="54" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="Q118" s="55" t="s">
-        <v>696</v>
+        <v>689</v>
       </c>
       <c r="R118" s="52" t="s">
         <v>9</v>
@@ -14566,10 +14578,10 @@
         <v>9</v>
       </c>
       <c r="Z118" s="53" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="AA118" s="37" t="s">
-        <v>834</v>
+        <v>827</v>
       </c>
     </row>
     <row r="119" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -14583,13 +14595,13 @@
         <v>95</v>
       </c>
       <c r="D119" s="56" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E119" s="56" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="F119" s="58" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="G119" s="50" t="s">
         <v>9</v>
@@ -14623,10 +14635,10 @@
         <v>Tel Fabricante</v>
       </c>
       <c r="P119" s="54" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="Q119" s="55" t="s">
-        <v>697</v>
+        <v>690</v>
       </c>
       <c r="R119" s="52" t="s">
         <v>9</v>
@@ -14657,10 +14669,10 @@
         <v>9</v>
       </c>
       <c r="Z119" s="53" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="AA119" s="37" t="s">
-        <v>835</v>
+        <v>828</v>
       </c>
     </row>
     <row r="120" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -14674,13 +14686,13 @@
         <v>95</v>
       </c>
       <c r="D120" s="56" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E120" s="56" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="F120" s="58" t="s">
-        <v>564</v>
+        <v>557</v>
       </c>
       <c r="G120" s="50" t="s">
         <v>9</v>
@@ -14714,10 +14726,10 @@
         <v>Tel Fornecedor</v>
       </c>
       <c r="P120" s="54" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="Q120" s="55" t="s">
-        <v>698</v>
+        <v>691</v>
       </c>
       <c r="R120" s="52" t="s">
         <v>9</v>
@@ -14748,10 +14760,10 @@
         <v>9</v>
       </c>
       <c r="Z120" s="53" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="AA120" s="37" t="s">
-        <v>836</v>
+        <v>829</v>
       </c>
     </row>
     <row r="121" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -14765,13 +14777,13 @@
         <v>95</v>
       </c>
       <c r="D121" s="56" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E121" s="56" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="F121" s="58" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="G121" s="50" t="s">
         <v>9</v>
@@ -14805,10 +14817,10 @@
         <v>Tel Projetista</v>
       </c>
       <c r="P121" s="54" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="Q121" s="55" t="s">
-        <v>699</v>
+        <v>692</v>
       </c>
       <c r="R121" s="52" t="s">
         <v>9</v>
@@ -14839,10 +14851,10 @@
         <v>9</v>
       </c>
       <c r="Z121" s="53" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="AA121" s="37" t="s">
-        <v>837</v>
+        <v>830</v>
       </c>
     </row>
     <row r="122" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -14856,13 +14868,13 @@
         <v>95</v>
       </c>
       <c r="D122" s="56" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E122" s="56" t="s">
+        <v>362</v>
+      </c>
+      <c r="F122" s="58" t="s">
         <v>367</v>
-      </c>
-      <c r="F122" s="58" t="s">
-        <v>372</v>
       </c>
       <c r="G122" s="50" t="s">
         <v>9</v>
@@ -14896,10 +14908,10 @@
         <v>Tel Serviço</v>
       </c>
       <c r="P122" s="54" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="Q122" s="55" t="s">
-        <v>700</v>
+        <v>693</v>
       </c>
       <c r="R122" s="52" t="s">
         <v>9</v>
@@ -14930,10 +14942,10 @@
         <v>9</v>
       </c>
       <c r="Z122" s="53" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="AA122" s="37" t="s">
-        <v>838</v>
+        <v>831</v>
       </c>
     </row>
     <row r="123" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -14947,13 +14959,13 @@
         <v>95</v>
       </c>
       <c r="D123" s="56" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E123" s="56" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="F123" s="58" t="s">
-        <v>577</v>
+        <v>570</v>
       </c>
       <c r="G123" s="50" t="s">
         <v>9</v>
@@ -14987,10 +14999,10 @@
         <v>Tel Vendedor</v>
       </c>
       <c r="P123" s="54" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="Q123" s="55" t="s">
-        <v>701</v>
+        <v>694</v>
       </c>
       <c r="R123" s="52" t="s">
         <v>9</v>
@@ -15021,10 +15033,10 @@
         <v>9</v>
       </c>
       <c r="Z123" s="53" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="AA123" s="37" t="s">
-        <v>839</v>
+        <v>832</v>
       </c>
     </row>
     <row r="124" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -15038,10 +15050,10 @@
         <v>158</v>
       </c>
       <c r="D124" s="56" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E124" s="56" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="F124" s="56" t="s">
         <v>159</v>
@@ -15081,7 +15093,7 @@
         <v>189</v>
       </c>
       <c r="Q124" s="55" t="s">
-        <v>702</v>
+        <v>695</v>
       </c>
       <c r="R124" s="52" t="s">
         <v>9</v>
@@ -15112,10 +15124,10 @@
         <v>9</v>
       </c>
       <c r="Z124" s="63" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="AA124" s="37" t="s">
-        <v>840</v>
+        <v>833</v>
       </c>
     </row>
     <row r="125" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -15129,10 +15141,10 @@
         <v>158</v>
       </c>
       <c r="D125" s="56" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E125" s="56" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="F125" s="56" t="s">
         <v>131</v>
@@ -15172,7 +15184,7 @@
         <v>215</v>
       </c>
       <c r="Q125" s="55" t="s">
-        <v>703</v>
+        <v>696</v>
       </c>
       <c r="R125" s="52" t="s">
         <v>9</v>
@@ -15203,10 +15215,10 @@
         <v>9</v>
       </c>
       <c r="Z125" s="63" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="AA125" s="37" t="s">
-        <v>841</v>
+        <v>834</v>
       </c>
     </row>
     <row r="126" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -15220,10 +15232,10 @@
         <v>158</v>
       </c>
       <c r="D126" s="56" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E126" s="56" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="F126" s="56" t="s">
         <v>132</v>
@@ -15263,7 +15275,7 @@
         <v>190</v>
       </c>
       <c r="Q126" s="55" t="s">
-        <v>704</v>
+        <v>697</v>
       </c>
       <c r="R126" s="52" t="s">
         <v>9</v>
@@ -15294,10 +15306,10 @@
         <v>9</v>
       </c>
       <c r="Z126" s="63" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="AA126" s="37" t="s">
-        <v>842</v>
+        <v>835</v>
       </c>
     </row>
     <row r="127" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -15311,10 +15323,10 @@
         <v>158</v>
       </c>
       <c r="D127" s="56" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E127" s="56" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="F127" s="56" t="s">
         <v>133</v>
@@ -15354,7 +15366,7 @@
         <v>214</v>
       </c>
       <c r="Q127" s="55" t="s">
-        <v>705</v>
+        <v>698</v>
       </c>
       <c r="R127" s="52" t="s">
         <v>9</v>
@@ -15385,10 +15397,10 @@
         <v>9</v>
       </c>
       <c r="Z127" s="63" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="AA127" s="37" t="s">
-        <v>843</v>
+        <v>836</v>
       </c>
     </row>
     <row r="128" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -15402,10 +15414,10 @@
         <v>158</v>
       </c>
       <c r="D128" s="56" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E128" s="56" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="F128" s="56" t="s">
         <v>134</v>
@@ -15445,7 +15457,7 @@
         <v>188</v>
       </c>
       <c r="Q128" s="55" t="s">
-        <v>706</v>
+        <v>699</v>
       </c>
       <c r="R128" s="52" t="s">
         <v>9</v>
@@ -15476,10 +15488,10 @@
         <v>9</v>
       </c>
       <c r="Z128" s="63" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="AA128" s="37" t="s">
-        <v>844</v>
+        <v>837</v>
       </c>
     </row>
     <row r="129" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -15493,10 +15505,10 @@
         <v>158</v>
       </c>
       <c r="D129" s="56" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E129" s="56" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="F129" s="56" t="s">
         <v>135</v>
@@ -15536,7 +15548,7 @@
         <v>191</v>
       </c>
       <c r="Q129" s="55" t="s">
-        <v>707</v>
+        <v>700</v>
       </c>
       <c r="R129" s="52" t="s">
         <v>9</v>
@@ -15567,10 +15579,10 @@
         <v>9</v>
       </c>
       <c r="Z129" s="63" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="AA129" s="37" t="s">
-        <v>845</v>
+        <v>838</v>
       </c>
     </row>
     <row r="130" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -15584,10 +15596,10 @@
         <v>158</v>
       </c>
       <c r="D130" s="56" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E130" s="56" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="F130" s="56" t="s">
         <v>136</v>
@@ -15627,7 +15639,7 @@
         <v>213</v>
       </c>
       <c r="Q130" s="55" t="s">
-        <v>708</v>
+        <v>701</v>
       </c>
       <c r="R130" s="52" t="s">
         <v>9</v>
@@ -15658,10 +15670,10 @@
         <v>9</v>
       </c>
       <c r="Z130" s="63" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="AA130" s="37" t="s">
-        <v>846</v>
+        <v>839</v>
       </c>
     </row>
     <row r="131" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -15675,10 +15687,10 @@
         <v>158</v>
       </c>
       <c r="D131" s="56" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E131" s="56" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="F131" s="56" t="s">
         <v>137</v>
@@ -15718,7 +15730,7 @@
         <v>192</v>
       </c>
       <c r="Q131" s="55" t="s">
-        <v>709</v>
+        <v>702</v>
       </c>
       <c r="R131" s="52" t="s">
         <v>9</v>
@@ -15749,10 +15761,10 @@
         <v>9</v>
       </c>
       <c r="Z131" s="63" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="AA131" s="37" t="s">
-        <v>847</v>
+        <v>840</v>
       </c>
     </row>
     <row r="132" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -15766,10 +15778,10 @@
         <v>158</v>
       </c>
       <c r="D132" s="56" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E132" s="56" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="F132" s="56" t="s">
         <v>138</v>
@@ -15809,7 +15821,7 @@
         <v>212</v>
       </c>
       <c r="Q132" s="55" t="s">
-        <v>710</v>
+        <v>703</v>
       </c>
       <c r="R132" s="52" t="s">
         <v>9</v>
@@ -15840,10 +15852,10 @@
         <v>9</v>
       </c>
       <c r="Z132" s="63" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="AA132" s="37" t="s">
-        <v>848</v>
+        <v>841</v>
       </c>
     </row>
     <row r="133" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -15857,10 +15869,10 @@
         <v>158</v>
       </c>
       <c r="D133" s="56" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E133" s="56" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="F133" s="56" t="s">
         <v>139</v>
@@ -15900,7 +15912,7 @@
         <v>193</v>
       </c>
       <c r="Q133" s="55" t="s">
-        <v>711</v>
+        <v>704</v>
       </c>
       <c r="R133" s="52" t="s">
         <v>9</v>
@@ -15931,10 +15943,10 @@
         <v>9</v>
       </c>
       <c r="Z133" s="63" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="AA133" s="37" t="s">
-        <v>849</v>
+        <v>842</v>
       </c>
     </row>
     <row r="134" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -15948,10 +15960,10 @@
         <v>158</v>
       </c>
       <c r="D134" s="56" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E134" s="56" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="F134" s="56" t="s">
         <v>140</v>
@@ -15991,7 +16003,7 @@
         <v>194</v>
       </c>
       <c r="Q134" s="55" t="s">
-        <v>712</v>
+        <v>705</v>
       </c>
       <c r="R134" s="52" t="s">
         <v>9</v>
@@ -16022,10 +16034,10 @@
         <v>9</v>
       </c>
       <c r="Z134" s="63" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="AA134" s="37" t="s">
-        <v>850</v>
+        <v>843</v>
       </c>
     </row>
     <row r="135" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -16039,10 +16051,10 @@
         <v>158</v>
       </c>
       <c r="D135" s="56" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E135" s="56" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="F135" s="56" t="s">
         <v>141</v>
@@ -16082,7 +16094,7 @@
         <v>180</v>
       </c>
       <c r="Q135" s="55" t="s">
-        <v>713</v>
+        <v>706</v>
       </c>
       <c r="R135" s="52" t="s">
         <v>9</v>
@@ -16113,10 +16125,10 @@
         <v>9</v>
       </c>
       <c r="Z135" s="63" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="AA135" s="37" t="s">
-        <v>851</v>
+        <v>844</v>
       </c>
     </row>
     <row r="136" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -16130,10 +16142,10 @@
         <v>158</v>
       </c>
       <c r="D136" s="56" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E136" s="56" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="F136" s="56" t="s">
         <v>142</v>
@@ -16173,7 +16185,7 @@
         <v>195</v>
       </c>
       <c r="Q136" s="55" t="s">
-        <v>714</v>
+        <v>707</v>
       </c>
       <c r="R136" s="52" t="s">
         <v>9</v>
@@ -16204,10 +16216,10 @@
         <v>9</v>
       </c>
       <c r="Z136" s="63" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="AA136" s="37" t="s">
-        <v>852</v>
+        <v>845</v>
       </c>
     </row>
     <row r="137" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -16221,10 +16233,10 @@
         <v>158</v>
       </c>
       <c r="D137" s="56" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E137" s="56" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="F137" s="56" t="s">
         <v>143</v>
@@ -16264,7 +16276,7 @@
         <v>200</v>
       </c>
       <c r="Q137" s="55" t="s">
-        <v>715</v>
+        <v>708</v>
       </c>
       <c r="R137" s="52" t="s">
         <v>9</v>
@@ -16295,10 +16307,10 @@
         <v>9</v>
       </c>
       <c r="Z137" s="63" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="AA137" s="37" t="s">
-        <v>853</v>
+        <v>846</v>
       </c>
     </row>
     <row r="138" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -16312,10 +16324,10 @@
         <v>158</v>
       </c>
       <c r="D138" s="56" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E138" s="56" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="F138" s="56" t="s">
         <v>144</v>
@@ -16355,7 +16367,7 @@
         <v>201</v>
       </c>
       <c r="Q138" s="55" t="s">
-        <v>716</v>
+        <v>709</v>
       </c>
       <c r="R138" s="52" t="s">
         <v>9</v>
@@ -16386,10 +16398,10 @@
         <v>9</v>
       </c>
       <c r="Z138" s="63" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="AA138" s="37" t="s">
-        <v>854</v>
+        <v>847</v>
       </c>
     </row>
     <row r="139" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -16403,10 +16415,10 @@
         <v>158</v>
       </c>
       <c r="D139" s="56" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E139" s="56" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="F139" s="56" t="s">
         <v>145</v>
@@ -16446,7 +16458,7 @@
         <v>199</v>
       </c>
       <c r="Q139" s="55" t="s">
-        <v>717</v>
+        <v>710</v>
       </c>
       <c r="R139" s="52" t="s">
         <v>9</v>
@@ -16477,10 +16489,10 @@
         <v>9</v>
       </c>
       <c r="Z139" s="63" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="AA139" s="37" t="s">
-        <v>855</v>
+        <v>848</v>
       </c>
     </row>
     <row r="140" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -16494,10 +16506,10 @@
         <v>158</v>
       </c>
       <c r="D140" s="56" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E140" s="56" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="F140" s="56" t="s">
         <v>146</v>
@@ -16537,7 +16549,7 @@
         <v>198</v>
       </c>
       <c r="Q140" s="55" t="s">
-        <v>718</v>
+        <v>711</v>
       </c>
       <c r="R140" s="52" t="s">
         <v>9</v>
@@ -16568,10 +16580,10 @@
         <v>9</v>
       </c>
       <c r="Z140" s="63" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="AA140" s="37" t="s">
-        <v>856</v>
+        <v>849</v>
       </c>
     </row>
     <row r="141" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -16585,10 +16597,10 @@
         <v>158</v>
       </c>
       <c r="D141" s="56" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E141" s="56" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="F141" s="56" t="s">
         <v>147</v>
@@ -16628,7 +16640,7 @@
         <v>202</v>
       </c>
       <c r="Q141" s="55" t="s">
-        <v>719</v>
+        <v>712</v>
       </c>
       <c r="R141" s="52" t="s">
         <v>9</v>
@@ -16659,10 +16671,10 @@
         <v>9</v>
       </c>
       <c r="Z141" s="63" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="AA141" s="37" t="s">
-        <v>857</v>
+        <v>850</v>
       </c>
     </row>
     <row r="142" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -16676,10 +16688,10 @@
         <v>158</v>
       </c>
       <c r="D142" s="56" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E142" s="56" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="F142" s="56" t="s">
         <v>148</v>
@@ -16719,7 +16731,7 @@
         <v>196</v>
       </c>
       <c r="Q142" s="55" t="s">
-        <v>720</v>
+        <v>713</v>
       </c>
       <c r="R142" s="52" t="s">
         <v>9</v>
@@ -16750,10 +16762,10 @@
         <v>9</v>
       </c>
       <c r="Z142" s="63" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="AA142" s="37" t="s">
-        <v>858</v>
+        <v>851</v>
       </c>
     </row>
     <row r="143" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -16767,10 +16779,10 @@
         <v>158</v>
       </c>
       <c r="D143" s="56" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E143" s="56" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="F143" s="56" t="s">
         <v>149</v>
@@ -16810,7 +16822,7 @@
         <v>197</v>
       </c>
       <c r="Q143" s="55" t="s">
-        <v>721</v>
+        <v>714</v>
       </c>
       <c r="R143" s="52" t="s">
         <v>9</v>
@@ -16841,10 +16853,10 @@
         <v>9</v>
       </c>
       <c r="Z143" s="63" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="AA143" s="37" t="s">
-        <v>859</v>
+        <v>852</v>
       </c>
     </row>
     <row r="144" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -16858,10 +16870,10 @@
         <v>158</v>
       </c>
       <c r="D144" s="56" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E144" s="56" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="F144" s="56" t="s">
         <v>150</v>
@@ -16901,7 +16913,7 @@
         <v>203</v>
       </c>
       <c r="Q144" s="55" t="s">
-        <v>722</v>
+        <v>715</v>
       </c>
       <c r="R144" s="52" t="s">
         <v>9</v>
@@ -16932,10 +16944,10 @@
         <v>9</v>
       </c>
       <c r="Z144" s="63" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="AA144" s="37" t="s">
-        <v>860</v>
+        <v>853</v>
       </c>
     </row>
     <row r="145" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -16949,10 +16961,10 @@
         <v>158</v>
       </c>
       <c r="D145" s="56" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E145" s="56" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="F145" s="56" t="s">
         <v>151</v>
@@ -16992,7 +17004,7 @@
         <v>204</v>
       </c>
       <c r="Q145" s="55" t="s">
-        <v>723</v>
+        <v>716</v>
       </c>
       <c r="R145" s="52" t="s">
         <v>9</v>
@@ -17023,10 +17035,10 @@
         <v>9</v>
       </c>
       <c r="Z145" s="63" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="AA145" s="37" t="s">
-        <v>861</v>
+        <v>854</v>
       </c>
     </row>
     <row r="146" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -17040,10 +17052,10 @@
         <v>158</v>
       </c>
       <c r="D146" s="56" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E146" s="56" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="F146" s="56" t="s">
         <v>152</v>
@@ -17083,7 +17095,7 @@
         <v>205</v>
       </c>
       <c r="Q146" s="55" t="s">
-        <v>724</v>
+        <v>717</v>
       </c>
       <c r="R146" s="52" t="s">
         <v>9</v>
@@ -17114,10 +17126,10 @@
         <v>9</v>
       </c>
       <c r="Z146" s="63" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="AA146" s="37" t="s">
-        <v>862</v>
+        <v>855</v>
       </c>
     </row>
     <row r="147" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -17131,10 +17143,10 @@
         <v>158</v>
       </c>
       <c r="D147" s="56" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E147" s="56" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="F147" s="56" t="s">
         <v>153</v>
@@ -17174,7 +17186,7 @@
         <v>206</v>
       </c>
       <c r="Q147" s="55" t="s">
-        <v>725</v>
+        <v>718</v>
       </c>
       <c r="R147" s="52" t="s">
         <v>9</v>
@@ -17205,10 +17217,10 @@
         <v>9</v>
       </c>
       <c r="Z147" s="63" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="AA147" s="37" t="s">
-        <v>863</v>
+        <v>856</v>
       </c>
     </row>
     <row r="148" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -17222,10 +17234,10 @@
         <v>158</v>
       </c>
       <c r="D148" s="56" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E148" s="56" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="F148" s="56" t="s">
         <v>154</v>
@@ -17265,7 +17277,7 @@
         <v>207</v>
       </c>
       <c r="Q148" s="55" t="s">
-        <v>726</v>
+        <v>719</v>
       </c>
       <c r="R148" s="52" t="s">
         <v>9</v>
@@ -17296,10 +17308,10 @@
         <v>9</v>
       </c>
       <c r="Z148" s="63" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="AA148" s="37" t="s">
-        <v>864</v>
+        <v>857</v>
       </c>
     </row>
     <row r="149" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -17313,10 +17325,10 @@
         <v>158</v>
       </c>
       <c r="D149" s="56" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E149" s="56" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="F149" s="56" t="s">
         <v>155</v>
@@ -17356,7 +17368,7 @@
         <v>208</v>
       </c>
       <c r="Q149" s="55" t="s">
-        <v>727</v>
+        <v>720</v>
       </c>
       <c r="R149" s="52" t="s">
         <v>9</v>
@@ -17387,10 +17399,10 @@
         <v>9</v>
       </c>
       <c r="Z149" s="63" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="AA149" s="37" t="s">
-        <v>865</v>
+        <v>858</v>
       </c>
     </row>
     <row r="150" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -17404,10 +17416,10 @@
         <v>158</v>
       </c>
       <c r="D150" s="56" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E150" s="56" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="F150" s="56" t="s">
         <v>161</v>
@@ -17447,7 +17459,7 @@
         <v>209</v>
       </c>
       <c r="Q150" s="55" t="s">
-        <v>728</v>
+        <v>721</v>
       </c>
       <c r="R150" s="52" t="s">
         <v>9</v>
@@ -17478,10 +17490,10 @@
         <v>9</v>
       </c>
       <c r="Z150" s="63" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="AA150" s="37" t="s">
-        <v>866</v>
+        <v>859</v>
       </c>
     </row>
     <row r="151" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -17495,10 +17507,10 @@
         <v>158</v>
       </c>
       <c r="D151" s="56" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E151" s="56" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="F151" s="56" t="s">
         <v>156</v>
@@ -17538,7 +17550,7 @@
         <v>210</v>
       </c>
       <c r="Q151" s="55" t="s">
-        <v>729</v>
+        <v>722</v>
       </c>
       <c r="R151" s="52" t="s">
         <v>9</v>
@@ -17569,10 +17581,10 @@
         <v>9</v>
       </c>
       <c r="Z151" s="63" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="AA151" s="37" t="s">
-        <v>867</v>
+        <v>860</v>
       </c>
     </row>
     <row r="152" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -17586,10 +17598,10 @@
         <v>158</v>
       </c>
       <c r="D152" s="56" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E152" s="56" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="F152" s="56" t="s">
         <v>157</v>
@@ -17629,7 +17641,7 @@
         <v>211</v>
       </c>
       <c r="Q152" s="55" t="s">
-        <v>730</v>
+        <v>723</v>
       </c>
       <c r="R152" s="52" t="s">
         <v>9</v>
@@ -17660,10 +17672,10 @@
         <v>9</v>
       </c>
       <c r="Z152" s="63" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="AA152" s="37" t="s">
-        <v>868</v>
+        <v>861</v>
       </c>
     </row>
   </sheetData>
@@ -17893,8 +17905,9 @@
   <cols>
     <col min="1" max="1" width="2.53515625" style="43" customWidth="1"/>
     <col min="2" max="2" width="8.69140625" style="43" customWidth="1"/>
-    <col min="3" max="4" width="7.15234375" style="43" customWidth="1"/>
-    <col min="5" max="5" width="6.15234375" style="43" customWidth="1"/>
+    <col min="3" max="3" width="7.15234375" style="43" customWidth="1"/>
+    <col min="4" max="4" width="6.23046875" style="43" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.69140625" style="43" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="2.3828125" style="47" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="2.84375" style="47" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="2.3828125" style="47" bestFit="1" customWidth="1"/>
@@ -17902,11 +17915,11 @@
     <col min="10" max="10" width="4.53515625" style="47" customWidth="1"/>
     <col min="11" max="11" width="29.84375" style="47" customWidth="1"/>
     <col min="12" max="12" width="3.69140625" style="47" customWidth="1"/>
-    <col min="13" max="13" width="21.3046875" style="48" customWidth="1"/>
-    <col min="14" max="14" width="6.15234375" style="47" customWidth="1"/>
-    <col min="15" max="15" width="74.23046875" style="47" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="2.3828125" style="43" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="2.84375" style="43" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.3046875" style="48" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.23046875" style="47" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="59.4609375" style="47" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="6.4609375" style="43" customWidth="1"/>
+    <col min="17" max="17" width="58.53515625" style="43" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="2.3828125" style="43" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="2.84375" style="43" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="2.3828125" style="43" bestFit="1" customWidth="1"/>
@@ -18024,10 +18037,10 @@
         <v>2</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>894</v>
+        <v>887</v>
       </c>
       <c r="C2" s="44" t="s">
-        <v>584</v>
+        <v>577</v>
       </c>
       <c r="D2" s="32" t="s">
         <v>9</v>
@@ -18051,7 +18064,7 @@
         <v>16</v>
       </c>
       <c r="K2" s="18" t="s">
-        <v>545</v>
+        <v>540</v>
       </c>
       <c r="L2" s="30" t="s">
         <v>9</v>
@@ -18119,16 +18132,16 @@
         <v>3</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>893</v>
+        <v>886</v>
       </c>
       <c r="C3" s="44" t="s">
-        <v>584</v>
+        <v>577</v>
       </c>
       <c r="D3" s="32" t="s">
         <v>79</v>
       </c>
       <c r="E3" s="33" t="s">
-        <v>894</v>
+        <v>887</v>
       </c>
       <c r="F3" s="32" t="s">
         <v>9</v>
@@ -18146,7 +18159,7 @@
         <v>16</v>
       </c>
       <c r="K3" s="18" t="s">
-        <v>546</v>
+        <v>541</v>
       </c>
       <c r="L3" s="30" t="s">
         <v>9</v>
@@ -18217,13 +18230,13 @@
         <v>234</v>
       </c>
       <c r="C4" s="44" t="s">
-        <v>584</v>
+        <v>577</v>
       </c>
       <c r="D4" s="32" t="s">
         <v>79</v>
       </c>
       <c r="E4" s="33" t="s">
-        <v>893</v>
+        <v>886</v>
       </c>
       <c r="F4" s="32" t="s">
         <v>9</v>
@@ -18241,7 +18254,7 @@
         <v>16</v>
       </c>
       <c r="K4" s="18" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="L4" s="30" t="s">
         <v>9</v>
@@ -18312,13 +18325,13 @@
         <v>235</v>
       </c>
       <c r="C5" s="44" t="s">
-        <v>584</v>
+        <v>577</v>
       </c>
       <c r="D5" s="32" t="s">
         <v>79</v>
       </c>
       <c r="E5" s="33" t="s">
-        <v>893</v>
+        <v>886</v>
       </c>
       <c r="F5" s="32" t="s">
         <v>9</v>
@@ -18336,7 +18349,7 @@
         <v>16</v>
       </c>
       <c r="K5" s="18" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="L5" s="30" t="s">
         <v>9</v>
@@ -18407,13 +18420,13 @@
         <v>236</v>
       </c>
       <c r="C6" s="44" t="s">
-        <v>584</v>
+        <v>577</v>
       </c>
       <c r="D6" s="32" t="s">
         <v>79</v>
       </c>
       <c r="E6" s="33" t="s">
-        <v>893</v>
+        <v>886</v>
       </c>
       <c r="F6" s="32" t="s">
         <v>9</v>
@@ -18431,7 +18444,7 @@
         <v>16</v>
       </c>
       <c r="K6" s="18" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="L6" s="30" t="s">
         <v>9</v>
@@ -18502,13 +18515,13 @@
         <v>237</v>
       </c>
       <c r="C7" s="44" t="s">
-        <v>584</v>
+        <v>577</v>
       </c>
       <c r="D7" s="32" t="s">
         <v>79</v>
       </c>
       <c r="E7" s="33" t="s">
-        <v>893</v>
+        <v>886</v>
       </c>
       <c r="F7" s="32" t="s">
         <v>9</v>
@@ -18526,7 +18539,7 @@
         <v>16</v>
       </c>
       <c r="K7" s="18" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="L7" s="30" t="s">
         <v>9</v>
@@ -18594,16 +18607,16 @@
         <v>8</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="C8" s="44" t="s">
-        <v>584</v>
+        <v>577</v>
       </c>
       <c r="D8" s="32" t="s">
         <v>79</v>
       </c>
       <c r="E8" s="33" t="s">
-        <v>893</v>
+        <v>886</v>
       </c>
       <c r="F8" s="32" t="s">
         <v>9</v>
@@ -18621,7 +18634,7 @@
         <v>16</v>
       </c>
       <c r="K8" s="18" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="L8" s="30" t="s">
         <v>9</v>
@@ -18689,16 +18702,16 @@
         <v>9</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="C9" s="44" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="D9" s="32" t="s">
         <v>79</v>
       </c>
       <c r="E9" s="33" t="s">
-        <v>893</v>
+        <v>886</v>
       </c>
       <c r="F9" s="32" t="s">
         <v>9</v>
@@ -18716,19 +18729,19 @@
         <v>16</v>
       </c>
       <c r="K9" s="18" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="L9" s="30" t="s">
         <v>219</v>
       </c>
       <c r="M9" s="45" t="s">
-        <v>878</v>
+        <v>871</v>
       </c>
       <c r="N9" s="30" t="s">
         <v>231</v>
       </c>
       <c r="O9" s="18" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="P9" s="65" t="s">
         <v>9</v>
@@ -18787,13 +18800,13 @@
         <v>243</v>
       </c>
       <c r="C10" s="44" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="D10" s="32" t="s">
         <v>79</v>
       </c>
       <c r="E10" s="33" t="s">
-        <v>893</v>
+        <v>886</v>
       </c>
       <c r="F10" s="32" t="s">
         <v>9</v>
@@ -18811,19 +18824,19 @@
         <v>16</v>
       </c>
       <c r="K10" s="18" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="L10" s="30" t="s">
         <v>219</v>
       </c>
       <c r="M10" s="46" t="s">
-        <v>869</v>
+        <v>862</v>
       </c>
       <c r="N10" s="30" t="s">
         <v>231</v>
       </c>
       <c r="O10" s="18" t="s">
-        <v>550</v>
+        <v>543</v>
       </c>
       <c r="P10" s="65" t="s">
         <v>9</v>
@@ -18882,13 +18895,13 @@
         <v>244</v>
       </c>
       <c r="C11" s="44" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="D11" s="32" t="s">
         <v>79</v>
       </c>
       <c r="E11" s="33" t="s">
-        <v>893</v>
+        <v>886</v>
       </c>
       <c r="F11" s="32" t="s">
         <v>9</v>
@@ -18906,13 +18919,13 @@
         <v>16</v>
       </c>
       <c r="K11" s="18" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="L11" s="30" t="s">
         <v>219</v>
       </c>
       <c r="M11" s="46" t="s">
-        <v>870</v>
+        <v>863</v>
       </c>
       <c r="N11" s="30" t="s">
         <v>231</v>
@@ -18977,13 +18990,13 @@
         <v>232</v>
       </c>
       <c r="C12" s="44" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="D12" s="32" t="s">
         <v>79</v>
       </c>
       <c r="E12" s="33" t="s">
-        <v>893</v>
+        <v>886</v>
       </c>
       <c r="F12" s="32" t="s">
         <v>9</v>
@@ -19001,19 +19014,19 @@
         <v>16</v>
       </c>
       <c r="K12" s="18" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="L12" s="30" t="s">
         <v>219</v>
       </c>
       <c r="M12" s="45" t="s">
-        <v>890</v>
+        <v>883</v>
       </c>
       <c r="N12" s="30" t="s">
         <v>231</v>
       </c>
       <c r="O12" s="18" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="P12" s="65" t="s">
         <v>9</v>
@@ -19072,13 +19085,13 @@
         <v>233</v>
       </c>
       <c r="C13" s="44" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="D13" s="32" t="s">
         <v>79</v>
       </c>
       <c r="E13" s="33" t="s">
-        <v>893</v>
+        <v>886</v>
       </c>
       <c r="F13" s="32" t="s">
         <v>9</v>
@@ -19096,19 +19109,19 @@
         <v>16</v>
       </c>
       <c r="K13" s="18" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="L13" s="30" t="s">
         <v>219</v>
       </c>
       <c r="M13" s="45" t="s">
-        <v>891</v>
+        <v>884</v>
       </c>
       <c r="N13" s="30" t="s">
         <v>231</v>
       </c>
       <c r="O13" s="18" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="P13" s="65" t="s">
         <v>9</v>
@@ -19167,13 +19180,13 @@
         <v>217</v>
       </c>
       <c r="C14" s="44" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="D14" s="32" t="s">
         <v>79</v>
       </c>
       <c r="E14" s="33" t="s">
-        <v>893</v>
+        <v>886</v>
       </c>
       <c r="F14" s="32" t="s">
         <v>9</v>
@@ -19191,19 +19204,19 @@
         <v>16</v>
       </c>
       <c r="K14" s="18" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="L14" s="30" t="s">
         <v>219</v>
       </c>
       <c r="M14" s="46" t="s">
-        <v>889</v>
+        <v>882</v>
       </c>
       <c r="N14" s="30" t="s">
         <v>231</v>
       </c>
       <c r="O14" s="18" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="P14" s="65" t="s">
         <v>9</v>
@@ -19259,16 +19272,16 @@
         <v>15</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>239</v>
+        <v>254</v>
       </c>
       <c r="C15" s="44" t="s">
-        <v>569</v>
+        <v>335</v>
       </c>
       <c r="D15" s="32" t="s">
         <v>79</v>
       </c>
       <c r="E15" s="33" t="s">
-        <v>893</v>
+        <v>886</v>
       </c>
       <c r="F15" s="32" t="s">
         <v>9</v>
@@ -19286,19 +19299,19 @@
         <v>16</v>
       </c>
       <c r="K15" s="18" t="s">
-        <v>240</v>
+        <v>270</v>
       </c>
       <c r="L15" s="30" t="s">
         <v>219</v>
       </c>
       <c r="M15" s="45" t="s">
-        <v>892</v>
+        <v>870</v>
       </c>
       <c r="N15" s="30" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="O15" s="18" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="P15" s="65" t="s">
         <v>9</v>
@@ -19354,16 +19367,16 @@
         <v>16</v>
       </c>
       <c r="B16" s="17" t="s">
-        <v>258</v>
+        <v>220</v>
       </c>
       <c r="C16" s="44" t="s">
-        <v>339</v>
+        <v>316</v>
       </c>
       <c r="D16" s="32" t="s">
         <v>79</v>
       </c>
       <c r="E16" s="33" t="s">
-        <v>893</v>
+        <v>886</v>
       </c>
       <c r="F16" s="32" t="s">
         <v>9</v>
@@ -19381,19 +19394,19 @@
         <v>16</v>
       </c>
       <c r="K16" s="18" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="L16" s="30" t="s">
         <v>219</v>
       </c>
-      <c r="M16" s="45" t="s">
-        <v>877</v>
+      <c r="M16" s="46" t="s">
+        <v>875</v>
       </c>
       <c r="N16" s="30" t="s">
         <v>231</v>
       </c>
       <c r="O16" s="18" t="s">
-        <v>259</v>
+        <v>542</v>
       </c>
       <c r="P16" s="65" t="s">
         <v>9</v>
@@ -19448,17 +19461,17 @@
       <c r="A17" s="16">
         <v>17</v>
       </c>
-      <c r="B17" s="49" t="s">
-        <v>540</v>
+      <c r="B17" s="17" t="s">
+        <v>261</v>
       </c>
       <c r="C17" s="44" t="s">
-        <v>358</v>
+        <v>316</v>
       </c>
       <c r="D17" s="32" t="s">
         <v>79</v>
       </c>
       <c r="E17" s="33" t="s">
-        <v>893</v>
+        <v>886</v>
       </c>
       <c r="F17" s="32" t="s">
         <v>9</v>
@@ -19476,19 +19489,19 @@
         <v>16</v>
       </c>
       <c r="K17" s="18" t="s">
-        <v>543</v>
+        <v>267</v>
       </c>
       <c r="L17" s="30" t="s">
         <v>219</v>
       </c>
       <c r="M17" s="46" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="N17" s="30" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="O17" s="18" t="s">
-        <v>548</v>
+        <v>262</v>
       </c>
       <c r="P17" s="65" t="s">
         <v>9</v>
@@ -19543,17 +19556,17 @@
       <c r="A18" s="16">
         <v>18</v>
       </c>
-      <c r="B18" s="49" t="s">
-        <v>541</v>
+      <c r="B18" s="17" t="s">
+        <v>257</v>
       </c>
       <c r="C18" s="44" t="s">
-        <v>358</v>
+        <v>316</v>
       </c>
       <c r="D18" s="32" t="s">
         <v>79</v>
       </c>
       <c r="E18" s="33" t="s">
-        <v>893</v>
+        <v>886</v>
       </c>
       <c r="F18" s="32" t="s">
         <v>9</v>
@@ -19571,19 +19584,19 @@
         <v>16</v>
       </c>
       <c r="K18" s="18" t="s">
-        <v>551</v>
+        <v>268</v>
       </c>
       <c r="L18" s="30" t="s">
         <v>219</v>
       </c>
       <c r="M18" s="46" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="N18" s="30" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="O18" s="18" t="s">
-        <v>547</v>
+        <v>258</v>
       </c>
       <c r="P18" s="65" t="s">
         <v>9</v>
@@ -19638,17 +19651,17 @@
       <c r="A19" s="16">
         <v>19</v>
       </c>
-      <c r="B19" s="49" t="s">
-        <v>544</v>
+      <c r="B19" s="17" t="s">
+        <v>259</v>
       </c>
       <c r="C19" s="44" t="s">
-        <v>358</v>
+        <v>316</v>
       </c>
       <c r="D19" s="32" t="s">
         <v>79</v>
       </c>
       <c r="E19" s="33" t="s">
-        <v>893</v>
+        <v>886</v>
       </c>
       <c r="F19" s="32" t="s">
         <v>9</v>
@@ -19666,19 +19679,19 @@
         <v>16</v>
       </c>
       <c r="K19" s="18" t="s">
-        <v>542</v>
+        <v>269</v>
       </c>
       <c r="L19" s="30" t="s">
         <v>219</v>
       </c>
       <c r="M19" s="46" t="s">
-        <v>881</v>
+        <v>878</v>
       </c>
       <c r="N19" s="30" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="O19" s="18" t="s">
-        <v>548</v>
+        <v>260</v>
       </c>
       <c r="P19" s="65" t="s">
         <v>9</v>
@@ -19734,16 +19747,16 @@
         <v>20</v>
       </c>
       <c r="B20" s="17" t="s">
-        <v>220</v>
+        <v>238</v>
       </c>
       <c r="C20" s="44" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="D20" s="32" t="s">
         <v>79</v>
       </c>
       <c r="E20" s="33" t="s">
-        <v>893</v>
+        <v>886</v>
       </c>
       <c r="F20" s="32" t="s">
         <v>9</v>
@@ -19761,19 +19774,19 @@
         <v>16</v>
       </c>
       <c r="K20" s="18" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="L20" s="30" t="s">
         <v>219</v>
       </c>
-      <c r="M20" s="46" t="s">
-        <v>882</v>
+      <c r="M20" s="45" t="s">
+        <v>879</v>
       </c>
       <c r="N20" s="30" t="s">
         <v>231</v>
       </c>
       <c r="O20" s="18" t="s">
-        <v>549</v>
+        <v>263</v>
       </c>
       <c r="P20" s="65" t="s">
         <v>9</v>
@@ -19829,16 +19842,16 @@
         <v>21</v>
       </c>
       <c r="B21" s="17" t="s">
-        <v>265</v>
+        <v>242</v>
       </c>
       <c r="C21" s="44" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="D21" s="32" t="s">
         <v>79</v>
       </c>
       <c r="E21" s="33" t="s">
-        <v>893</v>
+        <v>886</v>
       </c>
       <c r="F21" s="32" t="s">
         <v>9</v>
@@ -19856,19 +19869,19 @@
         <v>16</v>
       </c>
       <c r="K21" s="18" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="L21" s="30" t="s">
         <v>219</v>
       </c>
-      <c r="M21" s="46" t="s">
-        <v>883</v>
+      <c r="M21" s="45" t="s">
+        <v>880</v>
       </c>
       <c r="N21" s="30" t="s">
         <v>231</v>
       </c>
       <c r="O21" s="18" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="P21" s="65" t="s">
         <v>9</v>
@@ -19924,16 +19937,16 @@
         <v>22</v>
       </c>
       <c r="B22" s="17" t="s">
-        <v>261</v>
+        <v>216</v>
       </c>
       <c r="C22" s="44" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="D22" s="32" t="s">
         <v>79</v>
       </c>
       <c r="E22" s="33" t="s">
-        <v>893</v>
+        <v>886</v>
       </c>
       <c r="F22" s="32" t="s">
         <v>9</v>
@@ -19957,19 +19970,19 @@
         <v>219</v>
       </c>
       <c r="M22" s="46" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="N22" s="30" t="s">
         <v>231</v>
       </c>
       <c r="O22" s="18" t="s">
-        <v>262</v>
-      </c>
-      <c r="P22" s="65" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q22" s="66" t="s">
-        <v>9</v>
+        <v>248</v>
+      </c>
+      <c r="P22" s="30" t="s">
+        <v>241</v>
+      </c>
+      <c r="Q22" s="18" t="s">
+        <v>898</v>
       </c>
       <c r="R22" s="65" t="s">
         <v>9</v>
@@ -20018,17 +20031,17 @@
       <c r="A23" s="16">
         <v>23</v>
       </c>
-      <c r="B23" s="17" t="s">
-        <v>263</v>
+      <c r="B23" s="49" t="s">
+        <v>535</v>
       </c>
       <c r="C23" s="44" t="s">
-        <v>320</v>
+        <v>354</v>
       </c>
       <c r="D23" s="32" t="s">
         <v>79</v>
       </c>
       <c r="E23" s="33" t="s">
-        <v>893</v>
+        <v>886</v>
       </c>
       <c r="F23" s="32" t="s">
         <v>9</v>
@@ -20046,25 +20059,25 @@
         <v>16</v>
       </c>
       <c r="K23" s="18" t="s">
-        <v>273</v>
+        <v>538</v>
       </c>
       <c r="L23" s="30" t="s">
         <v>219</v>
       </c>
       <c r="M23" s="46" t="s">
-        <v>885</v>
+        <v>872</v>
       </c>
       <c r="N23" s="30" t="s">
         <v>231</v>
       </c>
       <c r="O23" s="18" t="s">
-        <v>264</v>
-      </c>
-      <c r="P23" s="65" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q23" s="66" t="s">
-        <v>9</v>
+        <v>894</v>
+      </c>
+      <c r="P23" s="30" t="s">
+        <v>241</v>
+      </c>
+      <c r="Q23" s="18" t="s">
+        <v>888</v>
       </c>
       <c r="R23" s="65" t="s">
         <v>9</v>
@@ -20113,17 +20126,17 @@
       <c r="A24" s="16">
         <v>24</v>
       </c>
-      <c r="B24" s="17" t="s">
-        <v>238</v>
+      <c r="B24" s="49" t="s">
+        <v>536</v>
       </c>
       <c r="C24" s="44" t="s">
-        <v>320</v>
+        <v>354</v>
       </c>
       <c r="D24" s="32" t="s">
         <v>79</v>
       </c>
       <c r="E24" s="33" t="s">
-        <v>893</v>
+        <v>886</v>
       </c>
       <c r="F24" s="32" t="s">
         <v>9</v>
@@ -20141,25 +20154,25 @@
         <v>16</v>
       </c>
       <c r="K24" s="18" t="s">
-        <v>280</v>
+        <v>544</v>
       </c>
       <c r="L24" s="30" t="s">
         <v>219</v>
       </c>
-      <c r="M24" s="45" t="s">
-        <v>886</v>
+      <c r="M24" s="46" t="s">
+        <v>873</v>
       </c>
       <c r="N24" s="30" t="s">
         <v>231</v>
       </c>
       <c r="O24" s="18" t="s">
-        <v>267</v>
-      </c>
-      <c r="P24" s="65" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q24" s="66" t="s">
-        <v>9</v>
+        <v>894</v>
+      </c>
+      <c r="P24" s="30" t="s">
+        <v>241</v>
+      </c>
+      <c r="Q24" s="18" t="s">
+        <v>889</v>
       </c>
       <c r="R24" s="65" t="s">
         <v>9</v>
@@ -20208,17 +20221,17 @@
       <c r="A25" s="16">
         <v>25</v>
       </c>
-      <c r="B25" s="17" t="s">
-        <v>242</v>
+      <c r="B25" s="49" t="s">
+        <v>539</v>
       </c>
       <c r="C25" s="44" t="s">
-        <v>320</v>
+        <v>354</v>
       </c>
       <c r="D25" s="32" t="s">
         <v>79</v>
       </c>
       <c r="E25" s="33" t="s">
-        <v>893</v>
+        <v>886</v>
       </c>
       <c r="F25" s="32" t="s">
         <v>9</v>
@@ -20236,25 +20249,25 @@
         <v>16</v>
       </c>
       <c r="K25" s="18" t="s">
-        <v>280</v>
+        <v>537</v>
       </c>
       <c r="L25" s="30" t="s">
         <v>219</v>
       </c>
-      <c r="M25" s="45" t="s">
-        <v>887</v>
+      <c r="M25" s="46" t="s">
+        <v>874</v>
       </c>
       <c r="N25" s="30" t="s">
         <v>231</v>
       </c>
       <c r="O25" s="18" t="s">
-        <v>267</v>
-      </c>
-      <c r="P25" s="65" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q25" s="66" t="s">
-        <v>9</v>
+        <v>894</v>
+      </c>
+      <c r="P25" s="30" t="s">
+        <v>241</v>
+      </c>
+      <c r="Q25" s="18" t="s">
+        <v>888</v>
       </c>
       <c r="R25" s="65" t="s">
         <v>9</v>
@@ -20303,17 +20316,17 @@
       <c r="A26" s="16">
         <v>26</v>
       </c>
-      <c r="B26" s="17" t="s">
-        <v>216</v>
+      <c r="B26" s="49" t="s">
+        <v>357</v>
       </c>
       <c r="C26" s="44" t="s">
-        <v>320</v>
+        <v>296</v>
       </c>
       <c r="D26" s="32" t="s">
         <v>79</v>
       </c>
       <c r="E26" s="33" t="s">
-        <v>893</v>
+        <v>886</v>
       </c>
       <c r="F26" s="32" t="s">
         <v>9</v>
@@ -20331,25 +20344,25 @@
         <v>16</v>
       </c>
       <c r="K26" s="18" t="s">
-        <v>276</v>
+        <v>359</v>
       </c>
       <c r="L26" s="30" t="s">
         <v>219</v>
       </c>
       <c r="M26" s="46" t="s">
-        <v>888</v>
+        <v>867</v>
       </c>
       <c r="N26" s="30" t="s">
         <v>231</v>
       </c>
       <c r="O26" s="18" t="s">
-        <v>249</v>
-      </c>
-      <c r="P26" s="65" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q26" s="66" t="s">
-        <v>9</v>
+        <v>895</v>
+      </c>
+      <c r="P26" s="30" t="s">
+        <v>241</v>
+      </c>
+      <c r="Q26" s="18" t="s">
+        <v>890</v>
       </c>
       <c r="R26" s="65" t="s">
         <v>9</v>
@@ -20399,16 +20412,16 @@
         <v>27</v>
       </c>
       <c r="B27" s="49" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C27" s="44" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="D27" s="32" t="s">
         <v>79</v>
       </c>
       <c r="E27" s="33" t="s">
-        <v>893</v>
+        <v>886</v>
       </c>
       <c r="F27" s="32" t="s">
         <v>9</v>
@@ -20426,25 +20439,25 @@
         <v>16</v>
       </c>
       <c r="K27" s="18" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="L27" s="30" t="s">
         <v>219</v>
       </c>
       <c r="M27" s="46" t="s">
-        <v>874</v>
+        <v>868</v>
       </c>
       <c r="N27" s="30" t="s">
+        <v>231</v>
+      </c>
+      <c r="O27" s="18" t="s">
+        <v>895</v>
+      </c>
+      <c r="P27" s="30" t="s">
         <v>241</v>
       </c>
-      <c r="O27" s="18" t="s">
-        <v>364</v>
-      </c>
-      <c r="P27" s="65" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q27" s="66" t="s">
-        <v>9</v>
+      <c r="Q27" s="18" t="s">
+        <v>890</v>
       </c>
       <c r="R27" s="65" t="s">
         <v>9</v>
@@ -20494,16 +20507,16 @@
         <v>28</v>
       </c>
       <c r="B28" s="49" t="s">
-        <v>365</v>
+        <v>358</v>
       </c>
       <c r="C28" s="44" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="D28" s="32" t="s">
         <v>79</v>
       </c>
       <c r="E28" s="33" t="s">
-        <v>893</v>
+        <v>886</v>
       </c>
       <c r="F28" s="32" t="s">
         <v>9</v>
@@ -20521,25 +20534,25 @@
         <v>16</v>
       </c>
       <c r="K28" s="18" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="L28" s="30" t="s">
         <v>219</v>
       </c>
       <c r="M28" s="46" t="s">
-        <v>875</v>
+        <v>869</v>
       </c>
       <c r="N28" s="30" t="s">
+        <v>231</v>
+      </c>
+      <c r="O28" s="18" t="s">
+        <v>895</v>
+      </c>
+      <c r="P28" s="30" t="s">
         <v>241</v>
       </c>
-      <c r="O28" s="18" t="s">
-        <v>364</v>
-      </c>
-      <c r="P28" s="65" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q28" s="66" t="s">
-        <v>9</v>
+      <c r="Q28" s="18" t="s">
+        <v>890</v>
       </c>
       <c r="R28" s="65" t="s">
         <v>9</v>
@@ -20589,16 +20602,16 @@
         <v>29</v>
       </c>
       <c r="B29" s="49" t="s">
-        <v>362</v>
+        <v>246</v>
       </c>
       <c r="C29" s="44" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D29" s="32" t="s">
         <v>79</v>
       </c>
       <c r="E29" s="33" t="s">
-        <v>893</v>
+        <v>886</v>
       </c>
       <c r="F29" s="32" t="s">
         <v>9</v>
@@ -20616,25 +20629,25 @@
         <v>16</v>
       </c>
       <c r="K29" s="18" t="s">
-        <v>363</v>
+        <v>278</v>
       </c>
       <c r="L29" s="30" t="s">
         <v>219</v>
       </c>
       <c r="M29" s="46" t="s">
-        <v>876</v>
+        <v>864</v>
       </c>
       <c r="N29" s="30" t="s">
+        <v>231</v>
+      </c>
+      <c r="O29" s="18" t="s">
+        <v>896</v>
+      </c>
+      <c r="P29" s="30" t="s">
         <v>241</v>
       </c>
-      <c r="O29" s="18" t="s">
-        <v>364</v>
-      </c>
-      <c r="P29" s="65" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q29" s="66" t="s">
-        <v>9</v>
+      <c r="Q29" s="18" t="s">
+        <v>891</v>
       </c>
       <c r="R29" s="65" t="s">
         <v>9</v>
@@ -20684,16 +20697,16 @@
         <v>30</v>
       </c>
       <c r="B30" s="49" t="s">
-        <v>246</v>
+        <v>277</v>
       </c>
       <c r="C30" s="44" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="D30" s="32" t="s">
         <v>79</v>
       </c>
       <c r="E30" s="33" t="s">
-        <v>893</v>
+        <v>886</v>
       </c>
       <c r="F30" s="32" t="s">
         <v>9</v>
@@ -20711,25 +20724,25 @@
         <v>16</v>
       </c>
       <c r="K30" s="18" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="L30" s="30" t="s">
         <v>219</v>
       </c>
       <c r="M30" s="46" t="s">
-        <v>871</v>
+        <v>865</v>
       </c>
       <c r="N30" s="30" t="s">
+        <v>231</v>
+      </c>
+      <c r="O30" s="18" t="s">
+        <v>897</v>
+      </c>
+      <c r="P30" s="30" t="s">
         <v>241</v>
       </c>
-      <c r="O30" s="18" t="s">
-        <v>248</v>
-      </c>
-      <c r="P30" s="65" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q30" s="66" t="s">
-        <v>9</v>
+      <c r="Q30" s="18" t="s">
+        <v>892</v>
       </c>
       <c r="R30" s="65" t="s">
         <v>9</v>
@@ -20779,16 +20792,16 @@
         <v>31</v>
       </c>
       <c r="B31" s="49" t="s">
-        <v>281</v>
+        <v>247</v>
       </c>
       <c r="C31" s="44" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="D31" s="32" t="s">
         <v>79</v>
       </c>
       <c r="E31" s="33" t="s">
-        <v>893</v>
+        <v>886</v>
       </c>
       <c r="F31" s="32" t="s">
         <v>9</v>
@@ -20806,25 +20819,25 @@
         <v>16</v>
       </c>
       <c r="K31" s="18" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="L31" s="30" t="s">
         <v>219</v>
       </c>
       <c r="M31" s="46" t="s">
-        <v>872</v>
+        <v>866</v>
       </c>
       <c r="N31" s="30" t="s">
+        <v>231</v>
+      </c>
+      <c r="O31" s="18" t="s">
+        <v>896</v>
+      </c>
+      <c r="P31" s="30" t="s">
         <v>241</v>
       </c>
-      <c r="O31" s="18" t="s">
-        <v>254</v>
-      </c>
-      <c r="P31" s="65" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q31" s="66" t="s">
-        <v>9</v>
+      <c r="Q31" s="18" t="s">
+        <v>893</v>
       </c>
       <c r="R31" s="65" t="s">
         <v>9</v>
@@ -20873,17 +20886,17 @@
       <c r="A32" s="16">
         <v>32</v>
       </c>
-      <c r="B32" s="49" t="s">
-        <v>247</v>
+      <c r="B32" s="17" t="s">
+        <v>239</v>
       </c>
       <c r="C32" s="44" t="s">
-        <v>305</v>
+        <v>562</v>
       </c>
       <c r="D32" s="32" t="s">
         <v>79</v>
       </c>
       <c r="E32" s="33" t="s">
-        <v>893</v>
+        <v>886</v>
       </c>
       <c r="F32" s="32" t="s">
         <v>9</v>
@@ -20901,19 +20914,19 @@
         <v>16</v>
       </c>
       <c r="K32" s="18" t="s">
-        <v>282</v>
+        <v>240</v>
       </c>
       <c r="L32" s="30" t="s">
         <v>219</v>
       </c>
-      <c r="M32" s="46" t="s">
-        <v>873</v>
+      <c r="M32" s="45" t="s">
+        <v>885</v>
       </c>
       <c r="N32" s="30" t="s">
-        <v>241</v>
+        <v>9</v>
       </c>
       <c r="O32" s="18" t="s">
-        <v>255</v>
+        <v>9</v>
       </c>
       <c r="P32" s="65" t="s">
         <v>9</v>
@@ -20965,16 +20978,16 @@
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A9:AE37">
-    <sortCondition ref="C1:C37"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A9:AE31">
+    <sortCondition ref="N1:N31"/>
   </sortState>
   <phoneticPr fontId="9" type="noConversion"/>
   <conditionalFormatting sqref="B1:B1048576">
     <cfRule type="duplicateValues" dxfId="2" priority="165"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B29:B32 B24:B25 B1:B17">
-    <cfRule type="duplicateValues" dxfId="1" priority="549"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="550"/>
+  <conditionalFormatting sqref="B30:B32 B1 B5:B23">
+    <cfRule type="duplicateValues" dxfId="1" priority="554"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="555"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/Versão5/FABR/Ontologia_FABRI.xlsx
+++ b/Versão5/FABR/Ontologia_FABRI.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\FABR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF14FF65-3F6C-4CBC-B32D-1F065DF5CE11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE6B26F3-317C-4048-AAD8-BD3F2507CCE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="527" activeTab="1" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="527" activeTab="1" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="31" r:id="rId1"/>
@@ -730,9 +730,6 @@
     <t>Segmento.Geral</t>
   </si>
   <si>
-    <t>website</t>
-  </si>
-  <si>
     <t>SG.Canalização</t>
   </si>
   <si>
@@ -2731,9 +2728,6 @@
     <t>"Tubos de alimentação e esgoto em PVC, conexões, ralos e acessórios para hidráulica predial."</t>
   </si>
   <si>
-    <t>Conceito</t>
-  </si>
-  <si>
     <t>Contêineres</t>
   </si>
   <si>
@@ -2741,6 +2735,12 @@
   </si>
   <si>
     <t>[ 5I ]</t>
+  </si>
+  <si>
+    <t>endereço.website</t>
+  </si>
+  <si>
+    <t>Conceitos</t>
   </si>
 </sst>
 </file>
@@ -3217,63 +3217,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="12">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="11">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -3331,6 +3275,54 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -3649,15 +3641,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1124724F-B8C4-4B86-9028-743FC73CDDB0}">
   <dimension ref="A1:C24"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="10.5" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="10.5" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.28515625" style="13" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="53.7109375" style="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="3.42578125" style="37" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="9.140625" style="13"/>
+    <col min="1" max="1" width="10.3046875" style="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="53.69140625" style="13" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="3.3828125" style="37" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.15234375" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="10" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" s="10" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
@@ -3668,7 +3660,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>17</v>
       </c>
@@ -3679,7 +3671,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>18</v>
       </c>
@@ -3690,7 +3682,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>7</v>
       </c>
@@ -3701,7 +3693,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>6</v>
       </c>
@@ -3713,7 +3705,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>8</v>
       </c>
@@ -3725,7 +3717,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>4</v>
       </c>
@@ -3736,7 +3728,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="8" spans="1:3" s="34" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" s="34" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="2" t="s">
         <v>5</v>
       </c>
@@ -3747,7 +3739,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>20</v>
       </c>
@@ -3758,7 +3750,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>22</v>
       </c>
@@ -3769,7 +3761,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>0</v>
       </c>
@@ -3780,7 +3772,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>1</v>
       </c>
@@ -3791,7 +3783,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>23</v>
       </c>
@@ -3802,7 +3794,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>24</v>
       </c>
@@ -3813,7 +3805,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>25</v>
       </c>
@@ -3824,7 +3816,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>26</v>
       </c>
@@ -3835,7 +3827,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>10</v>
       </c>
@@ -3846,19 +3838,19 @@
         <v>87</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>27</v>
       </c>
       <c r="B18" s="5">
         <f ca="1">NOW()</f>
-        <v>46216.379713657407</v>
+        <v>46243.520779282408</v>
       </c>
       <c r="C18" s="36" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>28</v>
       </c>
@@ -3869,7 +3861,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>29</v>
       </c>
@@ -3880,7 +3872,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>11</v>
       </c>
@@ -3891,7 +3883,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:3" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
         <v>32</v>
       </c>
@@ -3902,7 +3894,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:3" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="4" t="s">
         <v>33</v>
       </c>
@@ -3914,7 +3906,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="24" spans="1:3" s="34" customFormat="1" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" s="34" customFormat="1" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="4" t="s">
         <v>85</v>
       </c>
@@ -3934,35 +3926,35 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{348BB721-29D9-4DD8-81B8-03CCB3CE3CCF}">
   <dimension ref="A1:AA152"/>
-  <sheetFormatPr defaultColWidth="2.7109375" defaultRowHeight="6.6" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="2.69140625" defaultRowHeight="6.65" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="3.140625" style="60" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.7109375" style="31" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.140625" style="31" customWidth="1"/>
-    <col min="4" max="4" width="13.85546875" style="31" customWidth="1"/>
+    <col min="1" max="1" width="3.15234375" style="60" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.69140625" style="31" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.15234375" style="31" customWidth="1"/>
+    <col min="4" max="4" width="13.84375" style="31" customWidth="1"/>
     <col min="5" max="5" width="14" style="31" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.42578125" style="31" customWidth="1"/>
-    <col min="7" max="11" width="10.140625" style="31" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.140625" style="31" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="16.140625" style="31" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.3828125" style="31" customWidth="1"/>
+    <col min="7" max="11" width="10.15234375" style="31" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.15234375" style="31" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.15234375" style="31" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="14" style="31" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="19.42578125" style="31" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="64.5703125" style="31" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="54.28515625" style="31" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="4.28515625" style="31" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="8.140625" style="31" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="16.140625" style="31" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="19.3828125" style="31" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="64.53515625" style="31" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="54.3046875" style="31" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="4.3046875" style="31" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.15234375" style="31" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="16.15234375" style="31" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="14" style="31" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="8.5703125" style="31" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="8.7109375" style="31" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="8.53515625" style="31" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="8.69140625" style="31" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="6" style="31" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="4.42578125" style="31" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="15.140625" style="31" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="67.7109375" style="31" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="2.7109375" style="31"/>
+    <col min="25" max="25" width="4.3828125" style="31" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="15.15234375" style="31" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="67.69140625" style="31" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="2.69140625" style="31"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:27" ht="34" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="59">
         <v>0</v>
       </c>
@@ -4045,21 +4037,21 @@
         <v>83</v>
       </c>
     </row>
-    <row r="2" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="52">
         <v>2</v>
       </c>
       <c r="B2" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C2" s="47" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="D2" s="47" t="s">
         <v>159</v>
       </c>
       <c r="E2" s="48" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="F2" s="48" t="s">
         <v>93</v>
@@ -4096,10 +4088,10 @@
         <v>Contêiner</v>
       </c>
       <c r="P2" s="33" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="Q2" s="33" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="R2" s="33" t="s">
         <v>9</v>
@@ -4130,31 +4122,31 @@
         <v>9</v>
       </c>
       <c r="Z2" s="33" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="AA2" s="33" t="str">
         <f t="shared" ref="AA2:AA6" si="4">_xlfn.TRANSLATE(P2,"pt","en")</f>
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Project Definition.</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="52">
         <v>3</v>
       </c>
       <c r="B3" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C3" s="47" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="D3" s="47" t="s">
         <v>159</v>
       </c>
       <c r="E3" s="48" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="F3" s="48" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="G3" s="56" t="s">
         <v>9</v>
@@ -4188,10 +4180,10 @@
         <v>Requisito Espacial</v>
       </c>
       <c r="P3" s="33" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="Q3" s="33" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="R3" s="33" t="s">
         <v>9</v>
@@ -4229,24 +4221,24 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Spatial Requirements for the Project.</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="52">
         <v>4</v>
       </c>
       <c r="B4" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C4" s="47" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="D4" s="47" t="s">
         <v>159</v>
       </c>
       <c r="E4" s="48" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="F4" s="48" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="G4" s="56" t="s">
         <v>9</v>
@@ -4280,10 +4272,10 @@
         <v>Requisito Mobiliário</v>
       </c>
       <c r="P4" s="33" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="Q4" s="33" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="R4" s="33" t="s">
         <v>9</v>
@@ -4321,24 +4313,24 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Furniture Requirements for the Project.</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="52">
         <v>5</v>
       </c>
       <c r="B5" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C5" s="47" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="D5" s="47" t="s">
         <v>159</v>
       </c>
       <c r="E5" s="48" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="F5" s="48" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="G5" s="56" t="s">
         <v>9</v>
@@ -4372,10 +4364,10 @@
         <v>Requisito Equipamento</v>
       </c>
       <c r="P5" s="33" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="Q5" s="33" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="R5" s="33" t="s">
         <v>9</v>
@@ -4413,24 +4405,24 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Equipment Requirements for the Project.</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="52">
         <v>6</v>
       </c>
       <c r="B6" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C6" s="47" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="D6" s="47" t="s">
         <v>159</v>
       </c>
       <c r="E6" s="48" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="F6" s="48" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="G6" s="56" t="s">
         <v>9</v>
@@ -4464,10 +4456,10 @@
         <v>Requisito Sistemas</v>
       </c>
       <c r="P6" s="33" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="Q6" s="33" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="R6" s="33" t="s">
         <v>9</v>
@@ -4505,24 +4497,24 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Building Systems Requirements for the Project.</v>
       </c>
     </row>
-    <row r="7" spans="1:27" s="42" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:27" s="42" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="52">
         <v>7</v>
       </c>
       <c r="B7" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C7" s="47" t="s">
         <v>94</v>
       </c>
       <c r="D7" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E7" s="47" t="s">
         <v>161</v>
       </c>
       <c r="F7" s="57" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="G7" s="56" t="s">
         <v>9</v>
@@ -4556,10 +4548,10 @@
         <v>Acu Compra</v>
       </c>
       <c r="P7" s="46" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="Q7" s="46" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="R7" s="33" t="s">
         <v>9</v>
@@ -4590,30 +4582,30 @@
         <v>9</v>
       </c>
       <c r="Z7" s="33" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="AA7" s="33" t="s">
-        <v>715</v>
-      </c>
-    </row>
-    <row r="8" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="52">
         <v>8</v>
       </c>
       <c r="B8" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C8" s="49" t="s">
         <v>94</v>
       </c>
       <c r="D8" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E8" s="47" t="s">
         <v>161</v>
       </c>
       <c r="F8" s="57" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="G8" s="56" t="s">
         <v>9</v>
@@ -4650,7 +4642,7 @@
         <v>167</v>
       </c>
       <c r="Q8" s="46" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="R8" s="33" t="s">
         <v>9</v>
@@ -4681,30 +4673,30 @@
         <v>9</v>
       </c>
       <c r="Z8" s="33" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="AA8" s="33" t="s">
-        <v>716</v>
-      </c>
-    </row>
-    <row r="9" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="52">
         <v>9</v>
       </c>
       <c r="B9" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C9" s="49" t="s">
         <v>94</v>
       </c>
       <c r="D9" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E9" s="47" t="s">
         <v>161</v>
       </c>
       <c r="F9" s="57" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="G9" s="56" t="s">
         <v>9</v>
@@ -4725,19 +4717,19 @@
         <v>94</v>
       </c>
       <c r="M9" s="46" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="N9" s="46" t="s">
+        <v>470</v>
+      </c>
+      <c r="O9" s="46" t="s">
         <v>471</v>
       </c>
-      <c r="O9" s="46" t="s">
-        <v>472</v>
-      </c>
       <c r="P9" s="46" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="Q9" s="46" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="R9" s="33" t="s">
         <v>9</v>
@@ -4746,10 +4738,10 @@
         <v>94</v>
       </c>
       <c r="T9" s="33" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="U9" s="33" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="V9" s="33" t="s">
         <v>180</v>
@@ -4765,30 +4757,30 @@
         <v>9</v>
       </c>
       <c r="Z9" s="33" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="AA9" s="33" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="10" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="52">
         <v>10</v>
       </c>
       <c r="B10" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C10" s="49" t="s">
         <v>94</v>
       </c>
       <c r="D10" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E10" s="47" t="s">
         <v>161</v>
       </c>
       <c r="F10" s="57" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="G10" s="56" t="s">
         <v>9</v>
@@ -4825,7 +4817,7 @@
         <v>168</v>
       </c>
       <c r="Q10" s="46" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="R10" s="33" t="s">
         <v>9</v>
@@ -4856,30 +4848,30 @@
         <v>9</v>
       </c>
       <c r="Z10" s="33" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="AA10" s="33" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="11" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="52">
         <v>11</v>
       </c>
       <c r="B11" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C11" s="49" t="s">
         <v>94</v>
       </c>
       <c r="D11" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E11" s="47" t="s">
         <v>161</v>
       </c>
       <c r="F11" s="57" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="G11" s="56" t="s">
         <v>9</v>
@@ -4916,7 +4908,7 @@
         <v>169</v>
       </c>
       <c r="Q11" s="46" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="R11" s="33" t="s">
         <v>9</v>
@@ -4947,30 +4939,30 @@
         <v>9</v>
       </c>
       <c r="Z11" s="33" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AA11" s="33" t="s">
-        <v>718</v>
-      </c>
-    </row>
-    <row r="12" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="52">
         <v>12</v>
       </c>
       <c r="B12" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C12" s="49" t="s">
         <v>94</v>
       </c>
       <c r="D12" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E12" s="47" t="s">
         <v>161</v>
       </c>
       <c r="F12" s="57" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="G12" s="56" t="s">
         <v>9</v>
@@ -5007,7 +4999,7 @@
         <v>171</v>
       </c>
       <c r="Q12" s="46" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="R12" s="33" t="s">
         <v>9</v>
@@ -5038,30 +5030,30 @@
         <v>9</v>
       </c>
       <c r="Z12" s="33" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="AA12" s="33" t="s">
-        <v>719</v>
-      </c>
-    </row>
-    <row r="13" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="52">
         <v>13</v>
       </c>
       <c r="B13" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C13" s="49" t="s">
         <v>94</v>
       </c>
       <c r="D13" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E13" s="47" t="s">
         <v>161</v>
       </c>
       <c r="F13" s="57" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="G13" s="56" t="s">
         <v>9</v>
@@ -5095,10 +5087,10 @@
         <v>Acu Projetista</v>
       </c>
       <c r="P13" s="46" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="Q13" s="46" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="R13" s="33" t="s">
         <v>9</v>
@@ -5129,30 +5121,30 @@
         <v>9</v>
       </c>
       <c r="Z13" s="33" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="AA13" s="33" t="s">
-        <v>720</v>
-      </c>
-    </row>
-    <row r="14" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="52">
         <v>14</v>
       </c>
       <c r="B14" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C14" s="49" t="s">
         <v>94</v>
       </c>
       <c r="D14" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E14" s="47" t="s">
         <v>161</v>
       </c>
       <c r="F14" s="57" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="G14" s="56" t="s">
         <v>9</v>
@@ -5189,7 +5181,7 @@
         <v>166</v>
       </c>
       <c r="Q14" s="46" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="R14" s="33" t="s">
         <v>9</v>
@@ -5220,30 +5212,30 @@
         <v>9</v>
       </c>
       <c r="Z14" s="33" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="AA14" s="33" t="s">
-        <v>721</v>
-      </c>
-    </row>
-    <row r="15" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="52">
         <v>15</v>
       </c>
       <c r="B15" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C15" s="49" t="s">
         <v>94</v>
       </c>
       <c r="D15" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E15" s="47" t="s">
         <v>161</v>
       </c>
       <c r="F15" s="57" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="G15" s="56" t="s">
         <v>9</v>
@@ -5277,10 +5269,10 @@
         <v>Acu Vendedor</v>
       </c>
       <c r="P15" s="46" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="Q15" s="46" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="R15" s="33" t="s">
         <v>9</v>
@@ -5311,30 +5303,30 @@
         <v>9</v>
       </c>
       <c r="Z15" s="33" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="AA15" s="33" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="16" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="52">
         <v>16</v>
       </c>
       <c r="B16" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C16" s="49" t="s">
         <v>94</v>
       </c>
       <c r="D16" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E16" s="47" t="s">
         <v>95</v>
       </c>
       <c r="F16" s="57" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="G16" s="56" t="s">
         <v>9</v>
@@ -5368,10 +5360,10 @@
         <v>Arq Compra</v>
       </c>
       <c r="P16" s="46" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="Q16" s="46" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="R16" s="33" t="s">
         <v>9</v>
@@ -5402,30 +5394,30 @@
         <v>9</v>
       </c>
       <c r="Z16" s="33" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="AA16" s="33" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="17" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="17" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="52">
         <v>17</v>
       </c>
       <c r="B17" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C17" s="49" t="s">
         <v>94</v>
       </c>
       <c r="D17" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E17" s="47" t="s">
         <v>95</v>
       </c>
       <c r="F17" s="57" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="G17" s="56" t="s">
         <v>9</v>
@@ -5462,7 +5454,7 @@
         <v>163</v>
       </c>
       <c r="Q17" s="46" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="R17" s="33" t="s">
         <v>9</v>
@@ -5493,30 +5485,30 @@
         <v>9</v>
       </c>
       <c r="Z17" s="33" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="AA17" s="33" t="s">
-        <v>724</v>
-      </c>
-    </row>
-    <row r="18" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="18" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="52">
         <v>18</v>
       </c>
       <c r="B18" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C18" s="49" t="s">
         <v>94</v>
       </c>
       <c r="D18" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E18" s="47" t="s">
         <v>95</v>
       </c>
       <c r="F18" s="57" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="G18" s="56" t="s">
         <v>9</v>
@@ -5537,19 +5529,19 @@
         <v>94</v>
       </c>
       <c r="M18" s="46" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="N18" s="46" t="s">
+        <v>478</v>
+      </c>
+      <c r="O18" s="46" t="s">
         <v>479</v>
       </c>
-      <c r="O18" s="46" t="s">
-        <v>480</v>
-      </c>
       <c r="P18" s="46" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="Q18" s="46" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="R18" s="33" t="s">
         <v>9</v>
@@ -5558,10 +5550,10 @@
         <v>94</v>
       </c>
       <c r="T18" s="33" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="U18" s="33" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="V18" s="33" t="s">
         <v>180</v>
@@ -5577,30 +5569,30 @@
         <v>9</v>
       </c>
       <c r="Z18" s="33" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="AA18" s="33" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="19" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="19" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="52">
         <v>19</v>
       </c>
       <c r="B19" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C19" s="49" t="s">
         <v>94</v>
       </c>
       <c r="D19" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E19" s="47" t="s">
         <v>95</v>
       </c>
       <c r="F19" s="57" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="G19" s="56" t="s">
         <v>9</v>
@@ -5637,7 +5629,7 @@
         <v>164</v>
       </c>
       <c r="Q19" s="46" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="R19" s="33" t="s">
         <v>9</v>
@@ -5668,30 +5660,30 @@
         <v>9</v>
       </c>
       <c r="Z19" s="33" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="AA19" s="33" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="20" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="20" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="52">
         <v>20</v>
       </c>
       <c r="B20" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C20" s="49" t="s">
         <v>94</v>
       </c>
       <c r="D20" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E20" s="47" t="s">
         <v>95</v>
       </c>
       <c r="F20" s="57" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="G20" s="56" t="s">
         <v>9</v>
@@ -5728,7 +5720,7 @@
         <v>165</v>
       </c>
       <c r="Q20" s="46" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="R20" s="33" t="s">
         <v>9</v>
@@ -5759,30 +5751,30 @@
         <v>9</v>
       </c>
       <c r="Z20" s="33" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AA20" s="33" t="s">
-        <v>726</v>
-      </c>
-    </row>
-    <row r="21" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="21" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="52">
         <v>21</v>
       </c>
       <c r="B21" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C21" s="49" t="s">
         <v>94</v>
       </c>
       <c r="D21" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E21" s="47" t="s">
         <v>95</v>
       </c>
       <c r="F21" s="57" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="G21" s="56" t="s">
         <v>9</v>
@@ -5819,7 +5811,7 @@
         <v>170</v>
       </c>
       <c r="Q21" s="46" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="R21" s="33" t="s">
         <v>9</v>
@@ -5850,30 +5842,30 @@
         <v>9</v>
       </c>
       <c r="Z21" s="33" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="AA21" s="33" t="s">
-        <v>727</v>
-      </c>
-    </row>
-    <row r="22" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="22" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="52">
         <v>22</v>
       </c>
       <c r="B22" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C22" s="49" t="s">
         <v>94</v>
       </c>
       <c r="D22" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E22" s="47" t="s">
         <v>95</v>
       </c>
       <c r="F22" s="57" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="G22" s="56" t="s">
         <v>9</v>
@@ -5907,10 +5899,10 @@
         <v>Arq Projetista</v>
       </c>
       <c r="P22" s="46" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="Q22" s="46" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="R22" s="33" t="s">
         <v>9</v>
@@ -5941,30 +5933,30 @@
         <v>9</v>
       </c>
       <c r="Z22" s="33" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="AA22" s="33" t="s">
-        <v>728</v>
-      </c>
-    </row>
-    <row r="23" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="23" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="52">
         <v>23</v>
       </c>
       <c r="B23" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C23" s="49" t="s">
         <v>94</v>
       </c>
       <c r="D23" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E23" s="47" t="s">
         <v>95</v>
       </c>
       <c r="F23" s="57" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G23" s="56" t="s">
         <v>9</v>
@@ -6001,7 +5993,7 @@
         <v>162</v>
       </c>
       <c r="Q23" s="46" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="R23" s="33" t="s">
         <v>9</v>
@@ -6032,30 +6024,30 @@
         <v>9</v>
       </c>
       <c r="Z23" s="33" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="AA23" s="33" t="s">
-        <v>729</v>
-      </c>
-    </row>
-    <row r="24" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="24" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="52">
         <v>24</v>
       </c>
       <c r="B24" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C24" s="49" t="s">
         <v>94</v>
       </c>
       <c r="D24" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E24" s="47" t="s">
         <v>95</v>
       </c>
       <c r="F24" s="57" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="G24" s="56" t="s">
         <v>9</v>
@@ -6089,10 +6081,10 @@
         <v>Arq Vendedor</v>
       </c>
       <c r="P24" s="46" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="Q24" s="46" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="R24" s="33" t="s">
         <v>9</v>
@@ -6123,30 +6115,30 @@
         <v>9</v>
       </c>
       <c r="Z24" s="33" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="AA24" s="33" t="s">
-        <v>730</v>
-      </c>
-    </row>
-    <row r="25" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="25" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="52">
         <v>25</v>
       </c>
       <c r="B25" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C25" s="49" t="s">
         <v>94</v>
       </c>
       <c r="D25" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E25" s="47" t="s">
         <v>96</v>
       </c>
       <c r="F25" s="57" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="G25" s="56" t="s">
         <v>9</v>
@@ -6180,10 +6172,10 @@
         <v>Est Compra</v>
       </c>
       <c r="P25" s="46" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="Q25" s="46" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="R25" s="33" t="s">
         <v>9</v>
@@ -6214,30 +6206,30 @@
         <v>9</v>
       </c>
       <c r="Z25" s="33" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="AA25" s="33" t="s">
-        <v>731</v>
-      </c>
-    </row>
-    <row r="26" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="26" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="52">
         <v>26</v>
       </c>
       <c r="B26" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C26" s="49" t="s">
         <v>94</v>
       </c>
       <c r="D26" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E26" s="47" t="s">
         <v>96</v>
       </c>
       <c r="F26" s="57" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="G26" s="56" t="s">
         <v>9</v>
@@ -6274,7 +6266,7 @@
         <v>103</v>
       </c>
       <c r="Q26" s="46" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="R26" s="33" t="s">
         <v>9</v>
@@ -6305,30 +6297,30 @@
         <v>9</v>
       </c>
       <c r="Z26" s="33" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="AA26" s="33" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="27" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="27" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="52">
         <v>27</v>
       </c>
       <c r="B27" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C27" s="49" t="s">
         <v>94</v>
       </c>
       <c r="D27" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E27" s="47" t="s">
         <v>96</v>
       </c>
       <c r="F27" s="57" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="G27" s="56" t="s">
         <v>9</v>
@@ -6349,19 +6341,19 @@
         <v>94</v>
       </c>
       <c r="M27" s="46" t="s">
+        <v>453</v>
+      </c>
+      <c r="N27" s="46" t="s">
         <v>454</v>
       </c>
-      <c r="N27" s="46" t="s">
+      <c r="O27" s="46" t="s">
         <v>455</v>
       </c>
-      <c r="O27" s="46" t="s">
-        <v>456</v>
-      </c>
       <c r="P27" s="46" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="Q27" s="46" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="R27" s="33" t="s">
         <v>9</v>
@@ -6370,10 +6362,10 @@
         <v>94</v>
       </c>
       <c r="T27" s="33" t="s">
+        <v>453</v>
+      </c>
+      <c r="U27" s="33" t="s">
         <v>454</v>
-      </c>
-      <c r="U27" s="33" t="s">
-        <v>455</v>
       </c>
       <c r="V27" s="33" t="s">
         <v>180</v>
@@ -6389,30 +6381,30 @@
         <v>9</v>
       </c>
       <c r="Z27" s="33" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="AA27" s="33" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="28" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="28" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="52">
         <v>28</v>
       </c>
       <c r="B28" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C28" s="49" t="s">
         <v>94</v>
       </c>
       <c r="D28" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E28" s="47" t="s">
         <v>96</v>
       </c>
       <c r="F28" s="57" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G28" s="56" t="s">
         <v>9</v>
@@ -6449,7 +6441,7 @@
         <v>104</v>
       </c>
       <c r="Q28" s="46" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="R28" s="33" t="s">
         <v>9</v>
@@ -6480,30 +6472,30 @@
         <v>9</v>
       </c>
       <c r="Z28" s="33" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="AA28" s="33" t="s">
-        <v>733</v>
-      </c>
-    </row>
-    <row r="29" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="29" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="52">
         <v>29</v>
       </c>
       <c r="B29" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C29" s="49" t="s">
         <v>94</v>
       </c>
       <c r="D29" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E29" s="47" t="s">
         <v>96</v>
       </c>
       <c r="F29" s="57" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="G29" s="56" t="s">
         <v>9</v>
@@ -6540,7 +6532,7 @@
         <v>105</v>
       </c>
       <c r="Q29" s="46" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="R29" s="33" t="s">
         <v>9</v>
@@ -6571,30 +6563,30 @@
         <v>9</v>
       </c>
       <c r="Z29" s="33" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AA29" s="33" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="30" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="30" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="52">
         <v>30</v>
       </c>
       <c r="B30" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C30" s="49" t="s">
         <v>94</v>
       </c>
       <c r="D30" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E30" s="47" t="s">
         <v>96</v>
       </c>
       <c r="F30" s="57" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="G30" s="56" t="s">
         <v>9</v>
@@ -6631,7 +6623,7 @@
         <v>172</v>
       </c>
       <c r="Q30" s="46" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="R30" s="33" t="s">
         <v>9</v>
@@ -6662,30 +6654,30 @@
         <v>9</v>
       </c>
       <c r="Z30" s="33" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="AA30" s="33" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="31" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="31" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="52">
         <v>31</v>
       </c>
       <c r="B31" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C31" s="49" t="s">
         <v>94</v>
       </c>
       <c r="D31" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E31" s="47" t="s">
         <v>96</v>
       </c>
       <c r="F31" s="57" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="G31" s="56" t="s">
         <v>9</v>
@@ -6719,10 +6711,10 @@
         <v>Est Projetista</v>
       </c>
       <c r="P31" s="46" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="Q31" s="46" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="R31" s="33" t="s">
         <v>9</v>
@@ -6753,30 +6745,30 @@
         <v>9</v>
       </c>
       <c r="Z31" s="33" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="AA31" s="33" t="s">
-        <v>736</v>
-      </c>
-    </row>
-    <row r="32" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="32" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="52">
         <v>32</v>
       </c>
       <c r="B32" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C32" s="49" t="s">
         <v>94</v>
       </c>
       <c r="D32" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E32" s="47" t="s">
         <v>96</v>
       </c>
       <c r="F32" s="57" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="G32" s="56" t="s">
         <v>9</v>
@@ -6813,7 +6805,7 @@
         <v>102</v>
       </c>
       <c r="Q32" s="46" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="R32" s="33" t="s">
         <v>9</v>
@@ -6844,30 +6836,30 @@
         <v>9</v>
       </c>
       <c r="Z32" s="33" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="AA32" s="33" t="s">
-        <v>737</v>
-      </c>
-    </row>
-    <row r="33" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="33" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="52">
         <v>33</v>
       </c>
       <c r="B33" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C33" s="49" t="s">
         <v>94</v>
       </c>
       <c r="D33" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E33" s="47" t="s">
         <v>96</v>
       </c>
       <c r="F33" s="57" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="G33" s="56" t="s">
         <v>9</v>
@@ -6901,10 +6893,10 @@
         <v>Est Vendedor</v>
       </c>
       <c r="P33" s="46" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="Q33" s="46" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="R33" s="33" t="s">
         <v>9</v>
@@ -6935,30 +6927,30 @@
         <v>9</v>
       </c>
       <c r="Z33" s="33" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="AA33" s="33" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="34" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="34" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="52">
         <v>34</v>
       </c>
       <c r="B34" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C34" s="49" t="s">
         <v>94</v>
       </c>
       <c r="D34" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E34" s="47" t="s">
         <v>181</v>
       </c>
       <c r="F34" s="57" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="G34" s="56" t="s">
         <v>9</v>
@@ -6992,10 +6984,10 @@
         <v>Geo Compra</v>
       </c>
       <c r="P34" s="46" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="Q34" s="46" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="R34" s="33" t="s">
         <v>9</v>
@@ -7026,30 +7018,30 @@
         <v>9</v>
       </c>
       <c r="Z34" s="33" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="AA34" s="33" t="s">
-        <v>739</v>
-      </c>
-    </row>
-    <row r="35" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="35" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="52">
         <v>35</v>
       </c>
       <c r="B35" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C35" s="49" t="s">
         <v>94</v>
       </c>
       <c r="D35" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E35" s="47" t="s">
         <v>181</v>
       </c>
       <c r="F35" s="57" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="G35" s="56" t="s">
         <v>9</v>
@@ -7086,7 +7078,7 @@
         <v>123</v>
       </c>
       <c r="Q35" s="46" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="R35" s="33" t="s">
         <v>9</v>
@@ -7117,30 +7109,30 @@
         <v>9</v>
       </c>
       <c r="Z35" s="33" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="AA35" s="33" t="s">
-        <v>740</v>
-      </c>
-    </row>
-    <row r="36" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="36" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="52">
         <v>36</v>
       </c>
       <c r="B36" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C36" s="49" t="s">
         <v>94</v>
       </c>
       <c r="D36" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E36" s="47" t="s">
         <v>181</v>
       </c>
       <c r="F36" s="57" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="G36" s="56" t="s">
         <v>9</v>
@@ -7161,19 +7153,19 @@
         <v>94</v>
       </c>
       <c r="M36" s="46" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="N36" s="46" t="s">
+        <v>456</v>
+      </c>
+      <c r="O36" s="46" t="s">
         <v>457</v>
       </c>
-      <c r="O36" s="46" t="s">
-        <v>458</v>
-      </c>
       <c r="P36" s="46" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="Q36" s="46" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="R36" s="33" t="s">
         <v>9</v>
@@ -7182,10 +7174,10 @@
         <v>94</v>
       </c>
       <c r="T36" s="33" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="U36" s="33" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="V36" s="33" t="s">
         <v>180</v>
@@ -7201,30 +7193,30 @@
         <v>9</v>
       </c>
       <c r="Z36" s="33" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="AA36" s="33" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="37" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="37" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="52">
         <v>37</v>
       </c>
       <c r="B37" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C37" s="49" t="s">
         <v>94</v>
       </c>
       <c r="D37" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E37" s="47" t="s">
         <v>181</v>
       </c>
       <c r="F37" s="57" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="G37" s="56" t="s">
         <v>9</v>
@@ -7261,7 +7253,7 @@
         <v>124</v>
       </c>
       <c r="Q37" s="46" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="R37" s="33" t="s">
         <v>9</v>
@@ -7292,30 +7284,30 @@
         <v>9</v>
       </c>
       <c r="Z37" s="33" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="AA37" s="33" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="38" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="38" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" s="52">
         <v>38</v>
       </c>
       <c r="B38" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C38" s="49" t="s">
         <v>94</v>
       </c>
       <c r="D38" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E38" s="47" t="s">
         <v>181</v>
       </c>
       <c r="F38" s="57" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G38" s="56" t="s">
         <v>9</v>
@@ -7352,7 +7344,7 @@
         <v>125</v>
       </c>
       <c r="Q38" s="46" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="R38" s="33" t="s">
         <v>9</v>
@@ -7383,30 +7375,30 @@
         <v>9</v>
       </c>
       <c r="Z38" s="33" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AA38" s="33" t="s">
-        <v>742</v>
-      </c>
-    </row>
-    <row r="39" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="39" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A39" s="52">
         <v>39</v>
       </c>
       <c r="B39" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C39" s="49" t="s">
         <v>94</v>
       </c>
       <c r="D39" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E39" s="47" t="s">
         <v>181</v>
       </c>
       <c r="F39" s="57" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="G39" s="56" t="s">
         <v>9</v>
@@ -7443,7 +7435,7 @@
         <v>173</v>
       </c>
       <c r="Q39" s="46" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="R39" s="33" t="s">
         <v>9</v>
@@ -7474,30 +7466,30 @@
         <v>9</v>
       </c>
       <c r="Z39" s="33" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="AA39" s="33" t="s">
-        <v>743</v>
-      </c>
-    </row>
-    <row r="40" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="40" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A40" s="52">
         <v>40</v>
       </c>
       <c r="B40" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C40" s="49" t="s">
         <v>94</v>
       </c>
       <c r="D40" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E40" s="47" t="s">
         <v>181</v>
       </c>
       <c r="F40" s="57" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G40" s="56" t="s">
         <v>9</v>
@@ -7531,10 +7523,10 @@
         <v>Geo Projetista</v>
       </c>
       <c r="P40" s="46" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Q40" s="46" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="R40" s="33" t="s">
         <v>9</v>
@@ -7565,30 +7557,30 @@
         <v>9</v>
       </c>
       <c r="Z40" s="33" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="AA40" s="33" t="s">
-        <v>744</v>
-      </c>
-    </row>
-    <row r="41" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="41" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A41" s="52">
         <v>41</v>
       </c>
       <c r="B41" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C41" s="49" t="s">
         <v>94</v>
       </c>
       <c r="D41" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E41" s="47" t="s">
         <v>181</v>
       </c>
       <c r="F41" s="57" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G41" s="56" t="s">
         <v>9</v>
@@ -7625,7 +7617,7 @@
         <v>122</v>
       </c>
       <c r="Q41" s="46" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="R41" s="33" t="s">
         <v>9</v>
@@ -7656,30 +7648,30 @@
         <v>9</v>
       </c>
       <c r="Z41" s="33" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="AA41" s="33" t="s">
-        <v>745</v>
-      </c>
-    </row>
-    <row r="42" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="42" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A42" s="52">
         <v>42</v>
       </c>
       <c r="B42" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C42" s="49" t="s">
         <v>94</v>
       </c>
       <c r="D42" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E42" s="47" t="s">
         <v>181</v>
       </c>
       <c r="F42" s="57" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="G42" s="56" t="s">
         <v>9</v>
@@ -7713,10 +7705,10 @@
         <v>Geo Vendedor</v>
       </c>
       <c r="P42" s="46" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="Q42" s="46" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="R42" s="33" t="s">
         <v>9</v>
@@ -7747,30 +7739,30 @@
         <v>9</v>
       </c>
       <c r="Z42" s="33" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="AA42" s="33" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="43" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="43" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A43" s="52">
         <v>43</v>
       </c>
       <c r="B43" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C43" s="49" t="s">
         <v>94</v>
       </c>
       <c r="D43" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E43" s="47" t="s">
         <v>217</v>
       </c>
       <c r="F43" s="57" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="G43" s="56" t="s">
         <v>9</v>
@@ -7804,10 +7796,10 @@
         <v>Ger Compra</v>
       </c>
       <c r="P43" s="46" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="Q43" s="46" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="R43" s="33" t="s">
         <v>9</v>
@@ -7838,30 +7830,30 @@
         <v>9</v>
       </c>
       <c r="Z43" s="33" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="AA43" s="33" t="s">
-        <v>747</v>
-      </c>
-    </row>
-    <row r="44" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="44" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A44" s="52">
         <v>44</v>
       </c>
       <c r="B44" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C44" s="49" t="s">
         <v>94</v>
       </c>
       <c r="D44" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E44" s="47" t="s">
         <v>217</v>
       </c>
       <c r="F44" s="57" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G44" s="56" t="s">
         <v>9</v>
@@ -7898,7 +7890,7 @@
         <v>182</v>
       </c>
       <c r="Q44" s="46" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="R44" s="33" t="s">
         <v>9</v>
@@ -7929,30 +7921,30 @@
         <v>9</v>
       </c>
       <c r="Z44" s="33" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="AA44" s="33" t="s">
-        <v>748</v>
-      </c>
-    </row>
-    <row r="45" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="45" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A45" s="52">
         <v>45</v>
       </c>
       <c r="B45" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C45" s="49" t="s">
         <v>94</v>
       </c>
       <c r="D45" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E45" s="47" t="s">
         <v>217</v>
       </c>
       <c r="F45" s="57" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="G45" s="56" t="s">
         <v>9</v>
@@ -7973,19 +7965,19 @@
         <v>94</v>
       </c>
       <c r="M45" s="46" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="N45" s="46" t="s">
+        <v>472</v>
+      </c>
+      <c r="O45" s="46" t="s">
         <v>473</v>
       </c>
-      <c r="O45" s="46" t="s">
-        <v>474</v>
-      </c>
       <c r="P45" s="46" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="Q45" s="46" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="R45" s="33" t="s">
         <v>9</v>
@@ -7994,10 +7986,10 @@
         <v>94</v>
       </c>
       <c r="T45" s="33" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="U45" s="33" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="V45" s="33" t="s">
         <v>180</v>
@@ -8013,30 +8005,30 @@
         <v>9</v>
       </c>
       <c r="Z45" s="33" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="AA45" s="33" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="46" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="46" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A46" s="52">
         <v>46</v>
       </c>
       <c r="B46" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C46" s="49" t="s">
         <v>94</v>
       </c>
       <c r="D46" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E46" s="47" t="s">
         <v>217</v>
       </c>
       <c r="F46" s="57" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="G46" s="56" t="s">
         <v>9</v>
@@ -8073,7 +8065,7 @@
         <v>183</v>
       </c>
       <c r="Q46" s="46" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="R46" s="33" t="s">
         <v>9</v>
@@ -8104,30 +8096,30 @@
         <v>9</v>
       </c>
       <c r="Z46" s="33" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="AA46" s="33" t="s">
-        <v>749</v>
-      </c>
-    </row>
-    <row r="47" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="47" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A47" s="52">
         <v>47</v>
       </c>
       <c r="B47" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C47" s="49" t="s">
         <v>94</v>
       </c>
       <c r="D47" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E47" s="47" t="s">
         <v>217</v>
       </c>
       <c r="F47" s="57" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G47" s="56" t="s">
         <v>9</v>
@@ -8164,7 +8156,7 @@
         <v>184</v>
       </c>
       <c r="Q47" s="46" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="R47" s="33" t="s">
         <v>9</v>
@@ -8195,30 +8187,30 @@
         <v>9</v>
       </c>
       <c r="Z47" s="33" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AA47" s="33" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="48" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="48" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A48" s="52">
         <v>48</v>
       </c>
       <c r="B48" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C48" s="49" t="s">
         <v>94</v>
       </c>
       <c r="D48" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E48" s="47" t="s">
         <v>217</v>
       </c>
       <c r="F48" s="57" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="G48" s="56" t="s">
         <v>9</v>
@@ -8255,7 +8247,7 @@
         <v>185</v>
       </c>
       <c r="Q48" s="46" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="R48" s="33" t="s">
         <v>9</v>
@@ -8286,30 +8278,30 @@
         <v>9</v>
       </c>
       <c r="Z48" s="33" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="AA48" s="33" t="s">
-        <v>751</v>
-      </c>
-    </row>
-    <row r="49" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="49" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="52">
         <v>49</v>
       </c>
       <c r="B49" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C49" s="49" t="s">
         <v>94</v>
       </c>
       <c r="D49" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E49" s="47" t="s">
         <v>217</v>
       </c>
       <c r="F49" s="57" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="G49" s="56" t="s">
         <v>9</v>
@@ -8343,10 +8335,10 @@
         <v>Ger Projetista</v>
       </c>
       <c r="P49" s="46" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="Q49" s="46" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="R49" s="33" t="s">
         <v>9</v>
@@ -8377,30 +8369,30 @@
         <v>9</v>
       </c>
       <c r="Z49" s="33" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="AA49" s="33" t="s">
-        <v>752</v>
-      </c>
-    </row>
-    <row r="50" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="50" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A50" s="52">
         <v>50</v>
       </c>
       <c r="B50" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C50" s="49" t="s">
         <v>94</v>
       </c>
       <c r="D50" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E50" s="47" t="s">
         <v>217</v>
       </c>
       <c r="F50" s="57" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="G50" s="56" t="s">
         <v>9</v>
@@ -8437,7 +8429,7 @@
         <v>186</v>
       </c>
       <c r="Q50" s="46" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="R50" s="33" t="s">
         <v>9</v>
@@ -8468,30 +8460,30 @@
         <v>9</v>
       </c>
       <c r="Z50" s="33" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="AA50" s="33" t="s">
-        <v>753</v>
-      </c>
-    </row>
-    <row r="51" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="51" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A51" s="52">
         <v>51</v>
       </c>
       <c r="B51" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C51" s="49" t="s">
         <v>94</v>
       </c>
       <c r="D51" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E51" s="47" t="s">
         <v>217</v>
       </c>
       <c r="F51" s="57" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="G51" s="56" t="s">
         <v>9</v>
@@ -8525,10 +8517,10 @@
         <v>Ger Vendedor</v>
       </c>
       <c r="P51" s="46" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="Q51" s="46" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="R51" s="33" t="s">
         <v>9</v>
@@ -8559,30 +8551,30 @@
         <v>9</v>
       </c>
       <c r="Z51" s="33" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="AA51" s="33" t="s">
-        <v>754</v>
-      </c>
-    </row>
-    <row r="52" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="52" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A52" s="52">
         <v>52</v>
       </c>
       <c r="B52" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C52" s="49" t="s">
         <v>94</v>
       </c>
       <c r="D52" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E52" s="47" t="s">
         <v>100</v>
       </c>
       <c r="F52" s="57" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="G52" s="56" t="s">
         <v>9</v>
@@ -8616,10 +8608,10 @@
         <v>Hos Compra</v>
       </c>
       <c r="P52" s="46" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="Q52" s="46" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="R52" s="33" t="s">
         <v>9</v>
@@ -8650,30 +8642,30 @@
         <v>9</v>
       </c>
       <c r="Z52" s="33" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="AA52" s="33" t="s">
-        <v>755</v>
-      </c>
-    </row>
-    <row r="53" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="53" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A53" s="52">
         <v>53</v>
       </c>
       <c r="B53" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C53" s="49" t="s">
         <v>94</v>
       </c>
       <c r="D53" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E53" s="47" t="s">
         <v>100</v>
       </c>
       <c r="F53" s="57" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="G53" s="56" t="s">
         <v>9</v>
@@ -8710,7 +8702,7 @@
         <v>127</v>
       </c>
       <c r="Q53" s="46" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="R53" s="33" t="s">
         <v>9</v>
@@ -8741,30 +8733,30 @@
         <v>9</v>
       </c>
       <c r="Z53" s="33" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AA53" s="33" t="s">
-        <v>756</v>
-      </c>
-    </row>
-    <row r="54" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="54" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A54" s="52">
         <v>54</v>
       </c>
       <c r="B54" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C54" s="49" t="s">
         <v>94</v>
       </c>
       <c r="D54" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E54" s="47" t="s">
         <v>100</v>
       </c>
       <c r="F54" s="57" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="G54" s="56" t="s">
         <v>9</v>
@@ -8785,19 +8777,19 @@
         <v>94</v>
       </c>
       <c r="M54" s="46" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="N54" s="46" t="s">
+        <v>458</v>
+      </c>
+      <c r="O54" s="46" t="s">
         <v>459</v>
       </c>
-      <c r="O54" s="46" t="s">
-        <v>460</v>
-      </c>
       <c r="P54" s="46" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="Q54" s="46" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="R54" s="33" t="s">
         <v>9</v>
@@ -8806,10 +8798,10 @@
         <v>94</v>
       </c>
       <c r="T54" s="33" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="U54" s="33" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="V54" s="33" t="s">
         <v>180</v>
@@ -8825,30 +8817,30 @@
         <v>9</v>
       </c>
       <c r="Z54" s="33" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="AA54" s="33" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="55" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="55" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A55" s="52">
         <v>55</v>
       </c>
       <c r="B55" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C55" s="49" t="s">
         <v>94</v>
       </c>
       <c r="D55" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E55" s="47" t="s">
         <v>100</v>
       </c>
       <c r="F55" s="57" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="G55" s="56" t="s">
         <v>9</v>
@@ -8885,7 +8877,7 @@
         <v>128</v>
       </c>
       <c r="Q55" s="46" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="R55" s="33" t="s">
         <v>9</v>
@@ -8916,30 +8908,30 @@
         <v>9</v>
       </c>
       <c r="Z55" s="33" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AA55" s="33" t="s">
-        <v>757</v>
-      </c>
-    </row>
-    <row r="56" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="56" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A56" s="52">
         <v>56</v>
       </c>
       <c r="B56" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C56" s="49" t="s">
         <v>94</v>
       </c>
       <c r="D56" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E56" s="47" t="s">
         <v>100</v>
       </c>
       <c r="F56" s="57" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="G56" s="56" t="s">
         <v>9</v>
@@ -8976,7 +8968,7 @@
         <v>129</v>
       </c>
       <c r="Q56" s="46" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="R56" s="33" t="s">
         <v>9</v>
@@ -9007,30 +8999,30 @@
         <v>9</v>
       </c>
       <c r="Z56" s="33" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AA56" s="33" t="s">
-        <v>758</v>
-      </c>
-    </row>
-    <row r="57" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="57" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A57" s="52">
         <v>57</v>
       </c>
       <c r="B57" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C57" s="49" t="s">
         <v>94</v>
       </c>
       <c r="D57" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E57" s="47" t="s">
         <v>100</v>
       </c>
       <c r="F57" s="57" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="G57" s="56" t="s">
         <v>9</v>
@@ -9067,7 +9059,7 @@
         <v>176</v>
       </c>
       <c r="Q57" s="46" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="R57" s="33" t="s">
         <v>9</v>
@@ -9098,30 +9090,30 @@
         <v>9</v>
       </c>
       <c r="Z57" s="33" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="AA57" s="33" t="s">
-        <v>759</v>
-      </c>
-    </row>
-    <row r="58" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="58" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A58" s="52">
         <v>58</v>
       </c>
       <c r="B58" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C58" s="49" t="s">
         <v>94</v>
       </c>
       <c r="D58" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E58" s="47" t="s">
         <v>100</v>
       </c>
       <c r="F58" s="57" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="G58" s="56" t="s">
         <v>9</v>
@@ -9155,10 +9147,10 @@
         <v>Hos Projetista</v>
       </c>
       <c r="P58" s="46" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="Q58" s="46" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="R58" s="33" t="s">
         <v>9</v>
@@ -9189,30 +9181,30 @@
         <v>9</v>
       </c>
       <c r="Z58" s="33" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AA58" s="33" t="s">
-        <v>760</v>
-      </c>
-    </row>
-    <row r="59" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="59" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A59" s="52">
         <v>59</v>
       </c>
       <c r="B59" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C59" s="49" t="s">
         <v>94</v>
       </c>
       <c r="D59" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E59" s="47" t="s">
         <v>100</v>
       </c>
       <c r="F59" s="57" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="G59" s="56" t="s">
         <v>9</v>
@@ -9249,7 +9241,7 @@
         <v>126</v>
       </c>
       <c r="Q59" s="46" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="R59" s="33" t="s">
         <v>9</v>
@@ -9280,30 +9272,30 @@
         <v>9</v>
       </c>
       <c r="Z59" s="33" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AA59" s="33" t="s">
-        <v>761</v>
-      </c>
-    </row>
-    <row r="60" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="60" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A60" s="52">
         <v>60</v>
       </c>
       <c r="B60" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C60" s="49" t="s">
         <v>94</v>
       </c>
       <c r="D60" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E60" s="47" t="s">
         <v>100</v>
       </c>
       <c r="F60" s="57" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="G60" s="56" t="s">
         <v>9</v>
@@ -9337,10 +9329,10 @@
         <v>Hos Vendedor</v>
       </c>
       <c r="P60" s="46" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="Q60" s="46" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="R60" s="33" t="s">
         <v>9</v>
@@ -9371,30 +9363,30 @@
         <v>9</v>
       </c>
       <c r="Z60" s="33" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="AA60" s="33" t="s">
-        <v>762</v>
-      </c>
-    </row>
-    <row r="61" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="61" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A61" s="52">
         <v>61</v>
       </c>
       <c r="B61" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C61" s="49" t="s">
         <v>94</v>
       </c>
       <c r="D61" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E61" s="47" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F61" s="57" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="G61" s="56" t="s">
         <v>9</v>
@@ -9428,10 +9420,10 @@
         <v>Ilu Compra</v>
       </c>
       <c r="P61" s="46" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="Q61" s="46" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="R61" s="33" t="s">
         <v>9</v>
@@ -9462,30 +9454,30 @@
         <v>9</v>
       </c>
       <c r="Z61" s="33" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="AA61" s="33" t="s">
-        <v>763</v>
-      </c>
-    </row>
-    <row r="62" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="62" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A62" s="52">
         <v>62</v>
       </c>
       <c r="B62" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C62" s="49" t="s">
         <v>94</v>
       </c>
       <c r="D62" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E62" s="47" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F62" s="57" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="G62" s="56" t="s">
         <v>9</v>
@@ -9519,10 +9511,10 @@
         <v>Ilu Consultor</v>
       </c>
       <c r="P62" s="46" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="Q62" s="46" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="R62" s="33" t="s">
         <v>9</v>
@@ -9553,30 +9545,30 @@
         <v>9</v>
       </c>
       <c r="Z62" s="33" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="AA62" s="33" t="s">
-        <v>764</v>
-      </c>
-    </row>
-    <row r="63" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="63" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A63" s="52">
         <v>63</v>
       </c>
       <c r="B63" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C63" s="49" t="s">
         <v>94</v>
       </c>
       <c r="D63" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E63" s="47" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F63" s="57" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="G63" s="56" t="s">
         <v>9</v>
@@ -9597,19 +9589,19 @@
         <v>94</v>
       </c>
       <c r="M63" s="46" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="N63" s="46" t="s">
+        <v>474</v>
+      </c>
+      <c r="O63" s="46" t="s">
         <v>475</v>
       </c>
-      <c r="O63" s="46" t="s">
-        <v>476</v>
-      </c>
       <c r="P63" s="46" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="Q63" s="46" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="R63" s="33" t="s">
         <v>9</v>
@@ -9618,10 +9610,10 @@
         <v>94</v>
       </c>
       <c r="T63" s="33" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="U63" s="33" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="V63" s="33" t="s">
         <v>180</v>
@@ -9637,30 +9629,30 @@
         <v>9</v>
       </c>
       <c r="Z63" s="33" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="AA63" s="33" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="64" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="64" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A64" s="52">
         <v>64</v>
       </c>
       <c r="B64" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C64" s="49" t="s">
         <v>94</v>
       </c>
       <c r="D64" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E64" s="47" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F64" s="57" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="G64" s="56" t="s">
         <v>9</v>
@@ -9694,10 +9686,10 @@
         <v>Ilu Empresa Consultora</v>
       </c>
       <c r="P64" s="46" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="Q64" s="46" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="R64" s="33" t="s">
         <v>9</v>
@@ -9728,30 +9720,30 @@
         <v>9</v>
       </c>
       <c r="Z64" s="33" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="AA64" s="33" t="s">
-        <v>765</v>
-      </c>
-    </row>
-    <row r="65" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="65" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A65" s="52">
         <v>65</v>
       </c>
       <c r="B65" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C65" s="49" t="s">
         <v>94</v>
       </c>
       <c r="D65" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E65" s="47" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F65" s="57" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="G65" s="56" t="s">
         <v>9</v>
@@ -9785,10 +9777,10 @@
         <v>Ilu Fabricante</v>
       </c>
       <c r="P65" s="46" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="Q65" s="46" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="R65" s="33" t="s">
         <v>9</v>
@@ -9819,30 +9811,30 @@
         <v>9</v>
       </c>
       <c r="Z65" s="33" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AA65" s="33" t="s">
-        <v>766</v>
-      </c>
-    </row>
-    <row r="66" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="66" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A66" s="52">
         <v>66</v>
       </c>
       <c r="B66" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C66" s="49" t="s">
         <v>94</v>
       </c>
       <c r="D66" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E66" s="47" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F66" s="57" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="G66" s="56" t="s">
         <v>9</v>
@@ -9876,10 +9868,10 @@
         <v>Ilu Fornecedor</v>
       </c>
       <c r="P66" s="46" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="Q66" s="46" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="R66" s="33" t="s">
         <v>9</v>
@@ -9910,30 +9902,30 @@
         <v>9</v>
       </c>
       <c r="Z66" s="33" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="AA66" s="33" t="s">
-        <v>767</v>
-      </c>
-    </row>
-    <row r="67" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="67" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A67" s="52">
         <v>67</v>
       </c>
       <c r="B67" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C67" s="49" t="s">
         <v>94</v>
       </c>
       <c r="D67" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E67" s="47" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F67" s="57" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="G67" s="56" t="s">
         <v>9</v>
@@ -9967,10 +9959,10 @@
         <v>Ilu Projetista</v>
       </c>
       <c r="P67" s="46" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="Q67" s="46" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="R67" s="33" t="s">
         <v>9</v>
@@ -10001,30 +9993,30 @@
         <v>9</v>
       </c>
       <c r="Z67" s="33" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="AA67" s="33" t="s">
-        <v>768</v>
-      </c>
-    </row>
-    <row r="68" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="68" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A68" s="52">
         <v>68</v>
       </c>
       <c r="B68" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C68" s="49" t="s">
         <v>94</v>
       </c>
       <c r="D68" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E68" s="47" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F68" s="57" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G68" s="56" t="s">
         <v>9</v>
@@ -10058,10 +10050,10 @@
         <v>Ilu Serviço</v>
       </c>
       <c r="P68" s="46" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="Q68" s="46" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="R68" s="33" t="s">
         <v>9</v>
@@ -10092,30 +10084,30 @@
         <v>9</v>
       </c>
       <c r="Z68" s="33" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="AA68" s="33" t="s">
-        <v>769</v>
-      </c>
-    </row>
-    <row r="69" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="69" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A69" s="52">
         <v>69</v>
       </c>
       <c r="B69" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C69" s="49" t="s">
         <v>94</v>
       </c>
       <c r="D69" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E69" s="47" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F69" s="57" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="G69" s="56" t="s">
         <v>9</v>
@@ -10149,10 +10141,10 @@
         <v>Ilu Vendedor</v>
       </c>
       <c r="P69" s="46" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="Q69" s="46" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="R69" s="33" t="s">
         <v>9</v>
@@ -10183,30 +10175,30 @@
         <v>9</v>
       </c>
       <c r="Z69" s="33" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="AA69" s="33" t="s">
-        <v>770</v>
-      </c>
-    </row>
-    <row r="70" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="70" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A70" s="52">
         <v>70</v>
       </c>
       <c r="B70" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C70" s="49" t="s">
         <v>94</v>
       </c>
       <c r="D70" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>98</v>
       </c>
       <c r="F70" s="57" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="G70" s="56" t="s">
         <v>9</v>
@@ -10240,10 +10232,10 @@
         <v>Ino Compra</v>
       </c>
       <c r="P70" s="46" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="Q70" s="46" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="R70" s="33" t="s">
         <v>9</v>
@@ -10274,30 +10266,30 @@
         <v>9</v>
       </c>
       <c r="Z70" s="33" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="AA70" s="33" t="s">
-        <v>771</v>
-      </c>
-    </row>
-    <row r="71" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="71" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A71" s="52">
         <v>71</v>
       </c>
       <c r="B71" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C71" s="49" t="s">
         <v>94</v>
       </c>
       <c r="D71" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E71" s="47" t="s">
         <v>98</v>
       </c>
       <c r="F71" s="57" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="G71" s="56" t="s">
         <v>9</v>
@@ -10334,7 +10326,7 @@
         <v>119</v>
       </c>
       <c r="Q71" s="46" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="R71" s="33" t="s">
         <v>9</v>
@@ -10365,30 +10357,30 @@
         <v>9</v>
       </c>
       <c r="Z71" s="33" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="AA71" s="33" t="s">
-        <v>772</v>
-      </c>
-    </row>
-    <row r="72" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="72" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A72" s="52">
         <v>72</v>
       </c>
       <c r="B72" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C72" s="49" t="s">
         <v>94</v>
       </c>
       <c r="D72" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E72" s="47" t="s">
         <v>98</v>
       </c>
       <c r="F72" s="57" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="G72" s="56" t="s">
         <v>9</v>
@@ -10409,19 +10401,19 @@
         <v>94</v>
       </c>
       <c r="M72" s="46" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="N72" s="46" t="s">
+        <v>468</v>
+      </c>
+      <c r="O72" s="46" t="s">
         <v>469</v>
       </c>
-      <c r="O72" s="46" t="s">
-        <v>470</v>
-      </c>
       <c r="P72" s="46" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="Q72" s="46" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="R72" s="33" t="s">
         <v>9</v>
@@ -10430,10 +10422,10 @@
         <v>94</v>
       </c>
       <c r="T72" s="33" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="U72" s="33" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="V72" s="33" t="s">
         <v>180</v>
@@ -10449,30 +10441,30 @@
         <v>9</v>
       </c>
       <c r="Z72" s="33" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="AA72" s="33" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="73" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="73" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A73" s="52">
         <v>73</v>
       </c>
       <c r="B73" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C73" s="49" t="s">
         <v>94</v>
       </c>
       <c r="D73" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E73" s="47" t="s">
         <v>98</v>
       </c>
       <c r="F73" s="57" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="G73" s="56" t="s">
         <v>9</v>
@@ -10509,7 +10501,7 @@
         <v>120</v>
       </c>
       <c r="Q73" s="46" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="R73" s="33" t="s">
         <v>9</v>
@@ -10540,30 +10532,30 @@
         <v>9</v>
       </c>
       <c r="Z73" s="33" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="AA73" s="33" t="s">
-        <v>773</v>
-      </c>
-    </row>
-    <row r="74" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="74" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A74" s="52">
         <v>74</v>
       </c>
       <c r="B74" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C74" s="49" t="s">
         <v>94</v>
       </c>
       <c r="D74" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E74" s="47" t="s">
         <v>98</v>
       </c>
       <c r="F74" s="57" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="G74" s="56" t="s">
         <v>9</v>
@@ -10600,7 +10592,7 @@
         <v>121</v>
       </c>
       <c r="Q74" s="46" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="R74" s="33" t="s">
         <v>9</v>
@@ -10631,30 +10623,30 @@
         <v>9</v>
       </c>
       <c r="Z74" s="33" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AA74" s="33" t="s">
-        <v>774</v>
-      </c>
-    </row>
-    <row r="75" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="75" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A75" s="52">
         <v>75</v>
       </c>
       <c r="B75" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C75" s="49" t="s">
         <v>94</v>
       </c>
       <c r="D75" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E75" s="47" t="s">
         <v>98</v>
       </c>
       <c r="F75" s="57" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="G75" s="56" t="s">
         <v>9</v>
@@ -10691,7 +10683,7 @@
         <v>178</v>
       </c>
       <c r="Q75" s="46" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="R75" s="33" t="s">
         <v>9</v>
@@ -10722,30 +10714,30 @@
         <v>9</v>
       </c>
       <c r="Z75" s="33" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="AA75" s="33" t="s">
-        <v>775</v>
-      </c>
-    </row>
-    <row r="76" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="76" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A76" s="52">
         <v>76</v>
       </c>
       <c r="B76" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C76" s="49" t="s">
         <v>94</v>
       </c>
       <c r="D76" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E76" s="47" t="s">
         <v>98</v>
       </c>
       <c r="F76" s="57" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="G76" s="56" t="s">
         <v>9</v>
@@ -10779,10 +10771,10 @@
         <v>Ino Projetista</v>
       </c>
       <c r="P76" s="46" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Q76" s="46" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="R76" s="33" t="s">
         <v>9</v>
@@ -10813,30 +10805,30 @@
         <v>9</v>
       </c>
       <c r="Z76" s="33" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="AA76" s="33" t="s">
-        <v>776</v>
-      </c>
-    </row>
-    <row r="77" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="77" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A77" s="52">
         <v>77</v>
       </c>
       <c r="B77" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C77" s="49" t="s">
         <v>94</v>
       </c>
       <c r="D77" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E77" s="47" t="s">
         <v>98</v>
       </c>
       <c r="F77" s="57" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="G77" s="56" t="s">
         <v>9</v>
@@ -10873,7 +10865,7 @@
         <v>118</v>
       </c>
       <c r="Q77" s="46" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="R77" s="33" t="s">
         <v>9</v>
@@ -10904,30 +10896,30 @@
         <v>9</v>
       </c>
       <c r="Z77" s="33" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="AA77" s="33" t="s">
-        <v>777</v>
-      </c>
-    </row>
-    <row r="78" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="78" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A78" s="52">
         <v>78</v>
       </c>
       <c r="B78" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C78" s="49" t="s">
         <v>94</v>
       </c>
       <c r="D78" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E78" s="47" t="s">
         <v>98</v>
       </c>
       <c r="F78" s="57" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="G78" s="56" t="s">
         <v>9</v>
@@ -10961,10 +10953,10 @@
         <v>Ino Vendedor</v>
       </c>
       <c r="P78" s="46" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="Q78" s="46" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="R78" s="33" t="s">
         <v>9</v>
@@ -10995,30 +10987,30 @@
         <v>9</v>
       </c>
       <c r="Z78" s="33" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="AA78" s="33" t="s">
-        <v>778</v>
-      </c>
-    </row>
-    <row r="79" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="79" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A79" s="52">
         <v>79</v>
       </c>
       <c r="B79" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C79" s="49" t="s">
         <v>94</v>
       </c>
       <c r="D79" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E79" s="47" t="s">
         <v>97</v>
       </c>
       <c r="F79" s="57" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="G79" s="56" t="s">
         <v>9</v>
@@ -11052,10 +11044,10 @@
         <v>Ins Compra</v>
       </c>
       <c r="P79" s="46" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="Q79" s="46" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="R79" s="33" t="s">
         <v>9</v>
@@ -11086,30 +11078,30 @@
         <v>9</v>
       </c>
       <c r="Z79" s="33" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="AA79" s="33" t="s">
-        <v>779</v>
-      </c>
-    </row>
-    <row r="80" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="80" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A80" s="52">
         <v>80</v>
       </c>
       <c r="B80" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C80" s="49" t="s">
         <v>94</v>
       </c>
       <c r="D80" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E80" s="47" t="s">
         <v>97</v>
       </c>
       <c r="F80" s="57" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="G80" s="56" t="s">
         <v>9</v>
@@ -11146,7 +11138,7 @@
         <v>107</v>
       </c>
       <c r="Q80" s="46" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="R80" s="33" t="s">
         <v>9</v>
@@ -11177,30 +11169,30 @@
         <v>9</v>
       </c>
       <c r="Z80" s="33" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="AA80" s="33" t="s">
-        <v>780</v>
-      </c>
-    </row>
-    <row r="81" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="81" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A81" s="52">
         <v>81</v>
       </c>
       <c r="B81" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C81" s="49" t="s">
         <v>94</v>
       </c>
       <c r="D81" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E81" s="47" t="s">
         <v>97</v>
       </c>
       <c r="F81" s="57" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="G81" s="56" t="s">
         <v>9</v>
@@ -11221,19 +11213,19 @@
         <v>94</v>
       </c>
       <c r="M81" s="46" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="N81" s="46" t="s">
+        <v>460</v>
+      </c>
+      <c r="O81" s="46" t="s">
         <v>461</v>
       </c>
-      <c r="O81" s="46" t="s">
-        <v>462</v>
-      </c>
       <c r="P81" s="46" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="Q81" s="46" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="R81" s="33" t="s">
         <v>9</v>
@@ -11242,10 +11234,10 @@
         <v>94</v>
       </c>
       <c r="T81" s="33" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="U81" s="33" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="V81" s="33" t="s">
         <v>180</v>
@@ -11261,30 +11253,30 @@
         <v>9</v>
       </c>
       <c r="Z81" s="33" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="AA81" s="33" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="82" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="82" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A82" s="52">
         <v>82</v>
       </c>
       <c r="B82" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C82" s="49" t="s">
         <v>94</v>
       </c>
       <c r="D82" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E82" s="47" t="s">
         <v>97</v>
       </c>
       <c r="F82" s="57" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="G82" s="56" t="s">
         <v>9</v>
@@ -11321,7 +11313,7 @@
         <v>108</v>
       </c>
       <c r="Q82" s="46" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="R82" s="33" t="s">
         <v>9</v>
@@ -11352,30 +11344,30 @@
         <v>9</v>
       </c>
       <c r="Z82" s="33" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="AA82" s="33" t="s">
-        <v>781</v>
-      </c>
-    </row>
-    <row r="83" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="83" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A83" s="52">
         <v>83</v>
       </c>
       <c r="B83" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C83" s="49" t="s">
         <v>94</v>
       </c>
       <c r="D83" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E83" s="47" t="s">
         <v>97</v>
       </c>
       <c r="F83" s="57" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="G83" s="56" t="s">
         <v>9</v>
@@ -11412,7 +11404,7 @@
         <v>109</v>
       </c>
       <c r="Q83" s="46" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="R83" s="33" t="s">
         <v>9</v>
@@ -11443,30 +11435,30 @@
         <v>9</v>
       </c>
       <c r="Z83" s="33" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AA83" s="33" t="s">
-        <v>782</v>
-      </c>
-    </row>
-    <row r="84" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="84" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A84" s="52">
         <v>84</v>
       </c>
       <c r="B84" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C84" s="49" t="s">
         <v>94</v>
       </c>
       <c r="D84" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E84" s="47" t="s">
         <v>97</v>
       </c>
       <c r="F84" s="57" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="G84" s="56" t="s">
         <v>9</v>
@@ -11503,7 +11495,7 @@
         <v>174</v>
       </c>
       <c r="Q84" s="46" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="R84" s="33" t="s">
         <v>9</v>
@@ -11534,30 +11526,30 @@
         <v>9</v>
       </c>
       <c r="Z84" s="33" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="AA84" s="33" t="s">
-        <v>783</v>
-      </c>
-    </row>
-    <row r="85" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="85" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A85" s="52">
         <v>85</v>
       </c>
       <c r="B85" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C85" s="49" t="s">
         <v>94</v>
       </c>
       <c r="D85" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E85" s="47" t="s">
         <v>97</v>
       </c>
       <c r="F85" s="57" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="G85" s="56" t="s">
         <v>9</v>
@@ -11591,10 +11583,10 @@
         <v>Ins Projetista</v>
       </c>
       <c r="P85" s="46" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="Q85" s="46" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="R85" s="33" t="s">
         <v>9</v>
@@ -11625,30 +11617,30 @@
         <v>9</v>
       </c>
       <c r="Z85" s="33" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="AA85" s="33" t="s">
-        <v>784</v>
-      </c>
-    </row>
-    <row r="86" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="86" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A86" s="52">
         <v>86</v>
       </c>
       <c r="B86" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C86" s="49" t="s">
         <v>94</v>
       </c>
       <c r="D86" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E86" s="47" t="s">
         <v>97</v>
       </c>
       <c r="F86" s="57" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="G86" s="56" t="s">
         <v>9</v>
@@ -11685,7 +11677,7 @@
         <v>106</v>
       </c>
       <c r="Q86" s="46" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="R86" s="33" t="s">
         <v>9</v>
@@ -11716,30 +11708,30 @@
         <v>9</v>
       </c>
       <c r="Z86" s="33" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="AA86" s="33" t="s">
-        <v>785</v>
-      </c>
-    </row>
-    <row r="87" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="87" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A87" s="52">
         <v>87</v>
       </c>
       <c r="B87" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C87" s="49" t="s">
         <v>94</v>
       </c>
       <c r="D87" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E87" s="47" t="s">
         <v>97</v>
       </c>
       <c r="F87" s="57" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="G87" s="56" t="s">
         <v>9</v>
@@ -11773,10 +11765,10 @@
         <v>Ins Vendedor</v>
       </c>
       <c r="P87" s="46" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="Q87" s="46" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="R87" s="33" t="s">
         <v>9</v>
@@ -11807,30 +11799,30 @@
         <v>9</v>
       </c>
       <c r="Z87" s="33" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="AA87" s="33" t="s">
-        <v>786</v>
-      </c>
-    </row>
-    <row r="88" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="88" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A88" s="52">
         <v>88</v>
       </c>
       <c r="B88" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C88" s="49" t="s">
         <v>94</v>
       </c>
       <c r="D88" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E88" s="47" t="s">
         <v>101</v>
       </c>
       <c r="F88" s="57" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="G88" s="56" t="s">
         <v>9</v>
@@ -11864,10 +11856,10 @@
         <v>Lab Compra</v>
       </c>
       <c r="P88" s="46" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="Q88" s="46" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="R88" s="33" t="s">
         <v>9</v>
@@ -11898,30 +11890,30 @@
         <v>9</v>
       </c>
       <c r="Z88" s="33" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="AA88" s="33" t="s">
-        <v>787</v>
-      </c>
-    </row>
-    <row r="89" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="89" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A89" s="52">
         <v>89</v>
       </c>
       <c r="B89" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C89" s="49" t="s">
         <v>94</v>
       </c>
       <c r="D89" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E89" s="47" t="s">
         <v>101</v>
       </c>
       <c r="F89" s="57" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="G89" s="56" t="s">
         <v>9</v>
@@ -11958,7 +11950,7 @@
         <v>115</v>
       </c>
       <c r="Q89" s="46" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="R89" s="33" t="s">
         <v>9</v>
@@ -11989,30 +11981,30 @@
         <v>9</v>
       </c>
       <c r="Z89" s="33" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="AA89" s="33" t="s">
-        <v>788</v>
-      </c>
-    </row>
-    <row r="90" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="90" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A90" s="52">
         <v>90</v>
       </c>
       <c r="B90" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C90" s="49" t="s">
         <v>94</v>
       </c>
       <c r="D90" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E90" s="47" t="s">
         <v>101</v>
       </c>
       <c r="F90" s="57" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="G90" s="56" t="s">
         <v>9</v>
@@ -12033,19 +12025,19 @@
         <v>94</v>
       </c>
       <c r="M90" s="46" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="N90" s="46" t="s">
+        <v>462</v>
+      </c>
+      <c r="O90" s="46" t="s">
         <v>463</v>
       </c>
-      <c r="O90" s="46" t="s">
-        <v>464</v>
-      </c>
       <c r="P90" s="46" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="Q90" s="46" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="R90" s="33" t="s">
         <v>9</v>
@@ -12054,10 +12046,10 @@
         <v>94</v>
       </c>
       <c r="T90" s="33" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="U90" s="33" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="V90" s="33" t="s">
         <v>180</v>
@@ -12073,30 +12065,30 @@
         <v>9</v>
       </c>
       <c r="Z90" s="33" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="AA90" s="33" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="91" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="91" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A91" s="52">
         <v>91</v>
       </c>
       <c r="B91" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C91" s="49" t="s">
         <v>94</v>
       </c>
       <c r="D91" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E91" s="47" t="s">
         <v>101</v>
       </c>
       <c r="F91" s="57" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="G91" s="56" t="s">
         <v>9</v>
@@ -12133,7 +12125,7 @@
         <v>116</v>
       </c>
       <c r="Q91" s="46" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="R91" s="33" t="s">
         <v>9</v>
@@ -12164,30 +12156,30 @@
         <v>9</v>
       </c>
       <c r="Z91" s="33" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="AA91" s="33" t="s">
-        <v>789</v>
-      </c>
-    </row>
-    <row r="92" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="92" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A92" s="52">
         <v>92</v>
       </c>
       <c r="B92" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C92" s="49" t="s">
         <v>94</v>
       </c>
       <c r="D92" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E92" s="47" t="s">
         <v>101</v>
       </c>
       <c r="F92" s="57" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="G92" s="56" t="s">
         <v>9</v>
@@ -12224,7 +12216,7 @@
         <v>117</v>
       </c>
       <c r="Q92" s="46" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="R92" s="33" t="s">
         <v>9</v>
@@ -12255,30 +12247,30 @@
         <v>9</v>
       </c>
       <c r="Z92" s="33" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AA92" s="33" t="s">
-        <v>790</v>
-      </c>
-    </row>
-    <row r="93" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="93" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A93" s="52">
         <v>93</v>
       </c>
       <c r="B93" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C93" s="49" t="s">
         <v>94</v>
       </c>
       <c r="D93" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E93" s="47" t="s">
         <v>101</v>
       </c>
       <c r="F93" s="57" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="G93" s="56" t="s">
         <v>9</v>
@@ -12315,7 +12307,7 @@
         <v>177</v>
       </c>
       <c r="Q93" s="46" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="R93" s="33" t="s">
         <v>9</v>
@@ -12346,30 +12338,30 @@
         <v>9</v>
       </c>
       <c r="Z93" s="33" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="AA93" s="33" t="s">
-        <v>791</v>
-      </c>
-    </row>
-    <row r="94" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="94" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A94" s="52">
         <v>94</v>
       </c>
       <c r="B94" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C94" s="49" t="s">
         <v>94</v>
       </c>
       <c r="D94" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E94" s="47" t="s">
         <v>101</v>
       </c>
       <c r="F94" s="57" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="G94" s="56" t="s">
         <v>9</v>
@@ -12403,10 +12395,10 @@
         <v>Lab Projetista</v>
       </c>
       <c r="P94" s="46" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="Q94" s="46" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="R94" s="33" t="s">
         <v>9</v>
@@ -12437,30 +12429,30 @@
         <v>9</v>
       </c>
       <c r="Z94" s="33" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="AA94" s="33" t="s">
-        <v>792</v>
-      </c>
-    </row>
-    <row r="95" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="95" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A95" s="52">
         <v>95</v>
       </c>
       <c r="B95" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C95" s="49" t="s">
         <v>94</v>
       </c>
       <c r="D95" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E95" s="47" t="s">
         <v>101</v>
       </c>
       <c r="F95" s="57" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="G95" s="56" t="s">
         <v>9</v>
@@ -12497,7 +12489,7 @@
         <v>114</v>
       </c>
       <c r="Q95" s="46" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="R95" s="33" t="s">
         <v>9</v>
@@ -12528,30 +12520,30 @@
         <v>9</v>
       </c>
       <c r="Z95" s="33" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="AA95" s="33" t="s">
-        <v>793</v>
-      </c>
-    </row>
-    <row r="96" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="96" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A96" s="52">
         <v>96</v>
       </c>
       <c r="B96" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C96" s="49" t="s">
         <v>94</v>
       </c>
       <c r="D96" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E96" s="47" t="s">
         <v>101</v>
       </c>
       <c r="F96" s="57" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G96" s="56" t="s">
         <v>9</v>
@@ -12585,10 +12577,10 @@
         <v>Lab Vendedor</v>
       </c>
       <c r="P96" s="46" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="Q96" s="46" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="R96" s="33" t="s">
         <v>9</v>
@@ -12619,30 +12611,30 @@
         <v>9</v>
       </c>
       <c r="Z96" s="33" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="AA96" s="33" t="s">
-        <v>794</v>
-      </c>
-    </row>
-    <row r="97" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="97" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A97" s="52">
         <v>97</v>
       </c>
       <c r="B97" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C97" s="49" t="s">
         <v>94</v>
       </c>
       <c r="D97" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E97" s="47" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="F97" s="57" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G97" s="56" t="s">
         <v>9</v>
@@ -12676,10 +12668,10 @@
         <v>Mec Compra</v>
       </c>
       <c r="P97" s="46" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="Q97" s="46" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="R97" s="33" t="s">
         <v>9</v>
@@ -12710,30 +12702,30 @@
         <v>9</v>
       </c>
       <c r="Z97" s="33" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="AA97" s="33" t="s">
-        <v>795</v>
-      </c>
-    </row>
-    <row r="98" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="98" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A98" s="52">
         <v>98</v>
       </c>
       <c r="B98" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C98" s="49" t="s">
         <v>94</v>
       </c>
       <c r="D98" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E98" s="47" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="F98" s="57" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="G98" s="56" t="s">
         <v>9</v>
@@ -12767,10 +12759,10 @@
         <v>Mec Consultor</v>
       </c>
       <c r="P98" s="46" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="Q98" s="46" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="R98" s="33" t="s">
         <v>9</v>
@@ -12801,30 +12793,30 @@
         <v>9</v>
       </c>
       <c r="Z98" s="33" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="AA98" s="33" t="s">
-        <v>796</v>
-      </c>
-    </row>
-    <row r="99" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="99" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A99" s="52">
         <v>99</v>
       </c>
       <c r="B99" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C99" s="49" t="s">
         <v>94</v>
       </c>
       <c r="D99" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E99" s="47" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="F99" s="57" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="G99" s="56" t="s">
         <v>9</v>
@@ -12845,19 +12837,19 @@
         <v>94</v>
       </c>
       <c r="M99" s="46" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="N99" s="46" t="s">
+        <v>466</v>
+      </c>
+      <c r="O99" s="46" t="s">
         <v>467</v>
       </c>
-      <c r="O99" s="46" t="s">
-        <v>468</v>
-      </c>
       <c r="P99" s="46" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="Q99" s="46" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="R99" s="33" t="s">
         <v>9</v>
@@ -12866,10 +12858,10 @@
         <v>94</v>
       </c>
       <c r="T99" s="33" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="U99" s="33" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="V99" s="33" t="s">
         <v>180</v>
@@ -12885,30 +12877,30 @@
         <v>9</v>
       </c>
       <c r="Z99" s="33" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="AA99" s="33" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="100" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="100" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A100" s="52">
         <v>100</v>
       </c>
       <c r="B100" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C100" s="49" t="s">
         <v>94</v>
       </c>
       <c r="D100" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E100" s="47" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="F100" s="57" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="G100" s="56" t="s">
         <v>9</v>
@@ -12942,10 +12934,10 @@
         <v>Mec Empresa Consultora</v>
       </c>
       <c r="P100" s="46" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="Q100" s="46" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="R100" s="33" t="s">
         <v>9</v>
@@ -12976,30 +12968,30 @@
         <v>9</v>
       </c>
       <c r="Z100" s="33" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="AA100" s="33" t="s">
-        <v>797</v>
-      </c>
-    </row>
-    <row r="101" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="101" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A101" s="52">
         <v>101</v>
       </c>
       <c r="B101" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C101" s="49" t="s">
         <v>94</v>
       </c>
       <c r="D101" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E101" s="47" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="F101" s="57" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="G101" s="56" t="s">
         <v>9</v>
@@ -13033,10 +13025,10 @@
         <v>Mec Fabricante</v>
       </c>
       <c r="P101" s="46" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="Q101" s="46" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="R101" s="33" t="s">
         <v>9</v>
@@ -13067,30 +13059,30 @@
         <v>9</v>
       </c>
       <c r="Z101" s="33" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AA101" s="33" t="s">
-        <v>798</v>
-      </c>
-    </row>
-    <row r="102" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="102" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A102" s="52">
         <v>102</v>
       </c>
       <c r="B102" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C102" s="49" t="s">
         <v>94</v>
       </c>
       <c r="D102" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E102" s="47" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="F102" s="57" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="G102" s="56" t="s">
         <v>9</v>
@@ -13124,10 +13116,10 @@
         <v>Mec Fornecedor</v>
       </c>
       <c r="P102" s="46" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="Q102" s="46" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="R102" s="33" t="s">
         <v>9</v>
@@ -13158,30 +13150,30 @@
         <v>9</v>
       </c>
       <c r="Z102" s="33" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="AA102" s="33" t="s">
-        <v>799</v>
-      </c>
-    </row>
-    <row r="103" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="103" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A103" s="52">
         <v>103</v>
       </c>
       <c r="B103" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C103" s="49" t="s">
         <v>94</v>
       </c>
       <c r="D103" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E103" s="47" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="F103" s="57" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="G103" s="56" t="s">
         <v>9</v>
@@ -13215,10 +13207,10 @@
         <v>Mec Projetista</v>
       </c>
       <c r="P103" s="46" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="Q103" s="46" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="R103" s="33" t="s">
         <v>9</v>
@@ -13249,30 +13241,30 @@
         <v>9</v>
       </c>
       <c r="Z103" s="33" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="AA103" s="33" t="s">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="104" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="104" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A104" s="52">
         <v>104</v>
       </c>
       <c r="B104" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C104" s="49" t="s">
         <v>94</v>
       </c>
       <c r="D104" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E104" s="47" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="F104" s="57" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="G104" s="56" t="s">
         <v>9</v>
@@ -13306,10 +13298,10 @@
         <v>Mec Serviço</v>
       </c>
       <c r="P104" s="46" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="Q104" s="46" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="R104" s="33" t="s">
         <v>9</v>
@@ -13340,30 +13332,30 @@
         <v>9</v>
       </c>
       <c r="Z104" s="33" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="AA104" s="33" t="s">
-        <v>801</v>
-      </c>
-    </row>
-    <row r="105" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="105" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A105" s="52">
         <v>105</v>
       </c>
       <c r="B105" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C105" s="49" t="s">
         <v>94</v>
       </c>
       <c r="D105" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E105" s="47" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="F105" s="57" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="G105" s="56" t="s">
         <v>9</v>
@@ -13397,10 +13389,10 @@
         <v>Mec Vendedor</v>
       </c>
       <c r="P105" s="46" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="Q105" s="46" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="R105" s="33" t="s">
         <v>9</v>
@@ -13431,30 +13423,30 @@
         <v>9</v>
       </c>
       <c r="Z105" s="33" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="AA105" s="33" t="s">
-        <v>802</v>
-      </c>
-    </row>
-    <row r="106" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="106" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A106" s="52">
         <v>106</v>
       </c>
       <c r="B106" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C106" s="49" t="s">
         <v>94</v>
       </c>
       <c r="D106" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E106" s="47" t="s">
         <v>99</v>
       </c>
       <c r="F106" s="57" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="G106" s="56" t="s">
         <v>9</v>
@@ -13488,10 +13480,10 @@
         <v>Mob Compra</v>
       </c>
       <c r="P106" s="46" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="Q106" s="46" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="R106" s="33" t="s">
         <v>9</v>
@@ -13522,30 +13514,30 @@
         <v>9</v>
       </c>
       <c r="Z106" s="33" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="AA106" s="33" t="s">
-        <v>803</v>
-      </c>
-    </row>
-    <row r="107" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="107" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A107" s="52">
         <v>107</v>
       </c>
       <c r="B107" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C107" s="49" t="s">
         <v>94</v>
       </c>
       <c r="D107" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E107" s="47" t="s">
         <v>99</v>
       </c>
       <c r="F107" s="57" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="G107" s="56" t="s">
         <v>9</v>
@@ -13582,7 +13574,7 @@
         <v>111</v>
       </c>
       <c r="Q107" s="46" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="R107" s="33" t="s">
         <v>9</v>
@@ -13613,30 +13605,30 @@
         <v>9</v>
       </c>
       <c r="Z107" s="33" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="AA107" s="33" t="s">
-        <v>804</v>
-      </c>
-    </row>
-    <row r="108" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="108" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A108" s="52">
         <v>108</v>
       </c>
       <c r="B108" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C108" s="49" t="s">
         <v>94</v>
       </c>
       <c r="D108" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E108" s="47" t="s">
         <v>99</v>
       </c>
       <c r="F108" s="57" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="G108" s="56" t="s">
         <v>9</v>
@@ -13657,19 +13649,19 @@
         <v>94</v>
       </c>
       <c r="M108" s="46" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="N108" s="46" t="s">
+        <v>464</v>
+      </c>
+      <c r="O108" s="46" t="s">
         <v>465</v>
       </c>
-      <c r="O108" s="46" t="s">
-        <v>466</v>
-      </c>
       <c r="P108" s="46" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="Q108" s="46" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="R108" s="33" t="s">
         <v>9</v>
@@ -13678,10 +13670,10 @@
         <v>94</v>
       </c>
       <c r="T108" s="33" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="U108" s="33" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="V108" s="33" t="s">
         <v>180</v>
@@ -13697,30 +13689,30 @@
         <v>9</v>
       </c>
       <c r="Z108" s="33" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="AA108" s="33" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="109" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="109" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A109" s="52">
         <v>109</v>
       </c>
       <c r="B109" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C109" s="49" t="s">
         <v>94</v>
       </c>
       <c r="D109" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E109" s="47" t="s">
         <v>99</v>
       </c>
       <c r="F109" s="57" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="G109" s="56" t="s">
         <v>9</v>
@@ -13757,7 +13749,7 @@
         <v>112</v>
       </c>
       <c r="Q109" s="46" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="R109" s="33" t="s">
         <v>9</v>
@@ -13788,30 +13780,30 @@
         <v>9</v>
       </c>
       <c r="Z109" s="33" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="AA109" s="33" t="s">
-        <v>805</v>
-      </c>
-    </row>
-    <row r="110" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="110" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A110" s="52">
         <v>110</v>
       </c>
       <c r="B110" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C110" s="49" t="s">
         <v>94</v>
       </c>
       <c r="D110" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E110" s="47" t="s">
         <v>99</v>
       </c>
       <c r="F110" s="57" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="G110" s="56" t="s">
         <v>9</v>
@@ -13848,7 +13840,7 @@
         <v>113</v>
       </c>
       <c r="Q110" s="46" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="R110" s="33" t="s">
         <v>9</v>
@@ -13879,30 +13871,30 @@
         <v>9</v>
       </c>
       <c r="Z110" s="33" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AA110" s="33" t="s">
-        <v>806</v>
-      </c>
-    </row>
-    <row r="111" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="111" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A111" s="52">
         <v>111</v>
       </c>
       <c r="B111" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C111" s="49" t="s">
         <v>94</v>
       </c>
       <c r="D111" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E111" s="47" t="s">
         <v>99</v>
       </c>
       <c r="F111" s="57" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="G111" s="56" t="s">
         <v>9</v>
@@ -13939,7 +13931,7 @@
         <v>175</v>
       </c>
       <c r="Q111" s="46" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="R111" s="33" t="s">
         <v>9</v>
@@ -13970,30 +13962,30 @@
         <v>9</v>
       </c>
       <c r="Z111" s="33" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="AA111" s="33" t="s">
-        <v>807</v>
-      </c>
-    </row>
-    <row r="112" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="112" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A112" s="52">
         <v>112</v>
       </c>
       <c r="B112" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C112" s="49" t="s">
         <v>94</v>
       </c>
       <c r="D112" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E112" s="47" t="s">
         <v>99</v>
       </c>
       <c r="F112" s="57" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="G112" s="56" t="s">
         <v>9</v>
@@ -14027,10 +14019,10 @@
         <v>Mob Projetista</v>
       </c>
       <c r="P112" s="46" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="Q112" s="46" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="R112" s="33" t="s">
         <v>9</v>
@@ -14061,30 +14053,30 @@
         <v>9</v>
       </c>
       <c r="Z112" s="33" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="AA112" s="33" t="s">
-        <v>808</v>
-      </c>
-    </row>
-    <row r="113" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="113" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A113" s="52">
         <v>113</v>
       </c>
       <c r="B113" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C113" s="49" t="s">
         <v>94</v>
       </c>
       <c r="D113" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E113" s="47" t="s">
         <v>99</v>
       </c>
       <c r="F113" s="57" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="G113" s="56" t="s">
         <v>9</v>
@@ -14121,7 +14113,7 @@
         <v>110</v>
       </c>
       <c r="Q113" s="46" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="R113" s="33" t="s">
         <v>9</v>
@@ -14152,30 +14144,30 @@
         <v>9</v>
       </c>
       <c r="Z113" s="33" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="AA113" s="33" t="s">
-        <v>809</v>
-      </c>
-    </row>
-    <row r="114" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="114" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A114" s="52">
         <v>114</v>
       </c>
       <c r="B114" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C114" s="49" t="s">
         <v>94</v>
       </c>
       <c r="D114" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E114" s="47" t="s">
         <v>99</v>
       </c>
       <c r="F114" s="57" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="G114" s="56" t="s">
         <v>9</v>
@@ -14209,10 +14201,10 @@
         <v>Mob Vendedor</v>
       </c>
       <c r="P114" s="46" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="Q114" s="46" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="R114" s="33" t="s">
         <v>9</v>
@@ -14243,30 +14235,30 @@
         <v>9</v>
       </c>
       <c r="Z114" s="33" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="AA114" s="33" t="s">
-        <v>810</v>
-      </c>
-    </row>
-    <row r="115" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="115" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A115" s="52">
         <v>115</v>
       </c>
       <c r="B115" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C115" s="49" t="s">
         <v>94</v>
       </c>
       <c r="D115" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E115" s="47" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="F115" s="57" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="G115" s="56" t="s">
         <v>9</v>
@@ -14300,10 +14292,10 @@
         <v>Tel Compra</v>
       </c>
       <c r="P115" s="46" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="Q115" s="46" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="R115" s="33" t="s">
         <v>9</v>
@@ -14334,30 +14326,30 @@
         <v>9</v>
       </c>
       <c r="Z115" s="33" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="AA115" s="33" t="s">
-        <v>811</v>
-      </c>
-    </row>
-    <row r="116" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="116" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A116" s="52">
         <v>116</v>
       </c>
       <c r="B116" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C116" s="49" t="s">
         <v>94</v>
       </c>
       <c r="D116" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E116" s="47" t="s">
+        <v>360</v>
+      </c>
+      <c r="F116" s="57" t="s">
         <v>361</v>
-      </c>
-      <c r="F116" s="57" t="s">
-        <v>362</v>
       </c>
       <c r="G116" s="56" t="s">
         <v>9</v>
@@ -14391,10 +14383,10 @@
         <v>Tel Consultor</v>
       </c>
       <c r="P116" s="46" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="Q116" s="46" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="R116" s="33" t="s">
         <v>9</v>
@@ -14425,30 +14417,30 @@
         <v>9</v>
       </c>
       <c r="Z116" s="33" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="AA116" s="33" t="s">
-        <v>812</v>
-      </c>
-    </row>
-    <row r="117" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="117" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A117" s="52">
         <v>117</v>
       </c>
       <c r="B117" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C117" s="49" t="s">
         <v>94</v>
       </c>
       <c r="D117" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E117" s="47" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="F117" s="57" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="G117" s="56" t="s">
         <v>9</v>
@@ -14469,19 +14461,19 @@
         <v>94</v>
       </c>
       <c r="M117" s="46" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="N117" s="46" t="s">
+        <v>476</v>
+      </c>
+      <c r="O117" s="46" t="s">
         <v>477</v>
       </c>
-      <c r="O117" s="46" t="s">
-        <v>478</v>
-      </c>
       <c r="P117" s="46" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="Q117" s="46" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="R117" s="33" t="s">
         <v>9</v>
@@ -14490,10 +14482,10 @@
         <v>94</v>
       </c>
       <c r="T117" s="33" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="U117" s="33" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="V117" s="33" t="s">
         <v>180</v>
@@ -14509,30 +14501,30 @@
         <v>9</v>
       </c>
       <c r="Z117" s="33" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="AA117" s="33" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="118" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="118" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A118" s="52">
         <v>118</v>
       </c>
       <c r="B118" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C118" s="49" t="s">
         <v>94</v>
       </c>
       <c r="D118" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E118" s="47" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="F118" s="57" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="G118" s="56" t="s">
         <v>9</v>
@@ -14566,10 +14558,10 @@
         <v>Tel Empresa Consultora</v>
       </c>
       <c r="P118" s="46" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="Q118" s="46" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="R118" s="33" t="s">
         <v>9</v>
@@ -14600,30 +14592,30 @@
         <v>9</v>
       </c>
       <c r="Z118" s="33" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="AA118" s="33" t="s">
-        <v>813</v>
-      </c>
-    </row>
-    <row r="119" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="119" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A119" s="52">
         <v>119</v>
       </c>
       <c r="B119" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C119" s="49" t="s">
         <v>94</v>
       </c>
       <c r="D119" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E119" s="47" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="F119" s="57" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="G119" s="56" t="s">
         <v>9</v>
@@ -14657,10 +14649,10 @@
         <v>Tel Fabricante</v>
       </c>
       <c r="P119" s="46" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="Q119" s="46" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="R119" s="33" t="s">
         <v>9</v>
@@ -14691,30 +14683,30 @@
         <v>9</v>
       </c>
       <c r="Z119" s="33" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AA119" s="33" t="s">
-        <v>814</v>
-      </c>
-    </row>
-    <row r="120" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="120" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A120" s="52">
         <v>120</v>
       </c>
       <c r="B120" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C120" s="49" t="s">
         <v>94</v>
       </c>
       <c r="D120" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E120" s="47" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="F120" s="57" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="G120" s="56" t="s">
         <v>9</v>
@@ -14748,10 +14740,10 @@
         <v>Tel Fornecedor</v>
       </c>
       <c r="P120" s="46" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="Q120" s="46" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="R120" s="33" t="s">
         <v>9</v>
@@ -14782,30 +14774,30 @@
         <v>9</v>
       </c>
       <c r="Z120" s="33" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="AA120" s="33" t="s">
-        <v>815</v>
-      </c>
-    </row>
-    <row r="121" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="121" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A121" s="52">
         <v>121</v>
       </c>
       <c r="B121" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C121" s="49" t="s">
         <v>94</v>
       </c>
       <c r="D121" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E121" s="47" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="F121" s="57" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="G121" s="56" t="s">
         <v>9</v>
@@ -14839,10 +14831,10 @@
         <v>Tel Projetista</v>
       </c>
       <c r="P121" s="46" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="Q121" s="46" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="R121" s="33" t="s">
         <v>9</v>
@@ -14873,30 +14865,30 @@
         <v>9</v>
       </c>
       <c r="Z121" s="33" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="AA121" s="33" t="s">
-        <v>816</v>
-      </c>
-    </row>
-    <row r="122" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="122" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A122" s="52">
         <v>122</v>
       </c>
       <c r="B122" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C122" s="49" t="s">
         <v>94</v>
       </c>
       <c r="D122" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E122" s="47" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="F122" s="57" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="G122" s="56" t="s">
         <v>9</v>
@@ -14930,10 +14922,10 @@
         <v>Tel Serviço</v>
       </c>
       <c r="P122" s="46" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="Q122" s="46" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="R122" s="33" t="s">
         <v>9</v>
@@ -14964,30 +14956,30 @@
         <v>9</v>
       </c>
       <c r="Z122" s="33" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="AA122" s="33" t="s">
-        <v>817</v>
-      </c>
-    </row>
-    <row r="123" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="123" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A123" s="52">
         <v>123</v>
       </c>
       <c r="B123" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C123" s="49" t="s">
         <v>94</v>
       </c>
       <c r="D123" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E123" s="47" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="F123" s="57" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="G123" s="56" t="s">
         <v>9</v>
@@ -15021,10 +15013,10 @@
         <v>Tel Vendedor</v>
       </c>
       <c r="P123" s="46" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="Q123" s="46" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="R123" s="33" t="s">
         <v>9</v>
@@ -15055,27 +15047,27 @@
         <v>9</v>
       </c>
       <c r="Z123" s="33" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="AA123" s="33" t="s">
-        <v>818</v>
-      </c>
-    </row>
-    <row r="124" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="124" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A124" s="52">
         <v>124</v>
       </c>
       <c r="B124" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C124" s="49" t="s">
         <v>157</v>
       </c>
       <c r="D124" s="47" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E124" s="47" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F124" s="47" t="s">
         <v>158</v>
@@ -15115,7 +15107,7 @@
         <v>188</v>
       </c>
       <c r="Q124" s="46" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="R124" s="33" t="s">
         <v>9</v>
@@ -15146,27 +15138,27 @@
         <v>9</v>
       </c>
       <c r="Z124" s="58" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="AA124" s="33" t="s">
-        <v>819</v>
-      </c>
-    </row>
-    <row r="125" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="125" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A125" s="52">
         <v>125</v>
       </c>
       <c r="B125" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C125" s="49" t="s">
         <v>157</v>
       </c>
       <c r="D125" s="47" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E125" s="47" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F125" s="47" t="s">
         <v>130</v>
@@ -15206,7 +15198,7 @@
         <v>214</v>
       </c>
       <c r="Q125" s="46" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="R125" s="33" t="s">
         <v>9</v>
@@ -15237,27 +15229,27 @@
         <v>9</v>
       </c>
       <c r="Z125" s="58" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="AA125" s="33" t="s">
-        <v>820</v>
-      </c>
-    </row>
-    <row r="126" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="126" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A126" s="52">
         <v>126</v>
       </c>
       <c r="B126" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C126" s="49" t="s">
         <v>157</v>
       </c>
       <c r="D126" s="47" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E126" s="47" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F126" s="47" t="s">
         <v>131</v>
@@ -15297,7 +15289,7 @@
         <v>189</v>
       </c>
       <c r="Q126" s="46" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="R126" s="33" t="s">
         <v>9</v>
@@ -15328,27 +15320,27 @@
         <v>9</v>
       </c>
       <c r="Z126" s="58" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="AA126" s="33" t="s">
-        <v>821</v>
-      </c>
-    </row>
-    <row r="127" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="127" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A127" s="52">
         <v>127</v>
       </c>
       <c r="B127" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C127" s="49" t="s">
         <v>157</v>
       </c>
       <c r="D127" s="47" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E127" s="47" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F127" s="47" t="s">
         <v>132</v>
@@ -15388,7 +15380,7 @@
         <v>213</v>
       </c>
       <c r="Q127" s="46" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="R127" s="33" t="s">
         <v>9</v>
@@ -15419,27 +15411,27 @@
         <v>9</v>
       </c>
       <c r="Z127" s="58" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="AA127" s="33" t="s">
-        <v>822</v>
-      </c>
-    </row>
-    <row r="128" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="128" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A128" s="52">
         <v>128</v>
       </c>
       <c r="B128" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C128" s="49" t="s">
         <v>157</v>
       </c>
       <c r="D128" s="47" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E128" s="47" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F128" s="47" t="s">
         <v>133</v>
@@ -15479,7 +15471,7 @@
         <v>187</v>
       </c>
       <c r="Q128" s="46" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="R128" s="33" t="s">
         <v>9</v>
@@ -15510,27 +15502,27 @@
         <v>9</v>
       </c>
       <c r="Z128" s="58" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="AA128" s="33" t="s">
-        <v>823</v>
-      </c>
-    </row>
-    <row r="129" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="129" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A129" s="52">
         <v>129</v>
       </c>
       <c r="B129" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C129" s="49" t="s">
         <v>157</v>
       </c>
       <c r="D129" s="47" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E129" s="47" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F129" s="47" t="s">
         <v>134</v>
@@ -15570,7 +15562,7 @@
         <v>190</v>
       </c>
       <c r="Q129" s="46" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="R129" s="33" t="s">
         <v>9</v>
@@ -15601,27 +15593,27 @@
         <v>9</v>
       </c>
       <c r="Z129" s="58" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="AA129" s="33" t="s">
-        <v>824</v>
-      </c>
-    </row>
-    <row r="130" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="130" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A130" s="52">
         <v>130</v>
       </c>
       <c r="B130" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C130" s="49" t="s">
         <v>157</v>
       </c>
       <c r="D130" s="47" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E130" s="47" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F130" s="47" t="s">
         <v>135</v>
@@ -15661,7 +15653,7 @@
         <v>212</v>
       </c>
       <c r="Q130" s="46" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="R130" s="33" t="s">
         <v>9</v>
@@ -15692,27 +15684,27 @@
         <v>9</v>
       </c>
       <c r="Z130" s="58" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="AA130" s="33" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="131" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="131" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A131" s="52">
         <v>131</v>
       </c>
       <c r="B131" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C131" s="49" t="s">
         <v>157</v>
       </c>
       <c r="D131" s="47" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E131" s="47" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F131" s="47" t="s">
         <v>136</v>
@@ -15752,7 +15744,7 @@
         <v>191</v>
       </c>
       <c r="Q131" s="46" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="R131" s="33" t="s">
         <v>9</v>
@@ -15783,27 +15775,27 @@
         <v>9</v>
       </c>
       <c r="Z131" s="58" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="AA131" s="33" t="s">
-        <v>826</v>
-      </c>
-    </row>
-    <row r="132" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="132" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A132" s="52">
         <v>132</v>
       </c>
       <c r="B132" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C132" s="49" t="s">
         <v>157</v>
       </c>
       <c r="D132" s="47" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E132" s="47" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F132" s="47" t="s">
         <v>137</v>
@@ -15843,7 +15835,7 @@
         <v>211</v>
       </c>
       <c r="Q132" s="46" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="R132" s="33" t="s">
         <v>9</v>
@@ -15874,27 +15866,27 @@
         <v>9</v>
       </c>
       <c r="Z132" s="58" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="AA132" s="33" t="s">
-        <v>827</v>
-      </c>
-    </row>
-    <row r="133" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="133" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A133" s="52">
         <v>133</v>
       </c>
       <c r="B133" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C133" s="49" t="s">
         <v>157</v>
       </c>
       <c r="D133" s="47" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E133" s="47" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F133" s="47" t="s">
         <v>138</v>
@@ -15934,7 +15926,7 @@
         <v>192</v>
       </c>
       <c r="Q133" s="46" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="R133" s="33" t="s">
         <v>9</v>
@@ -15965,27 +15957,27 @@
         <v>9</v>
       </c>
       <c r="Z133" s="58" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="AA133" s="33" t="s">
-        <v>828</v>
-      </c>
-    </row>
-    <row r="134" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="134" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A134" s="52">
         <v>134</v>
       </c>
       <c r="B134" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C134" s="49" t="s">
         <v>157</v>
       </c>
       <c r="D134" s="47" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E134" s="47" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F134" s="47" t="s">
         <v>139</v>
@@ -16025,7 +16017,7 @@
         <v>193</v>
       </c>
       <c r="Q134" s="46" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="R134" s="33" t="s">
         <v>9</v>
@@ -16056,27 +16048,27 @@
         <v>9</v>
       </c>
       <c r="Z134" s="58" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="AA134" s="33" t="s">
-        <v>829</v>
-      </c>
-    </row>
-    <row r="135" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="135" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A135" s="52">
         <v>135</v>
       </c>
       <c r="B135" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C135" s="49" t="s">
         <v>157</v>
       </c>
       <c r="D135" s="47" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E135" s="47" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F135" s="47" t="s">
         <v>140</v>
@@ -16116,7 +16108,7 @@
         <v>179</v>
       </c>
       <c r="Q135" s="46" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="R135" s="33" t="s">
         <v>9</v>
@@ -16147,27 +16139,27 @@
         <v>9</v>
       </c>
       <c r="Z135" s="58" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AA135" s="33" t="s">
-        <v>830</v>
-      </c>
-    </row>
-    <row r="136" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="136" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A136" s="52">
         <v>136</v>
       </c>
       <c r="B136" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C136" s="49" t="s">
         <v>157</v>
       </c>
       <c r="D136" s="47" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E136" s="47" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F136" s="47" t="s">
         <v>141</v>
@@ -16207,7 +16199,7 @@
         <v>194</v>
       </c>
       <c r="Q136" s="46" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="R136" s="33" t="s">
         <v>9</v>
@@ -16238,27 +16230,27 @@
         <v>9</v>
       </c>
       <c r="Z136" s="58" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="AA136" s="33" t="s">
-        <v>831</v>
-      </c>
-    </row>
-    <row r="137" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="137" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A137" s="52">
         <v>137</v>
       </c>
       <c r="B137" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C137" s="49" t="s">
         <v>157</v>
       </c>
       <c r="D137" s="47" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E137" s="47" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F137" s="47" t="s">
         <v>142</v>
@@ -16298,7 +16290,7 @@
         <v>199</v>
       </c>
       <c r="Q137" s="46" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="R137" s="33" t="s">
         <v>9</v>
@@ -16329,27 +16321,27 @@
         <v>9</v>
       </c>
       <c r="Z137" s="58" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="AA137" s="33" t="s">
-        <v>832</v>
-      </c>
-    </row>
-    <row r="138" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="138" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A138" s="52">
         <v>138</v>
       </c>
       <c r="B138" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C138" s="49" t="s">
         <v>157</v>
       </c>
       <c r="D138" s="47" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E138" s="47" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F138" s="47" t="s">
         <v>143</v>
@@ -16389,7 +16381,7 @@
         <v>200</v>
       </c>
       <c r="Q138" s="46" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="R138" s="33" t="s">
         <v>9</v>
@@ -16420,27 +16412,27 @@
         <v>9</v>
       </c>
       <c r="Z138" s="58" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="AA138" s="33" t="s">
-        <v>833</v>
-      </c>
-    </row>
-    <row r="139" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="139" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A139" s="52">
         <v>139</v>
       </c>
       <c r="B139" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C139" s="49" t="s">
         <v>157</v>
       </c>
       <c r="D139" s="47" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E139" s="47" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F139" s="47" t="s">
         <v>144</v>
@@ -16480,7 +16472,7 @@
         <v>198</v>
       </c>
       <c r="Q139" s="46" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="R139" s="33" t="s">
         <v>9</v>
@@ -16511,27 +16503,27 @@
         <v>9</v>
       </c>
       <c r="Z139" s="58" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="AA139" s="33" t="s">
-        <v>834</v>
-      </c>
-    </row>
-    <row r="140" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="140" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A140" s="52">
         <v>140</v>
       </c>
       <c r="B140" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C140" s="49" t="s">
         <v>157</v>
       </c>
       <c r="D140" s="47" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E140" s="47" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F140" s="47" t="s">
         <v>145</v>
@@ -16571,7 +16563,7 @@
         <v>197</v>
       </c>
       <c r="Q140" s="46" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="R140" s="33" t="s">
         <v>9</v>
@@ -16602,27 +16594,27 @@
         <v>9</v>
       </c>
       <c r="Z140" s="58" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="AA140" s="33" t="s">
-        <v>835</v>
-      </c>
-    </row>
-    <row r="141" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="141" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A141" s="52">
         <v>141</v>
       </c>
       <c r="B141" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C141" s="49" t="s">
         <v>157</v>
       </c>
       <c r="D141" s="47" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E141" s="47" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F141" s="47" t="s">
         <v>146</v>
@@ -16662,7 +16654,7 @@
         <v>201</v>
       </c>
       <c r="Q141" s="46" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="R141" s="33" t="s">
         <v>9</v>
@@ -16693,27 +16685,27 @@
         <v>9</v>
       </c>
       <c r="Z141" s="58" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="AA141" s="33" t="s">
-        <v>836</v>
-      </c>
-    </row>
-    <row r="142" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="142" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A142" s="52">
         <v>142</v>
       </c>
       <c r="B142" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C142" s="49" t="s">
         <v>157</v>
       </c>
       <c r="D142" s="47" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E142" s="47" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F142" s="47" t="s">
         <v>147</v>
@@ -16753,7 +16745,7 @@
         <v>195</v>
       </c>
       <c r="Q142" s="46" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="R142" s="33" t="s">
         <v>9</v>
@@ -16784,27 +16776,27 @@
         <v>9</v>
       </c>
       <c r="Z142" s="58" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="AA142" s="33" t="s">
-        <v>837</v>
-      </c>
-    </row>
-    <row r="143" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="143" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A143" s="52">
         <v>143</v>
       </c>
       <c r="B143" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C143" s="49" t="s">
         <v>157</v>
       </c>
       <c r="D143" s="47" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E143" s="47" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F143" s="47" t="s">
         <v>148</v>
@@ -16844,7 +16836,7 @@
         <v>196</v>
       </c>
       <c r="Q143" s="46" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="R143" s="33" t="s">
         <v>9</v>
@@ -16875,27 +16867,27 @@
         <v>9</v>
       </c>
       <c r="Z143" s="58" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="AA143" s="33" t="s">
-        <v>838</v>
-      </c>
-    </row>
-    <row r="144" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="144" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A144" s="52">
         <v>144</v>
       </c>
       <c r="B144" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C144" s="49" t="s">
         <v>157</v>
       </c>
       <c r="D144" s="47" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E144" s="47" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F144" s="47" t="s">
         <v>149</v>
@@ -16935,7 +16927,7 @@
         <v>202</v>
       </c>
       <c r="Q144" s="46" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="R144" s="33" t="s">
         <v>9</v>
@@ -16966,27 +16958,27 @@
         <v>9</v>
       </c>
       <c r="Z144" s="58" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="AA144" s="33" t="s">
-        <v>839</v>
-      </c>
-    </row>
-    <row r="145" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="145" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A145" s="52">
         <v>145</v>
       </c>
       <c r="B145" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C145" s="49" t="s">
         <v>157</v>
       </c>
       <c r="D145" s="47" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E145" s="47" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F145" s="47" t="s">
         <v>150</v>
@@ -17026,7 +17018,7 @@
         <v>203</v>
       </c>
       <c r="Q145" s="46" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="R145" s="33" t="s">
         <v>9</v>
@@ -17057,27 +17049,27 @@
         <v>9</v>
       </c>
       <c r="Z145" s="58" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="AA145" s="33" t="s">
-        <v>840</v>
-      </c>
-    </row>
-    <row r="146" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="146" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A146" s="52">
         <v>146</v>
       </c>
       <c r="B146" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C146" s="49" t="s">
         <v>157</v>
       </c>
       <c r="D146" s="47" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E146" s="47" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F146" s="47" t="s">
         <v>151</v>
@@ -17117,7 +17109,7 @@
         <v>204</v>
       </c>
       <c r="Q146" s="46" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="R146" s="33" t="s">
         <v>9</v>
@@ -17148,27 +17140,27 @@
         <v>9</v>
       </c>
       <c r="Z146" s="58" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="AA146" s="33" t="s">
-        <v>841</v>
-      </c>
-    </row>
-    <row r="147" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="147" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A147" s="52">
         <v>147</v>
       </c>
       <c r="B147" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C147" s="49" t="s">
         <v>157</v>
       </c>
       <c r="D147" s="47" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E147" s="47" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F147" s="47" t="s">
         <v>152</v>
@@ -17208,7 +17200,7 @@
         <v>205</v>
       </c>
       <c r="Q147" s="46" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="R147" s="33" t="s">
         <v>9</v>
@@ -17239,27 +17231,27 @@
         <v>9</v>
       </c>
       <c r="Z147" s="58" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="AA147" s="33" t="s">
-        <v>842</v>
-      </c>
-    </row>
-    <row r="148" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="148" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A148" s="52">
         <v>148</v>
       </c>
       <c r="B148" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C148" s="49" t="s">
         <v>157</v>
       </c>
       <c r="D148" s="47" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E148" s="47" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F148" s="47" t="s">
         <v>153</v>
@@ -17299,7 +17291,7 @@
         <v>206</v>
       </c>
       <c r="Q148" s="46" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="R148" s="33" t="s">
         <v>9</v>
@@ -17330,27 +17322,27 @@
         <v>9</v>
       </c>
       <c r="Z148" s="58" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="AA148" s="33" t="s">
-        <v>843</v>
-      </c>
-    </row>
-    <row r="149" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="149" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A149" s="52">
         <v>149</v>
       </c>
       <c r="B149" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C149" s="49" t="s">
         <v>157</v>
       </c>
       <c r="D149" s="47" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E149" s="47" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F149" s="47" t="s">
         <v>154</v>
@@ -17390,7 +17382,7 @@
         <v>207</v>
       </c>
       <c r="Q149" s="46" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="R149" s="33" t="s">
         <v>9</v>
@@ -17421,27 +17413,27 @@
         <v>9</v>
       </c>
       <c r="Z149" s="58" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="AA149" s="33" t="s">
-        <v>844</v>
-      </c>
-    </row>
-    <row r="150" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="150" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A150" s="52">
         <v>150</v>
       </c>
       <c r="B150" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C150" s="49" t="s">
         <v>157</v>
       </c>
       <c r="D150" s="47" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E150" s="47" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F150" s="47" t="s">
         <v>160</v>
@@ -17481,7 +17473,7 @@
         <v>208</v>
       </c>
       <c r="Q150" s="46" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="R150" s="33" t="s">
         <v>9</v>
@@ -17512,27 +17504,27 @@
         <v>9</v>
       </c>
       <c r="Z150" s="58" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="AA150" s="33" t="s">
-        <v>845</v>
-      </c>
-    </row>
-    <row r="151" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="151" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A151" s="52">
         <v>151</v>
       </c>
       <c r="B151" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C151" s="49" t="s">
         <v>157</v>
       </c>
       <c r="D151" s="47" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E151" s="47" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F151" s="47" t="s">
         <v>155</v>
@@ -17572,7 +17564,7 @@
         <v>209</v>
       </c>
       <c r="Q151" s="46" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="R151" s="33" t="s">
         <v>9</v>
@@ -17603,27 +17595,27 @@
         <v>9</v>
       </c>
       <c r="Z151" s="58" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="AA151" s="33" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="152" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="152" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A152" s="52">
         <v>152</v>
       </c>
       <c r="B152" s="47" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C152" s="49" t="s">
         <v>157</v>
       </c>
       <c r="D152" s="47" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E152" s="47" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F152" s="47" t="s">
         <v>156</v>
@@ -17663,7 +17655,7 @@
         <v>210</v>
       </c>
       <c r="Q152" s="46" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="R152" s="33" t="s">
         <v>9</v>
@@ -17694,10 +17686,10 @@
         <v>9</v>
       </c>
       <c r="Z152" s="58" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="AA152" s="33" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
     </row>
   </sheetData>
@@ -17705,20 +17697,20 @@
     <sortCondition ref="F1:F123"/>
   </sortState>
   <phoneticPr fontId="9" type="noConversion"/>
-  <conditionalFormatting sqref="F1 F164:F1048576 F7:F153">
-    <cfRule type="duplicateValues" dxfId="11" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="10"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="A2:B152">
-    <cfRule type="cellIs" dxfId="9" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="6" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="F1 F164:F1048576 F7:F153">
+    <cfRule type="duplicateValues" dxfId="9" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="10"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="F3:F6">
-    <cfRule type="duplicateValues" dxfId="8" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA2:AA6">
     <cfRule type="cellIs" dxfId="3" priority="5" operator="equal">
@@ -17732,16 +17724,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{779E4F22-2568-4D5A-A538-DD63A5C43724}">
   <dimension ref="A1:U2"/>
-  <sheetFormatPr defaultColWidth="5.7109375" defaultRowHeight="7.9" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="5.69140625" defaultRowHeight="7.95" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="1.28515625" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.5703125" style="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="10" width="5.140625" style="12" bestFit="1" customWidth="1"/>
-    <col min="11" max="21" width="5.5703125" style="21" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="5.7109375" style="21"/>
+    <col min="1" max="1" width="1.3046875" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.53515625" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="10" width="5.15234375" style="12" bestFit="1" customWidth="1"/>
+    <col min="11" max="21" width="5.53515625" style="21" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="5.69140625" style="21"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="16.5" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:21" ht="15.45" x14ac:dyDescent="0.2">
       <c r="A1" s="19">
         <v>1</v>
       </c>
@@ -17806,7 +17798,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="8.25" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:21" ht="7.75" x14ac:dyDescent="0.2">
       <c r="A2" s="19">
         <v>2</v>
       </c>
@@ -17879,16 +17871,16 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4328B84A-AA24-421E-9F4E-92D6A71CA3BE}">
   <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="1.42578125" style="13" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4.140625" style="13" customWidth="1"/>
-    <col min="3" max="3" width="7.42578125" style="13" customWidth="1"/>
-    <col min="4" max="4" width="7.7109375" style="13" customWidth="1"/>
-    <col min="5" max="16384" width="9.140625" style="13"/>
+    <col min="1" max="1" width="1.3828125" style="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.15234375" style="13" customWidth="1"/>
+    <col min="3" max="3" width="7.3828125" style="13" customWidth="1"/>
+    <col min="4" max="4" width="7.69140625" style="13" customWidth="1"/>
+    <col min="5" max="16384" width="9.15234375" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="6.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:4" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="8">
         <v>1</v>
       </c>
@@ -17902,7 +17894,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="6.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:4" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="7">
         <v>2</v>
       </c>
@@ -17916,7 +17908,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="6.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:4" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="7">
         <v>3</v>
       </c>
@@ -17938,25 +17930,25 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3D50BAA-DAEA-47D5-8FAA-A68A87918655}">
   <dimension ref="A1:M32"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="6" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="6" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.5703125" style="38" customWidth="1"/>
-    <col min="2" max="2" width="11.7109375" style="38" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.28515625" style="38" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.7109375" style="38" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.53515625" style="38" customWidth="1"/>
+    <col min="2" max="2" width="11.69140625" style="38" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.3046875" style="38" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.69140625" style="38" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="8" style="38" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6" style="42" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="40.28515625" style="42" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5" style="42" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.5703125" style="43" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.7109375" style="42" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="64.28515625" style="42" customWidth="1"/>
-    <col min="12" max="12" width="8.28515625" style="38" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="62.5703125" style="38" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="38"/>
+    <col min="7" max="7" width="40.3046875" style="42" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.07421875" style="42" customWidth="1"/>
+    <col min="9" max="9" width="20.53515625" style="43" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.69140625" style="42" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="64.3046875" style="42" customWidth="1"/>
+    <col min="12" max="12" width="8.3046875" style="38" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="62.53515625" style="38" customWidth="1"/>
+    <col min="14" max="16384" width="9.15234375" style="38"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="14" t="s">
         <v>30</v>
       </c>
@@ -17997,12 +17989,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="16">
         <v>2</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="C2" s="39" t="s">
         <v>93</v>
@@ -18017,7 +18009,7 @@
         <v>16</v>
       </c>
       <c r="G2" s="18" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H2" s="28" t="s">
         <v>9</v>
@@ -18038,12 +18030,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="16">
         <v>3</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="C3" s="39" t="s">
         <v>93</v>
@@ -18052,13 +18044,13 @@
         <v>78</v>
       </c>
       <c r="E3" s="30" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="F3" s="28" t="s">
         <v>16</v>
       </c>
       <c r="G3" s="18" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="H3" s="28" t="s">
         <v>9</v>
@@ -18079,12 +18071,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="16">
         <v>4</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C4" s="39" t="s">
         <v>93</v>
@@ -18093,13 +18085,13 @@
         <v>78</v>
       </c>
       <c r="E4" s="30" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="F4" s="28" t="s">
         <v>16</v>
       </c>
       <c r="G4" s="18" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H4" s="28" t="s">
         <v>9</v>
@@ -18120,12 +18112,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="16">
         <v>5</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C5" s="39" t="s">
         <v>93</v>
@@ -18134,13 +18126,13 @@
         <v>78</v>
       </c>
       <c r="E5" s="30" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="F5" s="28" t="s">
         <v>16</v>
       </c>
       <c r="G5" s="18" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H5" s="28" t="s">
         <v>9</v>
@@ -18161,12 +18153,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="16">
         <v>6</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C6" s="39" t="s">
         <v>93</v>
@@ -18175,13 +18167,13 @@
         <v>78</v>
       </c>
       <c r="E6" s="30" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="F6" s="28" t="s">
         <v>16</v>
       </c>
       <c r="G6" s="18" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H6" s="28" t="s">
         <v>9</v>
@@ -18202,12 +18194,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="16">
         <v>7</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C7" s="39" t="s">
         <v>93</v>
@@ -18216,13 +18208,13 @@
         <v>78</v>
       </c>
       <c r="E7" s="30" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="F7" s="28" t="s">
         <v>16</v>
       </c>
       <c r="G7" s="18" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H7" s="28" t="s">
         <v>9</v>
@@ -18243,12 +18235,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="16">
         <v>8</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C8" s="39" t="s">
         <v>93</v>
@@ -18257,13 +18249,13 @@
         <v>78</v>
       </c>
       <c r="E8" s="30" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="F8" s="28" t="s">
         <v>16</v>
       </c>
       <c r="G8" s="18" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H8" s="28" t="s">
         <v>9</v>
@@ -18284,39 +18276,39 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="16">
         <v>9</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C9" s="39" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D9" s="29" t="s">
         <v>78</v>
       </c>
       <c r="E9" s="30" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="F9" s="28" t="s">
         <v>16</v>
       </c>
       <c r="G9" s="18" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H9" s="28" t="s">
-        <v>218</v>
+        <v>887</v>
       </c>
       <c r="I9" s="40" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="J9" s="28" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="K9" s="18" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="L9" s="50" t="s">
         <v>9</v>
@@ -18325,39 +18317,39 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="16">
         <v>10</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C10" s="39" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D10" s="29" t="s">
         <v>78</v>
       </c>
       <c r="E10" s="30" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="F10" s="28" t="s">
         <v>16</v>
       </c>
       <c r="G10" s="18" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H10" s="28" t="s">
-        <v>218</v>
+        <v>887</v>
       </c>
       <c r="I10" s="41" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="J10" s="28" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="K10" s="18" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="L10" s="50" t="s">
         <v>9</v>
@@ -18366,39 +18358,39 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="16">
         <v>11</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C11" s="39" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D11" s="29" t="s">
         <v>78</v>
       </c>
       <c r="E11" s="30" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="F11" s="28" t="s">
         <v>16</v>
       </c>
       <c r="G11" s="18" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H11" s="28" t="s">
-        <v>218</v>
+        <v>887</v>
       </c>
       <c r="I11" s="41" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="J11" s="28" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="K11" s="18" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="L11" s="50" t="s">
         <v>9</v>
@@ -18407,39 +18399,39 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="16">
         <v>12</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C12" s="39" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D12" s="29" t="s">
         <v>78</v>
       </c>
       <c r="E12" s="30" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="F12" s="28" t="s">
         <v>16</v>
       </c>
       <c r="G12" s="18" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H12" s="28" t="s">
-        <v>218</v>
+        <v>887</v>
       </c>
       <c r="I12" s="40" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="J12" s="28" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="K12" s="18" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="L12" s="50" t="s">
         <v>9</v>
@@ -18448,39 +18440,39 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="16">
         <v>13</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C13" s="39" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D13" s="29" t="s">
         <v>78</v>
       </c>
       <c r="E13" s="30" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="F13" s="28" t="s">
         <v>16</v>
       </c>
       <c r="G13" s="18" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H13" s="28" t="s">
-        <v>218</v>
+        <v>887</v>
       </c>
       <c r="I13" s="40" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="J13" s="28" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="K13" s="18" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="L13" s="50" t="s">
         <v>9</v>
@@ -18489,7 +18481,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="16">
         <v>14</v>
       </c>
@@ -18497,31 +18489,31 @@
         <v>216</v>
       </c>
       <c r="C14" s="39" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="D14" s="29" t="s">
         <v>78</v>
       </c>
       <c r="E14" s="30" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="F14" s="28" t="s">
         <v>16</v>
       </c>
       <c r="G14" s="18" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H14" s="28" t="s">
-        <v>218</v>
+        <v>887</v>
       </c>
       <c r="I14" s="41" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="J14" s="28" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="K14" s="18" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="L14" s="50" t="s">
         <v>9</v>
@@ -18530,39 +18522,39 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="16">
         <v>15</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C15" s="39" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="D15" s="29" t="s">
         <v>78</v>
       </c>
       <c r="E15" s="30" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="F15" s="28" t="s">
         <v>16</v>
       </c>
       <c r="G15" s="18" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H15" s="28" t="s">
-        <v>218</v>
+        <v>887</v>
       </c>
       <c r="I15" s="40" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="J15" s="28" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="K15" s="18" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="L15" s="50" t="s">
         <v>9</v>
@@ -18571,39 +18563,39 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="16">
         <v>16</v>
       </c>
       <c r="B16" s="17" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C16" s="39" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D16" s="29" t="s">
         <v>78</v>
       </c>
       <c r="E16" s="30" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="F16" s="28" t="s">
         <v>16</v>
       </c>
       <c r="G16" s="18" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H16" s="28" t="s">
-        <v>218</v>
+        <v>887</v>
       </c>
       <c r="I16" s="41" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="J16" s="28" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="K16" s="18" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="L16" s="50" t="s">
         <v>9</v>
@@ -18612,39 +18604,39 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="16">
         <v>17</v>
       </c>
       <c r="B17" s="17" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C17" s="39" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D17" s="29" t="s">
         <v>78</v>
       </c>
       <c r="E17" s="30" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="F17" s="28" t="s">
         <v>16</v>
       </c>
       <c r="G17" s="18" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H17" s="28" t="s">
-        <v>218</v>
+        <v>887</v>
       </c>
       <c r="I17" s="41" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="J17" s="28" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="K17" s="18" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="L17" s="50" t="s">
         <v>9</v>
@@ -18653,39 +18645,39 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="16">
         <v>18</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C18" s="39" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D18" s="29" t="s">
         <v>78</v>
       </c>
       <c r="E18" s="30" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="F18" s="28" t="s">
         <v>16</v>
       </c>
       <c r="G18" s="18" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H18" s="28" t="s">
-        <v>218</v>
+        <v>887</v>
       </c>
       <c r="I18" s="41" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="J18" s="28" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="K18" s="18" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="L18" s="50" t="s">
         <v>9</v>
@@ -18694,39 +18686,39 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="16">
         <v>19</v>
       </c>
       <c r="B19" s="17" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C19" s="39" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D19" s="29" t="s">
         <v>78</v>
       </c>
       <c r="E19" s="30" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="F19" s="28" t="s">
         <v>16</v>
       </c>
       <c r="G19" s="18" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H19" s="28" t="s">
-        <v>218</v>
+        <v>887</v>
       </c>
       <c r="I19" s="41" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="J19" s="28" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="K19" s="18" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="L19" s="50" t="s">
         <v>9</v>
@@ -18735,39 +18727,39 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="16">
         <v>20</v>
       </c>
       <c r="B20" s="17" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C20" s="39" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D20" s="29" t="s">
         <v>78</v>
       </c>
       <c r="E20" s="30" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="F20" s="28" t="s">
         <v>16</v>
       </c>
       <c r="G20" s="18" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H20" s="28" t="s">
-        <v>218</v>
+        <v>887</v>
       </c>
       <c r="I20" s="40" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="J20" s="28" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="K20" s="18" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="L20" s="50" t="s">
         <v>9</v>
@@ -18776,39 +18768,39 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:13" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="16">
         <v>21</v>
       </c>
       <c r="B21" s="17" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C21" s="39" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D21" s="29" t="s">
         <v>78</v>
       </c>
       <c r="E21" s="30" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="F21" s="28" t="s">
         <v>16</v>
       </c>
       <c r="G21" s="18" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H21" s="28" t="s">
-        <v>218</v>
+        <v>887</v>
       </c>
       <c r="I21" s="40" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="J21" s="28" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="K21" s="18" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="L21" s="50" t="s">
         <v>9</v>
@@ -18817,7 +18809,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:13" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="16">
         <v>22</v>
       </c>
@@ -18825,435 +18817,435 @@
         <v>215</v>
       </c>
       <c r="C22" s="39" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D22" s="29" t="s">
         <v>78</v>
       </c>
       <c r="E22" s="30" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="F22" s="28" t="s">
         <v>16</v>
       </c>
       <c r="G22" s="18" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H22" s="28" t="s">
-        <v>218</v>
+        <v>887</v>
       </c>
       <c r="I22" s="41" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="J22" s="28" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="K22" s="18" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="L22" s="28" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="M22" s="18" t="s">
-        <v>884</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="16">
         <v>23</v>
       </c>
       <c r="B23" s="44" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C23" s="39" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D23" s="29" t="s">
         <v>78</v>
       </c>
       <c r="E23" s="30" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="F23" s="28" t="s">
         <v>16</v>
       </c>
       <c r="G23" s="18" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H23" s="28" t="s">
-        <v>218</v>
+        <v>887</v>
       </c>
       <c r="I23" s="41" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="J23" s="28" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="K23" s="18" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="L23" s="28" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="M23" s="18" t="s">
-        <v>874</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="16">
         <v>24</v>
       </c>
       <c r="B24" s="44" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C24" s="39" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D24" s="29" t="s">
         <v>78</v>
       </c>
       <c r="E24" s="30" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="F24" s="28" t="s">
         <v>16</v>
       </c>
       <c r="G24" s="18" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H24" s="28" t="s">
-        <v>218</v>
+        <v>887</v>
       </c>
       <c r="I24" s="41" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="J24" s="28" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="K24" s="18" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="L24" s="28" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="M24" s="18" t="s">
-        <v>875</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="16">
         <v>25</v>
       </c>
       <c r="B25" s="44" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C25" s="39" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D25" s="29" t="s">
         <v>78</v>
       </c>
       <c r="E25" s="30" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="F25" s="28" t="s">
         <v>16</v>
       </c>
       <c r="G25" s="18" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H25" s="28" t="s">
-        <v>218</v>
+        <v>887</v>
       </c>
       <c r="I25" s="41" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="J25" s="28" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="K25" s="18" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="L25" s="28" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="M25" s="18" t="s">
-        <v>874</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="16">
         <v>26</v>
       </c>
       <c r="B26" s="44" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C26" s="39" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D26" s="29" t="s">
         <v>78</v>
       </c>
       <c r="E26" s="30" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="F26" s="28" t="s">
         <v>16</v>
       </c>
       <c r="G26" s="18" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H26" s="28" t="s">
-        <v>218</v>
+        <v>887</v>
       </c>
       <c r="I26" s="41" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="J26" s="28" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="K26" s="18" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="L26" s="28" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="M26" s="18" t="s">
-        <v>876</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="16">
         <v>27</v>
       </c>
       <c r="B27" s="44" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C27" s="39" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D27" s="29" t="s">
         <v>78</v>
       </c>
       <c r="E27" s="30" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="F27" s="28" t="s">
         <v>16</v>
       </c>
       <c r="G27" s="18" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H27" s="28" t="s">
-        <v>218</v>
+        <v>887</v>
       </c>
       <c r="I27" s="41" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="J27" s="28" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="K27" s="18" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="L27" s="28" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="M27" s="18" t="s">
-        <v>876</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="16">
         <v>28</v>
       </c>
       <c r="B28" s="44" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C28" s="39" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D28" s="29" t="s">
         <v>78</v>
       </c>
       <c r="E28" s="30" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="F28" s="28" t="s">
         <v>16</v>
       </c>
       <c r="G28" s="18" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H28" s="28" t="s">
-        <v>218</v>
+        <v>887</v>
       </c>
       <c r="I28" s="41" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="J28" s="28" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="K28" s="18" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="L28" s="28" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="M28" s="18" t="s">
-        <v>876</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="16">
         <v>29</v>
       </c>
       <c r="B29" s="44" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C29" s="39" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D29" s="29" t="s">
         <v>78</v>
       </c>
       <c r="E29" s="30" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="F29" s="28" t="s">
         <v>16</v>
       </c>
       <c r="G29" s="18" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H29" s="28" t="s">
-        <v>218</v>
+        <v>887</v>
       </c>
       <c r="I29" s="41" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="J29" s="28" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="K29" s="18" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="L29" s="28" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="M29" s="18" t="s">
-        <v>877</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="16">
         <v>30</v>
       </c>
       <c r="B30" s="44" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C30" s="39" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D30" s="29" t="s">
         <v>78</v>
       </c>
       <c r="E30" s="30" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="F30" s="28" t="s">
         <v>16</v>
       </c>
       <c r="G30" s="18" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H30" s="28" t="s">
-        <v>218</v>
+        <v>887</v>
       </c>
       <c r="I30" s="41" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="J30" s="28" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="K30" s="18" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="L30" s="28" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="M30" s="18" t="s">
-        <v>878</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="16">
         <v>31</v>
       </c>
       <c r="B31" s="44" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C31" s="39" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D31" s="29" t="s">
         <v>78</v>
       </c>
       <c r="E31" s="30" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="F31" s="28" t="s">
         <v>16</v>
       </c>
       <c r="G31" s="18" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H31" s="28" t="s">
-        <v>218</v>
+        <v>887</v>
       </c>
       <c r="I31" s="41" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="J31" s="28" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="K31" s="18" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="L31" s="28" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="M31" s="18" t="s">
-        <v>879</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="16">
         <v>32</v>
       </c>
       <c r="B32" s="17" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C32" s="39" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="D32" s="29" t="s">
         <v>78</v>
       </c>
       <c r="E32" s="30" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="F32" s="28" t="s">
         <v>16</v>
       </c>
       <c r="G32" s="18" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H32" s="28" t="s">
-        <v>218</v>
+        <v>887</v>
       </c>
       <c r="I32" s="40" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="J32" s="28" t="s">
         <v>9</v>
